--- a/data/raw/monthly-2026-10.xlsx
+++ b/data/raw/monthly-2026-10.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="636">
   <si>
     <t>วันที่</t>
   </si>
@@ -885,6 +885,1044 @@
   </si>
   <si>
     <t>https://ratchakitcha.soc.go.th/documents/131579.pdf</t>
+  </si>
+  <si>
+    <t>02/10/2026</t>
+  </si>
+  <si>
+    <t>กฎสำนักนายกรัฐมนตรีว่าด้วยเครื่องแบบพิเศษสำหรับข้าราชการกรมอุทยานแห่งชาติ สัตว์ป่า และพันธุ์พืช พ.ศ. 2569</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/133481.pdf</t>
+  </si>
+  <si>
+    <t>พระบรมราชโองการ ประกาศ ปรับลดชั้นยศข้าราชการในพระองค์ฝ่ายทหาร  และให้พ้นจากการปฏิบัติหน้าที่ราชองครักษ์ประจำพระองค์ [พลตรี จักรพงษ์  เส-ลา]</t>
+  </si>
+  <si>
+    <t>ข</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/133823.pdf</t>
+  </si>
+  <si>
+    <t>พระบรมราชโองการ ประกาศ ปรับลดชั้นยศข้าราชการในพระองค์ฝ่ายทหาร [พันตรี นพรัตน์  สาธร]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/133831.pdf</t>
+  </si>
+  <si>
+    <t>พระบรมราชโองการ ประกาศ พระราชทานยศข้าราชการในพระองค์ฝ่ายทหารชั้นสัญญาบัตรและแต่งตั้งให้ดำรงตำแหน่ง [จำนวน 3 นาย 1. พันเอก ศักดิ์ระวี  พึ่งเย็น ฯลฯ]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/133827.pdf</t>
+  </si>
+  <si>
+    <t>พระบรมราชโองการ ประกาศ พระราชทานยศข้าราชการในพระองค์ฝ่ายพลเรือน  [จำนวน 29 ราย 1. ร้อยตรี จุลกร  ชาตรีวัฒนกุล ฯลฯ]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/133828.pdf</t>
+  </si>
+  <si>
+    <t>พระบรมราชโองการ ประกาศ เรื่อง พระราชทานเครื่องราชอิสริยาภรณ์เป็นกรณีพิเศษ [พลตรี ธนศักดิ์ บัวขาว]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/128061.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศสำนักนายกรัฐมนตรี เรื่อง พระราชทานยศทหารเป็นกรณีพิเศษ [จ่าสิบเอก ธนศักดิ์ บัวขาว]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/128060.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศสำนักนายกรัฐมนตรี เรื่อง พระราชทานยศทหารเป็นกรณีพิเศษ [1. จ่าสิบเอก นิวัฒน์  ทองชัย 2. พันตรี ลิขิต วิทยประภารัตน์]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/128059.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศสำนักนายกรัฐมนตรี เรื่อง พระราชทานยศทหารเป็นกรณีพิเศษ [1. จ่าสิบเอก พิชิตชัย บุญชูหล้า 2. พลทหารกฤตภาส ลีเพ็ญ]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/128058.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศสำนักนายกรัฐมนตรี เรื่อง พระราชทานพระบรมราชานุญาตให้ถอดยศทหารและเรียกคืนเครื่องราชอิสริยาภรณ์ [จำนวน 10 ราย 1. พันเอก นิพนธ์ ศรีสัจจา ฯลฯ]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/133598.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศศาลเยาวชนและครอบครัวจังหวัดกระบี่ เรื่อง ขอให้ นางสาวปิยวรรณ อริยวงศ์ พ้นจากการเป็นคนเสมือนไร้ความสามารถ</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/128158.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศศาลเยาวชนและครอบครัวจังหวัดกระบี่ เรื่อง ศาลมีคำสั่งให้ นางสาวปราณี สุนาเสวีนนท์ เป็นคนไร้ความสามารถ และให้อยู่ในความอนุบาลของ นายธันวา สุนาเสวีนนท์</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/128159.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศศาลเยาวชนและครอบครัวจังหวัดกระบี่ เรื่อง ศาลมีคำสั่งให้ นางสาดีย๊ะ รักบุรี เป็นคนไร้ความสามารถ และให้อยู่ในความอนุบาลของ นางสาวพิมพ์ใจชนก หยงสตาร์</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/128160.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศศาลเยาวชนและครอบครัวจังหวัดกาญจนบุรี เรื่อง คำสั่งให้ นายวินุช ธนรักษ์ (เลขประจำตัวประชาชน ๕-๗๑๙๙-๐๐๐๐๘-๖๖-๓) เป็นคนไร้ความสามารถ และให้อยู่ในความอนุบาลของ นางสิรินรี ธนรักษ์ ผู้ร้อง</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/125812.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศศาลเยาวชนและครอบครัวจังหวัดกาญจนบุรี เรื่อง คำสั่งให้นายสมาน ดำทะมิส (เลขประจำตัวประชาชน ๓-๗๑๐๑-๐๐๑๗๓-๑๐-๐) เป็นคนไร้ความสามารถ และให้อยู่ในความอนุบาลของ นายสามารถ ดำทะมิส ผู้ร้อง</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/125814.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศศาลเยาวชนและครอบครัวจังหวัดกาญจนบุรี เรื่อง คำสั่งให้ นางสาวนกนิด เขียนโกลา (เลขประจำตัวประชาชน 3-7106-00112-10-0) เป็นคนไร้ความสามารถ และให้อยู่ในความอนุบาลของ นางอำพรรณ นาคแก้ว ผู้ร้อง</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/125815.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศศาลเยาวชนและครอบครัวจังหวัดกาญจนบุรี เรื่อง คำสั่งให้ นายบัณดิษฐ พรหมมา (เลขประจำตัวประชาชน 3-7106-00566-39-9) เป็นคนไร้ความสามารถ และให้อยู่ในความอนุบาลของ นางอี๊ด พรหมมา ผู้ร้อง</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/125813.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศศาลเยาวชนและครอบครัวจังหวัดชุมพร เรื่อง ศาลมีคำสั่งให้ นายสายัน ยอดเสน่ห์ เป็นคนไร้ความสามารถ และให้อยู่ในความอนุบาลของ นางสาวนัทธมน ยอดเสน่ห์</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/126650.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศศาลเยาวชนและครอบครัวจังหวัดชุมพร เรื่อง ศาลมีคำสั่งให้ นางสาวจันทร์เพ็ญ  ทิมวิลัย เป็นคนไร้ความสามารถ และให้อยู่ในความอนุบาลของ นายพีรวิชญ์  ฐิตะฐาน</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/127397.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศศาลเยาวชนและครอบครัวจังหวัดชุมพร เรื่อง ศาลมีคำสั่งให้ นางสาวศิรัญญา สุนทรหงษ์ เป็นคนไร้ความสามารถ และให้อยู่ในความอนุบาลของ นายณัฐพงษ์ สุนทรหงษ์</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/127399.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศศาลเยาวชนและครอบครัวจังหวัดชุมพร เรื่อง ศาลมีคำสั่งให้ นางบุญเลิศ ชังชะนา เป็นคนไร้ความสามารถ และให้อยู่ในความอนุบาลของ จ่าสิบตรี เสริมศักดิ์ ชังชะนา</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/127398.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศศาลเยาวชนและครอบครัวจังหวัดนครปฐม เรื่อง ศาลมีคำสั่งว่า นายธงชัยพัฒน์ ดีสวัสดิ์ เป็นคนไร้ความสามารถ และอยู่ในความอนุบาลของ นางสาวฤดีรัตน์ ดีสวัสดิ์</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/128541.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศศาลเยาวชนและครอบครัวจังหวัดนครปฐม เรื่อง ศาลมีคำสั่งว่า นายวรเดช คล้ายเมฆ เป็นคนไร้ความสามารถ และอยู่ในความอนุบาลของ นางพัทธยา คล้ายเมฆ</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/128546.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศศาลเยาวชนและครอบครัวจังหวัดนครปฐม เรื่อง  ศาลมีคำสั่งว่า นางสำอางค์ ใจอารีย์ เป็นคนไร้ความสามารถ และอยู่ในความอนุบาลของ นายอภิชาติ ใจอารีย์</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/128632.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศศาลเยาวชนและครอบครัวจังหวัดนครปฐม เรื่อง ศาลมีคำสั่งว่า นางสาหร่าย ดาลา เป็นคนไร้ความสามารถ และอยู่ในความอนุบาลของ นายยศพล ดารารุ่งโรจน์</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/128548.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศศาลเยาวชนและครอบครัวจังหวัดนครปฐม เรื่อง ศาลมีคำสั่งว่า นางวิไล สุทธาธาร เป็นคนไร้ความสามารถ และอยู่ในความอนุบาลของ นางมาลัยวัลย์ กิจเจริญ</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/128549.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศศาลเยาวชนและครอบครัวจังหวัดนครราชสีมา เรื่อง  ศาลมีคำสั่งให้ นายพรนรินทร์ รัตนสถาพร เป็นคนไร้ความสามารถ และให้อยู่ในความอนุบาลของ นางสาวพณิชา รัตนสถาพร</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/129051.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศศาลเยาวชนและครอบครัวจังหวัดนครราชสีมา เรื่อง  ศาลมีคำสั่งให้ นางสาวปราณี วงค์มะเริง เป็นคนไร้ความสามารถ และให้อยู่ในความอนุบาลของ นายชัยนาท เพ็งพะเนา</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/129052.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศศาลเยาวชนและครอบครัวจังหวัดนครราชสีมา เรื่อง ศาลมีคำสั่งให้ นางสุควร พรหมนิลพันธุ์ หรือพุกจันทึก เป็นคนไร้ความสามารถ และให้อยู่ในความอนุบาลของ นายกรมิษฐ์ พรหมนิลพันธุ์</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/129053.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศศาลเยาวชนและครอบครัวจังหวัดนครราชสีมา เรื่อง ศาลมีคำสั่งให้ นางจันทร์ ชูจิตร เป็นคนไร้ความสามารถ และให้อยู่ในความอนุบาลของ นายทองอินทร์ ชูจิตร</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/129054.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศศาลเยาวชนและครอบครัวจังหวัดนครราชสีมา เรื่อง ศาลมีคำสั่งให้ นางสุรีพร ชดกิ่ง เป็นคนไร้ความสามารถ และให้อยู่ในความอนุบาลของ นายพิสิษฐ์ ชดกิ่ง</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/129055.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศศาลเยาวชนและครอบครัวจังหวัดนครราชสีมา เรื่อง ศาลมีคำสั่งให้ นายวิสุทธิ์ สุวรรณชาติ ผู้คัดค้านที่ 1 เป็นคนไร้ความสามารถ และให้อยู่ในความอนุบาลของ นางสุพิน สุวรรณชาติ ผู้คัดค้านที่ 2</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/129056.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศศาลเยาวชนและครอบครัวจังหวัดบุรีรัมย์ เรื่อง ขอให้สั่งเป็นคนไร้ความสามารถและตั้งผู้อนุบาล [นางละม่อม  กองศรี  คนไร้ความสามารถ นายชาตรี  เนียมกุญชร ผู้อนุบาล]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/127544.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศศาลเยาวชนและครอบครัวจังหวัดบุรีรัมย์ เรื่อง ขอสั่งให้เป็นคนไร้ความสามารถหรือคนเสมือนไร้ความสามารถและตั้งผู้อนุบาลหรือผู้พิทักษ์ [นายเฉลิมเกียรติ พงษ์สว่าง คนเสมือนไร้ความสามารถ นางอนันตา หรือเล วงษานิล หรือพงษ์สว่าง ผู้พิทักษ์]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/128360.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศศาลเยาวชนและครอบครัวจังหวัดบุรีรัมย์ เรื่อง  ขอให้สั่งเป็นคนไร้ความสามารถ [นายธงชัย พาพลงาม]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/128558.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศศาลเยาวชนและครอบครัวจังหวัดบุรีรัมย์ เรื่อง ขอให้สั่งเป็นคนไร้ความสามารถและตั้งผู้อนุบาล [นางปภาดา หรือเสน่ห์จิต สุโข คนไร้ความสามารถ นางสาวสุชาฎา ศุภเลิศ ที่ 1 นายศุภฤกษ์ แคว้นไธสง ที่ 2 ผู้อนุบาล]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/129017.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศศาลเยาวชนและครอบครัวจังหวัดปทุมธานี เรื่อง  ศาลมีคำสั่งว่า นายธนกฤต  โสภาคำ เป็นคนไร้ความสามารถ และให้อยู่ในความอนุบาลของ นางสาว หรือนางฐิตารีย์ หรือนุจรินทร์  แขตสันเทียะ หรือโสภาคำ</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/128351.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศศาลเยาวชนและครอบครัวจังหวัดปทุมธานี เรื่อง  ศาลมีคำสั่งว่า นางสาวจิตรา  โพธิลักษณ์ เป็นคนไร้ความสามารถ และให้อยู่ในความอนุบาลของ นางดวงกมล  โพธิลักษณ์</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/128352.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศศาลเยาวชนและครอบครัวจังหวัดปทุมธานี เรื่อง ศาลมีคำสั่งให้ นางจิตราภา หรืออุไร  เต้าเกิด เป็นคนไร้ความสามารถ และแต่งตั้ง นางสาวกรองแก้ว  เต้าเกิด เป็นผู้อนุบาล</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/128353.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศศาลเยาวชนและครอบครัวจังหวัดปทุมธานี เรื่อง ศาลมีคำสั่งว่า นายทองเปลว จำเนียร เป็นคนไร้ความสามารถ และให้อยู่ในความอนุบาลของ นายทองดี จำเนียร</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/129151.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศศาลเยาวชนและครอบครัวจังหวัดปทุมธานี เรื่อง ศาลมีคำสั่งให้ นาย หรือร้อยตรีบุญส่ง สงกรานต์ เป็นคนไร้ความสามารถ และแต่งตั้ง นายอนุศิษฐ์ สงกรานต์ เป็นผู้อนุบาล</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/129152.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศศาลเยาวชนและครอบครัวจังหวัดประจวบคีรีขันธ์ เรื่อง ศาลมีคำสั่งให้ นางนันทา เนรภูศรี เป็นคนไร้ความสามารถ และให้อยู่ในความอนุบาลของ นางสาวลออ ทองสุข</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/128601.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศศาลเยาวชนและครอบครัวจังหวัดประจวบคีรีขันธ์ เรื่อง ศาลมีคำสั่งให้ นายเฉลิมพล สุขขำ เป็นคนไร้ความสามารถ และให้อยู่ในความอนุบาลของ นางสาววิไลลักษณ์ สุขขำ</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/128782.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศศาลเยาวชนและครอบครัวจังหวัดประจวบคีรีขันธ์ เรื่อง ศาลมีคำสั่งให้ นางจินตนา ตุลเตมีย์ เป็นคนไร้ความสามารถ และให้อยู่ในความอนุบาลของ นายนิตินันต์ สุวรรณหกาญจน์</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/128602.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศศาลเยาวชนและครอบครัวจังหวัดพัทลุง เรื่อง ศาลมีคำสั่งให้เป็นคนไร้ความสามารถ [นายมานพ ช่วยมณี]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/128328.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศศาลเยาวชนและครอบครัวจังหวัดพัทลุง เรื่อง ศาลมีคำสั่งให้เป็นคนไร้ความสามารถ [นางเดื่อม รักษาพล]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/129168.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศศาลเยาวชนและครอบครัวจังหวัดพัทลุง เรื่อง  ศาลมีคำสั่งให้เป็นคนไร้ความสามารถ [นายพิทักษ์ กิมาคม]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/129170.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศศาลเยาวชนและครอบครัวจังหวัดเพชรบุรี เรื่อง ขอให้ตั้งผู้อนุบาลคนไร้ความสามารถแทนผู้อนุบาลซึ่งถึงแก่ความตาย [นางสุภารัตน์  อนันตโชติ]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/126386.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศศาลเยาวชนและครอบครัวจังหวัดเพชรบุรี เรื่อง คำสั่งให้ นางสาวอเนตา ดิอานา ช็องเช็ค เป็นคนไร้ความสามารถ</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/126593.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศศาลเยาวชนและครอบครัวจังหวัดเพชรบุรี เรื่อง คำสั่งให้ นางธัญทิพย์ ชุติวัฒนเศรษฐ์ เป็นคนไร้ความสามารถ</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/126594.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศศาลเยาวชนและครอบครัวจังหวัดเพชรบุรี เรื่อง คำสั่งให้ นายวีระพงษ์ เหลืองอร่าม เป็นคนเสมือนไร้ความสามารถ และแต่งตั้งให้ นางสาวประภัสรา เหมหงษ์ เป็นผู้พิทักษ์</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/126595.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศศาลเยาวชนและครอบครัวจังหวัดเพชรบูรณ์ เรื่อง  มีคำสั่งว่า นายทวีศักดิ์  รอดช้างหรืออานนท์  เป็นคนไร้ความสามารถ และอยู่ในความอนุบาลของผู้ร้อง</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/127704.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศศาลเยาวชนและครอบครัวจังหวัดเพชรบูรณ์ เรื่อง มีคำสั่งว่า นางทองสุก นาทองคำ เป็นคนไร้ความสามารถ และอยู่ในความอนุบาลของผู้ร้อง</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/127703.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศศาลเยาวชนและครอบครัวจังหวัดเพชรบูรณ์ เรื่อง  มีคำสั่งว่า นายคมชาญ ตันธราพรฤกษ์ เป็นคนไร้ความสามารถ และอยู่ในความอนุบาลของผู้ร้อง</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/127705.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศศาลเยาวชนและครอบครัวจังหวัดเพชรบูรณ์ เรื่อง มีคำสั่งว่า นายสุดใจ แก้วเวียน เป็นคนไร้ความสามารถ และอยู่ในความอนุบาลของ นางอำพร แก้วเวียน</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/127706.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศศาลเยาวชนและครอบครัวจังหวัดลำปาง เรื่อง ศาลมีคำสั่งให้ นางตุ้มทอง จันทร์วงศ์ เป็นคนไร้ความสามารถ โดยให้อยู่ในความอนุบาลของ นายนคร จันทร์วงศ์</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/126905.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศศาลเยาวชนและครอบครัวจังหวัดลำปาง เรื่อง ศาลมีคำสั่งให้ นางสาวศุภศิริ อุปนันท์ เป็นคนไร้ความสามารถ โดยให้อยู่ในความอนุบาลของ นางสาวสิริภัสสร อุปนันท์</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/128164.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศศาลเยาวชนและครอบครัวจังหวัดลำปาง เรื่อง  ศาลมีคำสั่งให้ นายเผด็จ บานทรงกิจ เป็นคนไร้ความสามารถ โดยให้อยู่ในความอนุบาลของ นางวัลณีย์ คุ้มภัยเพื่อน</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/128162.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศศาลเยาวชนและครอบครัวจังหวัดลำปาง เรื่อง ศาลมีคำสั่งให้ นางสาวกัลยา โปทาสาย  เป็นคนไร้ความสามารถ โดยให้อยู่ในความอนุบาลของ นางศรีจันทร์ ฟูทอง</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/129173.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศศาลเยาวชนและครอบครัวจังหวัดลำปาง เรื่อง ศาลมีคำสั่งให้ นางสาวนภาพร นวลบุดดี เป็นคนไร้ความสามารถ โดยให้อยู่ในความอนุบาลของ นายภาณุพงศ์ นวลบุดดี</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/129174.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศศาลเยาวชนและครอบครัวจังหวัดสมุทรสาคร เรื่อง ศาลมีคำสั่งให้ เรือตรีหญิง คริษฐา แนงแหยม เป็นคนเสมือนไร้ความสามารถ และให้อยู่ในความพิทักษ์ของ นางสาวอังคณา ศรีพุทธชาติ</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/127242.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศศาลเยาวชนและครอบครัวจังหวัดสมุทรสาคร เรื่อง ศาลมีคำสั่งให้ นางอำนวย ประสิทธานันท์ เป็นคนไร้ความสามารถ และให้อยู่ในความอนุบาลของ นางวันทนา ซอศรีสาคร</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/128154.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศศาลเยาวชนและครอบครัวจังหวัดสมุทรสาคร เรื่อง ศาลมีคำสั่งให้ นางสาวอุไร เร่บ้านเกาะ เป็นคนไร้ความสามารถ และให้อยู่ในความอนุบาลของ นาย หรือร้อยตำรวจตรี สงวน เสพสมุทร</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/128153.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศศาลเยาวชนและครอบครัวจังหวัดสุพรรณบุรี เรื่อง ศาลมีคำสั่งให้ นางสาววันทนีย์ ศักดิ์สุพรรณ เป็นคนไร้ความสามารถ ให้อยู่ในความอนุบาลของ นางสาวพัชญ์สิตา พชิระพสิษฐ์</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/125943.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศศาลเยาวชนและครอบครัวจังหวัดสุพรรณบุรี เรื่อง ศาลมีคำสั่งให้ นางชุบ ประมูลวงษ์ เป็นคนไร้ความสามารถ ให้อยู่ในความอนุบาลของ นางสาวประกิจ ประมูลวงษ์</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/127463.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศศาลเยาวชนและครอบครัวจังหวัดสุพรรณบุรี เรื่อง ศาลมีคำสั่งให้ นายบุญเกื้อ  ดอกรัก เป็นคนไร้ความสามารถ ให้อยู่ในความอนุบาลของ นางกฤษณา  ดอกรัก</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/128156.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศศาลเยาวชนและครอบครัวจังหวัดสุรินทร์ เรื่อง มีคำสั่งว่า นางสม สาลี เป็นคนไร้ความสามารถ และให้อยู่ในความอนุบาลของนางสาวอัจฉรา สาลี</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/129009.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศศาลเยาวชนและครอบครัวจังหวัดสุรินทร์ เรื่อง มีคำสั่งว่า นางทิพย์ สมบูรณ์ เป็นคนไร้ความสามารถ และให้อยู่ในความอนุบาลของ นายมงคล สมบูรณ์</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/129010.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศศาลเยาวชนและครอบครัวจังหวัดสุรินทร์ เรื่อง มีคำสั่งว่า นางวรรณพิศ โก่งกระโทก เป็นคนเสมือนไร้ความสามารถ และอยู่ในความพิทักษ์ของ ร้อยโทวีรยุทธ โก่งกระโทก ผู้ร้อง</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/129011.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศศาลเยาวชนและครอบครัวจังหวัดหนองคาย เรื่อง ขอศาลมีคำสั่งให้สั่งเป็นคนไร้ความสามารถและขอตั้งผู้อนุบาล [นายบุญมี อาสนานิ คนไร้ความสามารถ นางวันนา อาสนานิ ผู้อนุบาล]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/125811.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศศาลเยาวชนและครอบครัวจังหวัดหนองคาย เรื่อง ขอให้สั่งเป็นคนไร้ความสามารถ และตั้งผู้อนุบาล [นายชัยวัฒน์ อัคร คนไร้ความสามารถ นางอุบล อัคร ผู้อนุบาล]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/126927.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศศาลเยาวชนและครอบครัวจังหวัดหนองคาย เรื่อง ขอให้สั่งเป็นคนไร้ความสามารถ และตั้งผู้อนุบาล [นางสาวกาญจนา  สัตบุตร คนไร้ความสามารถ นายสมศักดิ์  จัตกุล ผู้อนุบาล]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/126928.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศศาลเยาวชนและครอบครัวจังหวัดหนองคาย เรื่อง ขอให้เป็นคนไร้ความสามารถ  ขอให้ตั้งผู้อนุบาล [นายคำ  พรหมสูตร คนไร้ความสามารถ นางศุภกาญจ์  แสงโชติ ผู้อนุบาล]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/127710.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศศาลเยาวชนและครอบครัวจังหวัดอุตรดิตถ์ เรื่อง ขอให้สั่งเป็นคนเสมือนไร้ความสามารถและตั้งผู้พิทักษ์ [นายรัตนชัย  บุญปลื้ม  คนเสมือนไร้ความสามารถ นางสาวเนาวรัตน์  พุฒมาลา ผู้พิทักษ์]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/128559.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศศาลเยาวชนและครอบครัวจังหวัดอุบลราชธานี เรื่อง ศาลมีคำสั่งว่า นางสาวเสาวนีย์  นามโสภา เป็นคนไร้ความสามารถ และให้อยู่ในความอนุบาลของ นางสาววารุณี  นามโสภา</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/128289.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศศาลเยาวชนและครอบครัวจังหวัดอุบลราชธานี เรื่อง ศาลมีคำสั่งว่า นางอุไรวรรณ นาทศิโรรัตน์ เป็นคนไร้ความสามารถ และให้อยู่ในความอนุบาลของ นางสาวพรรณวดี  นาทศิโรรัตน์</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/128290.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศศาลเยาวชนและครอบครัวจังหวัดอุบลราชธานี เรื่อง ศาลมีคำสั่งว่า นายวิสุทธิ์ หว่างเทียน เป็นคนไร้ความสามารถ และให้อยู่ในความอนุบาลของ นางพิมพ์มาดา  ฤทธิทิศ</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/128355.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศศาลเยาวชนและครอบครัวจังหวัดอุบลราชธานี เรื่อง ศาลมีคำสั่งว่า นางหนูกร สุโภภาค เป็นคนไร้ความสามารถ และให้อยู่ในความอนุบาลของ นางกฤษณา  วิริยะสมบัติ</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/128356.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศศาลเยาวชนและครอบครัวจังหวัดอุบลราชธานี เรื่อง ศาลมีคำสั่งว่า นางถวิล พรมจำปา เป็นคนไร้ความสามารถ และให้อยู่ในความอนุบาลของ นางสาวไพรวรรณ  พรมจำปา</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/128358.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศศาลเยาวชนและครอบครัวจังหวัดอุบลราชธานี เรื่อง ศาลมีคำสั่งให้ถอน นางศิริพร  คำภา ผู้ร้อง ออกจากการเป็นผู้อนุบาลของ นายกังวาล  สุรินทราบูรณ์  และให้ตั้งนางภัทรวดี  รักษาศรี ผู้คัดค้านเป็นผู้อนุบาล</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/129006.pdf</t>
+  </si>
+  <si>
+    <t>พระบรมราชโองการ ประกาศ แต่งตั้งข้าราชการในพระองค์ฝ่ายทหารชั้นนายพล [1. พลตรี พงศ์ภพ  ทองอุไทย 2. พลตรี อรรถกร  ด่านสกุล]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/133839.pdf</t>
+  </si>
+  <si>
+    <t>พระบรมราชโองการ ประกาศ ให้นายทหารสัญญาบัตร  แต่งตั้งเป็นนายทหารราชองครักษ์ประจำพระองค์ [พันเอก รันดร  สอนนิ่ม]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/133844.pdf</t>
+  </si>
+  <si>
+    <t>พระบรมราชโองการ ประกาศ ให้นายทหารสัญญาบัตรและนายตำรวจชั้นสัญญาบัตร  แต่งตั้งเป็นนายทหารราชองครักษ์ในพระองค์และนายตำรวจราชองครักษ์ในพระองค์ [จำนวน 82 นาย 1. พลโท ชัชวาลย์  พยุงวงศ์ ฯลฯ]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/133851.pdf</t>
+  </si>
+  <si>
+    <t>พระบรมราชโองการ ประกาศ ให้นายทหารสัญญาบัตรและนายตำรวจชั้นสัญญาบัตร  แต่งตั้งเป็นนายทหารราชองครักษ์พิเศษและนายตำรวจราชองครักษ์พิเศษ  [จำนวน 28 นาย 1. พลเอก กิตติพงศ์  ชื่นใจชน  ฯลฯ]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/133856.pdf</t>
+  </si>
+  <si>
+    <t>พระบรมราชโองการ ประกาศ ให้รับโอนนายทหารสัญญาบัตรเป็นข้าราชการในพระองค์ฝ่ายทหารและพระราชทานยศทหาร [นาวาอากาศเอก สุรศักดิ์  เสสะเวช]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/133835.pdf</t>
+  </si>
+  <si>
+    <t>พระบรมราชโองการ ประกาศ ให้นายทหารสัญญาบัตร  พ้นจากการปฏิบัติหน้าที่นายทหารราชองครักษ์ประจำพระองค์  [จำนวน 10 นาย 1. พลโท อาทิตย์  ดีประเสริฐ  ฯลฯ]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/133859.pdf</t>
+  </si>
+  <si>
+    <t>พระบรมราชโองการ ประกาศ ให้นายทหารราชองครักษ์พิเศษและนายตำรวจราชองครักษ์พิเศษ  พ้นจากการปฏิบัติหน้าที่ราชองครักษ์  [จำนวน 15 นาย 1. พลเอก ชาญชัย  ยศสุนทร ฯลฯ]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/133863.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศกระทรวงการคลัง เรื่อง ผลการกู้เงินเพื่อชดเชยการขาดดุลงบประมาณโดยการทำสัญญากู้ยืมเงิน (Term Loan) ในปีงบประมาณ พ.ศ. 2569 ครั้งที่ 4</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131302.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศกระทรวงการคลัง เรื่อง ผลการกู้เงินเพื่อชดเชยการขาดดุลงบประมาณโดยการออกตั๋วสัญญาใช้เงิน ในปีงบประมาณ พ.ศ. 2569 ครั้งที่ 4</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131638.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศกระทรวงการคลัง เรื่อง ผลการกู้เงินเพื่อให้กู้ต่อแก่การรถไฟแห่งประเทศไทย ในปีงบประมาณ พ.ศ. 2569 ครั้งที่ 13</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/130444.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศกระทรวงการคลัง เรื่อง ผลการกู้เงินเพื่อให้กู้ต่อแก่การรถไฟแห่งประเทศไทย ในปีงบประมาณ พ.ศ. 2569 ครั้งที่ 14</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/130445.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศกระทรวงการคลัง เรื่อง ผลการกู้เงินเพื่อให้กู้ต่อแก่การรถไฟแห่งประเทศไทย ในปีงบประมาณ พ.ศ. 2569 ครั้งที่ 15</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/130446.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศกระทรวงการคลัง เรื่อง ผลการจำหน่ายตั๋วเงินคลังเพื่อการบริหารหนี้ ในปีงบประมาณ พ.ศ. 2569 ครั้งที่ 11</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/130095.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศกระทรวงการคลัง เรื่อง ผลการจำหน่ายพันธบัตรรัฐบาล ในปีงบประมาณ พ.ศ. 2569 ครั้งที่ 25 (LB299A)</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131671.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศกระทรวงการคลัง เรื่อง ผลการจำหน่ายพันธบัตรรัฐบาล ในปีงบประมาณ พ.ศ. 2569 ครั้งที่ 26 (LB556A)</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131672.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศกรมทรัพยากรธรณี เรื่อง ให้ซากดึกดำบรรพ์เป็นซากดึกดำบรรพ์ที่ขึ้นทะเบียน ลำดับที่ 568 ถึง 574 จำนวน 7 รายการ ชื่อซากดึกดำบรรพ์ วาราโนซูคัส สกลนครเอนซิส</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131255.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศกรมทรัพยากรธรณี เรื่อง ให้ซากดึกดำบรรพ์เป็นซากดึกดำบรรพ์ที่ขึ้นทะเบียน ลำดับที่ 575 จำนวน 1 รายการ ชื่อซากดึกดำบรรพ์ คานิโนฟิลลัม อินโดไซน์เอนเซ</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131256.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศกรมทรัพยากรธรณี เรื่อง ให้ซากดึกดำบรรพ์เป็นซากดึกดำบรรพ์ที่ขึ้นทะเบียน ลำดับที่ 576 จำนวน 1 รายการ ชื่อซากดึกดำบรรพ์ ชีเซียฟิลลัม แวคคิวอัม</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131257.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศกรมทรัพยากรธรณี เรื่อง ให้ซากดึกดำบรรพ์เป็นซากดึกดำบรรพ์ที่ขึ้นทะเบียน ลำดับที่ 577 จำนวน 1 รายการ ชื่อซากดึกดำบรรพ์ จอมบึงเจีย ราชบุรีนา</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131258.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศกรมทรัพยากรธรณี เรื่อง ให้ซากดึกดำบรรพ์เป็นซากดึกดำบรรพ์ที่ขึ้นทะเบียน ลำดับที่ 578 ถึง 580 จำนวน 3 รายการ ชื่อซากดึกดำบรรพ์ แครสซิปารีทิฟิลลัม สัตยารักษ์กิ</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131259.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศกรมทรัพยากรธรณี เรื่อง ให้ซากดึกดำบรรพ์เป็นซากดึกดำบรรพ์ที่ขึ้นทะเบียน ลำดับที่ 581 ถึง 582 จำนวน 2 รายการ ชื่อซากดึกดำบรรพ์ แครสซิปารีทิฟิลลัม เทนูเอ</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131260.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศกรมทรัพยากรธรณี เรื่อง ให้ซากดึกดำบรรพ์เป็นซากดึกดำบรรพ์ที่ขึ้นทะเบียน ลำดับที่ 583 จำนวน 1 รายการ ชื่อซากดึกดำบรรพ์ เดนซิคอลัมโนฟิลลัม ไทยแลนดิคัม</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131261.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศกรมทรัพยากรธรณี เรื่อง ให้ซากดึกดำบรรพ์เป็นซากดึกดำบรรพ์ที่ขึ้นทะเบียน ลำดับที่ 584 จำนวน 1 รายการ ชื่อซากดึกดำบรรพ์ อิปซิฟิลลัม ผาแดงเอนเซ</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131262.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศกรมทรัพยากรธรณี เรื่อง ให้ซากดึกดำบรรพ์เป็นซากดึกดำบรรพ์ที่ขึ้นทะเบียน ลำดับที่ 585 จำนวน 1 รายการ ชื่อซากดึกดำบรรพ์ โลโฟฟิลลิเดียม สยามเอนเซ</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131263.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศกรมทรัพยากรธรณี เรื่อง ให้ซากดึกดำบรรพ์เป็นซากดึกดำบรรพ์ที่ขึ้นทะเบียน ลำดับที่ 586 ถึง 587 จำนวน 2 รายการ ชื่อซากดึกดำบรรพ์ มัลติมูรินัส มะค่าเอนซิส</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131264.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศกรมทรัพยากรธรณี เรื่อง ให้ซากดึกดำบรรพ์เป็นซากดึกดำบรรพ์ที่ขึ้นทะเบียน ลำดับที่ 588 ถึง 589 จำนวน 2 รายการ ชื่อซากดึกดำบรรพ์ มัลติมูรินัส สุธีธรนิ</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131265.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศกรมทรัพยากรธรณี เรื่อง ให้ซากดึกดำบรรพ์เป็นซากดึกดำบรรพ์ที่ขึ้นทะเบียน ลำดับที่ 590 ถึง 591 จำนวน 2 รายการ ชื่อซากดึกดำบรรพ์ มัลติทีโคพอรา โพธิสัตย์ติ</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131266.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศกรมทรัพยากรธรณี เรื่อง ให้ซากดึกดำบรรพ์เป็นซากดึกดำบรรพ์ที่ขึ้นทะเบียน ลำดับที่ 592  จำนวน 1 รายการ ชื่อซากดึกดำบรรพ์ พาราอิปซิฟิลลัม กุลวานิชชิ</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131267.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศกรมทรัพยากรธรณี เรื่อง ให้ซากดึกดำบรรพ์เป็นซากดึกดำบรรพ์ที่ขึ้นทะเบียน ลำดับที่ 593 ถึง 598  จำนวน 6 รายการ ชื่อซากดึกดำบรรพ์ การูแดปเทอรัส บุฟโตติ</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131268.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศคณะกรรมการการแข่งขันทางการค้า เรื่อง การปฏิบัติทางการค้าที่เป็นธรรมเกี่ยวกับระยะเวลาการให้สินเชื่อการค้า (Credit Term) ระหว่างผู้ประกอบธุรกิจขนาดใหญ่หรือผู้ประกอบธุรกิจค้าส่งค้าปลีกขนาดใหญ่กับผู้ประกอบธุรกิจขนาดกลางและขนาดย่อม (SMEs)</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132256.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศคณะอนุกรรมการบริหารกองทุนภูมิปัญญาการแพทย์แผนไทย เรื่อง การบริหารจัดการทรัพย์สินทางปัญญาของกองทุนภูมิปัญญาการแพทย์แผนไทย พ.ศ. 2569</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131839.pdf</t>
+  </si>
+  <si>
+    <t>ข้อบังคับมหาวิทยาลัยมหิดล ว่าด้วยปริญญาในสาขาวิชา อักษรย่อสำหรับสาขาวิชา ครุยวิทยฐานะ และเข็มวิทยฐานะ พ.ศ. ๒๕๖๙</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131186.pdf</t>
+  </si>
+  <si>
+    <t>กระทู้ถามของสมาชิกสภาผู้แทนราษฎร กระทู้ถามที่ 048 ร. เรื่อง การทำงานของสำนักงานคณะกรรมการกิจการกระจายเสียง กิจการโทรทัศน์ และกิจการโทรคมนาคมแห่งชาติ [ของ นายเอกราช อุดมอำนวย สมาชิกสภาผู้แทนราษฎร พรรคประชาชน]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/130230.pdf</t>
+  </si>
+  <si>
+    <t>กระทู้ถามของสมาชิกสภาผุ้แทนราษฎร กระทู้ถามที่ 105 ร. เรื่อง แนวทางการแก้ไขปัญหาอาหารและเครื่องดื่มที่มีผลกระทบต่อสุขภาพเด็ก และการผลักดันกฎหมายการควบคุมการตลาดอาหารและเครื่องดื่มที่มีผลกระทบต่อสุขภาพเด็ก  [ของ นายณัฐวุฒิ บัวประทุม สมาชิกสภาผู้แทนราษฎร พรรคประชาชน]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131215.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.E1421/2569 นายธีรวัฒน์ สุมาลุย์ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132036.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.E1435/2569 นายเทพ อาจบำรุง ลูกหนี้ที่ 1 และนางสุชาดา ตันติวงศ์กร ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131997.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.E1437/2569 นายพิทักษ์ หนูสงค์ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132022.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.E1438/2569 นายสมบูรณ์ แซ่พ่าน ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131974.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.E1439/2569 นางอรทัย สมกาวิ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132009.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.E1440/2569 สิบโทหรือนายณรงค์เวทย์ ถ้ำแก้ว ลูกหนี้ที่ 1 และนายนิรัญ ถ้ำแก้ว ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131975.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.E1442/2569 นายภานุวัฒน์ จันดา ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132007.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.E1443/2569 นางสาวยุภาวดี ชินทวัน ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132023.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.E1444/2569 นายพินิตย์ โพธิ์ศรี ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131953.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.E1445/2569 นางสาวจินตนาหรือพบพร พิภพโยพิณกุล ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132042.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.E1446/2569 นางสาวปิยะพร สาริกาพงศ์ ลูกหนี้ที่ 1 และนายปัญญา สาริกาพงศ์ ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132008.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.E1447/2569 นายสุรศักดิ์ ปั้นบุญมี ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131980.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.E1448/2569 นางสาวปนัดดา สาทอง ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131940.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.7656/2569 นายนิเวทย์ โชงรัมย์ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131995.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.7828/2569 บริษัท นครสวรรค์ ธนาภา จำกัด ลูกหนี้ที่ 1, นางสุรีย์ เกษชนก ลูกหนี้ที่ 2, นายภูเบศหรืออิทธิชัย อัครวัฒนาภร ลูกหนี้ที่ 3 และนายฐาปดาหรือภัทรชัย อัครวัฒนาภร ลูกหนี้ที่ 4]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131979.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8028/2569 นายหรือพันจ่าเอกอำพล ชัยมงคล ลูกหนี้ที่ 1 และนายหรือจ่าเอกวุฒิพงศ์ ลายน้ำเงิน ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131959.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8029/2569 นายชัยวัฒน์ สินธบัณฑิต ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131998.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8051/2569 นายสุริยะ อิสระวัฒนา ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131989.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8052/2569 นางสาวอภิณห์พร เรืองวิวรรธน์ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132019.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8053/2569 สิบตรีหรือนายปิยวัฒน์ แดนอิน ลูกหนี้ที่ 1 และสิบเอกหรือนายธีรพล วัดแก้ว ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131971.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8062/2569 บริษัทเจซีซีบี บิสซิเนส จำกัด ลูกหนี้ที่ 1 และนางสาวละมัย ศรีคำ ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131987.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8069/2569 นายธีรชัย สิงคเสลิต ลูกหนี้ที่ 2 และนายประกิจ ลิชนะเธียร ลูกหนี้ที่ 3]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131983.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8092/2569 นางสาวณัฐกานต์ ทองรุ่ง ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132004.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8093/2569 นางจรินทร์ ทรงพุฒิปัญญา ลูกหนี้ที่ 1, นายอาจอง สังฆบุตร ลูกหนี้ที่ 2 และนางสาวบุษบา ฉายอรุณ ลูกหนี้ที่ 3]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132035.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8094/2569 นายครรชิต มลิวัลย์ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131981.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8112/2569 นายสุรศักดิ์ หมู่สกุล ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132017.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8113/2569 นายบุญรัตน์ มิ่งตี ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132034.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8114/2569 นายสุรศักดิ์ กุลลาย ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131938.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8116/2569 นายนพพร โชคลาภ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132010.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8117/2569 นางหรือนางสาวพรรณพัชนันท์หรือพรภิมล สุรนันท์หรือขันกสิกรรม ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132024.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8118/2569 นางสุมนา เจคอปส์ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131956.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8119/2569 นางสาวลัลล์ลลิลหรือกาญจนา วัชราวลีหรือโพธิ์ศรี ลูกหนี้ที่ 1 และนายสุรินทร์ เหลาประเสริฐ ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132044.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8120/2569 นางสาววรรณภา เทียบคำ ลูกหนี้ที่ 1 และนายกัมปนาท เหมือนศรีชัย ลูกหนี้ที่ 2]ชื่อเรื่อง</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131976.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8127/2569 ร้อยตำรวจโทหรือดาบตำรวจหรือสิบตำรวจโทเจริญ พิมพ์เรือง ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132038.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8128/2569 นายติณณภพ โพนทอง ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132021.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8129/2569 จ.ส.ต.หรือนางจินตนา อุตมะ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131946.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8130/2569 นายประสงค์ บุญเกิน ลูกหนี้ที่ 1, นายวิมุตติ หรือปรมี ป้อมพลอย ลูกหนี้ที่ 2 และนายจีรศักดิ์ ศรีสันต์ ลูกหนี้ที่ 3]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132006.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8131/2569 ห้างหุ้นส่วนจำกัด บุ๊คสตูล ลูกหนี้ที่ 1, นายอรรถกร รัตนนาคินทร์ ลูกหนี้ที่ 2, นายนาคินทร์ รัตนนาคินทร์ ลูกหนี้ที่ 3 และนางธิดารัตน์ รัตนนาคินทร์ ลูกหนี้ที่ 4]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131949.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8132/2569 นางสาวสวภัทร แป้นชุม ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132047.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8133/2569 นายณัฐวุฒิ เพชรมณี ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132000.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8134/2569 นางเบญจวรรณ เกนขุนทด ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131962.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8135/2569 นายชัยณรงค์ สุดสงวน ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131977.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8137/2569 นายวุฒิชาติหรือชัยวัฒน์ เครือชาติไทยหรือเครือลาว ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132013.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8138/2569 นายพิเชษไชย สอนถา ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132051.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8139/2569 นางสาววริศรา พวงแก้ว ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131978.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8140/2569 นายสัจจาวุธ โภคภิรมย์ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132032.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8141/2569 นายหรือจ่าสิบเอกพัชระเมศฐ์ ธนาปุตรานนท์ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132014.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8143/2569 นายประเสริฐ เหมรา ลูกหนี้ที่ 1 และนางวิจิตรา จันทร์ทะวงษ์ ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131967.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8144/2569 นางสาวปัทมา เกตุจุฬา ลูกหนี้ที่ 1 และนายณรงค์ศักดิ์ ไตรทาน ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132003.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8145/2569 นางสาวทัศนีย์ โชติธนภักดีกุลหรือแซ่เฮ้ง ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132031.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8146/2569 บริษัทวรพจน์ คอนเน็คชั่น จำกัด ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132039.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8147/2569 บริษัทซี.เอส.เคมีคอล เซอร์วิส จำกัด ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131972.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8148/2569 นางสาวนพเก้า ชื่นราตรี ลูกหนี้ที่ 1, นายยศวร ทัฬหสิริเวทย์ ลูกหนี้ที่ 2 และนายสุธี ทัฬหสิริเวทย์ ลูกหนี้ที่ 3]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131992.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8149/2569 นายสุระชิต ภูยาทิพย์หรือถูบาทิพย์ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131990.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8150/2569 นายสุรเดช ตาเซะ ลูกหนี้ที่ 1 และนายธรรมนูญ ตาเซะ ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131951.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8151/2569 นายณัฐวุฒิ ผลทรัพย์ ลูกหนี้ที่ 1 และนางสาวกนกพร นวลงาม ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132018.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8198/2569 นายรัฐรพี ดีสกุล ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132012.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8199/2569 นายเปรมประชา สุขวิเศษ ลูกหนี้ที่ 1 และนางสาวชบาลักษณ์ สุขวิเศษ ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132025.pdf</t>
   </si>
 </sst>
 </file>
@@ -1231,7 +2269,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:H141"/>
+  <dimension ref="A1:H313"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="12.02" customWidth="true" style="0"/>
@@ -4607,12 +5645,4140 @@
       </c>
     </row>
     <row r="141" spans="1:8">
-      <c r="A141" s="2"/>
-      <c r="C141" s="1"/>
-      <c r="D141" s="1"/>
-      <c r="E141" s="1"/>
-      <c r="F141" s="1"/>
+      <c r="A141" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B141" t="s">
+        <v>291</v>
+      </c>
+      <c r="C141" s="1">
+        <v>143</v>
+      </c>
+      <c r="D141" s="1">
+        <v>62</v>
+      </c>
+      <c r="E141" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F141" s="1">
+        <v>1</v>
+      </c>
       <c r="G141" s="1"/>
+      <c r="H141" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8">
+      <c r="A142" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B142" t="s">
+        <v>293</v>
+      </c>
+      <c r="C142" s="1">
+        <v>143</v>
+      </c>
+      <c r="D142" s="1">
+        <v>65</v>
+      </c>
+      <c r="E142" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="F142" s="1">
+        <v>1</v>
+      </c>
+      <c r="G142" s="1"/>
+      <c r="H142" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8">
+      <c r="A143" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B143" t="s">
+        <v>296</v>
+      </c>
+      <c r="C143" s="1">
+        <v>143</v>
+      </c>
+      <c r="D143" s="1">
+        <v>65</v>
+      </c>
+      <c r="E143" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="F143" s="1">
+        <v>2</v>
+      </c>
+      <c r="G143" s="1"/>
+      <c r="H143" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8">
+      <c r="A144" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B144" t="s">
+        <v>298</v>
+      </c>
+      <c r="C144" s="1">
+        <v>143</v>
+      </c>
+      <c r="D144" s="1">
+        <v>65</v>
+      </c>
+      <c r="E144" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="F144" s="1">
+        <v>3</v>
+      </c>
+      <c r="G144" s="1"/>
+      <c r="H144" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8">
+      <c r="A145" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B145" t="s">
+        <v>300</v>
+      </c>
+      <c r="C145" s="1">
+        <v>143</v>
+      </c>
+      <c r="D145" s="1">
+        <v>65</v>
+      </c>
+      <c r="E145" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="F145" s="1">
+        <v>5</v>
+      </c>
+      <c r="G145" s="1"/>
+      <c r="H145" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8">
+      <c r="A146" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B146" t="s">
+        <v>302</v>
+      </c>
+      <c r="C146" s="1">
+        <v>143</v>
+      </c>
+      <c r="D146" s="1">
+        <v>65</v>
+      </c>
+      <c r="E146" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="F146" s="1">
+        <v>7</v>
+      </c>
+      <c r="G146" s="1"/>
+      <c r="H146" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8">
+      <c r="A147" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B147" t="s">
+        <v>304</v>
+      </c>
+      <c r="C147" s="1">
+        <v>143</v>
+      </c>
+      <c r="D147" s="1">
+        <v>65</v>
+      </c>
+      <c r="E147" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="F147" s="1">
+        <v>8</v>
+      </c>
+      <c r="G147" s="1"/>
+      <c r="H147" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8">
+      <c r="A148" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B148" t="s">
+        <v>306</v>
+      </c>
+      <c r="C148" s="1">
+        <v>143</v>
+      </c>
+      <c r="D148" s="1">
+        <v>65</v>
+      </c>
+      <c r="E148" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="F148" s="1">
+        <v>9</v>
+      </c>
+      <c r="G148" s="1"/>
+      <c r="H148" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8">
+      <c r="A149" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B149" t="s">
+        <v>308</v>
+      </c>
+      <c r="C149" s="1">
+        <v>143</v>
+      </c>
+      <c r="D149" s="1">
+        <v>65</v>
+      </c>
+      <c r="E149" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="F149" s="1">
+        <v>10</v>
+      </c>
+      <c r="G149" s="1"/>
+      <c r="H149" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8">
+      <c r="A150" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B150" t="s">
+        <v>310</v>
+      </c>
+      <c r="C150" s="1">
+        <v>143</v>
+      </c>
+      <c r="D150" s="1">
+        <v>65</v>
+      </c>
+      <c r="E150" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="F150" s="1">
+        <v>11</v>
+      </c>
+      <c r="G150" s="1"/>
+      <c r="H150" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8">
+      <c r="A151" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B151" t="s">
+        <v>312</v>
+      </c>
+      <c r="C151" s="1">
+        <v>143</v>
+      </c>
+      <c r="D151" s="1">
+        <v>147</v>
+      </c>
+      <c r="E151" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F151" s="1">
+        <v>1</v>
+      </c>
+      <c r="G151" s="1"/>
+      <c r="H151" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8">
+      <c r="A152" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B152" t="s">
+        <v>314</v>
+      </c>
+      <c r="C152" s="1">
+        <v>143</v>
+      </c>
+      <c r="D152" s="1">
+        <v>147</v>
+      </c>
+      <c r="E152" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F152" s="1">
+        <v>2</v>
+      </c>
+      <c r="G152" s="1"/>
+      <c r="H152" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8">
+      <c r="A153" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B153" t="s">
+        <v>316</v>
+      </c>
+      <c r="C153" s="1">
+        <v>143</v>
+      </c>
+      <c r="D153" s="1">
+        <v>147</v>
+      </c>
+      <c r="E153" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F153" s="1">
+        <v>3</v>
+      </c>
+      <c r="G153" s="1"/>
+      <c r="H153" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8">
+      <c r="A154" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B154" t="s">
+        <v>318</v>
+      </c>
+      <c r="C154" s="1">
+        <v>143</v>
+      </c>
+      <c r="D154" s="1">
+        <v>147</v>
+      </c>
+      <c r="E154" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F154" s="1">
+        <v>4</v>
+      </c>
+      <c r="G154" s="1"/>
+      <c r="H154" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8">
+      <c r="A155" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B155" t="s">
+        <v>320</v>
+      </c>
+      <c r="C155" s="1">
+        <v>143</v>
+      </c>
+      <c r="D155" s="1">
+        <v>147</v>
+      </c>
+      <c r="E155" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F155" s="1">
+        <v>5</v>
+      </c>
+      <c r="G155" s="1"/>
+      <c r="H155" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8">
+      <c r="A156" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B156" t="s">
+        <v>322</v>
+      </c>
+      <c r="C156" s="1">
+        <v>143</v>
+      </c>
+      <c r="D156" s="1">
+        <v>147</v>
+      </c>
+      <c r="E156" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F156" s="1">
+        <v>6</v>
+      </c>
+      <c r="G156" s="1"/>
+      <c r="H156" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8">
+      <c r="A157" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B157" t="s">
+        <v>324</v>
+      </c>
+      <c r="C157" s="1">
+        <v>143</v>
+      </c>
+      <c r="D157" s="1">
+        <v>147</v>
+      </c>
+      <c r="E157" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F157" s="1">
+        <v>7</v>
+      </c>
+      <c r="G157" s="1"/>
+      <c r="H157" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8">
+      <c r="A158" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B158" t="s">
+        <v>326</v>
+      </c>
+      <c r="C158" s="1">
+        <v>143</v>
+      </c>
+      <c r="D158" s="1">
+        <v>147</v>
+      </c>
+      <c r="E158" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F158" s="1">
+        <v>8</v>
+      </c>
+      <c r="G158" s="1"/>
+      <c r="H158" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8">
+      <c r="A159" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B159" t="s">
+        <v>328</v>
+      </c>
+      <c r="C159" s="1">
+        <v>143</v>
+      </c>
+      <c r="D159" s="1">
+        <v>147</v>
+      </c>
+      <c r="E159" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F159" s="1">
+        <v>9</v>
+      </c>
+      <c r="G159" s="1"/>
+      <c r="H159" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8">
+      <c r="A160" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B160" t="s">
+        <v>330</v>
+      </c>
+      <c r="C160" s="1">
+        <v>143</v>
+      </c>
+      <c r="D160" s="1">
+        <v>147</v>
+      </c>
+      <c r="E160" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F160" s="1">
+        <v>10</v>
+      </c>
+      <c r="G160" s="1"/>
+      <c r="H160" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8">
+      <c r="A161" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B161" t="s">
+        <v>332</v>
+      </c>
+      <c r="C161" s="1">
+        <v>143</v>
+      </c>
+      <c r="D161" s="1">
+        <v>147</v>
+      </c>
+      <c r="E161" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F161" s="1">
+        <v>11</v>
+      </c>
+      <c r="G161" s="1"/>
+      <c r="H161" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8">
+      <c r="A162" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B162" t="s">
+        <v>334</v>
+      </c>
+      <c r="C162" s="1">
+        <v>143</v>
+      </c>
+      <c r="D162" s="1">
+        <v>147</v>
+      </c>
+      <c r="E162" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F162" s="1">
+        <v>12</v>
+      </c>
+      <c r="G162" s="1"/>
+      <c r="H162" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8">
+      <c r="A163" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B163" t="s">
+        <v>336</v>
+      </c>
+      <c r="C163" s="1">
+        <v>143</v>
+      </c>
+      <c r="D163" s="1">
+        <v>147</v>
+      </c>
+      <c r="E163" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F163" s="1">
+        <v>14</v>
+      </c>
+      <c r="G163" s="1"/>
+      <c r="H163" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8">
+      <c r="A164" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B164" t="s">
+        <v>338</v>
+      </c>
+      <c r="C164" s="1">
+        <v>143</v>
+      </c>
+      <c r="D164" s="1">
+        <v>147</v>
+      </c>
+      <c r="E164" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F164" s="1">
+        <v>15</v>
+      </c>
+      <c r="G164" s="1"/>
+      <c r="H164" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="165" spans="1:8">
+      <c r="A165" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B165" t="s">
+        <v>340</v>
+      </c>
+      <c r="C165" s="1">
+        <v>143</v>
+      </c>
+      <c r="D165" s="1">
+        <v>147</v>
+      </c>
+      <c r="E165" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F165" s="1">
+        <v>16</v>
+      </c>
+      <c r="G165" s="1"/>
+      <c r="H165" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="166" spans="1:8">
+      <c r="A166" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B166" t="s">
+        <v>342</v>
+      </c>
+      <c r="C166" s="1">
+        <v>143</v>
+      </c>
+      <c r="D166" s="1">
+        <v>147</v>
+      </c>
+      <c r="E166" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F166" s="1">
+        <v>17</v>
+      </c>
+      <c r="G166" s="1"/>
+      <c r="H166" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="167" spans="1:8">
+      <c r="A167" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B167" t="s">
+        <v>344</v>
+      </c>
+      <c r="C167" s="1">
+        <v>143</v>
+      </c>
+      <c r="D167" s="1">
+        <v>147</v>
+      </c>
+      <c r="E167" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F167" s="1">
+        <v>18</v>
+      </c>
+      <c r="G167" s="1"/>
+      <c r="H167" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8">
+      <c r="A168" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B168" t="s">
+        <v>346</v>
+      </c>
+      <c r="C168" s="1">
+        <v>143</v>
+      </c>
+      <c r="D168" s="1">
+        <v>147</v>
+      </c>
+      <c r="E168" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F168" s="1">
+        <v>19</v>
+      </c>
+      <c r="G168" s="1"/>
+      <c r="H168" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8">
+      <c r="A169" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B169" t="s">
+        <v>348</v>
+      </c>
+      <c r="C169" s="1">
+        <v>143</v>
+      </c>
+      <c r="D169" s="1">
+        <v>147</v>
+      </c>
+      <c r="E169" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F169" s="1">
+        <v>20</v>
+      </c>
+      <c r="G169" s="1"/>
+      <c r="H169" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="170" spans="1:8">
+      <c r="A170" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B170" t="s">
+        <v>350</v>
+      </c>
+      <c r="C170" s="1">
+        <v>143</v>
+      </c>
+      <c r="D170" s="1">
+        <v>147</v>
+      </c>
+      <c r="E170" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F170" s="1">
+        <v>21</v>
+      </c>
+      <c r="G170" s="1"/>
+      <c r="H170" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="171" spans="1:8">
+      <c r="A171" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B171" t="s">
+        <v>352</v>
+      </c>
+      <c r="C171" s="1">
+        <v>143</v>
+      </c>
+      <c r="D171" s="1">
+        <v>147</v>
+      </c>
+      <c r="E171" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F171" s="1">
+        <v>22</v>
+      </c>
+      <c r="G171" s="1"/>
+      <c r="H171" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="172" spans="1:8">
+      <c r="A172" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B172" t="s">
+        <v>354</v>
+      </c>
+      <c r="C172" s="1">
+        <v>143</v>
+      </c>
+      <c r="D172" s="1">
+        <v>147</v>
+      </c>
+      <c r="E172" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F172" s="1">
+        <v>23</v>
+      </c>
+      <c r="G172" s="1"/>
+      <c r="H172" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="173" spans="1:8">
+      <c r="A173" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B173" t="s">
+        <v>356</v>
+      </c>
+      <c r="C173" s="1">
+        <v>143</v>
+      </c>
+      <c r="D173" s="1">
+        <v>147</v>
+      </c>
+      <c r="E173" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F173" s="1">
+        <v>26</v>
+      </c>
+      <c r="G173" s="1"/>
+      <c r="H173" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="174" spans="1:8">
+      <c r="A174" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B174" t="s">
+        <v>358</v>
+      </c>
+      <c r="C174" s="1">
+        <v>143</v>
+      </c>
+      <c r="D174" s="1">
+        <v>147</v>
+      </c>
+      <c r="E174" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F174" s="1">
+        <v>27</v>
+      </c>
+      <c r="G174" s="1"/>
+      <c r="H174" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="175" spans="1:8">
+      <c r="A175" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B175" t="s">
+        <v>360</v>
+      </c>
+      <c r="C175" s="1">
+        <v>143</v>
+      </c>
+      <c r="D175" s="1">
+        <v>147</v>
+      </c>
+      <c r="E175" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F175" s="1">
+        <v>28</v>
+      </c>
+      <c r="G175" s="1"/>
+      <c r="H175" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="176" spans="1:8">
+      <c r="A176" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B176" t="s">
+        <v>362</v>
+      </c>
+      <c r="C176" s="1">
+        <v>143</v>
+      </c>
+      <c r="D176" s="1">
+        <v>147</v>
+      </c>
+      <c r="E176" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F176" s="1">
+        <v>29</v>
+      </c>
+      <c r="G176" s="1"/>
+      <c r="H176" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="177" spans="1:8">
+      <c r="A177" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B177" t="s">
+        <v>364</v>
+      </c>
+      <c r="C177" s="1">
+        <v>143</v>
+      </c>
+      <c r="D177" s="1">
+        <v>147</v>
+      </c>
+      <c r="E177" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F177" s="1">
+        <v>30</v>
+      </c>
+      <c r="G177" s="1"/>
+      <c r="H177" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="178" spans="1:8">
+      <c r="A178" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B178" t="s">
+        <v>366</v>
+      </c>
+      <c r="C178" s="1">
+        <v>143</v>
+      </c>
+      <c r="D178" s="1">
+        <v>147</v>
+      </c>
+      <c r="E178" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F178" s="1">
+        <v>31</v>
+      </c>
+      <c r="G178" s="1"/>
+      <c r="H178" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="179" spans="1:8">
+      <c r="A179" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B179" t="s">
+        <v>368</v>
+      </c>
+      <c r="C179" s="1">
+        <v>143</v>
+      </c>
+      <c r="D179" s="1">
+        <v>147</v>
+      </c>
+      <c r="E179" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F179" s="1">
+        <v>32</v>
+      </c>
+      <c r="G179" s="1"/>
+      <c r="H179" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="180" spans="1:8">
+      <c r="A180" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B180" t="s">
+        <v>370</v>
+      </c>
+      <c r="C180" s="1">
+        <v>143</v>
+      </c>
+      <c r="D180" s="1">
+        <v>147</v>
+      </c>
+      <c r="E180" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F180" s="1">
+        <v>33</v>
+      </c>
+      <c r="G180" s="1"/>
+      <c r="H180" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="181" spans="1:8">
+      <c r="A181" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B181" t="s">
+        <v>372</v>
+      </c>
+      <c r="C181" s="1">
+        <v>143</v>
+      </c>
+      <c r="D181" s="1">
+        <v>147</v>
+      </c>
+      <c r="E181" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F181" s="1">
+        <v>34</v>
+      </c>
+      <c r="G181" s="1"/>
+      <c r="H181" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="182" spans="1:8">
+      <c r="A182" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B182" t="s">
+        <v>374</v>
+      </c>
+      <c r="C182" s="1">
+        <v>143</v>
+      </c>
+      <c r="D182" s="1">
+        <v>147</v>
+      </c>
+      <c r="E182" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F182" s="1">
+        <v>35</v>
+      </c>
+      <c r="G182" s="1"/>
+      <c r="H182" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="183" spans="1:8">
+      <c r="A183" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B183" t="s">
+        <v>376</v>
+      </c>
+      <c r="C183" s="1">
+        <v>143</v>
+      </c>
+      <c r="D183" s="1">
+        <v>147</v>
+      </c>
+      <c r="E183" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F183" s="1">
+        <v>36</v>
+      </c>
+      <c r="G183" s="1"/>
+      <c r="H183" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="184" spans="1:8">
+      <c r="A184" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B184" t="s">
+        <v>378</v>
+      </c>
+      <c r="C184" s="1">
+        <v>143</v>
+      </c>
+      <c r="D184" s="1">
+        <v>147</v>
+      </c>
+      <c r="E184" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F184" s="1">
+        <v>37</v>
+      </c>
+      <c r="G184" s="1"/>
+      <c r="H184" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="185" spans="1:8">
+      <c r="A185" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B185" t="s">
+        <v>380</v>
+      </c>
+      <c r="C185" s="1">
+        <v>143</v>
+      </c>
+      <c r="D185" s="1">
+        <v>147</v>
+      </c>
+      <c r="E185" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F185" s="1">
+        <v>38</v>
+      </c>
+      <c r="G185" s="1"/>
+      <c r="H185" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="186" spans="1:8">
+      <c r="A186" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B186" t="s">
+        <v>382</v>
+      </c>
+      <c r="C186" s="1">
+        <v>143</v>
+      </c>
+      <c r="D186" s="1">
+        <v>147</v>
+      </c>
+      <c r="E186" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F186" s="1">
+        <v>39</v>
+      </c>
+      <c r="G186" s="1"/>
+      <c r="H186" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="187" spans="1:8">
+      <c r="A187" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B187" t="s">
+        <v>384</v>
+      </c>
+      <c r="C187" s="1">
+        <v>143</v>
+      </c>
+      <c r="D187" s="1">
+        <v>147</v>
+      </c>
+      <c r="E187" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F187" s="1">
+        <v>40</v>
+      </c>
+      <c r="G187" s="1"/>
+      <c r="H187" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="188" spans="1:8">
+      <c r="A188" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B188" t="s">
+        <v>386</v>
+      </c>
+      <c r="C188" s="1">
+        <v>143</v>
+      </c>
+      <c r="D188" s="1">
+        <v>147</v>
+      </c>
+      <c r="E188" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F188" s="1">
+        <v>41</v>
+      </c>
+      <c r="G188" s="1"/>
+      <c r="H188" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="189" spans="1:8">
+      <c r="A189" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B189" t="s">
+        <v>388</v>
+      </c>
+      <c r="C189" s="1">
+        <v>143</v>
+      </c>
+      <c r="D189" s="1">
+        <v>147</v>
+      </c>
+      <c r="E189" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F189" s="1">
+        <v>42</v>
+      </c>
+      <c r="G189" s="1"/>
+      <c r="H189" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="190" spans="1:8">
+      <c r="A190" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B190" t="s">
+        <v>390</v>
+      </c>
+      <c r="C190" s="1">
+        <v>143</v>
+      </c>
+      <c r="D190" s="1">
+        <v>147</v>
+      </c>
+      <c r="E190" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F190" s="1">
+        <v>43</v>
+      </c>
+      <c r="G190" s="1"/>
+      <c r="H190" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="191" spans="1:8">
+      <c r="A191" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B191" t="s">
+        <v>392</v>
+      </c>
+      <c r="C191" s="1">
+        <v>143</v>
+      </c>
+      <c r="D191" s="1">
+        <v>147</v>
+      </c>
+      <c r="E191" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F191" s="1">
+        <v>44</v>
+      </c>
+      <c r="G191" s="1"/>
+      <c r="H191" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="192" spans="1:8">
+      <c r="A192" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B192" t="s">
+        <v>394</v>
+      </c>
+      <c r="C192" s="1">
+        <v>143</v>
+      </c>
+      <c r="D192" s="1">
+        <v>147</v>
+      </c>
+      <c r="E192" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F192" s="1">
+        <v>45</v>
+      </c>
+      <c r="G192" s="1"/>
+      <c r="H192" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="193" spans="1:8">
+      <c r="A193" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B193" t="s">
+        <v>396</v>
+      </c>
+      <c r="C193" s="1">
+        <v>143</v>
+      </c>
+      <c r="D193" s="1">
+        <v>147</v>
+      </c>
+      <c r="E193" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F193" s="1">
+        <v>46</v>
+      </c>
+      <c r="G193" s="1"/>
+      <c r="H193" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="194" spans="1:8">
+      <c r="A194" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B194" t="s">
+        <v>398</v>
+      </c>
+      <c r="C194" s="1">
+        <v>143</v>
+      </c>
+      <c r="D194" s="1">
+        <v>147</v>
+      </c>
+      <c r="E194" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F194" s="1">
+        <v>47</v>
+      </c>
+      <c r="G194" s="1"/>
+      <c r="H194" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="195" spans="1:8">
+      <c r="A195" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B195" t="s">
+        <v>400</v>
+      </c>
+      <c r="C195" s="1">
+        <v>143</v>
+      </c>
+      <c r="D195" s="1">
+        <v>147</v>
+      </c>
+      <c r="E195" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F195" s="1">
+        <v>48</v>
+      </c>
+      <c r="G195" s="1"/>
+      <c r="H195" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="196" spans="1:8">
+      <c r="A196" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B196" t="s">
+        <v>402</v>
+      </c>
+      <c r="C196" s="1">
+        <v>143</v>
+      </c>
+      <c r="D196" s="1">
+        <v>147</v>
+      </c>
+      <c r="E196" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F196" s="1">
+        <v>49</v>
+      </c>
+      <c r="G196" s="1"/>
+      <c r="H196" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="197" spans="1:8">
+      <c r="A197" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B197" t="s">
+        <v>404</v>
+      </c>
+      <c r="C197" s="1">
+        <v>143</v>
+      </c>
+      <c r="D197" s="1">
+        <v>147</v>
+      </c>
+      <c r="E197" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F197" s="1">
+        <v>51</v>
+      </c>
+      <c r="G197" s="1"/>
+      <c r="H197" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="198" spans="1:8">
+      <c r="A198" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B198" t="s">
+        <v>406</v>
+      </c>
+      <c r="C198" s="1">
+        <v>143</v>
+      </c>
+      <c r="D198" s="1">
+        <v>147</v>
+      </c>
+      <c r="E198" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F198" s="1">
+        <v>53</v>
+      </c>
+      <c r="G198" s="1"/>
+      <c r="H198" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="199" spans="1:8">
+      <c r="A199" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B199" t="s">
+        <v>408</v>
+      </c>
+      <c r="C199" s="1">
+        <v>143</v>
+      </c>
+      <c r="D199" s="1">
+        <v>147</v>
+      </c>
+      <c r="E199" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F199" s="1">
+        <v>55</v>
+      </c>
+      <c r="G199" s="1"/>
+      <c r="H199" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="200" spans="1:8">
+      <c r="A200" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B200" t="s">
+        <v>410</v>
+      </c>
+      <c r="C200" s="1">
+        <v>143</v>
+      </c>
+      <c r="D200" s="1">
+        <v>147</v>
+      </c>
+      <c r="E200" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F200" s="1">
+        <v>57</v>
+      </c>
+      <c r="G200" s="1"/>
+      <c r="H200" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="201" spans="1:8">
+      <c r="A201" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B201" t="s">
+        <v>412</v>
+      </c>
+      <c r="C201" s="1">
+        <v>143</v>
+      </c>
+      <c r="D201" s="1">
+        <v>147</v>
+      </c>
+      <c r="E201" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F201" s="1">
+        <v>59</v>
+      </c>
+      <c r="G201" s="1"/>
+      <c r="H201" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="202" spans="1:8">
+      <c r="A202" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B202" t="s">
+        <v>414</v>
+      </c>
+      <c r="C202" s="1">
+        <v>143</v>
+      </c>
+      <c r="D202" s="1">
+        <v>147</v>
+      </c>
+      <c r="E202" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F202" s="1">
+        <v>60</v>
+      </c>
+      <c r="G202" s="1"/>
+      <c r="H202" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="203" spans="1:8">
+      <c r="A203" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B203" t="s">
+        <v>416</v>
+      </c>
+      <c r="C203" s="1">
+        <v>143</v>
+      </c>
+      <c r="D203" s="1">
+        <v>147</v>
+      </c>
+      <c r="E203" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F203" s="1">
+        <v>61</v>
+      </c>
+      <c r="G203" s="1"/>
+      <c r="H203" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="204" spans="1:8">
+      <c r="A204" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B204" t="s">
+        <v>418</v>
+      </c>
+      <c r="C204" s="1">
+        <v>143</v>
+      </c>
+      <c r="D204" s="1">
+        <v>147</v>
+      </c>
+      <c r="E204" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F204" s="1">
+        <v>62</v>
+      </c>
+      <c r="G204" s="1"/>
+      <c r="H204" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="205" spans="1:8">
+      <c r="A205" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B205" t="s">
+        <v>420</v>
+      </c>
+      <c r="C205" s="1">
+        <v>143</v>
+      </c>
+      <c r="D205" s="1">
+        <v>147</v>
+      </c>
+      <c r="E205" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F205" s="1">
+        <v>63</v>
+      </c>
+      <c r="G205" s="1"/>
+      <c r="H205" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="206" spans="1:8">
+      <c r="A206" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B206" t="s">
+        <v>422</v>
+      </c>
+      <c r="C206" s="1">
+        <v>143</v>
+      </c>
+      <c r="D206" s="1">
+        <v>147</v>
+      </c>
+      <c r="E206" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F206" s="1">
+        <v>64</v>
+      </c>
+      <c r="G206" s="1"/>
+      <c r="H206" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="207" spans="1:8">
+      <c r="A207" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B207" t="s">
+        <v>424</v>
+      </c>
+      <c r="C207" s="1">
+        <v>143</v>
+      </c>
+      <c r="D207" s="1">
+        <v>147</v>
+      </c>
+      <c r="E207" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F207" s="1">
+        <v>65</v>
+      </c>
+      <c r="G207" s="1"/>
+      <c r="H207" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="208" spans="1:8">
+      <c r="A208" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B208" t="s">
+        <v>426</v>
+      </c>
+      <c r="C208" s="1">
+        <v>143</v>
+      </c>
+      <c r="D208" s="1">
+        <v>147</v>
+      </c>
+      <c r="E208" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F208" s="1">
+        <v>66</v>
+      </c>
+      <c r="G208" s="1"/>
+      <c r="H208" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="209" spans="1:8">
+      <c r="A209" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B209" t="s">
+        <v>428</v>
+      </c>
+      <c r="C209" s="1">
+        <v>143</v>
+      </c>
+      <c r="D209" s="1">
+        <v>147</v>
+      </c>
+      <c r="E209" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F209" s="1">
+        <v>67</v>
+      </c>
+      <c r="G209" s="1"/>
+      <c r="H209" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="210" spans="1:8">
+      <c r="A210" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B210" t="s">
+        <v>430</v>
+      </c>
+      <c r="C210" s="1">
+        <v>143</v>
+      </c>
+      <c r="D210" s="1">
+        <v>147</v>
+      </c>
+      <c r="E210" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F210" s="1">
+        <v>69</v>
+      </c>
+      <c r="G210" s="1"/>
+      <c r="H210" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="211" spans="1:8">
+      <c r="A211" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B211" t="s">
+        <v>432</v>
+      </c>
+      <c r="C211" s="1">
+        <v>143</v>
+      </c>
+      <c r="D211" s="1">
+        <v>147</v>
+      </c>
+      <c r="E211" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F211" s="1">
+        <v>70</v>
+      </c>
+      <c r="G211" s="1"/>
+      <c r="H211" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="212" spans="1:8">
+      <c r="A212" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B212" t="s">
+        <v>434</v>
+      </c>
+      <c r="C212" s="1">
+        <v>143</v>
+      </c>
+      <c r="D212" s="1">
+        <v>147</v>
+      </c>
+      <c r="E212" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F212" s="1">
+        <v>71</v>
+      </c>
+      <c r="G212" s="1"/>
+      <c r="H212" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="213" spans="1:8">
+      <c r="A213" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B213" t="s">
+        <v>436</v>
+      </c>
+      <c r="C213" s="1">
+        <v>143</v>
+      </c>
+      <c r="D213" s="1">
+        <v>147</v>
+      </c>
+      <c r="E213" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F213" s="1">
+        <v>72</v>
+      </c>
+      <c r="G213" s="1"/>
+      <c r="H213" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="214" spans="1:8">
+      <c r="A214" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B214" t="s">
+        <v>438</v>
+      </c>
+      <c r="C214" s="1">
+        <v>143</v>
+      </c>
+      <c r="D214" s="1">
+        <v>147</v>
+      </c>
+      <c r="E214" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F214" s="1">
+        <v>73</v>
+      </c>
+      <c r="G214" s="1"/>
+      <c r="H214" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="215" spans="1:8">
+      <c r="A215" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B215" t="s">
+        <v>440</v>
+      </c>
+      <c r="C215" s="1">
+        <v>143</v>
+      </c>
+      <c r="D215" s="1">
+        <v>147</v>
+      </c>
+      <c r="E215" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F215" s="1">
+        <v>74</v>
+      </c>
+      <c r="G215" s="1"/>
+      <c r="H215" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="216" spans="1:8">
+      <c r="A216" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B216" t="s">
+        <v>442</v>
+      </c>
+      <c r="C216" s="1">
+        <v>143</v>
+      </c>
+      <c r="D216" s="1">
+        <v>147</v>
+      </c>
+      <c r="E216" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F216" s="1">
+        <v>76</v>
+      </c>
+      <c r="G216" s="1"/>
+      <c r="H216" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="217" spans="1:8">
+      <c r="A217" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B217" t="s">
+        <v>444</v>
+      </c>
+      <c r="C217" s="1">
+        <v>143</v>
+      </c>
+      <c r="D217" s="1">
+        <v>147</v>
+      </c>
+      <c r="E217" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F217" s="1">
+        <v>78</v>
+      </c>
+      <c r="G217" s="1"/>
+      <c r="H217" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="218" spans="1:8">
+      <c r="A218" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B218" t="s">
+        <v>446</v>
+      </c>
+      <c r="C218" s="1">
+        <v>143</v>
+      </c>
+      <c r="D218" s="1">
+        <v>147</v>
+      </c>
+      <c r="E218" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F218" s="1">
+        <v>79</v>
+      </c>
+      <c r="G218" s="1"/>
+      <c r="H218" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="219" spans="1:8">
+      <c r="A219" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B219" t="s">
+        <v>448</v>
+      </c>
+      <c r="C219" s="1">
+        <v>143</v>
+      </c>
+      <c r="D219" s="1">
+        <v>147</v>
+      </c>
+      <c r="E219" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F219" s="1">
+        <v>80</v>
+      </c>
+      <c r="G219" s="1"/>
+      <c r="H219" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="220" spans="1:8">
+      <c r="A220" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B220" t="s">
+        <v>450</v>
+      </c>
+      <c r="C220" s="1">
+        <v>143</v>
+      </c>
+      <c r="D220" s="1">
+        <v>147</v>
+      </c>
+      <c r="E220" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F220" s="1">
+        <v>81</v>
+      </c>
+      <c r="G220" s="1"/>
+      <c r="H220" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="221" spans="1:8">
+      <c r="A221" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B221" t="s">
+        <v>452</v>
+      </c>
+      <c r="C221" s="1">
+        <v>143</v>
+      </c>
+      <c r="D221" s="1">
+        <v>239</v>
+      </c>
+      <c r="E221" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F221" s="1">
+        <v>1</v>
+      </c>
+      <c r="G221" s="1"/>
+      <c r="H221" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="222" spans="1:8">
+      <c r="A222" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B222" t="s">
+        <v>454</v>
+      </c>
+      <c r="C222" s="1">
+        <v>143</v>
+      </c>
+      <c r="D222" s="1">
+        <v>239</v>
+      </c>
+      <c r="E222" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F222" s="1">
+        <v>2</v>
+      </c>
+      <c r="G222" s="1"/>
+      <c r="H222" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="223" spans="1:8">
+      <c r="A223" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B223" t="s">
+        <v>456</v>
+      </c>
+      <c r="C223" s="1">
+        <v>143</v>
+      </c>
+      <c r="D223" s="1">
+        <v>239</v>
+      </c>
+      <c r="E223" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F223" s="1">
+        <v>3</v>
+      </c>
+      <c r="G223" s="1"/>
+      <c r="H223" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="224" spans="1:8">
+      <c r="A224" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B224" t="s">
+        <v>458</v>
+      </c>
+      <c r="C224" s="1">
+        <v>143</v>
+      </c>
+      <c r="D224" s="1">
+        <v>239</v>
+      </c>
+      <c r="E224" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F224" s="1">
+        <v>7</v>
+      </c>
+      <c r="G224" s="1"/>
+      <c r="H224" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="225" spans="1:8">
+      <c r="A225" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B225" t="s">
+        <v>460</v>
+      </c>
+      <c r="C225" s="1">
+        <v>143</v>
+      </c>
+      <c r="D225" s="1">
+        <v>239</v>
+      </c>
+      <c r="E225" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F225" s="1">
+        <v>9</v>
+      </c>
+      <c r="G225" s="1"/>
+      <c r="H225" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="226" spans="1:8">
+      <c r="A226" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B226" t="s">
+        <v>462</v>
+      </c>
+      <c r="C226" s="1">
+        <v>143</v>
+      </c>
+      <c r="D226" s="1">
+        <v>239</v>
+      </c>
+      <c r="E226" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F226" s="1">
+        <v>10</v>
+      </c>
+      <c r="G226" s="1"/>
+      <c r="H226" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="227" spans="1:8">
+      <c r="A227" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B227" t="s">
+        <v>464</v>
+      </c>
+      <c r="C227" s="1">
+        <v>143</v>
+      </c>
+      <c r="D227" s="1">
+        <v>239</v>
+      </c>
+      <c r="E227" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F227" s="1">
+        <v>11</v>
+      </c>
+      <c r="G227" s="1"/>
+      <c r="H227" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="228" spans="1:8">
+      <c r="A228" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B228" t="s">
+        <v>466</v>
+      </c>
+      <c r="C228" s="1">
+        <v>143</v>
+      </c>
+      <c r="D228" s="1">
+        <v>239</v>
+      </c>
+      <c r="E228" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F228" s="1">
+        <v>13</v>
+      </c>
+      <c r="G228" s="1"/>
+      <c r="H228" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="229" spans="1:8">
+      <c r="A229" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B229" t="s">
+        <v>468</v>
+      </c>
+      <c r="C229" s="1">
+        <v>143</v>
+      </c>
+      <c r="D229" s="1">
+        <v>239</v>
+      </c>
+      <c r="E229" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F229" s="1">
+        <v>15</v>
+      </c>
+      <c r="G229" s="1"/>
+      <c r="H229" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="230" spans="1:8">
+      <c r="A230" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B230" t="s">
+        <v>470</v>
+      </c>
+      <c r="C230" s="1">
+        <v>143</v>
+      </c>
+      <c r="D230" s="1">
+        <v>239</v>
+      </c>
+      <c r="E230" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F230" s="1">
+        <v>17</v>
+      </c>
+      <c r="G230" s="1"/>
+      <c r="H230" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="231" spans="1:8">
+      <c r="A231" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B231" t="s">
+        <v>472</v>
+      </c>
+      <c r="C231" s="1">
+        <v>143</v>
+      </c>
+      <c r="D231" s="1">
+        <v>239</v>
+      </c>
+      <c r="E231" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F231" s="1">
+        <v>19</v>
+      </c>
+      <c r="G231" s="1"/>
+      <c r="H231" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="232" spans="1:8">
+      <c r="A232" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B232" t="s">
+        <v>474</v>
+      </c>
+      <c r="C232" s="1">
+        <v>143</v>
+      </c>
+      <c r="D232" s="1">
+        <v>239</v>
+      </c>
+      <c r="E232" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F232" s="1">
+        <v>21</v>
+      </c>
+      <c r="G232" s="1"/>
+      <c r="H232" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="233" spans="1:8">
+      <c r="A233" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B233" t="s">
+        <v>476</v>
+      </c>
+      <c r="C233" s="1">
+        <v>143</v>
+      </c>
+      <c r="D233" s="1">
+        <v>239</v>
+      </c>
+      <c r="E233" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F233" s="1">
+        <v>23</v>
+      </c>
+      <c r="G233" s="1"/>
+      <c r="H233" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="234" spans="1:8">
+      <c r="A234" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B234" t="s">
+        <v>478</v>
+      </c>
+      <c r="C234" s="1">
+        <v>143</v>
+      </c>
+      <c r="D234" s="1">
+        <v>239</v>
+      </c>
+      <c r="E234" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F234" s="1">
+        <v>25</v>
+      </c>
+      <c r="G234" s="1"/>
+      <c r="H234" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="235" spans="1:8">
+      <c r="A235" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B235" t="s">
+        <v>480</v>
+      </c>
+      <c r="C235" s="1">
+        <v>143</v>
+      </c>
+      <c r="D235" s="1">
+        <v>239</v>
+      </c>
+      <c r="E235" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F235" s="1">
+        <v>27</v>
+      </c>
+      <c r="G235" s="1"/>
+      <c r="H235" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="236" spans="1:8">
+      <c r="A236" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B236" t="s">
+        <v>482</v>
+      </c>
+      <c r="C236" s="1">
+        <v>143</v>
+      </c>
+      <c r="D236" s="1">
+        <v>239</v>
+      </c>
+      <c r="E236" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F236" s="1">
+        <v>29</v>
+      </c>
+      <c r="G236" s="1"/>
+      <c r="H236" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="237" spans="1:8">
+      <c r="A237" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B237" t="s">
+        <v>484</v>
+      </c>
+      <c r="C237" s="1">
+        <v>143</v>
+      </c>
+      <c r="D237" s="1">
+        <v>239</v>
+      </c>
+      <c r="E237" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F237" s="1">
+        <v>30</v>
+      </c>
+      <c r="G237" s="1"/>
+      <c r="H237" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="238" spans="1:8">
+      <c r="A238" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B238" t="s">
+        <v>486</v>
+      </c>
+      <c r="C238" s="1">
+        <v>143</v>
+      </c>
+      <c r="D238" s="1">
+        <v>239</v>
+      </c>
+      <c r="E238" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F238" s="1">
+        <v>31</v>
+      </c>
+      <c r="G238" s="1"/>
+      <c r="H238" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="239" spans="1:8">
+      <c r="A239" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B239" t="s">
+        <v>488</v>
+      </c>
+      <c r="C239" s="1">
+        <v>143</v>
+      </c>
+      <c r="D239" s="1">
+        <v>239</v>
+      </c>
+      <c r="E239" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F239" s="1">
+        <v>32</v>
+      </c>
+      <c r="G239" s="1"/>
+      <c r="H239" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="240" spans="1:8">
+      <c r="A240" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B240" t="s">
+        <v>490</v>
+      </c>
+      <c r="C240" s="1">
+        <v>143</v>
+      </c>
+      <c r="D240" s="1">
+        <v>239</v>
+      </c>
+      <c r="E240" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F240" s="1">
+        <v>33</v>
+      </c>
+      <c r="G240" s="1"/>
+      <c r="H240" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="241" spans="1:8">
+      <c r="A241" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B241" t="s">
+        <v>492</v>
+      </c>
+      <c r="C241" s="1">
+        <v>143</v>
+      </c>
+      <c r="D241" s="1">
+        <v>239</v>
+      </c>
+      <c r="E241" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F241" s="1">
+        <v>34</v>
+      </c>
+      <c r="G241" s="1"/>
+      <c r="H241" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="242" spans="1:8">
+      <c r="A242" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B242" t="s">
+        <v>494</v>
+      </c>
+      <c r="C242" s="1">
+        <v>143</v>
+      </c>
+      <c r="D242" s="1">
+        <v>239</v>
+      </c>
+      <c r="E242" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F242" s="1">
+        <v>35</v>
+      </c>
+      <c r="G242" s="1"/>
+      <c r="H242" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="243" spans="1:8">
+      <c r="A243" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B243" t="s">
+        <v>496</v>
+      </c>
+      <c r="C243" s="1">
+        <v>143</v>
+      </c>
+      <c r="D243" s="1">
+        <v>239</v>
+      </c>
+      <c r="E243" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F243" s="1">
+        <v>36</v>
+      </c>
+      <c r="G243" s="1"/>
+      <c r="H243" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="244" spans="1:8">
+      <c r="A244" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B244" t="s">
+        <v>498</v>
+      </c>
+      <c r="C244" s="1">
+        <v>143</v>
+      </c>
+      <c r="D244" s="1">
+        <v>239</v>
+      </c>
+      <c r="E244" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F244" s="1">
+        <v>37</v>
+      </c>
+      <c r="G244" s="1"/>
+      <c r="H244" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="245" spans="1:8">
+      <c r="A245" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B245" t="s">
+        <v>500</v>
+      </c>
+      <c r="C245" s="1">
+        <v>143</v>
+      </c>
+      <c r="D245" s="1">
+        <v>239</v>
+      </c>
+      <c r="E245" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F245" s="1">
+        <v>38</v>
+      </c>
+      <c r="G245" s="1"/>
+      <c r="H245" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="246" spans="1:8">
+      <c r="A246" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B246" t="s">
+        <v>502</v>
+      </c>
+      <c r="C246" s="1">
+        <v>143</v>
+      </c>
+      <c r="D246" s="1">
+        <v>239</v>
+      </c>
+      <c r="E246" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F246" s="1">
+        <v>39</v>
+      </c>
+      <c r="G246" s="1"/>
+      <c r="H246" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="247" spans="1:8">
+      <c r="A247" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B247" t="s">
+        <v>504</v>
+      </c>
+      <c r="C247" s="1">
+        <v>143</v>
+      </c>
+      <c r="D247" s="1">
+        <v>239</v>
+      </c>
+      <c r="E247" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F247" s="1">
+        <v>40</v>
+      </c>
+      <c r="G247" s="1"/>
+      <c r="H247" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="248" spans="1:8">
+      <c r="A248" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B248" t="s">
+        <v>506</v>
+      </c>
+      <c r="C248" s="1">
+        <v>143</v>
+      </c>
+      <c r="D248" s="1">
+        <v>239</v>
+      </c>
+      <c r="E248" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F248" s="1">
+        <v>41</v>
+      </c>
+      <c r="G248" s="1"/>
+      <c r="H248" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="249" spans="1:8">
+      <c r="A249" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B249" t="s">
+        <v>508</v>
+      </c>
+      <c r="C249" s="1">
+        <v>143</v>
+      </c>
+      <c r="D249" s="1">
+        <v>239</v>
+      </c>
+      <c r="E249" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F249" s="1">
+        <v>42</v>
+      </c>
+      <c r="G249" s="1"/>
+      <c r="H249" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="250" spans="1:8">
+      <c r="A250" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B250" t="s">
+        <v>510</v>
+      </c>
+      <c r="C250" s="1">
+        <v>143</v>
+      </c>
+      <c r="D250" s="1">
+        <v>239</v>
+      </c>
+      <c r="E250" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F250" s="1">
+        <v>43</v>
+      </c>
+      <c r="G250" s="1"/>
+      <c r="H250" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="251" spans="1:8">
+      <c r="A251" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B251" t="s">
+        <v>512</v>
+      </c>
+      <c r="C251" s="1">
+        <v>143</v>
+      </c>
+      <c r="D251" s="1">
+        <v>239</v>
+      </c>
+      <c r="E251" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F251" s="1">
+        <v>47</v>
+      </c>
+      <c r="G251" s="1"/>
+      <c r="H251" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="252" spans="1:8">
+      <c r="A252" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B252" t="s">
+        <v>514</v>
+      </c>
+      <c r="C252" s="1">
+        <v>143</v>
+      </c>
+      <c r="D252" s="1">
+        <v>239</v>
+      </c>
+      <c r="E252" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F252" s="1">
+        <v>51</v>
+      </c>
+      <c r="G252" s="1"/>
+      <c r="H252" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="253" spans="1:8">
+      <c r="A253" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B253" t="s">
+        <v>516</v>
+      </c>
+      <c r="C253" s="1">
+        <v>143</v>
+      </c>
+      <c r="D253" s="1">
+        <v>239</v>
+      </c>
+      <c r="E253" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F253" s="1">
+        <v>59</v>
+      </c>
+      <c r="G253" s="1"/>
+      <c r="H253" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="254" spans="1:8">
+      <c r="A254" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B254" t="s">
+        <v>518</v>
+      </c>
+      <c r="C254" s="1">
+        <v>143</v>
+      </c>
+      <c r="D254" s="1">
+        <v>239</v>
+      </c>
+      <c r="E254" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F254" s="1">
+        <v>67</v>
+      </c>
+      <c r="G254" s="1"/>
+      <c r="H254" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="255" spans="1:8">
+      <c r="A255" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B255" t="s">
+        <v>520</v>
+      </c>
+      <c r="C255" s="1">
+        <v>143</v>
+      </c>
+      <c r="D255" s="1">
+        <v>239</v>
+      </c>
+      <c r="E255" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F255" s="1">
+        <v>73</v>
+      </c>
+      <c r="G255" s="1"/>
+      <c r="H255" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="256" spans="1:8">
+      <c r="A256" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B256" t="s">
+        <v>522</v>
+      </c>
+      <c r="C256" s="1">
+        <v>143</v>
+      </c>
+      <c r="D256" s="1">
+        <v>239</v>
+      </c>
+      <c r="E256" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F256" s="1">
+        <v>74</v>
+      </c>
+      <c r="G256" s="1"/>
+      <c r="H256" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="257" spans="1:8">
+      <c r="A257" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B257" t="s">
+        <v>524</v>
+      </c>
+      <c r="C257" s="1">
+        <v>143</v>
+      </c>
+      <c r="D257" s="1">
+        <v>239</v>
+      </c>
+      <c r="E257" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F257" s="1">
+        <v>75</v>
+      </c>
+      <c r="G257" s="1"/>
+      <c r="H257" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="258" spans="1:8">
+      <c r="A258" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B258" t="s">
+        <v>526</v>
+      </c>
+      <c r="C258" s="1">
+        <v>143</v>
+      </c>
+      <c r="D258" s="1">
+        <v>239</v>
+      </c>
+      <c r="E258" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F258" s="1">
+        <v>76</v>
+      </c>
+      <c r="G258" s="1"/>
+      <c r="H258" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="259" spans="1:8">
+      <c r="A259" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B259" t="s">
+        <v>528</v>
+      </c>
+      <c r="C259" s="1">
+        <v>143</v>
+      </c>
+      <c r="D259" s="1">
+        <v>239</v>
+      </c>
+      <c r="E259" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F259" s="1">
+        <v>77</v>
+      </c>
+      <c r="G259" s="1"/>
+      <c r="H259" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="260" spans="1:8">
+      <c r="A260" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B260" t="s">
+        <v>530</v>
+      </c>
+      <c r="C260" s="1">
+        <v>143</v>
+      </c>
+      <c r="D260" s="1">
+        <v>239</v>
+      </c>
+      <c r="E260" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F260" s="1">
+        <v>78</v>
+      </c>
+      <c r="G260" s="1"/>
+      <c r="H260" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="261" spans="1:8">
+      <c r="A261" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B261" t="s">
+        <v>532</v>
+      </c>
+      <c r="C261" s="1">
+        <v>143</v>
+      </c>
+      <c r="D261" s="1">
+        <v>239</v>
+      </c>
+      <c r="E261" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F261" s="1">
+        <v>79</v>
+      </c>
+      <c r="G261" s="1"/>
+      <c r="H261" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="262" spans="1:8">
+      <c r="A262" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B262" t="s">
+        <v>534</v>
+      </c>
+      <c r="C262" s="1">
+        <v>143</v>
+      </c>
+      <c r="D262" s="1">
+        <v>239</v>
+      </c>
+      <c r="E262" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F262" s="1">
+        <v>80</v>
+      </c>
+      <c r="G262" s="1"/>
+      <c r="H262" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="263" spans="1:8">
+      <c r="A263" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B263" t="s">
+        <v>536</v>
+      </c>
+      <c r="C263" s="1">
+        <v>143</v>
+      </c>
+      <c r="D263" s="1">
+        <v>239</v>
+      </c>
+      <c r="E263" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F263" s="1">
+        <v>81</v>
+      </c>
+      <c r="G263" s="1"/>
+      <c r="H263" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="264" spans="1:8">
+      <c r="A264" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B264" t="s">
+        <v>538</v>
+      </c>
+      <c r="C264" s="1">
+        <v>143</v>
+      </c>
+      <c r="D264" s="1">
+        <v>239</v>
+      </c>
+      <c r="E264" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F264" s="1">
+        <v>82</v>
+      </c>
+      <c r="G264" s="1"/>
+      <c r="H264" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="265" spans="1:8">
+      <c r="A265" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B265" t="s">
+        <v>540</v>
+      </c>
+      <c r="C265" s="1">
+        <v>143</v>
+      </c>
+      <c r="D265" s="1">
+        <v>239</v>
+      </c>
+      <c r="E265" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F265" s="1">
+        <v>83</v>
+      </c>
+      <c r="G265" s="1"/>
+      <c r="H265" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="266" spans="1:8">
+      <c r="A266" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B266" t="s">
+        <v>542</v>
+      </c>
+      <c r="C266" s="1">
+        <v>143</v>
+      </c>
+      <c r="D266" s="1">
+        <v>239</v>
+      </c>
+      <c r="E266" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F266" s="1">
+        <v>84</v>
+      </c>
+      <c r="G266" s="1"/>
+      <c r="H266" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="267" spans="1:8">
+      <c r="A267" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B267" t="s">
+        <v>544</v>
+      </c>
+      <c r="C267" s="1">
+        <v>143</v>
+      </c>
+      <c r="D267" s="1">
+        <v>239</v>
+      </c>
+      <c r="E267" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F267" s="1">
+        <v>85</v>
+      </c>
+      <c r="G267" s="1"/>
+      <c r="H267" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="268" spans="1:8">
+      <c r="A268" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B268" t="s">
+        <v>546</v>
+      </c>
+      <c r="C268" s="1">
+        <v>143</v>
+      </c>
+      <c r="D268" s="1">
+        <v>239</v>
+      </c>
+      <c r="E268" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F268" s="1">
+        <v>86</v>
+      </c>
+      <c r="G268" s="1"/>
+      <c r="H268" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="269" spans="1:8">
+      <c r="A269" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B269" t="s">
+        <v>548</v>
+      </c>
+      <c r="C269" s="1">
+        <v>143</v>
+      </c>
+      <c r="D269" s="1">
+        <v>239</v>
+      </c>
+      <c r="E269" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F269" s="1">
+        <v>87</v>
+      </c>
+      <c r="G269" s="1"/>
+      <c r="H269" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="270" spans="1:8">
+      <c r="A270" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B270" t="s">
+        <v>550</v>
+      </c>
+      <c r="C270" s="1">
+        <v>143</v>
+      </c>
+      <c r="D270" s="1">
+        <v>239</v>
+      </c>
+      <c r="E270" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F270" s="1">
+        <v>89</v>
+      </c>
+      <c r="G270" s="1"/>
+      <c r="H270" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="271" spans="1:8">
+      <c r="A271" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B271" t="s">
+        <v>552</v>
+      </c>
+      <c r="C271" s="1">
+        <v>143</v>
+      </c>
+      <c r="D271" s="1">
+        <v>239</v>
+      </c>
+      <c r="E271" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F271" s="1">
+        <v>90</v>
+      </c>
+      <c r="G271" s="1"/>
+      <c r="H271" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="272" spans="1:8">
+      <c r="A272" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B272" t="s">
+        <v>554</v>
+      </c>
+      <c r="C272" s="1">
+        <v>143</v>
+      </c>
+      <c r="D272" s="1">
+        <v>239</v>
+      </c>
+      <c r="E272" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F272" s="1">
+        <v>91</v>
+      </c>
+      <c r="G272" s="1"/>
+      <c r="H272" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="273" spans="1:8">
+      <c r="A273" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B273" t="s">
+        <v>556</v>
+      </c>
+      <c r="C273" s="1">
+        <v>143</v>
+      </c>
+      <c r="D273" s="1">
+        <v>239</v>
+      </c>
+      <c r="E273" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F273" s="1">
+        <v>92</v>
+      </c>
+      <c r="G273" s="1"/>
+      <c r="H273" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="274" spans="1:8">
+      <c r="A274" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B274" t="s">
+        <v>558</v>
+      </c>
+      <c r="C274" s="1">
+        <v>143</v>
+      </c>
+      <c r="D274" s="1">
+        <v>239</v>
+      </c>
+      <c r="E274" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F274" s="1">
+        <v>93</v>
+      </c>
+      <c r="G274" s="1"/>
+      <c r="H274" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="275" spans="1:8">
+      <c r="A275" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B275" t="s">
+        <v>560</v>
+      </c>
+      <c r="C275" s="1">
+        <v>143</v>
+      </c>
+      <c r="D275" s="1">
+        <v>239</v>
+      </c>
+      <c r="E275" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F275" s="1">
+        <v>94</v>
+      </c>
+      <c r="G275" s="1"/>
+      <c r="H275" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="276" spans="1:8">
+      <c r="A276" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B276" t="s">
+        <v>562</v>
+      </c>
+      <c r="C276" s="1">
+        <v>143</v>
+      </c>
+      <c r="D276" s="1">
+        <v>239</v>
+      </c>
+      <c r="E276" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F276" s="1">
+        <v>95</v>
+      </c>
+      <c r="G276" s="1"/>
+      <c r="H276" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="277" spans="1:8">
+      <c r="A277" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B277" t="s">
+        <v>564</v>
+      </c>
+      <c r="C277" s="1">
+        <v>143</v>
+      </c>
+      <c r="D277" s="1">
+        <v>239</v>
+      </c>
+      <c r="E277" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F277" s="1">
+        <v>96</v>
+      </c>
+      <c r="G277" s="1"/>
+      <c r="H277" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="278" spans="1:8">
+      <c r="A278" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B278" t="s">
+        <v>566</v>
+      </c>
+      <c r="C278" s="1">
+        <v>143</v>
+      </c>
+      <c r="D278" s="1">
+        <v>239</v>
+      </c>
+      <c r="E278" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F278" s="1">
+        <v>97</v>
+      </c>
+      <c r="G278" s="1"/>
+      <c r="H278" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="279" spans="1:8">
+      <c r="A279" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B279" t="s">
+        <v>568</v>
+      </c>
+      <c r="C279" s="1">
+        <v>143</v>
+      </c>
+      <c r="D279" s="1">
+        <v>239</v>
+      </c>
+      <c r="E279" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F279" s="1">
+        <v>99</v>
+      </c>
+      <c r="G279" s="1"/>
+      <c r="H279" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="280" spans="1:8">
+      <c r="A280" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B280" t="s">
+        <v>570</v>
+      </c>
+      <c r="C280" s="1">
+        <v>143</v>
+      </c>
+      <c r="D280" s="1">
+        <v>239</v>
+      </c>
+      <c r="E280" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F280" s="1">
+        <v>100</v>
+      </c>
+      <c r="G280" s="1"/>
+      <c r="H280" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="281" spans="1:8">
+      <c r="A281" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B281" t="s">
+        <v>572</v>
+      </c>
+      <c r="C281" s="1">
+        <v>143</v>
+      </c>
+      <c r="D281" s="1">
+        <v>239</v>
+      </c>
+      <c r="E281" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F281" s="1">
+        <v>101</v>
+      </c>
+      <c r="G281" s="1"/>
+      <c r="H281" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="282" spans="1:8">
+      <c r="A282" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B282" t="s">
+        <v>574</v>
+      </c>
+      <c r="C282" s="1">
+        <v>143</v>
+      </c>
+      <c r="D282" s="1">
+        <v>239</v>
+      </c>
+      <c r="E282" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F282" s="1">
+        <v>102</v>
+      </c>
+      <c r="G282" s="1"/>
+      <c r="H282" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="283" spans="1:8">
+      <c r="A283" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B283" t="s">
+        <v>576</v>
+      </c>
+      <c r="C283" s="1">
+        <v>143</v>
+      </c>
+      <c r="D283" s="1">
+        <v>239</v>
+      </c>
+      <c r="E283" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F283" s="1">
+        <v>103</v>
+      </c>
+      <c r="G283" s="1"/>
+      <c r="H283" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="284" spans="1:8">
+      <c r="A284" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B284" t="s">
+        <v>578</v>
+      </c>
+      <c r="C284" s="1">
+        <v>143</v>
+      </c>
+      <c r="D284" s="1">
+        <v>239</v>
+      </c>
+      <c r="E284" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F284" s="1">
+        <v>104</v>
+      </c>
+      <c r="G284" s="1"/>
+      <c r="H284" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="285" spans="1:8">
+      <c r="A285" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B285" t="s">
+        <v>580</v>
+      </c>
+      <c r="C285" s="1">
+        <v>143</v>
+      </c>
+      <c r="D285" s="1">
+        <v>239</v>
+      </c>
+      <c r="E285" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F285" s="1">
+        <v>105</v>
+      </c>
+      <c r="G285" s="1"/>
+      <c r="H285" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="286" spans="1:8">
+      <c r="A286" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B286" t="s">
+        <v>582</v>
+      </c>
+      <c r="C286" s="1">
+        <v>143</v>
+      </c>
+      <c r="D286" s="1">
+        <v>239</v>
+      </c>
+      <c r="E286" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F286" s="1">
+        <v>106</v>
+      </c>
+      <c r="G286" s="1"/>
+      <c r="H286" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="287" spans="1:8">
+      <c r="A287" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B287" t="s">
+        <v>584</v>
+      </c>
+      <c r="C287" s="1">
+        <v>143</v>
+      </c>
+      <c r="D287" s="1">
+        <v>239</v>
+      </c>
+      <c r="E287" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F287" s="1">
+        <v>107</v>
+      </c>
+      <c r="G287" s="1"/>
+      <c r="H287" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="288" spans="1:8">
+      <c r="A288" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B288" t="s">
+        <v>586</v>
+      </c>
+      <c r="C288" s="1">
+        <v>143</v>
+      </c>
+      <c r="D288" s="1">
+        <v>239</v>
+      </c>
+      <c r="E288" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F288" s="1">
+        <v>108</v>
+      </c>
+      <c r="G288" s="1"/>
+      <c r="H288" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="289" spans="1:8">
+      <c r="A289" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B289" t="s">
+        <v>588</v>
+      </c>
+      <c r="C289" s="1">
+        <v>143</v>
+      </c>
+      <c r="D289" s="1">
+        <v>239</v>
+      </c>
+      <c r="E289" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F289" s="1">
+        <v>109</v>
+      </c>
+      <c r="G289" s="1"/>
+      <c r="H289" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="290" spans="1:8">
+      <c r="A290" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B290" t="s">
+        <v>590</v>
+      </c>
+      <c r="C290" s="1">
+        <v>143</v>
+      </c>
+      <c r="D290" s="1">
+        <v>239</v>
+      </c>
+      <c r="E290" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F290" s="1">
+        <v>110</v>
+      </c>
+      <c r="G290" s="1"/>
+      <c r="H290" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="291" spans="1:8">
+      <c r="A291" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B291" t="s">
+        <v>592</v>
+      </c>
+      <c r="C291" s="1">
+        <v>143</v>
+      </c>
+      <c r="D291" s="1">
+        <v>239</v>
+      </c>
+      <c r="E291" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F291" s="1">
+        <v>111</v>
+      </c>
+      <c r="G291" s="1"/>
+      <c r="H291" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="292" spans="1:8">
+      <c r="A292" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B292" t="s">
+        <v>594</v>
+      </c>
+      <c r="C292" s="1">
+        <v>143</v>
+      </c>
+      <c r="D292" s="1">
+        <v>239</v>
+      </c>
+      <c r="E292" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F292" s="1">
+        <v>113</v>
+      </c>
+      <c r="G292" s="1"/>
+      <c r="H292" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="293" spans="1:8">
+      <c r="A293" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B293" t="s">
+        <v>596</v>
+      </c>
+      <c r="C293" s="1">
+        <v>143</v>
+      </c>
+      <c r="D293" s="1">
+        <v>239</v>
+      </c>
+      <c r="E293" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F293" s="1">
+        <v>115</v>
+      </c>
+      <c r="G293" s="1"/>
+      <c r="H293" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="294" spans="1:8">
+      <c r="A294" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B294" t="s">
+        <v>598</v>
+      </c>
+      <c r="C294" s="1">
+        <v>143</v>
+      </c>
+      <c r="D294" s="1">
+        <v>239</v>
+      </c>
+      <c r="E294" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F294" s="1">
+        <v>116</v>
+      </c>
+      <c r="G294" s="1"/>
+      <c r="H294" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="295" spans="1:8">
+      <c r="A295" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B295" t="s">
+        <v>600</v>
+      </c>
+      <c r="C295" s="1">
+        <v>143</v>
+      </c>
+      <c r="D295" s="1">
+        <v>239</v>
+      </c>
+      <c r="E295" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F295" s="1">
+        <v>117</v>
+      </c>
+      <c r="G295" s="1"/>
+      <c r="H295" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="296" spans="1:8">
+      <c r="A296" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B296" t="s">
+        <v>602</v>
+      </c>
+      <c r="C296" s="1">
+        <v>143</v>
+      </c>
+      <c r="D296" s="1">
+        <v>239</v>
+      </c>
+      <c r="E296" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F296" s="1">
+        <v>118</v>
+      </c>
+      <c r="G296" s="1"/>
+      <c r="H296" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="297" spans="1:8">
+      <c r="A297" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B297" t="s">
+        <v>604</v>
+      </c>
+      <c r="C297" s="1">
+        <v>143</v>
+      </c>
+      <c r="D297" s="1">
+        <v>239</v>
+      </c>
+      <c r="E297" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F297" s="1">
+        <v>119</v>
+      </c>
+      <c r="G297" s="1"/>
+      <c r="H297" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="298" spans="1:8">
+      <c r="A298" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B298" t="s">
+        <v>606</v>
+      </c>
+      <c r="C298" s="1">
+        <v>143</v>
+      </c>
+      <c r="D298" s="1">
+        <v>239</v>
+      </c>
+      <c r="E298" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F298" s="1">
+        <v>120</v>
+      </c>
+      <c r="G298" s="1"/>
+      <c r="H298" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="299" spans="1:8">
+      <c r="A299" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B299" t="s">
+        <v>608</v>
+      </c>
+      <c r="C299" s="1">
+        <v>143</v>
+      </c>
+      <c r="D299" s="1">
+        <v>239</v>
+      </c>
+      <c r="E299" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F299" s="1">
+        <v>121</v>
+      </c>
+      <c r="G299" s="1"/>
+      <c r="H299" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="300" spans="1:8">
+      <c r="A300" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B300" t="s">
+        <v>610</v>
+      </c>
+      <c r="C300" s="1">
+        <v>143</v>
+      </c>
+      <c r="D300" s="1">
+        <v>239</v>
+      </c>
+      <c r="E300" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F300" s="1">
+        <v>122</v>
+      </c>
+      <c r="G300" s="1"/>
+      <c r="H300" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="301" spans="1:8">
+      <c r="A301" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B301" t="s">
+        <v>612</v>
+      </c>
+      <c r="C301" s="1">
+        <v>143</v>
+      </c>
+      <c r="D301" s="1">
+        <v>239</v>
+      </c>
+      <c r="E301" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F301" s="1">
+        <v>123</v>
+      </c>
+      <c r="G301" s="1"/>
+      <c r="H301" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="302" spans="1:8">
+      <c r="A302" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B302" t="s">
+        <v>614</v>
+      </c>
+      <c r="C302" s="1">
+        <v>143</v>
+      </c>
+      <c r="D302" s="1">
+        <v>239</v>
+      </c>
+      <c r="E302" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F302" s="1">
+        <v>124</v>
+      </c>
+      <c r="G302" s="1"/>
+      <c r="H302" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="303" spans="1:8">
+      <c r="A303" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B303" t="s">
+        <v>616</v>
+      </c>
+      <c r="C303" s="1">
+        <v>143</v>
+      </c>
+      <c r="D303" s="1">
+        <v>239</v>
+      </c>
+      <c r="E303" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F303" s="1">
+        <v>125</v>
+      </c>
+      <c r="G303" s="1"/>
+      <c r="H303" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="304" spans="1:8">
+      <c r="A304" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B304" t="s">
+        <v>618</v>
+      </c>
+      <c r="C304" s="1">
+        <v>143</v>
+      </c>
+      <c r="D304" s="1">
+        <v>239</v>
+      </c>
+      <c r="E304" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F304" s="1">
+        <v>126</v>
+      </c>
+      <c r="G304" s="1"/>
+      <c r="H304" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="305" spans="1:8">
+      <c r="A305" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B305" t="s">
+        <v>620</v>
+      </c>
+      <c r="C305" s="1">
+        <v>143</v>
+      </c>
+      <c r="D305" s="1">
+        <v>239</v>
+      </c>
+      <c r="E305" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F305" s="1">
+        <v>127</v>
+      </c>
+      <c r="G305" s="1"/>
+      <c r="H305" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="306" spans="1:8">
+      <c r="A306" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B306" t="s">
+        <v>622</v>
+      </c>
+      <c r="C306" s="1">
+        <v>143</v>
+      </c>
+      <c r="D306" s="1">
+        <v>239</v>
+      </c>
+      <c r="E306" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F306" s="1">
+        <v>128</v>
+      </c>
+      <c r="G306" s="1"/>
+      <c r="H306" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="307" spans="1:8">
+      <c r="A307" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B307" t="s">
+        <v>624</v>
+      </c>
+      <c r="C307" s="1">
+        <v>143</v>
+      </c>
+      <c r="D307" s="1">
+        <v>239</v>
+      </c>
+      <c r="E307" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F307" s="1">
+        <v>129</v>
+      </c>
+      <c r="G307" s="1"/>
+      <c r="H307" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="308" spans="1:8">
+      <c r="A308" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B308" t="s">
+        <v>626</v>
+      </c>
+      <c r="C308" s="1">
+        <v>143</v>
+      </c>
+      <c r="D308" s="1">
+        <v>239</v>
+      </c>
+      <c r="E308" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F308" s="1">
+        <v>131</v>
+      </c>
+      <c r="G308" s="1"/>
+      <c r="H308" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="309" spans="1:8">
+      <c r="A309" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B309" t="s">
+        <v>628</v>
+      </c>
+      <c r="C309" s="1">
+        <v>143</v>
+      </c>
+      <c r="D309" s="1">
+        <v>239</v>
+      </c>
+      <c r="E309" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F309" s="1">
+        <v>132</v>
+      </c>
+      <c r="G309" s="1"/>
+      <c r="H309" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="310" spans="1:8">
+      <c r="A310" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B310" t="s">
+        <v>630</v>
+      </c>
+      <c r="C310" s="1">
+        <v>143</v>
+      </c>
+      <c r="D310" s="1">
+        <v>239</v>
+      </c>
+      <c r="E310" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F310" s="1">
+        <v>133</v>
+      </c>
+      <c r="G310" s="1"/>
+      <c r="H310" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="311" spans="1:8">
+      <c r="A311" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B311" t="s">
+        <v>632</v>
+      </c>
+      <c r="C311" s="1">
+        <v>143</v>
+      </c>
+      <c r="D311" s="1">
+        <v>239</v>
+      </c>
+      <c r="E311" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F311" s="1">
+        <v>134</v>
+      </c>
+      <c r="G311" s="1"/>
+      <c r="H311" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="312" spans="1:8">
+      <c r="A312" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B312" t="s">
+        <v>634</v>
+      </c>
+      <c r="C312" s="1">
+        <v>143</v>
+      </c>
+      <c r="D312" s="1">
+        <v>239</v>
+      </c>
+      <c r="E312" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F312" s="1">
+        <v>135</v>
+      </c>
+      <c r="G312" s="1"/>
+      <c r="H312" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="313" spans="1:8">
+      <c r="A313" s="2"/>
+      <c r="C313" s="1"/>
+      <c r="D313" s="1"/>
+      <c r="E313" s="1"/>
+      <c r="F313" s="1"/>
+      <c r="G313" s="1"/>
     </row>
   </sheetData>
   <sheetProtection sheet="false" objects="false" scenarios="false" formatCells="false" formatColumns="false" formatRows="false" insertColumns="false" insertRows="false" insertHyperlinks="false" deleteColumns="false" deleteRows="false" selectLockedCells="false" sort="false" autoFilter="false" pivotTables="false" selectUnlockedCells="false"/>

--- a/data/raw/monthly-2026-10.xlsx
+++ b/data/raw/monthly-2026-10.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="636">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="651">
   <si>
     <t>วันที่</t>
   </si>
@@ -1923,6 +1923,51 @@
   </si>
   <si>
     <t>https://ratchakitcha.soc.go.th/documents/132025.pdf</t>
+  </si>
+  <si>
+    <t>03/10/2026</t>
+  </si>
+  <si>
+    <t>ประกาศสำนักนายกรัฐมนตรี เรื่อง แต่งตั้งข้าราชการพลเรือนสามัญ [สำนักนายกรัฐมนตรี : นายณัฐพล รังสิตพล]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/133740.pdf</t>
+  </si>
+  <si>
+    <t>กระทู้ถามของสมาชิกสภาผู้แทนราษฎร กระทู้ถามที่ 154 ร. เรื่อง มาตรการป้องกันการแพร่ระบาดของโรคไข้เลือดออก และแนวทางการจัดการวัคซีน Qdenga [ของนายเอกราช อุดมอำนวย สมาชิกสภาผู้แทนราษฎร พรรคประชาชน กรุงเทพมหานคร]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/130925.pdf</t>
+  </si>
+  <si>
+    <t>กระทู้ถามของสมาชิกสภาผู้แทนราษฎร กระทู้ถามที่ 052/ร. เรื่อง แนวทางและมาตรการเยียวยาป้องกันผู้ประกอบการและชาวบ้านบริเวณโดยรอบที่ได้รับผลกระทบจากการก่อสร้างโครงการรถไฟฟ้าใต้ดินสายสีส้ม (ตะวันตก) เริ่มต้น ณ บริเวณถนนเพชรบุรี กรุงเทพมหานคร [นายเสกสิทธิ์ แย้มสงวนศักดิ์ สมาชิกสภาผู้แทนราษฎร พรรคประชาชน กรุงเทพมหานคร]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131108.pdf</t>
+  </si>
+  <si>
+    <t>กระทู้ถามของสมาชิกสภาผู้แทนราษฎร กระทู้ถามที่ 099/ร. เรื่อง ขอให้พิจารณาเร่งรัดดำเนินการบรรเทาความเดือดร้อนของประชาชนผู้ใช้รถใช้ถนนจากการดำเนินโครงการก่อสร้างถนนสาย สป. 1006 อำเภอบางบ่อ และอำเภอบางเสาธง จังหวัดสมุทรปราการ ทั้งสองช่วง [ของนายเทพฤทธิ์ ภาษี สมาชิกสภาผู้แทนราษฎร พรรคประชาชน จังหวัดสมุทรปราการ]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131291.pdf</t>
+  </si>
+  <si>
+    <t>กระทู้ถามของสมาชิกสภาผู้แทนราษฎร กระทู้ถามที่ 112/ร. เรื่อง ปัญหาการไม่ได้รับการแก้ไขจากภาครัฐกรณีไม่มีรถขนส่งสาธารณะในหลายพื้นที่ของกรุงเทพมหานคร [ของนายภูริวรรธก์ ใจสำราญ สมาชิกสภาผู้แทนราษฎร พรรคประชาชน กรุงเทพมหานคร]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131292.pdf</t>
+  </si>
+  <si>
+    <t>กระทู้ถามของสมาชิกสภาผู้แทนราษฎร กระทู้ถามที่ 113/ร. เรื่อง ขอทราบแนวทางการบริหารจัดการพื้นที่และโครงข่ายจราจรต่อเนื่องของทางหลวงพิเศษหมายเลข 81 (บางใหญ่ – กาญจนบุรี) เพื่อบรรเทาผลกระทบและพัฒนาคุณภาพชีวิตของประชาชนในพื้นที่อำเภอบางใหญ่ จังหวัดนนทบุรี [ของนายสุทัศน์ มีศิริ สมาชิกสภาผู้แทนราษฎร พรรคประชาชน จังหวัดนนทบุรี]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131293.pdf</t>
+  </si>
+  <si>
+    <t>กระทู้ถามของสมาชิกสภาผู้แทนราษฎร กระทู้ถามที่ 114/ร. เรื่อง แนวทางแก้ไขปัญหาความเดือดร้อนให้กับประชาชนที่ได้รับผลกระทบจากการดำเนินการโครงการฟลัดเวย์ (Flood way) และโครงการนำสายสื่อสารและสายไฟฟ้าลงดิน [ของนายกรณ์ มีดี สมาชิกสภาผู้แทนราษฎร พรรคประชาชน จังหวัดนนทบุรี]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131294.pdf</t>
   </si>
 </sst>
 </file>
@@ -2269,7 +2314,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:H313"/>
+  <dimension ref="A1:H320"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="12.02" customWidth="true" style="0"/>
@@ -9773,12 +9818,180 @@
       </c>
     </row>
     <row r="313" spans="1:8">
-      <c r="A313" s="2"/>
-      <c r="C313" s="1"/>
-      <c r="D313" s="1"/>
-      <c r="E313" s="1"/>
-      <c r="F313" s="1"/>
+      <c r="A313" s="2" t="s">
+        <v>636</v>
+      </c>
+      <c r="B313" t="s">
+        <v>637</v>
+      </c>
+      <c r="C313" s="1">
+        <v>143</v>
+      </c>
+      <c r="D313" s="1">
+        <v>240</v>
+      </c>
+      <c r="E313" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F313" s="1">
+        <v>1</v>
+      </c>
       <c r="G313" s="1"/>
+      <c r="H313" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="314" spans="1:8">
+      <c r="A314" s="2" t="s">
+        <v>636</v>
+      </c>
+      <c r="B314" t="s">
+        <v>639</v>
+      </c>
+      <c r="C314" s="1">
+        <v>143</v>
+      </c>
+      <c r="D314" s="1">
+        <v>240</v>
+      </c>
+      <c r="E314" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F314" s="1">
+        <v>2</v>
+      </c>
+      <c r="G314" s="1"/>
+      <c r="H314" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="315" spans="1:8">
+      <c r="A315" s="2" t="s">
+        <v>636</v>
+      </c>
+      <c r="B315" t="s">
+        <v>641</v>
+      </c>
+      <c r="C315" s="1">
+        <v>143</v>
+      </c>
+      <c r="D315" s="1">
+        <v>240</v>
+      </c>
+      <c r="E315" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F315" s="1">
+        <v>10</v>
+      </c>
+      <c r="G315" s="1"/>
+      <c r="H315" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="316" spans="1:8">
+      <c r="A316" s="2" t="s">
+        <v>636</v>
+      </c>
+      <c r="B316" t="s">
+        <v>643</v>
+      </c>
+      <c r="C316" s="1">
+        <v>143</v>
+      </c>
+      <c r="D316" s="1">
+        <v>240</v>
+      </c>
+      <c r="E316" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F316" s="1">
+        <v>19</v>
+      </c>
+      <c r="G316" s="1"/>
+      <c r="H316" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="317" spans="1:8">
+      <c r="A317" s="2" t="s">
+        <v>636</v>
+      </c>
+      <c r="B317" t="s">
+        <v>645</v>
+      </c>
+      <c r="C317" s="1">
+        <v>143</v>
+      </c>
+      <c r="D317" s="1">
+        <v>240</v>
+      </c>
+      <c r="E317" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F317" s="1">
+        <v>25</v>
+      </c>
+      <c r="G317" s="1"/>
+      <c r="H317" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="318" spans="1:8">
+      <c r="A318" s="2" t="s">
+        <v>636</v>
+      </c>
+      <c r="B318" t="s">
+        <v>647</v>
+      </c>
+      <c r="C318" s="1">
+        <v>143</v>
+      </c>
+      <c r="D318" s="1">
+        <v>240</v>
+      </c>
+      <c r="E318" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F318" s="1">
+        <v>30</v>
+      </c>
+      <c r="G318" s="1"/>
+      <c r="H318" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="319" spans="1:8">
+      <c r="A319" s="2" t="s">
+        <v>636</v>
+      </c>
+      <c r="B319" t="s">
+        <v>649</v>
+      </c>
+      <c r="C319" s="1">
+        <v>143</v>
+      </c>
+      <c r="D319" s="1">
+        <v>240</v>
+      </c>
+      <c r="E319" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F319" s="1">
+        <v>35</v>
+      </c>
+      <c r="G319" s="1"/>
+      <c r="H319" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="320" spans="1:8">
+      <c r="A320" s="2"/>
+      <c r="C320" s="1"/>
+      <c r="D320" s="1"/>
+      <c r="E320" s="1"/>
+      <c r="F320" s="1"/>
+      <c r="G320" s="1"/>
     </row>
   </sheetData>
   <sheetProtection sheet="false" objects="false" scenarios="false" formatCells="false" formatColumns="false" formatRows="false" insertColumns="false" insertRows="false" insertHyperlinks="false" deleteColumns="false" deleteRows="false" selectLockedCells="false" sort="false" autoFilter="false" pivotTables="false" selectUnlockedCells="false"/>

--- a/data/raw/monthly-2026-10.xlsx
+++ b/data/raw/monthly-2026-10.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="651">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="814">
   <si>
     <t>วันที่</t>
   </si>
@@ -1968,6 +1968,495 @@
   </si>
   <si>
     <t>https://ratchakitcha.soc.go.th/documents/131294.pdf</t>
+  </si>
+  <si>
+    <t>05/10/2026</t>
+  </si>
+  <si>
+    <t>ข้อบัญญัติองค์การบริหารส่วนตำบลรำแดง เรื่อง การติดตั้งบ่อดักไขมันบำบัดน้ำเสียในอาคาร พ.ศ. 2566</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/125086.pdf</t>
+  </si>
+  <si>
+    <t>ข้อบัญญัติองค์การบริหารส่วนตำบลเขามีเกียรติ เรื่อง การจัดการสิ่งปฏิกูลและมูลฝอย พ.ศ. 2569</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/126328.pdf</t>
+  </si>
+  <si>
+    <t>ข้อบัญญัติองค์การบริหารส่วนตำบลฆะมัง เรื่อง อัตราค่าธรรมเนียมและยกเว้นค่าธรรมเนียมเกี่ยวกับการจัดการสิ่งปฏิกูลและมูลฝอย พ.ศ. 2569</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/124976.pdf</t>
+  </si>
+  <si>
+    <t>ข้อบัญญัติองค์การบริหารส่วนตำบลโซ่ เรื่อง การเก็บค่าธรรมเนียมจากผู้ใช้หรือได้รับประโยชน์จากทรัพย์สินหรือบริการขององค์การบริหารส่วนตำบลโซ่ พ.ศ. 2569</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/123878.pdf</t>
+  </si>
+  <si>
+    <t>ข้อบัญญัติองค์การบริหารส่วนตำบลดอนทราย เรื่อง การควบคุมการเลี้ยงหรือปล่อยสัตว์ พ.ศ. 2569</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/125832.pdf</t>
+  </si>
+  <si>
+    <t>ข้อบัญญัติองค์การบริหารส่วนตำบลตลิ่งชัน เรื่อง การควบคุมการเลี้ยงหรือปล่อยสัตว์ พ.ศ. 2569</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/125602.pdf</t>
+  </si>
+  <si>
+    <t>ข้อบัญญัติองค์การบริหารส่วนตำบลนากะชะ เรื่อง การจัดการมูลฝอยทั่วไป พ.ศ. 2569</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/124521.pdf</t>
+  </si>
+  <si>
+    <t>ข้อบัญญัติองค์การบริหารส่วนตำบลนากะชะ เรื่อง การจัดการสิ่งปฏิกูล พ.ศ. 2569</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/124951.pdf</t>
+  </si>
+  <si>
+    <t>ข้อบัญญัติองค์การบริหารส่วนตำบลนางาม เรื่อง การจัดการมูลฝอยทั่วไป พ.ศ. 2569</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/125236.pdf</t>
+  </si>
+  <si>
+    <t>ข้อบัญญัติองค์การบริหารส่วนตำบลบางหลวง เรื่อง สถานที่จำหน่ายอาหารและสถานที่สะสมอาหาร พ.ศ. 2569</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/123644.pdf</t>
+  </si>
+  <si>
+    <t>ข้อบัญญัติองค์การบริหารส่วนตำบลบางหลวง เรื่อง ควบคุมกิจการที่เป็นอันตรายต่อสุขภาพ พ.ศ. 2569</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/123646.pdf</t>
+  </si>
+  <si>
+    <t>ข้อบัญญัติองค์การบริหารส่วนตำบลโพธิ์ศรี เรื่อง การจัดการสิ่งปฏิกูลและมูลฝอย พ.ศ. 2569</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/118748.pdf</t>
+  </si>
+  <si>
+    <t>ข้อบัญญัติองค์การบริหารส่วนตำบลรังนก เรื่อง การบริหารกิจการสถานีสูบน้ำด้วยไฟฟ้า พ.ศ. 2569</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/124873.pdf</t>
+  </si>
+  <si>
+    <t>ข้อบัญญัติองค์การบริหารส่วนตำบลวังน้ำขาว เรื่อง อัตราค่าธรรมเนียมและยกเว้นค่าธรรมเนียมเกี่ยวกับการจัดการสิ่งปฏิกูลและมูลฝอย พ.ศ. 2569</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/125829.pdf</t>
+  </si>
+  <si>
+    <t>ข้อบัญญัติองค์การบริหารส่วนตำบลวังเพลิง เรื่อง กิจการประปาหมู่บ้าน พ.ศ.2569</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/126243.pdf</t>
+  </si>
+  <si>
+    <t>ข้อบัญญัติองค์การบริหารส่วนตำบลสีสุก เรื่อง ควบคุมกิจการรังนกแอ่นและการทำความสะอาดหรือตัดแต่งรังนกแอ่น พ.ศ. 2569</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/124932.pdf</t>
+  </si>
+  <si>
+    <t>ข้อบัญญัติองค์การบริหารส่วนตำบลสีสุก เรื่อง อัตราค่าธรรมเนียมและยกเว้นค่าธรรมเนียมเกี่ยวกับการจัดการสิ่งปฏิกูลและมูลฝอย พ.ศ. 2569</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/124927.pdf</t>
+  </si>
+  <si>
+    <t>ข้อบัญญัติองค์การบริหารส่วนตำบลหนองเเสงใหญ่ เรื่อง การบริหารกิจการสถานีสูบน้ำด้วยไฟฟ้า พ.ศ. 2569</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/125157.pdf</t>
+  </si>
+  <si>
+    <t>ข้อบัญญัติองค์การบริหารส่วนตำบลหนองหลัก เรื่อง อัตราค่าธรรมเนียมและยกเว้นค่าธรรมเนียมเกี่ยวกับการจัดการสิ่งปฏิกูลและมูลฝอย พ.ศ. 2569</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/124227.pdf</t>
+  </si>
+  <si>
+    <t>ข้อบัญญัติองค์การบริหารส่วนตำบลหินเหล็กไฟ เรื่อง การเก็บค่าธรรมเนียมการให้บริการจากทรัพย์สินขององค์การบริหารส่วนตำบลหินเหล็กไฟ พ.ศ. 2569</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/125028.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศกรมการค้าต่างประเทศ เรื่อง การขยายการเรียกเก็บอากรตอบโต้การทุ่มตลาดในอัตราร้อยละ 0 ของราคา ซี ไอ เอฟ กรณีการนำเข้าสินค้าเหล็กแผ่นรีดเย็นเคลือบสังกะสีผสมอะลูมิเนียมและแมกนีเซียมแบบจุ่มร้อนชนิดเป็นม้วนและไม่เป็นม้วน ที่มีแหล่งกำเนิดจากสาธารณรัฐประชาชนจีน ของผู้ผลิต จำนวน 10 ราย เพื่อใช้ในการผลิตเหล็กแผ่นรีดเย็นเคลือบสังกะสีผสมอะลูมิเนียมและแมกนีเซียมแบบจุ่มร้อนแล้วทาสีชนิดเป็นม้วน เพื่อการส่งออกภายใต้กฎหมายว่าด้วยการส่งเสริมการลงทุน พ.ศ. 2569</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132733.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศสำนักงานคณะกรรมการส่วนจังหวัดว่าด้วยราคาสินค้าและบริการ จังหวัดแพร่ ฉบับที่ 1 พ.ศ. 2569 เรื่อง หลักเกณฑ์และวิธีการในการขออนุญาต การอนุญาต แบบหนังสืออนุญาต และวิธีการขนย้ายต้นพันธุ์ ท่อนพันธุ์มันสำปะหลัง</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/130524.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศคณะกรรมการพิจารณาการทุ่มตลาดและการอุดหนุน เรื่อง การตอบโต้การหลบเลี่ยงมาตรการตอบโต้การทุ่มตลาด กรณีสินค้าเหล็กแผ่นรีดเย็นเคลือบสังกะสีแบบจุ่มร้อนชนิดเป็นม้วนและไม่เป็นม้วน ที่มีแหล่งกำเนิดจากสาธารณรัฐประชาชนจีน เพื่อขยายการเรียกเก็บอากรตอบโต้การทุ่มตลาดกับการนำเข้าสินค้าเหล็กแผ่นรีดเย็นเคลือบสังกะสีผสมอะลูมิเนียมและแมกนีเซียมแบบจุ่มร้อนชนิดเป็นม้วนและไม่เป็นม้วน ที่มีแหล่งกำเนิดจากสาธารณรัฐประชาชนจีน ของผู้ผลิต จำนวน 10 ราย พ.ศ. 2569</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132732.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศคณะกรรมการส่วนจังหวัดว่าด้วยราคาสินค้าและบริการ จังหวัดแพร่ ฉบับที่ 1 พ.ศ. 2569 เรื่อง การควบคุมการขนย้ายต้นพันธุ์ ท่อนพันธุ์มันสำปะหลัง</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/130518.pdf</t>
+  </si>
+  <si>
+    <t>กระทู้ถามของสมาชิกสภาผู้แทนราษฎร  กระทู้ถามที่ 125 ร. เรื่อง ปัญหาศูนย์บริการส่งเสริมสุขภาพสำหรับผู้มีความหลากหลายทางเพศในพื้นที่กรุงเทพตอนเหนือมีจำนวนไม่เพียงพอต่อการให้บริการประชาชน [ของ นายเอกราช อุดมอำนวย สมาชิกสภาผู้แทนราษฎร พรรคประชาชน]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131214.pdf</t>
+  </si>
+  <si>
+    <t>กระทู้ถามของสมาชิกสภาผู้แทนราษฎร กระทู้ถามที่ 467 ร.  เรื่อง การเพิ่มศักยภาพสถานสงเคราะห์ ตลอดจนมาตรการดูแลเด็ก ผู้สูงอายุ ผู้พิการ และคนไร้บ้าน [ของ นายอนุสรณ์ ไกรวัตนุสสรณ์ สมาชิกสภาผู้แทนราษฎร พรรคภูมิใจไทย]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131941.pdf</t>
+  </si>
+  <si>
+    <t>กระทู้ถามของสมาชิกสภาผู้แทนราษฎร กระทู้ถามที่ 549 ร. เรื่อง การแก้ไขปัญหาราคาอ้อยและผลกระทบต่อเกษตรกรจังหวัดกาฬสินธุ์ [ของ นางสาวบุญญาภา นาชัยเวียง ปุณณนิฏฐา สมาชิกสภาผู้แทนราษฎร พรรคภูมิใจไทย]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131590.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำพิพากษาให้จัดการทรัพย์มรดกจำเลย [คดีหมายเลขแดงที่ ล.E1434/2569 ให้จัดการทรัพย์กองมรดกของ นางสาวกิ่งรัตนา กรีพลฤกษ์ โดยนายพัสกร กรีพลฤกษ์ ในฐานะทายาทโดยชอบธรรม ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131905.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำพิพากษาให้จัดการทรัพย์มรดกจำเลย [คดีหมายเลขแดงที่ ล.8157/2569 ให้จัดการทรัพย์กองมรดกของนางเอกอนงค์ บุญสนอง โดยนางละออ พราหมณ์เอม และนายภูวดิน บุญสนอง ในฐานะทายาทโดยธรรม ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132087.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.E1420/2569 พันตรีหญิงหรือนางสาวระวิจิต เบ็ญจพันธุ์ ลูกหนี้ที่ 1 และนายอมรเดช หอมศักดิ์ ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132131.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.E1427/2569 นายฐานวีร์ เอกตาแสง ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132106.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.E1428/2569 นางสาวสุนันทา หงษ์มณี ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132118.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.E1436/2569 นายอรุณ จันทร์สุข ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132092.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.E1449/2569 บริษัทอินบอคซ์ เอ็นเตอร์ไพรส์ จำกัด ลูกหนี้ที่ 1, นางสาวหรือนางธัญสิริณัชหรือรุจรินทร์ แก่นประยูรวัจน์หรือโสภณพันธ์ ลูกหนี้ที่ 2 และนายกมล โสภณพันธ์ ลูกหนี้ที่ 3]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132125.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.E1463/2569 นางสาวทิฐิมา ริมดุสิต ลูกหนี้ที่ 1]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132113.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8030/2569 นางสาววิรากานต์ นาคมณี ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132094.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8046/2569 บริษัทเคเจซี เอ็นจิเนียริ่ง จำกัด ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132122.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8047/2569 นางสาวแก้วเพชร รักการ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132085.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8048/2569 นายเต็มศักดิ์ วงค์วรพันธ์ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132121.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8049/2569 บริษัทพี แอนด์ เอ็น เอาท์ซอร์ซซิ่ง กรุ๊ป จำกัด ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132098.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8050/2569 บริษัททีเคที ซีคิวริตี้ เซอร์วิส จำกัด ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131918.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8074/2569 บริษัทวีเอสพี ฟอร์จูน บิสซิเนส จำกัด ลูกหนี้ที่ 1, นายนันธเนศร์ เอื้อกิตติโรจน์ ลูกหนี้ที่ 2 และนางสุรางค์ เอื้อกิตติโรจน์ ลูกหนี้ที่ 3]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131907.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8089/2569 นายประเสริฐ เฮ้าชัยภูมิ ลูกหนี้ที่ 1 และนางลัดดาวรรณ เฮ้าชัยภูมิหรือประเสริฐกุล ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132080.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8090/2569 นายประยูร อรัญโชติ ลูกหนี้ที่ 1 และนางสำลี อรัญโชติ ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132107.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8091/2569 นายอุทัย ใจสุทธิ ลูกหนี้ที่ 1 และนางสาวชูศรี เจริญพืช ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132128.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8100/2569 นางอำภาภรณ์ วรรพเนตร ลูกหนี้ที่ 1]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132110.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8101/2569 นายนิรันดร์หรือบุณยสิทธิ์ อุดมเจริญไมตรีหรือสินสมบูรณ์อาภา ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132086.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8102/2569 นางจารุภาหรือศรีพัชราหรือลักษมีหรือเมทิส พานิชกุลหรือศรีสัตตะพงศ์หรือเซอุสชายา ลูกหนี้ที่ 1 และนางสดใส สุขสำราญ ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132132.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8103/2569 นายพวัสส์ ศิริฐิตินันท์ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131925.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8104/2569 นายชาญณรงค์ สันติภราภพ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132100.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8107/2569 นายพรเทพ ทองเอี่ยม ลูกหนี้ที่ 1 และนายวณัฐพงศ์หรือทนงศักดิ์ ศรีธำรงศักดิ์หรือศรีศักดิ์นอก ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131921.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8122/2569 นางสาวจรีญา บุญประเสริฐ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132123.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8123/2569 นายดวงเด่น บุบผา ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132104.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8124/2569 นางสาวทองใบ พุฒโสม ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132117.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8125/2569 นายวัชระ ขจรวิจิตร์ ลูกหนี้ที่ 1, นายนิทัศน์ ขจรวิจิตร์ ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132079.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8126/2569 นางสมร แสงวิชัย ลูกหนี้ที่ 1 และนายประสงค์ แสงวิชัย ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132116.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8142/2569 บริษัทหนึ่งศูนย์หนึ่ง เอ็นจิเนียริ่ง จำกัด ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132127.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8152/2569 บริษัทพาร์ท ออโต้ ไนน์ 888 จำกัด ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132102.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8153/2569 บริษัทที.ซี.รีไซเคิล จำกัด โดยนายวิฑูร แซ่โค้ว ผู้ชำระบัญชี ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132133.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8154/2569 นายภัตติมาหรือกิตติพงษ์ ไหวพริบ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131936.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8155/2569 ห้างหุ้นส่วนจำกัด ที.ซี.พี. คอนสตรัคชั่น แอนด์ เดคเคอเรชั่น ลูกหนี้ที่ 1 และนางสาวพรจันทร์ กุดแถลง ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132111.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8156/2569 นายนอรามิล ยูนุ๊ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132112.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8158/2569 นายณัตฒุพล แสงมุข ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132101.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8164/2569 นายธนากร เมฆอรุณ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132129.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8167/2569 นายวิชัย คล้ายคลึง ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132130.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8168/2569 นายฉันทกิจ อินสุทน ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132109.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8169/2569 นางสาวลัดดาวัลย์ จันใด ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132083.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8170/2569 นายไตรศักดิ์ สอนพันธ์ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132097.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8171/2569 นายสุวิทย์ ศาสนสุพินธ์ ลูกหนี้ที่ 1 และนางสุมาลี ศาสนสุพินธ์หรือค้ำชู ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132096.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8173/2569 นางสาววิพาพรหรือภิสรินธันญ์ วุ่นสุข ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132108.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8175/2569 นายฤทธิ์ธิพร ดือราแม ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132081.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8176/2569 นายสมศรี จิตมั่น ลูกหนี้ที่ 1 นายสัมอาง คำอาจ ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132120.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8177/2569 นางสาวกัญญาภัค มหาวรรณ์ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132119.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8178/2569 บริษัทพรีม่า ด๊อก จำกัด ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131912.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8193/2569 บริษัทพระยา จอมเทียน จำกัด หรือบริษัทณุศาศิริ อินเตอร์เนชั่นแนล จำกัด หรือบริษัทณุศาพลาญ่า โฮเทล แอนด์ สปา จำกัด หรือบริษัทณุศาศิริ กรุ๊ป จำกัด ลูกหนี้ที่ 1, นายวิษณุ เทพเจริญ ลูกหนี้ที่ 2, นางศิริมลหรือศิริญา เทพเจริญ ลูกหนี้ที่ 3 และบริษัทเคเอ็น ฟาร์มาซี จำกัด หรือบริษัทเคเอ็น เรียลเอสเตท จำกัด ลูกหนี้ที่ 4]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132137.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8195/2569 นางสวภัทร สีดำหรือเกื้อสกุล ลูกหนี้ที่ 1 และนายวิโรจน์ เกื้อสกุล ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132078.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8196/2569 ดาบตำรวจหรือจ่าสิบตำรวจจรวย ศรีชัย ลูกหนี้ที่ 1]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132090.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8197/2569 นางสาวณฐมน เขื่อนเพชร ลูกหนี้ที่ 1, นายบุญเทียน สมใจ ลูกหนี้ที่ 2, นายวิเชียร สมใจ ลูกหนี้ที่ 3 และนางสาวเฟื่องฟู รามางกูร ลูกหนี้ที่ 4]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132134.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8200/2569 นายบุญมาหรือธนบูรณ์ ทับภูมี ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132093.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8204/2569 นายนิพนธ์ บุญเลิศ ลูกหนี้ที่ 1 และนางสาวกรณพชร แก้วขวัญ ลูกหนี้ที่ 3]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132136.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8211/2569 นางสาวอนันชนก ศักดิ์จิรยุทธ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132124.pdf</t>
   </si>
 </sst>
 </file>
@@ -2314,7 +2803,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:H320"/>
+  <dimension ref="A1:H401"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="12.02" customWidth="true" style="0"/>
@@ -9986,12 +10475,1956 @@
       </c>
     </row>
     <row r="320" spans="1:8">
-      <c r="A320" s="2"/>
-      <c r="C320" s="1"/>
-      <c r="D320" s="1"/>
-      <c r="E320" s="1"/>
-      <c r="F320" s="1"/>
+      <c r="A320" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="B320" t="s">
+        <v>652</v>
+      </c>
+      <c r="C320" s="1">
+        <v>143</v>
+      </c>
+      <c r="D320" s="1">
+        <v>241</v>
+      </c>
+      <c r="E320" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F320" s="1">
+        <v>1</v>
+      </c>
       <c r="G320" s="1"/>
+      <c r="H320" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="321" spans="1:8">
+      <c r="A321" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="B321" t="s">
+        <v>654</v>
+      </c>
+      <c r="C321" s="1">
+        <v>143</v>
+      </c>
+      <c r="D321" s="1">
+        <v>241</v>
+      </c>
+      <c r="E321" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F321" s="1">
+        <v>3</v>
+      </c>
+      <c r="G321" s="1"/>
+      <c r="H321" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="322" spans="1:8">
+      <c r="A322" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="B322" t="s">
+        <v>656</v>
+      </c>
+      <c r="C322" s="1">
+        <v>143</v>
+      </c>
+      <c r="D322" s="1">
+        <v>241</v>
+      </c>
+      <c r="E322" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F322" s="1">
+        <v>22</v>
+      </c>
+      <c r="G322" s="1"/>
+      <c r="H322" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="323" spans="1:8">
+      <c r="A323" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="B323" t="s">
+        <v>658</v>
+      </c>
+      <c r="C323" s="1">
+        <v>143</v>
+      </c>
+      <c r="D323" s="1">
+        <v>241</v>
+      </c>
+      <c r="E323" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F323" s="1">
+        <v>27</v>
+      </c>
+      <c r="G323" s="1"/>
+      <c r="H323" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="324" spans="1:8">
+      <c r="A324" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="B324" t="s">
+        <v>660</v>
+      </c>
+      <c r="C324" s="1">
+        <v>143</v>
+      </c>
+      <c r="D324" s="1">
+        <v>241</v>
+      </c>
+      <c r="E324" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F324" s="1">
+        <v>30</v>
+      </c>
+      <c r="G324" s="1"/>
+      <c r="H324" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="325" spans="1:8">
+      <c r="A325" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="B325" t="s">
+        <v>662</v>
+      </c>
+      <c r="C325" s="1">
+        <v>143</v>
+      </c>
+      <c r="D325" s="1">
+        <v>241</v>
+      </c>
+      <c r="E325" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F325" s="1">
+        <v>36</v>
+      </c>
+      <c r="G325" s="1"/>
+      <c r="H325" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="326" spans="1:8">
+      <c r="A326" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="B326" t="s">
+        <v>664</v>
+      </c>
+      <c r="C326" s="1">
+        <v>143</v>
+      </c>
+      <c r="D326" s="1">
+        <v>241</v>
+      </c>
+      <c r="E326" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F326" s="1">
+        <v>43</v>
+      </c>
+      <c r="G326" s="1"/>
+      <c r="H326" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="327" spans="1:8">
+      <c r="A327" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="B327" t="s">
+        <v>666</v>
+      </c>
+      <c r="C327" s="1">
+        <v>143</v>
+      </c>
+      <c r="D327" s="1">
+        <v>241</v>
+      </c>
+      <c r="E327" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F327" s="1">
+        <v>54</v>
+      </c>
+      <c r="G327" s="1"/>
+      <c r="H327" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="328" spans="1:8">
+      <c r="A328" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="B328" t="s">
+        <v>668</v>
+      </c>
+      <c r="C328" s="1">
+        <v>143</v>
+      </c>
+      <c r="D328" s="1">
+        <v>241</v>
+      </c>
+      <c r="E328" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F328" s="1">
+        <v>65</v>
+      </c>
+      <c r="G328" s="1"/>
+      <c r="H328" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="329" spans="1:8">
+      <c r="A329" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="B329" t="s">
+        <v>670</v>
+      </c>
+      <c r="C329" s="1">
+        <v>143</v>
+      </c>
+      <c r="D329" s="1">
+        <v>241</v>
+      </c>
+      <c r="E329" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F329" s="1">
+        <v>77</v>
+      </c>
+      <c r="G329" s="1"/>
+      <c r="H329" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="330" spans="1:8">
+      <c r="A330" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="B330" t="s">
+        <v>672</v>
+      </c>
+      <c r="C330" s="1">
+        <v>143</v>
+      </c>
+      <c r="D330" s="1">
+        <v>241</v>
+      </c>
+      <c r="E330" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F330" s="1">
+        <v>90</v>
+      </c>
+      <c r="G330" s="1"/>
+      <c r="H330" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="331" spans="1:8">
+      <c r="A331" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="B331" t="s">
+        <v>674</v>
+      </c>
+      <c r="C331" s="1">
+        <v>143</v>
+      </c>
+      <c r="D331" s="1">
+        <v>241</v>
+      </c>
+      <c r="E331" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F331" s="1">
+        <v>106</v>
+      </c>
+      <c r="G331" s="1"/>
+      <c r="H331" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="332" spans="1:8">
+      <c r="A332" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="B332" t="s">
+        <v>676</v>
+      </c>
+      <c r="C332" s="1">
+        <v>143</v>
+      </c>
+      <c r="D332" s="1">
+        <v>241</v>
+      </c>
+      <c r="E332" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F332" s="1">
+        <v>118</v>
+      </c>
+      <c r="G332" s="1"/>
+      <c r="H332" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="333" spans="1:8">
+      <c r="A333" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="B333" t="s">
+        <v>678</v>
+      </c>
+      <c r="C333" s="1">
+        <v>143</v>
+      </c>
+      <c r="D333" s="1">
+        <v>241</v>
+      </c>
+      <c r="E333" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F333" s="1">
+        <v>123</v>
+      </c>
+      <c r="G333" s="1"/>
+      <c r="H333" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="334" spans="1:8">
+      <c r="A334" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="B334" t="s">
+        <v>680</v>
+      </c>
+      <c r="C334" s="1">
+        <v>143</v>
+      </c>
+      <c r="D334" s="1">
+        <v>241</v>
+      </c>
+      <c r="E334" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F334" s="1">
+        <v>128</v>
+      </c>
+      <c r="G334" s="1"/>
+      <c r="H334" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="335" spans="1:8">
+      <c r="A335" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="B335" t="s">
+        <v>682</v>
+      </c>
+      <c r="C335" s="1">
+        <v>143</v>
+      </c>
+      <c r="D335" s="1">
+        <v>241</v>
+      </c>
+      <c r="E335" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F335" s="1">
+        <v>135</v>
+      </c>
+      <c r="G335" s="1"/>
+      <c r="H335" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="336" spans="1:8">
+      <c r="A336" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="B336" t="s">
+        <v>684</v>
+      </c>
+      <c r="C336" s="1">
+        <v>143</v>
+      </c>
+      <c r="D336" s="1">
+        <v>241</v>
+      </c>
+      <c r="E336" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F336" s="1">
+        <v>143</v>
+      </c>
+      <c r="G336" s="1"/>
+      <c r="H336" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="337" spans="1:8">
+      <c r="A337" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="B337" t="s">
+        <v>686</v>
+      </c>
+      <c r="C337" s="1">
+        <v>143</v>
+      </c>
+      <c r="D337" s="1">
+        <v>241</v>
+      </c>
+      <c r="E337" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F337" s="1">
+        <v>148</v>
+      </c>
+      <c r="G337" s="1"/>
+      <c r="H337" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="338" spans="1:8">
+      <c r="A338" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="B338" t="s">
+        <v>688</v>
+      </c>
+      <c r="C338" s="1">
+        <v>143</v>
+      </c>
+      <c r="D338" s="1">
+        <v>241</v>
+      </c>
+      <c r="E338" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F338" s="1">
+        <v>154</v>
+      </c>
+      <c r="G338" s="1"/>
+      <c r="H338" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="339" spans="1:8">
+      <c r="A339" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="B339" t="s">
+        <v>690</v>
+      </c>
+      <c r="C339" s="1">
+        <v>143</v>
+      </c>
+      <c r="D339" s="1">
+        <v>241</v>
+      </c>
+      <c r="E339" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F339" s="1">
+        <v>160</v>
+      </c>
+      <c r="G339" s="1"/>
+      <c r="H339" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="340" spans="1:8">
+      <c r="A340" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="B340" t="s">
+        <v>692</v>
+      </c>
+      <c r="C340" s="1">
+        <v>143</v>
+      </c>
+      <c r="D340" s="1">
+        <v>242</v>
+      </c>
+      <c r="E340" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F340" s="1">
+        <v>1</v>
+      </c>
+      <c r="G340" s="1"/>
+      <c r="H340" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="341" spans="1:8">
+      <c r="A341" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="B341" t="s">
+        <v>694</v>
+      </c>
+      <c r="C341" s="1">
+        <v>143</v>
+      </c>
+      <c r="D341" s="1">
+        <v>242</v>
+      </c>
+      <c r="E341" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F341" s="1">
+        <v>7</v>
+      </c>
+      <c r="G341" s="1"/>
+      <c r="H341" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="342" spans="1:8">
+      <c r="A342" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="B342" t="s">
+        <v>696</v>
+      </c>
+      <c r="C342" s="1">
+        <v>143</v>
+      </c>
+      <c r="D342" s="1">
+        <v>242</v>
+      </c>
+      <c r="E342" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F342" s="1">
+        <v>13</v>
+      </c>
+      <c r="G342" s="1"/>
+      <c r="H342" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="343" spans="1:8">
+      <c r="A343" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="B343" t="s">
+        <v>698</v>
+      </c>
+      <c r="C343" s="1">
+        <v>143</v>
+      </c>
+      <c r="D343" s="1">
+        <v>242</v>
+      </c>
+      <c r="E343" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F343" s="1">
+        <v>18</v>
+      </c>
+      <c r="G343" s="1"/>
+      <c r="H343" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="344" spans="1:8">
+      <c r="A344" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="B344" t="s">
+        <v>700</v>
+      </c>
+      <c r="C344" s="1">
+        <v>143</v>
+      </c>
+      <c r="D344" s="1">
+        <v>242</v>
+      </c>
+      <c r="E344" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F344" s="1">
+        <v>20</v>
+      </c>
+      <c r="G344" s="1"/>
+      <c r="H344" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="345" spans="1:8">
+      <c r="A345" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="B345" t="s">
+        <v>702</v>
+      </c>
+      <c r="C345" s="1">
+        <v>143</v>
+      </c>
+      <c r="D345" s="1">
+        <v>242</v>
+      </c>
+      <c r="E345" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F345" s="1">
+        <v>23</v>
+      </c>
+      <c r="G345" s="1"/>
+      <c r="H345" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="346" spans="1:8">
+      <c r="A346" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="B346" t="s">
+        <v>704</v>
+      </c>
+      <c r="C346" s="1">
+        <v>143</v>
+      </c>
+      <c r="D346" s="1">
+        <v>242</v>
+      </c>
+      <c r="E346" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F346" s="1">
+        <v>37</v>
+      </c>
+      <c r="G346" s="1"/>
+      <c r="H346" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="347" spans="1:8">
+      <c r="A347" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="B347" t="s">
+        <v>706</v>
+      </c>
+      <c r="C347" s="1">
+        <v>143</v>
+      </c>
+      <c r="D347" s="1">
+        <v>242</v>
+      </c>
+      <c r="E347" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F347" s="1">
+        <v>41</v>
+      </c>
+      <c r="G347" s="1"/>
+      <c r="H347" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="348" spans="1:8">
+      <c r="A348" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="B348" t="s">
+        <v>708</v>
+      </c>
+      <c r="C348" s="1">
+        <v>143</v>
+      </c>
+      <c r="D348" s="1">
+        <v>242</v>
+      </c>
+      <c r="E348" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F348" s="1">
+        <v>42</v>
+      </c>
+      <c r="G348" s="1"/>
+      <c r="H348" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="349" spans="1:8">
+      <c r="A349" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="B349" t="s">
+        <v>710</v>
+      </c>
+      <c r="C349" s="1">
+        <v>143</v>
+      </c>
+      <c r="D349" s="1">
+        <v>242</v>
+      </c>
+      <c r="E349" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F349" s="1">
+        <v>43</v>
+      </c>
+      <c r="G349" s="1"/>
+      <c r="H349" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="350" spans="1:8">
+      <c r="A350" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="B350" t="s">
+        <v>712</v>
+      </c>
+      <c r="C350" s="1">
+        <v>143</v>
+      </c>
+      <c r="D350" s="1">
+        <v>242</v>
+      </c>
+      <c r="E350" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F350" s="1">
+        <v>44</v>
+      </c>
+      <c r="G350" s="1"/>
+      <c r="H350" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="351" spans="1:8">
+      <c r="A351" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="B351" t="s">
+        <v>714</v>
+      </c>
+      <c r="C351" s="1">
+        <v>143</v>
+      </c>
+      <c r="D351" s="1">
+        <v>242</v>
+      </c>
+      <c r="E351" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F351" s="1">
+        <v>45</v>
+      </c>
+      <c r="G351" s="1"/>
+      <c r="H351" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="352" spans="1:8">
+      <c r="A352" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="B352" t="s">
+        <v>716</v>
+      </c>
+      <c r="C352" s="1">
+        <v>143</v>
+      </c>
+      <c r="D352" s="1">
+        <v>242</v>
+      </c>
+      <c r="E352" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F352" s="1">
+        <v>46</v>
+      </c>
+      <c r="G352" s="1"/>
+      <c r="H352" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="353" spans="1:8">
+      <c r="A353" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="B353" t="s">
+        <v>718</v>
+      </c>
+      <c r="C353" s="1">
+        <v>143</v>
+      </c>
+      <c r="D353" s="1">
+        <v>242</v>
+      </c>
+      <c r="E353" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F353" s="1">
+        <v>47</v>
+      </c>
+      <c r="G353" s="1"/>
+      <c r="H353" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="354" spans="1:8">
+      <c r="A354" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="B354" t="s">
+        <v>720</v>
+      </c>
+      <c r="C354" s="1">
+        <v>143</v>
+      </c>
+      <c r="D354" s="1">
+        <v>242</v>
+      </c>
+      <c r="E354" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F354" s="1">
+        <v>49</v>
+      </c>
+      <c r="G354" s="1"/>
+      <c r="H354" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="355" spans="1:8">
+      <c r="A355" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="B355" t="s">
+        <v>722</v>
+      </c>
+      <c r="C355" s="1">
+        <v>143</v>
+      </c>
+      <c r="D355" s="1">
+        <v>242</v>
+      </c>
+      <c r="E355" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F355" s="1">
+        <v>50</v>
+      </c>
+      <c r="G355" s="1"/>
+      <c r="H355" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="356" spans="1:8">
+      <c r="A356" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="B356" t="s">
+        <v>724</v>
+      </c>
+      <c r="C356" s="1">
+        <v>143</v>
+      </c>
+      <c r="D356" s="1">
+        <v>242</v>
+      </c>
+      <c r="E356" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F356" s="1">
+        <v>51</v>
+      </c>
+      <c r="G356" s="1"/>
+      <c r="H356" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="357" spans="1:8">
+      <c r="A357" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="B357" t="s">
+        <v>726</v>
+      </c>
+      <c r="C357" s="1">
+        <v>143</v>
+      </c>
+      <c r="D357" s="1">
+        <v>242</v>
+      </c>
+      <c r="E357" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F357" s="1">
+        <v>52</v>
+      </c>
+      <c r="G357" s="1"/>
+      <c r="H357" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="358" spans="1:8">
+      <c r="A358" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="B358" t="s">
+        <v>728</v>
+      </c>
+      <c r="C358" s="1">
+        <v>143</v>
+      </c>
+      <c r="D358" s="1">
+        <v>242</v>
+      </c>
+      <c r="E358" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F358" s="1">
+        <v>53</v>
+      </c>
+      <c r="G358" s="1"/>
+      <c r="H358" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="359" spans="1:8">
+      <c r="A359" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="B359" t="s">
+        <v>730</v>
+      </c>
+      <c r="C359" s="1">
+        <v>143</v>
+      </c>
+      <c r="D359" s="1">
+        <v>242</v>
+      </c>
+      <c r="E359" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F359" s="1">
+        <v>54</v>
+      </c>
+      <c r="G359" s="1"/>
+      <c r="H359" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="360" spans="1:8">
+      <c r="A360" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="B360" t="s">
+        <v>732</v>
+      </c>
+      <c r="C360" s="1">
+        <v>143</v>
+      </c>
+      <c r="D360" s="1">
+        <v>242</v>
+      </c>
+      <c r="E360" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F360" s="1">
+        <v>55</v>
+      </c>
+      <c r="G360" s="1"/>
+      <c r="H360" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="361" spans="1:8">
+      <c r="A361" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="B361" t="s">
+        <v>734</v>
+      </c>
+      <c r="C361" s="1">
+        <v>143</v>
+      </c>
+      <c r="D361" s="1">
+        <v>242</v>
+      </c>
+      <c r="E361" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F361" s="1">
+        <v>56</v>
+      </c>
+      <c r="G361" s="1"/>
+      <c r="H361" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="362" spans="1:8">
+      <c r="A362" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="B362" t="s">
+        <v>736</v>
+      </c>
+      <c r="C362" s="1">
+        <v>143</v>
+      </c>
+      <c r="D362" s="1">
+        <v>242</v>
+      </c>
+      <c r="E362" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F362" s="1">
+        <v>58</v>
+      </c>
+      <c r="G362" s="1"/>
+      <c r="H362" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="363" spans="1:8">
+      <c r="A363" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="B363" t="s">
+        <v>738</v>
+      </c>
+      <c r="C363" s="1">
+        <v>143</v>
+      </c>
+      <c r="D363" s="1">
+        <v>242</v>
+      </c>
+      <c r="E363" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F363" s="1">
+        <v>59</v>
+      </c>
+      <c r="G363" s="1"/>
+      <c r="H363" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="364" spans="1:8">
+      <c r="A364" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="B364" t="s">
+        <v>740</v>
+      </c>
+      <c r="C364" s="1">
+        <v>143</v>
+      </c>
+      <c r="D364" s="1">
+        <v>242</v>
+      </c>
+      <c r="E364" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F364" s="1">
+        <v>60</v>
+      </c>
+      <c r="G364" s="1"/>
+      <c r="H364" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="365" spans="1:8">
+      <c r="A365" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="B365" t="s">
+        <v>742</v>
+      </c>
+      <c r="C365" s="1">
+        <v>143</v>
+      </c>
+      <c r="D365" s="1">
+        <v>242</v>
+      </c>
+      <c r="E365" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F365" s="1">
+        <v>61</v>
+      </c>
+      <c r="G365" s="1"/>
+      <c r="H365" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="366" spans="1:8">
+      <c r="A366" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="B366" t="s">
+        <v>744</v>
+      </c>
+      <c r="C366" s="1">
+        <v>143</v>
+      </c>
+      <c r="D366" s="1">
+        <v>242</v>
+      </c>
+      <c r="E366" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F366" s="1">
+        <v>62</v>
+      </c>
+      <c r="G366" s="1"/>
+      <c r="H366" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="367" spans="1:8">
+      <c r="A367" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="B367" t="s">
+        <v>746</v>
+      </c>
+      <c r="C367" s="1">
+        <v>143</v>
+      </c>
+      <c r="D367" s="1">
+        <v>242</v>
+      </c>
+      <c r="E367" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F367" s="1">
+        <v>63</v>
+      </c>
+      <c r="G367" s="1"/>
+      <c r="H367" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="368" spans="1:8">
+      <c r="A368" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="B368" t="s">
+        <v>748</v>
+      </c>
+      <c r="C368" s="1">
+        <v>143</v>
+      </c>
+      <c r="D368" s="1">
+        <v>242</v>
+      </c>
+      <c r="E368" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F368" s="1">
+        <v>64</v>
+      </c>
+      <c r="G368" s="1"/>
+      <c r="H368" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="369" spans="1:8">
+      <c r="A369" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="B369" t="s">
+        <v>750</v>
+      </c>
+      <c r="C369" s="1">
+        <v>143</v>
+      </c>
+      <c r="D369" s="1">
+        <v>242</v>
+      </c>
+      <c r="E369" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F369" s="1">
+        <v>65</v>
+      </c>
+      <c r="G369" s="1"/>
+      <c r="H369" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="370" spans="1:8">
+      <c r="A370" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="B370" t="s">
+        <v>752</v>
+      </c>
+      <c r="C370" s="1">
+        <v>143</v>
+      </c>
+      <c r="D370" s="1">
+        <v>242</v>
+      </c>
+      <c r="E370" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F370" s="1">
+        <v>66</v>
+      </c>
+      <c r="G370" s="1"/>
+      <c r="H370" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="371" spans="1:8">
+      <c r="A371" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="B371" t="s">
+        <v>754</v>
+      </c>
+      <c r="C371" s="1">
+        <v>143</v>
+      </c>
+      <c r="D371" s="1">
+        <v>242</v>
+      </c>
+      <c r="E371" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F371" s="1">
+        <v>67</v>
+      </c>
+      <c r="G371" s="1"/>
+      <c r="H371" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="372" spans="1:8">
+      <c r="A372" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="B372" t="s">
+        <v>756</v>
+      </c>
+      <c r="C372" s="1">
+        <v>143</v>
+      </c>
+      <c r="D372" s="1">
+        <v>242</v>
+      </c>
+      <c r="E372" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F372" s="1">
+        <v>68</v>
+      </c>
+      <c r="G372" s="1"/>
+      <c r="H372" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="373" spans="1:8">
+      <c r="A373" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="B373" t="s">
+        <v>758</v>
+      </c>
+      <c r="C373" s="1">
+        <v>143</v>
+      </c>
+      <c r="D373" s="1">
+        <v>242</v>
+      </c>
+      <c r="E373" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F373" s="1">
+        <v>69</v>
+      </c>
+      <c r="G373" s="1"/>
+      <c r="H373" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="374" spans="1:8">
+      <c r="A374" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="B374" t="s">
+        <v>760</v>
+      </c>
+      <c r="C374" s="1">
+        <v>143</v>
+      </c>
+      <c r="D374" s="1">
+        <v>242</v>
+      </c>
+      <c r="E374" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F374" s="1">
+        <v>70</v>
+      </c>
+      <c r="G374" s="1"/>
+      <c r="H374" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="375" spans="1:8">
+      <c r="A375" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="B375" t="s">
+        <v>762</v>
+      </c>
+      <c r="C375" s="1">
+        <v>143</v>
+      </c>
+      <c r="D375" s="1">
+        <v>242</v>
+      </c>
+      <c r="E375" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F375" s="1">
+        <v>71</v>
+      </c>
+      <c r="G375" s="1"/>
+      <c r="H375" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="376" spans="1:8">
+      <c r="A376" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="B376" t="s">
+        <v>764</v>
+      </c>
+      <c r="C376" s="1">
+        <v>143</v>
+      </c>
+      <c r="D376" s="1">
+        <v>242</v>
+      </c>
+      <c r="E376" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F376" s="1">
+        <v>72</v>
+      </c>
+      <c r="G376" s="1"/>
+      <c r="H376" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="377" spans="1:8">
+      <c r="A377" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="B377" t="s">
+        <v>766</v>
+      </c>
+      <c r="C377" s="1">
+        <v>143</v>
+      </c>
+      <c r="D377" s="1">
+        <v>242</v>
+      </c>
+      <c r="E377" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F377" s="1">
+        <v>73</v>
+      </c>
+      <c r="G377" s="1"/>
+      <c r="H377" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="378" spans="1:8">
+      <c r="A378" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="B378" t="s">
+        <v>768</v>
+      </c>
+      <c r="C378" s="1">
+        <v>143</v>
+      </c>
+      <c r="D378" s="1">
+        <v>242</v>
+      </c>
+      <c r="E378" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F378" s="1">
+        <v>74</v>
+      </c>
+      <c r="G378" s="1"/>
+      <c r="H378" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="379" spans="1:8">
+      <c r="A379" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="B379" t="s">
+        <v>770</v>
+      </c>
+      <c r="C379" s="1">
+        <v>143</v>
+      </c>
+      <c r="D379" s="1">
+        <v>242</v>
+      </c>
+      <c r="E379" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F379" s="1">
+        <v>75</v>
+      </c>
+      <c r="G379" s="1"/>
+      <c r="H379" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="380" spans="1:8">
+      <c r="A380" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="B380" t="s">
+        <v>772</v>
+      </c>
+      <c r="C380" s="1">
+        <v>143</v>
+      </c>
+      <c r="D380" s="1">
+        <v>242</v>
+      </c>
+      <c r="E380" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F380" s="1">
+        <v>76</v>
+      </c>
+      <c r="G380" s="1"/>
+      <c r="H380" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="381" spans="1:8">
+      <c r="A381" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="B381" t="s">
+        <v>774</v>
+      </c>
+      <c r="C381" s="1">
+        <v>143</v>
+      </c>
+      <c r="D381" s="1">
+        <v>242</v>
+      </c>
+      <c r="E381" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F381" s="1">
+        <v>77</v>
+      </c>
+      <c r="G381" s="1"/>
+      <c r="H381" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="382" spans="1:8">
+      <c r="A382" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="B382" t="s">
+        <v>776</v>
+      </c>
+      <c r="C382" s="1">
+        <v>143</v>
+      </c>
+      <c r="D382" s="1">
+        <v>242</v>
+      </c>
+      <c r="E382" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F382" s="1">
+        <v>78</v>
+      </c>
+      <c r="G382" s="1"/>
+      <c r="H382" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="383" spans="1:8">
+      <c r="A383" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="B383" t="s">
+        <v>778</v>
+      </c>
+      <c r="C383" s="1">
+        <v>143</v>
+      </c>
+      <c r="D383" s="1">
+        <v>242</v>
+      </c>
+      <c r="E383" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F383" s="1">
+        <v>79</v>
+      </c>
+      <c r="G383" s="1"/>
+      <c r="H383" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="384" spans="1:8">
+      <c r="A384" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="B384" t="s">
+        <v>780</v>
+      </c>
+      <c r="C384" s="1">
+        <v>143</v>
+      </c>
+      <c r="D384" s="1">
+        <v>242</v>
+      </c>
+      <c r="E384" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F384" s="1">
+        <v>80</v>
+      </c>
+      <c r="G384" s="1"/>
+      <c r="H384" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="385" spans="1:8">
+      <c r="A385" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="B385" t="s">
+        <v>782</v>
+      </c>
+      <c r="C385" s="1">
+        <v>143</v>
+      </c>
+      <c r="D385" s="1">
+        <v>242</v>
+      </c>
+      <c r="E385" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F385" s="1">
+        <v>81</v>
+      </c>
+      <c r="G385" s="1"/>
+      <c r="H385" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="386" spans="1:8">
+      <c r="A386" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="B386" t="s">
+        <v>784</v>
+      </c>
+      <c r="C386" s="1">
+        <v>143</v>
+      </c>
+      <c r="D386" s="1">
+        <v>242</v>
+      </c>
+      <c r="E386" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F386" s="1">
+        <v>82</v>
+      </c>
+      <c r="G386" s="1"/>
+      <c r="H386" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="387" spans="1:8">
+      <c r="A387" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="B387" t="s">
+        <v>786</v>
+      </c>
+      <c r="C387" s="1">
+        <v>143</v>
+      </c>
+      <c r="D387" s="1">
+        <v>242</v>
+      </c>
+      <c r="E387" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F387" s="1">
+        <v>83</v>
+      </c>
+      <c r="G387" s="1"/>
+      <c r="H387" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="388" spans="1:8">
+      <c r="A388" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="B388" t="s">
+        <v>788</v>
+      </c>
+      <c r="C388" s="1">
+        <v>143</v>
+      </c>
+      <c r="D388" s="1">
+        <v>242</v>
+      </c>
+      <c r="E388" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F388" s="1">
+        <v>84</v>
+      </c>
+      <c r="G388" s="1"/>
+      <c r="H388" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="389" spans="1:8">
+      <c r="A389" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="B389" t="s">
+        <v>790</v>
+      </c>
+      <c r="C389" s="1">
+        <v>143</v>
+      </c>
+      <c r="D389" s="1">
+        <v>242</v>
+      </c>
+      <c r="E389" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F389" s="1">
+        <v>85</v>
+      </c>
+      <c r="G389" s="1"/>
+      <c r="H389" t="s">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="390" spans="1:8">
+      <c r="A390" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="B390" t="s">
+        <v>792</v>
+      </c>
+      <c r="C390" s="1">
+        <v>143</v>
+      </c>
+      <c r="D390" s="1">
+        <v>242</v>
+      </c>
+      <c r="E390" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F390" s="1">
+        <v>86</v>
+      </c>
+      <c r="G390" s="1"/>
+      <c r="H390" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="391" spans="1:8">
+      <c r="A391" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="B391" t="s">
+        <v>794</v>
+      </c>
+      <c r="C391" s="1">
+        <v>143</v>
+      </c>
+      <c r="D391" s="1">
+        <v>242</v>
+      </c>
+      <c r="E391" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F391" s="1">
+        <v>87</v>
+      </c>
+      <c r="G391" s="1"/>
+      <c r="H391" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="392" spans="1:8">
+      <c r="A392" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="B392" t="s">
+        <v>796</v>
+      </c>
+      <c r="C392" s="1">
+        <v>143</v>
+      </c>
+      <c r="D392" s="1">
+        <v>242</v>
+      </c>
+      <c r="E392" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F392" s="1">
+        <v>88</v>
+      </c>
+      <c r="G392" s="1"/>
+      <c r="H392" t="s">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="393" spans="1:8">
+      <c r="A393" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="B393" t="s">
+        <v>798</v>
+      </c>
+      <c r="C393" s="1">
+        <v>143</v>
+      </c>
+      <c r="D393" s="1">
+        <v>242</v>
+      </c>
+      <c r="E393" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F393" s="1">
+        <v>89</v>
+      </c>
+      <c r="G393" s="1"/>
+      <c r="H393" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="394" spans="1:8">
+      <c r="A394" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="B394" t="s">
+        <v>800</v>
+      </c>
+      <c r="C394" s="1">
+        <v>143</v>
+      </c>
+      <c r="D394" s="1">
+        <v>242</v>
+      </c>
+      <c r="E394" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F394" s="1">
+        <v>90</v>
+      </c>
+      <c r="G394" s="1"/>
+      <c r="H394" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="395" spans="1:8">
+      <c r="A395" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="B395" t="s">
+        <v>802</v>
+      </c>
+      <c r="C395" s="1">
+        <v>143</v>
+      </c>
+      <c r="D395" s="1">
+        <v>242</v>
+      </c>
+      <c r="E395" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F395" s="1">
+        <v>92</v>
+      </c>
+      <c r="G395" s="1"/>
+      <c r="H395" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="396" spans="1:8">
+      <c r="A396" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="B396" t="s">
+        <v>804</v>
+      </c>
+      <c r="C396" s="1">
+        <v>143</v>
+      </c>
+      <c r="D396" s="1">
+        <v>242</v>
+      </c>
+      <c r="E396" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F396" s="1">
+        <v>93</v>
+      </c>
+      <c r="G396" s="1"/>
+      <c r="H396" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="397" spans="1:8">
+      <c r="A397" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="B397" t="s">
+        <v>806</v>
+      </c>
+      <c r="C397" s="1">
+        <v>143</v>
+      </c>
+      <c r="D397" s="1">
+        <v>242</v>
+      </c>
+      <c r="E397" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F397" s="1">
+        <v>94</v>
+      </c>
+      <c r="G397" s="1"/>
+      <c r="H397" t="s">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="398" spans="1:8">
+      <c r="A398" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="B398" t="s">
+        <v>808</v>
+      </c>
+      <c r="C398" s="1">
+        <v>143</v>
+      </c>
+      <c r="D398" s="1">
+        <v>242</v>
+      </c>
+      <c r="E398" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F398" s="1">
+        <v>96</v>
+      </c>
+      <c r="G398" s="1"/>
+      <c r="H398" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="399" spans="1:8">
+      <c r="A399" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="B399" t="s">
+        <v>810</v>
+      </c>
+      <c r="C399" s="1">
+        <v>143</v>
+      </c>
+      <c r="D399" s="1">
+        <v>242</v>
+      </c>
+      <c r="E399" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F399" s="1">
+        <v>97</v>
+      </c>
+      <c r="G399" s="1"/>
+      <c r="H399" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="400" spans="1:8">
+      <c r="A400" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="B400" t="s">
+        <v>812</v>
+      </c>
+      <c r="C400" s="1">
+        <v>143</v>
+      </c>
+      <c r="D400" s="1">
+        <v>242</v>
+      </c>
+      <c r="E400" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F400" s="1">
+        <v>98</v>
+      </c>
+      <c r="G400" s="1"/>
+      <c r="H400" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="401" spans="1:8">
+      <c r="A401" s="2"/>
+      <c r="C401" s="1"/>
+      <c r="D401" s="1"/>
+      <c r="E401" s="1"/>
+      <c r="F401" s="1"/>
+      <c r="G401" s="1"/>
     </row>
   </sheetData>
   <sheetProtection sheet="false" objects="false" scenarios="false" formatCells="false" formatColumns="false" formatRows="false" insertColumns="false" insertRows="false" insertHyperlinks="false" deleteColumns="false" deleteRows="false" selectLockedCells="false" sort="false" autoFilter="false" pivotTables="false" selectUnlockedCells="false"/>

--- a/data/raw/monthly-2026-10.xlsx
+++ b/data/raw/monthly-2026-10.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="814">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="824">
   <si>
     <t>วันที่</t>
   </si>
@@ -2457,6 +2457,36 @@
   </si>
   <si>
     <t>https://ratchakitcha.soc.go.th/documents/132124.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8212/2569 นายณัฐพงศ์หรือธนกฤต ปัญญาชนะกุล ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132126.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8219/2569 นางมังคลาพรหรือนารา กุลาหงษ์ ลูกหนี้ที่ 1 และนางปราณี ยะทะนะ ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132077.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8220/2569 นางสาวสุวิมล มะลิวัลย์ ลูกหนี้ที่ 1, นางสาวณัฐนันกรณ์ ทันเจริญหรือจุโด ลูกหนี้ที่ 2 และนายอาทร อัคควุฒิกุล ลูกหนี้ที่ 3]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132135.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8221/2569 ร้อยโทหรือนายวิรัตน์หรือร้อยตรีวิชยุตม์ ชาติชนา ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132091.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8222/2569 นางสาวนุชรา พลเมฆ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132103.pdf</t>
   </si>
 </sst>
 </file>
@@ -2803,7 +2833,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:H401"/>
+  <dimension ref="A1:H406"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="12.02" customWidth="true" style="0"/>
@@ -12419,12 +12449,132 @@
       </c>
     </row>
     <row r="401" spans="1:8">
-      <c r="A401" s="2"/>
-      <c r="C401" s="1"/>
-      <c r="D401" s="1"/>
-      <c r="E401" s="1"/>
-      <c r="F401" s="1"/>
+      <c r="A401" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="B401" t="s">
+        <v>814</v>
+      </c>
+      <c r="C401" s="1">
+        <v>143</v>
+      </c>
+      <c r="D401" s="1">
+        <v>242</v>
+      </c>
+      <c r="E401" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F401" s="1">
+        <v>99</v>
+      </c>
       <c r="G401" s="1"/>
+      <c r="H401" t="s">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="402" spans="1:8">
+      <c r="A402" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="B402" t="s">
+        <v>816</v>
+      </c>
+      <c r="C402" s="1">
+        <v>143</v>
+      </c>
+      <c r="D402" s="1">
+        <v>242</v>
+      </c>
+      <c r="E402" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F402" s="1">
+        <v>100</v>
+      </c>
+      <c r="G402" s="1"/>
+      <c r="H402" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="403" spans="1:8">
+      <c r="A403" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="B403" t="s">
+        <v>818</v>
+      </c>
+      <c r="C403" s="1">
+        <v>143</v>
+      </c>
+      <c r="D403" s="1">
+        <v>242</v>
+      </c>
+      <c r="E403" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F403" s="1">
+        <v>101</v>
+      </c>
+      <c r="G403" s="1"/>
+      <c r="H403" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="404" spans="1:8">
+      <c r="A404" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="B404" t="s">
+        <v>820</v>
+      </c>
+      <c r="C404" s="1">
+        <v>143</v>
+      </c>
+      <c r="D404" s="1">
+        <v>242</v>
+      </c>
+      <c r="E404" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F404" s="1">
+        <v>103</v>
+      </c>
+      <c r="G404" s="1"/>
+      <c r="H404" t="s">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="405" spans="1:8">
+      <c r="A405" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="B405" t="s">
+        <v>822</v>
+      </c>
+      <c r="C405" s="1">
+        <v>143</v>
+      </c>
+      <c r="D405" s="1">
+        <v>242</v>
+      </c>
+      <c r="E405" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F405" s="1">
+        <v>104</v>
+      </c>
+      <c r="G405" s="1"/>
+      <c r="H405" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="406" spans="1:8">
+      <c r="A406" s="2"/>
+      <c r="C406" s="1"/>
+      <c r="D406" s="1"/>
+      <c r="E406" s="1"/>
+      <c r="F406" s="1"/>
+      <c r="G406" s="1"/>
     </row>
   </sheetData>
   <sheetProtection sheet="false" objects="false" scenarios="false" formatCells="false" formatColumns="false" formatRows="false" insertColumns="false" insertRows="false" insertHyperlinks="false" deleteColumns="false" deleteRows="false" selectLockedCells="false" sort="false" autoFilter="false" pivotTables="false" selectUnlockedCells="false"/>

--- a/data/raw/monthly-2026-10.xlsx
+++ b/data/raw/monthly-2026-10.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="824">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1083">
   <si>
     <t>วันที่</t>
   </si>
@@ -2117,6 +2117,12 @@
     <t>https://ratchakitcha.soc.go.th/documents/130518.pdf</t>
   </si>
   <si>
+    <t>ประกาศคณะกรรมการนโยบายการผังเมืองแห่งชาติ เรื่อง ผังนโยบายระดับประเทศ (พ.ศ. 2569 - 2580)</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132285.pdf</t>
+  </si>
+  <si>
     <t>กระทู้ถามของสมาชิกสภาผู้แทนราษฎร  กระทู้ถามที่ 125 ร. เรื่อง ปัญหาศูนย์บริการส่งเสริมสุขภาพสำหรับผู้มีความหลากหลายทางเพศในพื้นที่กรุงเทพตอนเหนือมีจำนวนไม่เพียงพอต่อการให้บริการประชาชน [ของ นายเอกราช อุดมอำนวย สมาชิกสภาผู้แทนราษฎร พรรคประชาชน]</t>
   </si>
   <si>
@@ -2487,6 +2493,777 @@
   </si>
   <si>
     <t>https://ratchakitcha.soc.go.th/documents/132103.pdf</t>
+  </si>
+  <si>
+    <t>06/10/2026</t>
+  </si>
+  <si>
+    <t>ประกาศกระทรวงการคลัง เรื่องรายงานฐานะการเงินประจำสัปดาห์ของธนาคารแห่งประเทศไทย ทุนสำรองเงินตรา และกิจการธนบัตร [งวดประจำสัปดาห์ สิ้นสุด ณ วันพฤหัสบดี ที่ 23 และ 30 กรกฎาคม 2569]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/129064.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศกระทรวงมหาดไทย เรื่อง การประกาศรายชื่อผู้ได้รับคัดเลือกเป็นกรรมการอิสลามประจำจังหวัดตากแทนตำแหน่งที่ว่าง [นายณรงค์ กะลำคาร]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/128079.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศคณะกรรมการควบคุมการขนส่งทางบกกลาง ฉบับที่  ๒๓๓๗ (พ.ศ. ๒๕๖๙) เรื่อง กำหนดเส้นทางสำหรับการขนส่งประจำทางด้วยรถโดยสาร หมวด ๑ ในเขตกรุงเทพมหานครและจังหวัดที่มีเส้นทางต่อเนื่อง สายที่ ๔ - ๗๒ วงกลมวัดสหธรรมาราม - ถนนพระรามที่ ๒</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/128550.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศคณะกรรมการควบคุมการขนส่งทางบกกลาง ฉบับที่  ๒๓๓๘ (พ.ศ. ๒๕๖๙) เรื่อง กำหนดเส้นทางสำหรับการขนส่งประจำทางด้วยรถโดยสาร หมวด ๔ กรุงเทพมหานคร สายที่ ๑๕๕๔ สถานีรถไฟฟ้าวัดเสมียนนารี - ตลาดประชานิเวศน์ ๑</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/128551.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศคณะกรรมการควบคุมการขนส่งทางบกกลาง ฉบับที่ ๒๓๓๙ (พ.ศ. ๒๕๖๙) เรื่อง  กำหนด (ปรับปรุง) เส้นทางสำหรับการขนส่งประจำทางด้วยรถโดยสาร หมวด ๑ ในเขตกรุงเทพมหานครและจังหวัดที่มีเส้นทางต่อเนื่อง จำนวน ๒ เส้นทาง</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/128552.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศคณะกรรมการควบคุมการขนส่งทางบกกลาง ฉบับที่ ๒๓๔๐ (พ.ศ. ๒๕๖๙) เรื่อง  กำหนด (ปรับปรุง) เส้นทางสำหรับการขนส่งประจำทางด้วยรถโดยสาร หมวด ๓ จำนวน ๓ เส้นทาง</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/128553.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศคณะกรรมการควบคุมการขนส่งทางบกกลาง ฉบับที่  ๒๓๔๑ (พ.ศ. ๒๕๖๙) เรื่อง  กำหนด (ปรับปรุง) เส้นทางสำหรับการขนส่งประจำทางด้วยรถโดยสาร หมวด ๔ กรุงเทพมหานคร จำนวน ๒ เส้นทาง</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/128554.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศสำนักงานกลางทะเบียนสมาคมการค้า ที่ 15/2569 เรื่อง การเลิกสมาคมการค้า [สมาคมผู้ประกอบธุรกิจบริการซ่อมรถยนต์จังหวัดนนทบุรี]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/128202.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศอธิบดีกรมสรรพากร เรื่อง  รายชื่อผู้รับทำการวิจัยและพัฒนาเทคโนโลยีและนวัตกรรม (ฉบับที่ 313)</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/124060.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศนายทะเบียนมูลนิธิจังหวัดเชียงราย เรื่อง จดทะเบียนจัดตั้ง "มูลนิธิกั๊ตพัฒน์เอเล"</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/128459.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศนายทะเบียนมูลนิธิจังหวัดพังงา เรื่อง จดทะเบียนจัดตั้ง "มูลนิธิไผ่ลอดกอ"</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/128557.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศนายทะเบียนมูลนิธิจังหวัดระยอง เรื่อง จดทะเบียนจัดตั้งมูลนิธิ [มูลนิธิโรงเรียนวัดหนองกันเกรา]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/128334.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศนายทะเบียนมูลนิธิจังหวัดอุดรธานี เรื่อง จดทะเบียนจัดตั้ง "มูลนิธิส่งเสริมสวัสดิภาพและเชิดชูเกียรติวิชาชีพครู (มสชค.)"</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/129024.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศนายทะเบียนมูลนิธิจังหวัดชลบุรี เรื่อง จดทะเบียนแก้ไขเพิ่มเติมข้อบังคับของมูลนิธิ [มูลนิธิปรารถนาสมบูรณ์]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/128599.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศนายทะเบียนมูลนิธิจังหวัดตาก เรื่อง จดทะเบียนแก้ไขเพิ่มเติมข้อบังคับของมูลนิธิ [มูลนิธิพันธกิจสมานสามัคคี]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/128364.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศนายทะเบียนมูลนิธิจังหวัดตาก เรื่อง จดทะเบียนแก้ไขเพิ่มเติมข้อบังคับของมูลนิธิ [มูลนิธิช่วยเหลือเด็กชายแดนจังหวัดตาก]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/128399.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศนายทะเบียนมูลนิธิจังหวัดปทุมธานี เรื่อง การขอจดทะเบียนการแก้ไขเพิ่มเติมข้อบังคับของ "มูลนิธิบุญยง - อรรณพ นิโครธานนท์"</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/128393.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศนายทะเบียนมูลนิธิจังหวัดปทุมธานี เรื่อง การขอจดทะเบียนการแก้ไขเพิ่มเติมข้อบังคับของ "มูลนิธิโพชฌงค์ธรรมสถาน"</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/128395.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศนายทะเบียนมูลนิธิจังหวัดปทุมธานี เรื่อง การขอจดทะเบียนการแก้ไขเพิ่มเติมข้อบังคับของ "มูลนิธิ ส.ส.สุรทิน พิจารณ์ (ครูทิน)"</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/128396.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศนายทะเบียนมูลนิธิจังหวัดสกลนคร เรื่อง จดทะเบียนแก้ไขเพิ่มเติมข้อบังคับของมูลนิธิ [มูลนิธิหลวงพ่อสุภา กนฺตสีโล]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/128531.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศนายทะเบียนมูลนิธิจังหวัดอุดรธานี เรื่อง จดทะเบียนแก้ไขเพิ่มเติมข้อบังคับของมูลนิธิ [มูลนิธิศาลเจ้าปู่-ย่า อุดรธานี]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/129065.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศนายทะเบียนมูลนิธิจังหวัดปทุมธานี เรื่อง การขอจดทะเบียนการแก้ไขเพิ่มเติมข้อบังคับ และการขอจดทะเบียนการแต่งตั้งกรรมการของ "มูลนิธิสถาบันศึกษาเมือง" ขึ้นใหม่ทั้งชุด</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/128387.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศนายทะเบียนมูลนิธิจังหวัดปทุมธานี เรื่อง การขอจดทะเบียนการแก้ไขเพิ่มเติมข้อบังคับ และการขอจดทะเบียนการแต่งตั้งกรรมการของ "มูลนิธิแชริตี้ฟอคิดส์" ขึ้นใหม่ทั้งชุด</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/128398.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศนายทะเบียนมูลนิธิจังหวัดนนทบุรี เรื่อง การขอจดทะเบียนการเปลี่ยนแปลงกรรมการของมูลนิธิ [มูลนิธินายอยู่ นางเลื่อน สายสุพรรณ]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/129000.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศนายทะเบียนมูลนิธิจังหวัดนนทบุรี เรื่อง การขอจดทะเบียนการเปลี่ยนแปลงกรรมการของมูลนิธิ [มูลนิธิเพื่อการพัฒนากีฬาจังหวัดนนทบุรี]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/129021.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศนายทะเบียนมูลนิธิจังหวัดปทุมธานี เรื่อง การขอจดทะเบียนการเปลี่ยนแปลงกรรมการของ "มูลนิธิไทยพระคุณมิชชั่น"</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/128392.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศนายทะเบียนมูลนิธิจังหวัดปทุมธานี เรื่อง การขอจดทะเบียนการแต่งตั้งกรรมการของ "มูลนิธิเพื่อการพัฒนาเด็กที่มีความต้องการพิเศษ" ขึ้นใหม่ทั้งชุด</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/128379.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศนายทะเบียนมูลนิธิจังหวัดปทุมธานี เรื่อง การขอจดทะเบียนการแต่งตั้งกรรมการของ "มูลนิธิสวนธรรมศรีปทุม" ขึ้นใหม่ทั้งชุด</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/128394.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศนายทะเบียนสมาคมประจำจังหวัดปทุมธานี เรื่อง การจดทะเบียนจัดตั้งสมาคมสืบสานพุทธศิลป์พระเครื่องไทย</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/128371.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศนายทะเบียนสมาคมประจำจังหวัดปทุมธานี เรื่อง การขอจดทะเบียนจัดตั้งสมาคมสาธารณสุขปทุมธานี</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/128381.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศนายทะเบียนสมาคมประจำจังหวัดปทุมธานี เรื่อง การขอจดทะเบียนจัดตั้งสมาคมโครงสร้างพื้นฐานดิจิทัลประเทศไทย</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/128384.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศนายทะเบียนสมาคมประจำจังหวัดปทุมธานี เรื่อง การขอจดทะเบียนจัดตั้งสมาคมอนุรักษ์พลังงานเพื่อสังคมและสิ่งแวดล้อม</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/128461.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศนายทะเบียนสมาคมประจำจังหวัดเชียงราย เรื่อง จดทะเบียนแก้ไขเพิ่มเติมข้อบังคับของสมาคม [สมาคมผู้ปกครอง ครู และศิษย์เก่าโรงเรียนบ้านแม่จัน (เชียงแสนประชายุสาสน์)]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/128283.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศนายทะเบียนสมาคมประจำจังหวัดเชียงราย เรื่อง จดทะเบียนแก้ไขเพิ่มเติมข้อบังคับของสมาคม [สมาคมผู้ปกครอง ครู โรงเรียนแม่สายประสิทธิศาสตร์]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/128332.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศนายทะเบียนสมาคมประจำจังหวัดอุดรธานี เรื่อง จดทะเบียนแก้ไขเพิ่มเติมข้อบังคับของสมาคม [สมาคมครู ผู้ปกครอง และศิษย์เก่าวิทยาลัยเทคนิคอุดรธานี )</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/129068.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศนายทะเบียนสมาคมประจำจังหวัดปทุมธานี เรื่อง ขอจดทะเบียนการเปลี่ยนแปลงกรรมการของสมาคมแม่ดีเด่นแห่งชาติประจำจังหวัดปทุมธานี</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/128391.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศนายทะเบียนสมาคมประจำจังหวัดปทุมธานี เรื่อง การขอจดทะเบียนการเปลี่ยนแปลงกรรมการของสมาคมการบินไทย อินเตอร์ ไฟลอิ้ง</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/128397.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศนายทะเบียนสมาคมประจำจังหวัดปทุมธานี เรื่อง การจดทะเบียนการแต่งตั้งกรรมการของสมาคมผู้ปกครองและครูโรงเรียนธัญบุรี ขึ้นใหม่ทั้งชุด</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/128372.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศนายทะเบียนสมาคมประจำจังหวัดปทุมธานี เรื่อง การขอจดทะเบียนการแต่งตั้งกรรมการของสมาคมหยูนหนาน (ประเทศไทย) ขึ้นใหม่ทั้งชุด</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/128373.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศนายทะเบียนสมาคมประจำจังหวัดปทุมธานี เรื่อง การขอจดทะเบียนการแต่งตั้งกรรมการของสมาคมผู้ปกครองและครูสวนกุหลาบวิทยาลัย รังสิต ขึ้นใหม่ทั้งชุด</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/128377.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศนายทะเบียนสมาคมจังหวัดแม่ฮ่องสอน เรื่อง การจดทะเบียนการแต่งตั้งกรรมการของสมาคมขึ้นใหม่ทั้งชุด [สมาคมธุรกิจท่องเที่ยวปาย]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/129048.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศสำนักงานที่ดินจังหวัดเชียงใหม่ สาขาสันทราย เรื่อง การจดทะเบียนอาคารชุด [อะไรซ์ ฮิลล์]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/128538.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศสำนักงานที่ดินจังหวัดเชียงใหม่ เรื่อง  การจดทะเบียนอาคารชุด [วันพลัส สวนดอก ไลฟ์ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/128535.pdf</t>
+  </si>
+  <si>
+    <t>บันทึกการประชุมสภาผู้แทนราษฎร ชุดที่ 27 ปีที่ 1 ครั้งที่ 1 (สมัยสามัญประจำปีครั้งที่สอง) วันพุธที่ 26 สิงหาคม พุทธศักราช 2569 ณ ห้องประชุมสภาผู้แทนราษฎร อาคารรัฐสภา</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/129028.pdf</t>
+  </si>
+  <si>
+    <t>บันทึกการประชุมสภาผู้แทนราษฎร ชุดที่ 27 ปีที่ 1 ครั้งที่ 2 (สมัยสามัญประจำปีครั้งที่สอง) วันพฤหัสบดีที่ 27 สิงหาคม พุทธศักราช 2569 ณ ห้องประชุมสภาผู้แทนราษฎร อาคารรัฐสภา</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/129029.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศสำนักนายกรัฐมนตรี เรื่อง แต่งตั้งเอกอัครราชทูตวิสามัญผู้มีอำนาจเต็มประจำสหพันธ์สาธารณรัฐโซมาเลีย [นางสาวจิรัสยา  พีรานนท์]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/134125.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศสำนักนายกรัฐมนตรี เรื่อง แต่งตั้งเอกอัครราชทูตวิสามัญผู้มีอำนาจเต็มประจำสาธารณรัฐบุรุนดี [นางสาวจิรัสยา  พีรานนท์]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/134126.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศสำนักนายกรัฐมนตรี เรื่อง แต่งตั้งเอกอัครราชทูตวิสามัญผู้มีอำนาจเต็มประจำสาธารณรัฐตรินิแดดและโตเบโก [นายดามพ์  บุญธรรม]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/133773.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศสำนักนายกรัฐมนตรี เรื่อง แต่งตั้งกรรมการผู้ช่วยรัฐมนตรี [นายพจน์ หาญพล]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/134007.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศสำนักนายกรัฐมนตรี เรื่อง แต่งตั้งกรรมการผู้ทรงคุณวุฒิในคณะกรรมการการรถไฟฟ้าขนส่งมวลชนแห่งประเทศไทย [จำนวน 3 คน 1. นายปิยพงษ์ จิวัฒนกุลไพศาล ฯลฯ]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/133785.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศสำนักนายกรัฐมนตรี เรื่อง แต่งตั้งศาสตราจารย์ [จำนวน ๕ ราย ๑. รองศาสตราจารย์วรศักดิ์  ทุมมานนท์ ฯลฯ]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/130728.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศสำนักนายกรัฐมนตรี เรื่อง แต่งตั้งศาสตราจารย์ [รวม ๗ ราย ๑. รองศาสตราจารย์ทศพล พรพรหม ฯลฯ]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/130725.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศสำนักนายกรัฐมนตรี เรื่อง แต่งตั้งนายกสภามหาวิทยาลัยราชภัฏเพชรบูรณ์ [นายสมเจตน์ ภูศรี]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131274.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศสำนักนายกรัฐมนตรี เรื่อง แต่งตั้งอธิการบดีมหาวิทยาลัยราชภัฏรำไพพรรณี [นายพอพันธ์ สุทธิวัฒนะ]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/130207.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศสำนักนายกรัฐมนตรี เรื่อง แต่งตั้งกรรมการสภามหาวิทยาลัยผู้ทรงคุณวุฒิของมหาวิทยาลัยศรีนครินทรวิโรฒ [นายเฉลิมชัย บุญยะลีพรรณ]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/130210.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศสำนักนายกรัฐมนตรี เรื่อง แต่งตั้งกรรมการสภามหาวิทยาลัยผู้ทรงคุณวุฒิของมหาวิทยาลัยเชียงใหม่ [นายบวรศักดิ์ อุวรรณโณ]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131210.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศสำนักนายกรัฐมนตรี เรื่อง แต่งตั้งกรรมการสภามหาวิทยาลัยผู้ทรงคุณวุฒิของมหาวิทยาลัยราชภัฏภูเก็ต [จำนวน 11 ราย 1. นายจำรัส  ปิติกุลสถิตย์ ฯลฯ]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/130243.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศกระทรวงทรัพยากรธรรมชาติและสิ่งแวดล้อม เรื่อง เพิกถอนเขตห้ามล่าสัตว์ป่า ป่าพรุเสม็ด และป่าอ่าวบางเต็ง ป่าชายเลน ทะเลสาบสงขลา และทะเลหลวง (บางส่วน) ในท้องที่ตำบลจองถนน อำเภอเขาชัยสน จังหวัดพัทลุง และตำบลเกาะใหญ่ อำเภอกระแสสินธุ์ จังหวัดสงขลา พ.ศ. 2569</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131164.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศกระทรวงยุติธรรม เรื่อง กำหนดสถานที่เพื่อให้การสงเคราะห์บุคคลตามมาตรา 41 แห่งพระราชบัญญัติคุมประพฤติ พ.ศ. 2559 พ.ศ. 2569</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/130110.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศกระทรวงแรงงาน เรื่อง  ประเภท  ขนาดของกิจการ  ท้องที่ที่ให้นายจ้างจ่ายเงินสมทบ อัตราเงินสมทบ  อัตราเงินฝาก  วิธีการประเมินและการเรียกเก็บเงินสมทบ  (ฉบับที่  2)</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131201.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศอธิบดีกรมบังคับคดี เรื่อง หลักเกณฑ์การวางหลักประกันพิเศษ</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131270.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศกรมเจ้าท่า ที่ 199/2569 เรื่อง มาตรการความปลอดภัยและป้องกันการเกิดอุบัติเหตุสำหรับเรือ กลุ่มบรรทุกสินค้าเหลวในระวาง (Tankers) ยกเว้น เรือที่มีประเภทการใช้ บรรทุกน้ำจืด (Fresh water tanker) บรรทุกก๊าซเหลว (Gas carrier) และบรรทุกยางมะตอย (Asphalt tanker)</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/129706.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศสำนักงานการตรวจเงินแผ่นดิน เรื่อง แต่งตั้งข้าราชการสำนักงานการตรวจเงินแผ่นดิน [1. นางสาวสุนทรี  ตัังกาญจนภาสน์ 2. นายศิร์รัฐ ศรีสุนทรพินิต]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/133853.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศสำนักงานประมงจังหวัดขอนแก่น เรื่อง กำหนดห้วงเวลาให้ผู้ประสงค์จะทำการเพาะเลี้ยงสัตว์น้ำในที่จับสัตว์น้ำซึ่งเป็นสาธารณสมบัติของแผ่นดิน ประเภท การเพาะเลี้ยงสัตว์น้ำในกระชัง มายื่นคำขอรับใบอนุญาต (ฉบับที่ 2) พ.ศ. 2569</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131845.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศสำนักงานคณะกรรมการส่วนจังหวัดว่าด้วยราคาสินค้าและบริการ จังหวัดจันทบุรี ฉบับที่ 1 พ.ศ. 2569 เรื่อง หลักเกณฑ์และวิธีการในการขออนุญาต การอนุญาต แบบหนังสืออนุญาต และวิธีการขนย้ายต้นพันธุ์ ท่อนพันธุ์มันสำปะหลัง</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131211.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศคณะกรรมการส่วนจังหวัดว่าด้วยราคาสินค้าและบริการ จังหวัดจันทบุรี ฉบับที่ 1 พ.ศ. 2569 เรื่อง การควบคุมการขนย้ายต้นพันธุ์ ท่อนพันธุ์มันสำปะหลัง</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131151.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง พิทักษ์ทรัพย์เด็ดขาดและจัดการทรัพย์มรดก [คดีหมายเลขแดงที่ ล.E1441/2569 ให้พิทักษ์ทรัพย์ของ ห้างหุ้นส่วนจํากัด เมนสเตย์ ลูกหนี้ที่ 1 และพิพากษาให้จัดการทรัพย์มรดกของ นายวิจัย อุทธิสินธ์ ลูกหนี้ที่ 2 โดยนางอาทิตยา อุทธิสินธ์]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132233.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.E1433/2569 นางสาวนงนภัส ทองกุลกิตติ์ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132319.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.E1450/2569 นายอรรถชัย ฝ่ายไทย ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132217.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.E1451/2569 นางสาวอุมาพร ยสะวัฒนพงศ์ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132241.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.E1452/2569 นางสาวสุรีรัตน์ แซ่อึ้ง ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132284.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.E1453/2569 นางสาวสุภาพร สิงห์วี ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132329.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.E1454/2569 นายทวีศักดิ์ บุญใสย์ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132215.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.E1455/2569 นายอนุชา จันทร์แก้ว ลูกหนี้ที่ 1 และนางสาวกัลยา วิชาจารย์ ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132348.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.E1456/2569 นายฉลอง พิมสุธรรม ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132278.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.E1457/2569 นางสาวพัชรา พรหมเชื้อ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132347.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.E1459/2569 นางสาวสร้อยสุดา กาละ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132255.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.E1460/2569 นางสาวพิมพร สังข์ทอง ลูกหนี้ที่ 1 และนายสุขสันต์ หอมกลิ่น ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132279.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.E1461/2569 นางสาวมณีรัตน์ เขาลาด ลูกหนี้ที่ 1 และนายสมชาย ชัยกาวิล ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132266.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.E1462/2569 นางกาณษรหรือนิธินาท ขวัญเดชสกุล ลูกหนี้ที่ 1 และนางสาวสุนันทา ขวัญเดชสกุล ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132286.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.7055/2569 บริษัทฐิติพร ซับคอนแทร็ก จำกัด ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132231.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.7058/2569 บริษัท สุเทพ ส.รุ่งโรจน์ก่อสร้าง จำกัด (เดิมห้างหุ้นส่วนจำกัด สุเทพ ส.รุ่งโรจน์ก่อสร้าง) ลูกหนี้ที่ 1, นายสุเทพ เมืองเปลี่ยน ในฐานะหุ้นส่วนผู้จัดการของ ห้างหุ้นส่วนจำกัด สุเทพ ส.รุ่งโรจน์ก่อสร้าง ลูกหนี้ที่ 2 และนายสุชาติ เมืองเปลี่ยน ในฐานะหุ้นส่วนผู้จัดการของ ห้างหุ้นส่วนจำกัด สุเทพ ส.รุ่งโรจน์ก่อสร้าง ลูกหนี้ที่ 3]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132339.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.7271/2569 นางเกษร เลยหยุด ลูกหนี้ที่ 1, นางศิริพร หลากสุขถม ลูกหนี้ที่ 2, นายเวชสิทธิ์ วรรณพิน ลูกหนี้ที่ 3, นางอุดมลักษณ์ ผ่องอักษร ลูกหนี้ที่ 4, นางวันดี สมิตอุปถัมภ์ ลูกหนี้ที่ 5, นางพิมพ์อนงค์ ทรัพย์พิพัฒน์ ลูกหนี้ที่ 6 และนางวีณา จิรานนท์ ลูกหนี้ที่ 7]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132228.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.7374/2569 นางสาว หรือนางนันท์นภัส หรือธรรศวรัมพร ภริตาบุณยวัทน์ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132295.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.7924/2569 บริษัทเดือน 9 จำกัด ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132355.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด คดีหมายเลขแดงที่ ล.8033/2569 นายสมชาย ทันนิเทศ ลูกหนี้ที่ 1, นายสมพงษ์ คล่องสั่งสอน ลูกหนี้ที่ 2, นายประโยชน์ สิงห์โต ลูกหนี้ที่ 3, นางณัฎฐา ชินารักษ์หรือช่างกล่อม ลูกหนี้ที่ 4, นายธนวัตน์หรือฐานพัชร์  ขยันหรือเลิศจารุอนันต์ ลูกหนี้ที่ 5, นายเชิดชัย คุณาพัทธ์ ลูกหนี้ที่ 6 และนางพุทธิพร เถื่อนใหญ่ ลูกหนี้ที่ 7]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132247.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8060/2569 นายอนุสิทธิ์ แก่นจันทร์ ลูกหนี้ที่ 1 และนางสาวศิริพร แก่นจันทร์ หรือสมศิริ ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132352.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8061/2569 นางสาวสุดาทิพย์ บุญพิทักษ์ชัย ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132317.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8085/2569 นางสาวภัคภิญญาหรืออ่อนโยน แซ่อึ้ง ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132327.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8086/2569 นายณรงค์ยศ น้อยตั้ง ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132240.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8087/2569 ว่าที่ร้อยตรีโชคชัย เริงนิสสัย ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132237.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8088/2569 บริษัทสรรพสินค้าตั้งฮั่วเส็ง จำกัด ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132214.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8097/2569 นางสาวยุวดี บุญวงษ์เมือง ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132274.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8098/2569 นางสาวเมธาญา แสงทอง ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132346.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8099/2569 นายพีรวุฒิ บุญวัติ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132249.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8105/2569 นายธนะเมศฐ์ โชตน์ธนภัทร์กุล ลูกหนี้ที่ 1, นายธนศักดิ์ เวียงกมล ลูกหนี้ที่ 2, นายดำริ เหล่าเจริญ ลูกหนี้ที่ 3 และนายฉลองชัย เมืองมัจฉา ลูกหนี้ที่ 4]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132276.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8106/2569 นางสาวสุรีมาส ขาวขำ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132235.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8108/2569 นางหรือนางสาวณปพัชญ์หรือบาลฤดี บาลจ่ายหรือชนะราวี ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132324.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8109/2569 นายชูเกียรติ จรูญวัชรพันธ์ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132234.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8110/2569 นางสาวปัตติยา นาคชุ่ม ลูกหนี้ที่ 1 และนายปิยะพงศ์ คงวัดใหม่ ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132212.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8111/2569 นายคมชัช บรรยง ลูกหนี้ที่ 1 และนางหรือนางสาวพรนิภาหรือพิธาพร บรรยงหรือพิพัฒน์ยรรยง ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132250.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8159/2569 นางสาวอาอีเสาะห์ กาเซ็ง ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132243.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8161/2569 นายวรชัย ไม้ทอง ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132244.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8162/2569 นางสาวนัทธ์ฐภัคหรือสุทารัตน์ แก่นโคตร ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132332.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8163/2569 นางสาวนภา ท้วมทวยหาญ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132330.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8165/2569 นางสาวโสภิญญา เสือเพชร ลูกหนี้ที่ 1]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132218.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8166/2569 บริษัททีพีพี.ฟู้ดส์ จำกัด ลูกหนี้ที่ 1, นายถวิลหรือวิน กาวิสุขหรือภัทรพูลสุข ลูกหนี้ที่ 2, นายพงษ์นรินทร์ กาวิสุข ลูกหนี้ที่ 3 และนางสาวพฤฒิรัตน์ กาวิสุขหรือเพิ่มพูล ลูกหนี้ที่ 4]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132245.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8172/2569 นายภีม์พัฒน์หรือศุภฤกษ์หรือภวดลหรือณวัสน์ วัชรวิสิฐกุลหรือโคศุภหรือธัญฉัตรธรรม ลูกหนี้ที่ 3]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132226.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8174/2569 นางตราทิพย์ ชมิดหรือเกเบสฮูเบอร์ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132345.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8179/2569 นางสาวสุทธภา เชื้อช่วยชู ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132267.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8180/2569 นายพิเชษฐ์ บูชา ลูกหนี้ที่ 1 และนางสาวอินทหว๋า เบื้องบน ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132268.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8181/2569 บริษัทเมย์จิกรุ๊ป จำกัด ลูกหนี้ที่ 1 และนางสาวอนิกาหรือมัทญา  ศิยาภรณ์หรือแซ่ซูม ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132349.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8182/2569 นายเอกชัย ทองคำ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132213.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8183/2569 จ่าสิบเอกพงศธร แก้วกงพาน ลูกหนี้ที่ 1 และสิบเอกหรือจ่าสิบเอกนพรัตน์ เกษร ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132282.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8184/2569 นายสมเกียรติ กอผา ลูกหนี้ที่ 1 และนางสาวขวัญชนก ทาแกง ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132325.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8194/2569 นายเอกพงศ์ ศรีขาว ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132351.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8201/2569 นายนิคม ชูสกุลวงศ์ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132356.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8202/2569 บริษัทส.ประภาคาร จำกัด ลูกหนี้ที่ 1 และนางสาวชนกมน อยู่ปาน ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132353.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8203/2569 นางสาวอัญชลี เมืองราช ลูกหนี้ที่ 1 และนายสมศักดิ์ สร้อยสุข ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132246.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8205/2569 นายอนิรุต สุธรรมรักษ์ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132248.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8206/2569 บริษัทเกรท รอยัล เอ็นจิเนียริ่ง จำกัด ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132300.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8207/2569 นางจารีพร เกษเพ็ชร ลูกหนี้ที่ 1 และนางหรือนางสาววาสนา ช่วยเพ็งหรืออ่อนส่งหรือหนูแก้ว ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132211.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8209/2569 บริษัท ตะวันสองเมือง จำกัด ลูกหนี้ที่ 1, นายพูนพงศ์หรือเอกปุณณญาณ์ มะเริงสิทธิ์ปภา ลูกหนี้ที่ 2 และนางณัฐภัสสร มะเริงสิทธิ์ปภา ลูกหนี้ที่ 3]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132350.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8210/2569 นายฆฤต วานิชยานนท์ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132273.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8223/2569 บริษัทไทยโอเซี่ยน อินเตอร์เนชั่นแนล จำกัด ลูกหนี้ที่ 1 และนายจิราวุฒิ เจริญสุข ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132335.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8224/2569 บริษัทเดียร์ ดี เทรดดิ้ง จำกัด ลูกหนี้ที่ 1, นางสาวเรชุนาถ ไชยลังกา ลูกหนี้ที่ 2 และนางสาวอัญชนา ไชยลังกา ลูกหนี้ที่ 3]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132291.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8225/2569 บริษัทแอ็ดเด็กซ์ จำกัด ลูกหนี้ที่ 1 และนายณัทกรหรือทัศพันธุ์หรือชัยรัฐปฐม อิศรศักดิ์ ณ อยุธยา ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132272.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8226/2569 ห้างหุ้นส่วนจำกัด ยิ่งรวย ฟาร์ม ลูกหนี้ที่ 1, นายอัญชนะ พุ่มวงศ์ ลูกหนี้ที่ 2 และนายณัฐวุฒิ พุ่มวงศ์ ลูกหนี้ที่ 3]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132334.pdf</t>
   </si>
 </sst>
 </file>
@@ -2833,7 +3610,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:H406"/>
+  <dimension ref="A1:H535"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="12.02" customWidth="true" style="0"/>
@@ -11121,7 +11898,7 @@
         <v>100</v>
       </c>
       <c r="F345" s="1">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G345" s="1"/>
       <c r="H345" t="s">
@@ -11145,7 +11922,7 @@
         <v>100</v>
       </c>
       <c r="F346" s="1">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="G346" s="1"/>
       <c r="H346" t="s">
@@ -11169,7 +11946,7 @@
         <v>100</v>
       </c>
       <c r="F347" s="1">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G347" s="1"/>
       <c r="H347" t="s">
@@ -11337,7 +12114,7 @@
         <v>100</v>
       </c>
       <c r="F354" s="1">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G354" s="1"/>
       <c r="H354" t="s">
@@ -11529,7 +12306,7 @@
         <v>100</v>
       </c>
       <c r="F362" s="1">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G362" s="1"/>
       <c r="H362" t="s">
@@ -12321,7 +13098,7 @@
         <v>100</v>
       </c>
       <c r="F395" s="1">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G395" s="1"/>
       <c r="H395" t="s">
@@ -12393,7 +13170,7 @@
         <v>100</v>
       </c>
       <c r="F398" s="1">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G398" s="1"/>
       <c r="H398" t="s">
@@ -12537,7 +13314,7 @@
         <v>100</v>
       </c>
       <c r="F404" s="1">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G404" s="1"/>
       <c r="H404" t="s">
@@ -12569,12 +13346,3108 @@
       </c>
     </row>
     <row r="406" spans="1:8">
-      <c r="A406" s="2"/>
-      <c r="C406" s="1"/>
-      <c r="D406" s="1"/>
-      <c r="E406" s="1"/>
-      <c r="F406" s="1"/>
+      <c r="A406" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="B406" t="s">
+        <v>824</v>
+      </c>
+      <c r="C406" s="1">
+        <v>143</v>
+      </c>
+      <c r="D406" s="1">
+        <v>242</v>
+      </c>
+      <c r="E406" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F406" s="1">
+        <v>105</v>
+      </c>
       <c r="G406" s="1"/>
+      <c r="H406" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="407" spans="1:8">
+      <c r="A407" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B407" t="s">
+        <v>827</v>
+      </c>
+      <c r="C407" s="1">
+        <v>143</v>
+      </c>
+      <c r="D407" s="1">
+        <v>148</v>
+      </c>
+      <c r="E407" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F407" s="1">
+        <v>1</v>
+      </c>
+      <c r="G407" s="1"/>
+      <c r="H407" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="408" spans="1:8">
+      <c r="A408" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B408" t="s">
+        <v>829</v>
+      </c>
+      <c r="C408" s="1">
+        <v>143</v>
+      </c>
+      <c r="D408" s="1">
+        <v>148</v>
+      </c>
+      <c r="E408" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F408" s="1">
+        <v>2</v>
+      </c>
+      <c r="G408" s="1"/>
+      <c r="H408" t="s">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="409" spans="1:8">
+      <c r="A409" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B409" t="s">
+        <v>831</v>
+      </c>
+      <c r="C409" s="1">
+        <v>143</v>
+      </c>
+      <c r="D409" s="1">
+        <v>148</v>
+      </c>
+      <c r="E409" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F409" s="1">
+        <v>3</v>
+      </c>
+      <c r="G409" s="1"/>
+      <c r="H409" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="410" spans="1:8">
+      <c r="A410" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B410" t="s">
+        <v>833</v>
+      </c>
+      <c r="C410" s="1">
+        <v>143</v>
+      </c>
+      <c r="D410" s="1">
+        <v>148</v>
+      </c>
+      <c r="E410" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F410" s="1">
+        <v>5</v>
+      </c>
+      <c r="G410" s="1"/>
+      <c r="H410" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="411" spans="1:8">
+      <c r="A411" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B411" t="s">
+        <v>835</v>
+      </c>
+      <c r="C411" s="1">
+        <v>143</v>
+      </c>
+      <c r="D411" s="1">
+        <v>148</v>
+      </c>
+      <c r="E411" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F411" s="1">
+        <v>6</v>
+      </c>
+      <c r="G411" s="1"/>
+      <c r="H411" t="s">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="412" spans="1:8">
+      <c r="A412" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B412" t="s">
+        <v>837</v>
+      </c>
+      <c r="C412" s="1">
+        <v>143</v>
+      </c>
+      <c r="D412" s="1">
+        <v>148</v>
+      </c>
+      <c r="E412" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F412" s="1">
+        <v>8</v>
+      </c>
+      <c r="G412" s="1"/>
+      <c r="H412" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="413" spans="1:8">
+      <c r="A413" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B413" t="s">
+        <v>839</v>
+      </c>
+      <c r="C413" s="1">
+        <v>143</v>
+      </c>
+      <c r="D413" s="1">
+        <v>148</v>
+      </c>
+      <c r="E413" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F413" s="1">
+        <v>11</v>
+      </c>
+      <c r="G413" s="1"/>
+      <c r="H413" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="414" spans="1:8">
+      <c r="A414" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B414" t="s">
+        <v>841</v>
+      </c>
+      <c r="C414" s="1">
+        <v>143</v>
+      </c>
+      <c r="D414" s="1">
+        <v>148</v>
+      </c>
+      <c r="E414" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F414" s="1">
+        <v>13</v>
+      </c>
+      <c r="G414" s="1"/>
+      <c r="H414" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="415" spans="1:8">
+      <c r="A415" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B415" t="s">
+        <v>843</v>
+      </c>
+      <c r="C415" s="1">
+        <v>143</v>
+      </c>
+      <c r="D415" s="1">
+        <v>148</v>
+      </c>
+      <c r="E415" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F415" s="1">
+        <v>14</v>
+      </c>
+      <c r="G415" s="1"/>
+      <c r="H415" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="416" spans="1:8">
+      <c r="A416" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B416" t="s">
+        <v>845</v>
+      </c>
+      <c r="C416" s="1">
+        <v>143</v>
+      </c>
+      <c r="D416" s="1">
+        <v>148</v>
+      </c>
+      <c r="E416" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F416" s="1">
+        <v>15</v>
+      </c>
+      <c r="G416" s="1"/>
+      <c r="H416" t="s">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="417" spans="1:8">
+      <c r="A417" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B417" t="s">
+        <v>847</v>
+      </c>
+      <c r="C417" s="1">
+        <v>143</v>
+      </c>
+      <c r="D417" s="1">
+        <v>148</v>
+      </c>
+      <c r="E417" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F417" s="1">
+        <v>17</v>
+      </c>
+      <c r="G417" s="1"/>
+      <c r="H417" t="s">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="418" spans="1:8">
+      <c r="A418" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B418" t="s">
+        <v>849</v>
+      </c>
+      <c r="C418" s="1">
+        <v>143</v>
+      </c>
+      <c r="D418" s="1">
+        <v>148</v>
+      </c>
+      <c r="E418" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F418" s="1">
+        <v>19</v>
+      </c>
+      <c r="G418" s="1"/>
+      <c r="H418" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="419" spans="1:8">
+      <c r="A419" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B419" t="s">
+        <v>851</v>
+      </c>
+      <c r="C419" s="1">
+        <v>143</v>
+      </c>
+      <c r="D419" s="1">
+        <v>148</v>
+      </c>
+      <c r="E419" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F419" s="1">
+        <v>21</v>
+      </c>
+      <c r="G419" s="1"/>
+      <c r="H419" t="s">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="420" spans="1:8">
+      <c r="A420" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B420" t="s">
+        <v>853</v>
+      </c>
+      <c r="C420" s="1">
+        <v>143</v>
+      </c>
+      <c r="D420" s="1">
+        <v>148</v>
+      </c>
+      <c r="E420" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F420" s="1">
+        <v>23</v>
+      </c>
+      <c r="G420" s="1"/>
+      <c r="H420" t="s">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="421" spans="1:8">
+      <c r="A421" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B421" t="s">
+        <v>855</v>
+      </c>
+      <c r="C421" s="1">
+        <v>143</v>
+      </c>
+      <c r="D421" s="1">
+        <v>148</v>
+      </c>
+      <c r="E421" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F421" s="1">
+        <v>25</v>
+      </c>
+      <c r="G421" s="1"/>
+      <c r="H421" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="422" spans="1:8">
+      <c r="A422" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B422" t="s">
+        <v>857</v>
+      </c>
+      <c r="C422" s="1">
+        <v>143</v>
+      </c>
+      <c r="D422" s="1">
+        <v>148</v>
+      </c>
+      <c r="E422" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F422" s="1">
+        <v>26</v>
+      </c>
+      <c r="G422" s="1"/>
+      <c r="H422" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="423" spans="1:8">
+      <c r="A423" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B423" t="s">
+        <v>859</v>
+      </c>
+      <c r="C423" s="1">
+        <v>143</v>
+      </c>
+      <c r="D423" s="1">
+        <v>148</v>
+      </c>
+      <c r="E423" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F423" s="1">
+        <v>28</v>
+      </c>
+      <c r="G423" s="1"/>
+      <c r="H423" t="s">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="424" spans="1:8">
+      <c r="A424" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B424" t="s">
+        <v>861</v>
+      </c>
+      <c r="C424" s="1">
+        <v>143</v>
+      </c>
+      <c r="D424" s="1">
+        <v>148</v>
+      </c>
+      <c r="E424" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F424" s="1">
+        <v>29</v>
+      </c>
+      <c r="G424" s="1"/>
+      <c r="H424" t="s">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="425" spans="1:8">
+      <c r="A425" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B425" t="s">
+        <v>863</v>
+      </c>
+      <c r="C425" s="1">
+        <v>143</v>
+      </c>
+      <c r="D425" s="1">
+        <v>148</v>
+      </c>
+      <c r="E425" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F425" s="1">
+        <v>31</v>
+      </c>
+      <c r="G425" s="1"/>
+      <c r="H425" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="426" spans="1:8">
+      <c r="A426" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B426" t="s">
+        <v>865</v>
+      </c>
+      <c r="C426" s="1">
+        <v>143</v>
+      </c>
+      <c r="D426" s="1">
+        <v>148</v>
+      </c>
+      <c r="E426" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F426" s="1">
+        <v>32</v>
+      </c>
+      <c r="G426" s="1"/>
+      <c r="H426" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="427" spans="1:8">
+      <c r="A427" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B427" t="s">
+        <v>867</v>
+      </c>
+      <c r="C427" s="1">
+        <v>143</v>
+      </c>
+      <c r="D427" s="1">
+        <v>148</v>
+      </c>
+      <c r="E427" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F427" s="1">
+        <v>33</v>
+      </c>
+      <c r="G427" s="1"/>
+      <c r="H427" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="428" spans="1:8">
+      <c r="A428" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B428" t="s">
+        <v>869</v>
+      </c>
+      <c r="C428" s="1">
+        <v>143</v>
+      </c>
+      <c r="D428" s="1">
+        <v>148</v>
+      </c>
+      <c r="E428" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F428" s="1">
+        <v>35</v>
+      </c>
+      <c r="G428" s="1"/>
+      <c r="H428" t="s">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="429" spans="1:8">
+      <c r="A429" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B429" t="s">
+        <v>871</v>
+      </c>
+      <c r="C429" s="1">
+        <v>143</v>
+      </c>
+      <c r="D429" s="1">
+        <v>148</v>
+      </c>
+      <c r="E429" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F429" s="1">
+        <v>36</v>
+      </c>
+      <c r="G429" s="1"/>
+      <c r="H429" t="s">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="430" spans="1:8">
+      <c r="A430" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B430" t="s">
+        <v>873</v>
+      </c>
+      <c r="C430" s="1">
+        <v>143</v>
+      </c>
+      <c r="D430" s="1">
+        <v>148</v>
+      </c>
+      <c r="E430" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F430" s="1">
+        <v>38</v>
+      </c>
+      <c r="G430" s="1"/>
+      <c r="H430" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="431" spans="1:8">
+      <c r="A431" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B431" t="s">
+        <v>875</v>
+      </c>
+      <c r="C431" s="1">
+        <v>143</v>
+      </c>
+      <c r="D431" s="1">
+        <v>148</v>
+      </c>
+      <c r="E431" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F431" s="1">
+        <v>39</v>
+      </c>
+      <c r="G431" s="1"/>
+      <c r="H431" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="432" spans="1:8">
+      <c r="A432" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B432" t="s">
+        <v>877</v>
+      </c>
+      <c r="C432" s="1">
+        <v>143</v>
+      </c>
+      <c r="D432" s="1">
+        <v>148</v>
+      </c>
+      <c r="E432" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F432" s="1">
+        <v>40</v>
+      </c>
+      <c r="G432" s="1"/>
+      <c r="H432" t="s">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="433" spans="1:8">
+      <c r="A433" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B433" t="s">
+        <v>879</v>
+      </c>
+      <c r="C433" s="1">
+        <v>143</v>
+      </c>
+      <c r="D433" s="1">
+        <v>148</v>
+      </c>
+      <c r="E433" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F433" s="1">
+        <v>41</v>
+      </c>
+      <c r="G433" s="1"/>
+      <c r="H433" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="434" spans="1:8">
+      <c r="A434" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B434" t="s">
+        <v>881</v>
+      </c>
+      <c r="C434" s="1">
+        <v>143</v>
+      </c>
+      <c r="D434" s="1">
+        <v>148</v>
+      </c>
+      <c r="E434" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F434" s="1">
+        <v>42</v>
+      </c>
+      <c r="G434" s="1"/>
+      <c r="H434" t="s">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="435" spans="1:8">
+      <c r="A435" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B435" t="s">
+        <v>883</v>
+      </c>
+      <c r="C435" s="1">
+        <v>143</v>
+      </c>
+      <c r="D435" s="1">
+        <v>148</v>
+      </c>
+      <c r="E435" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F435" s="1">
+        <v>43</v>
+      </c>
+      <c r="G435" s="1"/>
+      <c r="H435" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="436" spans="1:8">
+      <c r="A436" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B436" t="s">
+        <v>885</v>
+      </c>
+      <c r="C436" s="1">
+        <v>143</v>
+      </c>
+      <c r="D436" s="1">
+        <v>148</v>
+      </c>
+      <c r="E436" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F436" s="1">
+        <v>45</v>
+      </c>
+      <c r="G436" s="1"/>
+      <c r="H436" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="437" spans="1:8">
+      <c r="A437" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B437" t="s">
+        <v>887</v>
+      </c>
+      <c r="C437" s="1">
+        <v>143</v>
+      </c>
+      <c r="D437" s="1">
+        <v>148</v>
+      </c>
+      <c r="E437" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F437" s="1">
+        <v>48</v>
+      </c>
+      <c r="G437" s="1"/>
+      <c r="H437" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="438" spans="1:8">
+      <c r="A438" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B438" t="s">
+        <v>889</v>
+      </c>
+      <c r="C438" s="1">
+        <v>143</v>
+      </c>
+      <c r="D438" s="1">
+        <v>148</v>
+      </c>
+      <c r="E438" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F438" s="1">
+        <v>51</v>
+      </c>
+      <c r="G438" s="1"/>
+      <c r="H438" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="439" spans="1:8">
+      <c r="A439" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B439" t="s">
+        <v>891</v>
+      </c>
+      <c r="C439" s="1">
+        <v>143</v>
+      </c>
+      <c r="D439" s="1">
+        <v>148</v>
+      </c>
+      <c r="E439" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F439" s="1">
+        <v>54</v>
+      </c>
+      <c r="G439" s="1"/>
+      <c r="H439" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="440" spans="1:8">
+      <c r="A440" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B440" t="s">
+        <v>893</v>
+      </c>
+      <c r="C440" s="1">
+        <v>143</v>
+      </c>
+      <c r="D440" s="1">
+        <v>148</v>
+      </c>
+      <c r="E440" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F440" s="1">
+        <v>55</v>
+      </c>
+      <c r="G440" s="1"/>
+      <c r="H440" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="441" spans="1:8">
+      <c r="A441" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B441" t="s">
+        <v>895</v>
+      </c>
+      <c r="C441" s="1">
+        <v>143</v>
+      </c>
+      <c r="D441" s="1">
+        <v>148</v>
+      </c>
+      <c r="E441" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F441" s="1">
+        <v>58</v>
+      </c>
+      <c r="G441" s="1"/>
+      <c r="H441" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="442" spans="1:8">
+      <c r="A442" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B442" t="s">
+        <v>897</v>
+      </c>
+      <c r="C442" s="1">
+        <v>143</v>
+      </c>
+      <c r="D442" s="1">
+        <v>148</v>
+      </c>
+      <c r="E442" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F442" s="1">
+        <v>60</v>
+      </c>
+      <c r="G442" s="1"/>
+      <c r="H442" t="s">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="443" spans="1:8">
+      <c r="A443" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B443" t="s">
+        <v>899</v>
+      </c>
+      <c r="C443" s="1">
+        <v>143</v>
+      </c>
+      <c r="D443" s="1">
+        <v>148</v>
+      </c>
+      <c r="E443" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F443" s="1">
+        <v>61</v>
+      </c>
+      <c r="G443" s="1"/>
+      <c r="H443" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="444" spans="1:8">
+      <c r="A444" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B444" t="s">
+        <v>901</v>
+      </c>
+      <c r="C444" s="1">
+        <v>143</v>
+      </c>
+      <c r="D444" s="1">
+        <v>148</v>
+      </c>
+      <c r="E444" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F444" s="1">
+        <v>62</v>
+      </c>
+      <c r="G444" s="1"/>
+      <c r="H444" t="s">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="445" spans="1:8">
+      <c r="A445" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B445" t="s">
+        <v>903</v>
+      </c>
+      <c r="C445" s="1">
+        <v>143</v>
+      </c>
+      <c r="D445" s="1">
+        <v>148</v>
+      </c>
+      <c r="E445" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F445" s="1">
+        <v>64</v>
+      </c>
+      <c r="G445" s="1"/>
+      <c r="H445" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="446" spans="1:8">
+      <c r="A446" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B446" t="s">
+        <v>905</v>
+      </c>
+      <c r="C446" s="1">
+        <v>143</v>
+      </c>
+      <c r="D446" s="1">
+        <v>148</v>
+      </c>
+      <c r="E446" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F446" s="1">
+        <v>65</v>
+      </c>
+      <c r="G446" s="1"/>
+      <c r="H446" t="s">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="447" spans="1:8">
+      <c r="A447" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B447" t="s">
+        <v>907</v>
+      </c>
+      <c r="C447" s="1">
+        <v>143</v>
+      </c>
+      <c r="D447" s="1">
+        <v>148</v>
+      </c>
+      <c r="E447" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F447" s="1">
+        <v>67</v>
+      </c>
+      <c r="G447" s="1"/>
+      <c r="H447" t="s">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="448" spans="1:8">
+      <c r="A448" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B448" t="s">
+        <v>909</v>
+      </c>
+      <c r="C448" s="1">
+        <v>143</v>
+      </c>
+      <c r="D448" s="1">
+        <v>148</v>
+      </c>
+      <c r="E448" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F448" s="1">
+        <v>68</v>
+      </c>
+      <c r="G448" s="1"/>
+      <c r="H448" t="s">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="449" spans="1:8">
+      <c r="A449" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B449" t="s">
+        <v>911</v>
+      </c>
+      <c r="C449" s="1">
+        <v>143</v>
+      </c>
+      <c r="D449" s="1">
+        <v>148</v>
+      </c>
+      <c r="E449" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F449" s="1">
+        <v>69</v>
+      </c>
+      <c r="G449" s="1"/>
+      <c r="H449" t="s">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="450" spans="1:8">
+      <c r="A450" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B450" t="s">
+        <v>913</v>
+      </c>
+      <c r="C450" s="1">
+        <v>143</v>
+      </c>
+      <c r="D450" s="1">
+        <v>148</v>
+      </c>
+      <c r="E450" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F450" s="1">
+        <v>70</v>
+      </c>
+      <c r="G450" s="1"/>
+      <c r="H450" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="451" spans="1:8">
+      <c r="A451" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B451" t="s">
+        <v>915</v>
+      </c>
+      <c r="C451" s="1">
+        <v>143</v>
+      </c>
+      <c r="D451" s="1">
+        <v>148</v>
+      </c>
+      <c r="E451" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F451" s="1">
+        <v>73</v>
+      </c>
+      <c r="G451" s="1"/>
+      <c r="H451" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="452" spans="1:8">
+      <c r="A452" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B452" t="s">
+        <v>917</v>
+      </c>
+      <c r="C452" s="1">
+        <v>143</v>
+      </c>
+      <c r="D452" s="1">
+        <v>243</v>
+      </c>
+      <c r="E452" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F452" s="1">
+        <v>1</v>
+      </c>
+      <c r="G452" s="1"/>
+      <c r="H452" t="s">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="453" spans="1:8">
+      <c r="A453" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B453" t="s">
+        <v>919</v>
+      </c>
+      <c r="C453" s="1">
+        <v>143</v>
+      </c>
+      <c r="D453" s="1">
+        <v>243</v>
+      </c>
+      <c r="E453" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F453" s="1">
+        <v>2</v>
+      </c>
+      <c r="G453" s="1"/>
+      <c r="H453" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="454" spans="1:8">
+      <c r="A454" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B454" t="s">
+        <v>921</v>
+      </c>
+      <c r="C454" s="1">
+        <v>143</v>
+      </c>
+      <c r="D454" s="1">
+        <v>243</v>
+      </c>
+      <c r="E454" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F454" s="1">
+        <v>3</v>
+      </c>
+      <c r="G454" s="1"/>
+      <c r="H454" t="s">
+        <v>922</v>
+      </c>
+    </row>
+    <row r="455" spans="1:8">
+      <c r="A455" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B455" t="s">
+        <v>923</v>
+      </c>
+      <c r="C455" s="1">
+        <v>143</v>
+      </c>
+      <c r="D455" s="1">
+        <v>243</v>
+      </c>
+      <c r="E455" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F455" s="1">
+        <v>4</v>
+      </c>
+      <c r="G455" s="1"/>
+      <c r="H455" t="s">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="456" spans="1:8">
+      <c r="A456" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B456" t="s">
+        <v>925</v>
+      </c>
+      <c r="C456" s="1">
+        <v>143</v>
+      </c>
+      <c r="D456" s="1">
+        <v>243</v>
+      </c>
+      <c r="E456" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F456" s="1">
+        <v>5</v>
+      </c>
+      <c r="G456" s="1"/>
+      <c r="H456" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="457" spans="1:8">
+      <c r="A457" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B457" t="s">
+        <v>927</v>
+      </c>
+      <c r="C457" s="1">
+        <v>143</v>
+      </c>
+      <c r="D457" s="1">
+        <v>243</v>
+      </c>
+      <c r="E457" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F457" s="1">
+        <v>6</v>
+      </c>
+      <c r="G457" s="1"/>
+      <c r="H457" t="s">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="458" spans="1:8">
+      <c r="A458" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B458" t="s">
+        <v>929</v>
+      </c>
+      <c r="C458" s="1">
+        <v>143</v>
+      </c>
+      <c r="D458" s="1">
+        <v>243</v>
+      </c>
+      <c r="E458" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F458" s="1">
+        <v>7</v>
+      </c>
+      <c r="G458" s="1"/>
+      <c r="H458" t="s">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="459" spans="1:8">
+      <c r="A459" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B459" t="s">
+        <v>931</v>
+      </c>
+      <c r="C459" s="1">
+        <v>143</v>
+      </c>
+      <c r="D459" s="1">
+        <v>243</v>
+      </c>
+      <c r="E459" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F459" s="1">
+        <v>9</v>
+      </c>
+      <c r="G459" s="1"/>
+      <c r="H459" t="s">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="460" spans="1:8">
+      <c r="A460" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B460" t="s">
+        <v>933</v>
+      </c>
+      <c r="C460" s="1">
+        <v>143</v>
+      </c>
+      <c r="D460" s="1">
+        <v>243</v>
+      </c>
+      <c r="E460" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F460" s="1">
+        <v>10</v>
+      </c>
+      <c r="G460" s="1"/>
+      <c r="H460" t="s">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="461" spans="1:8">
+      <c r="A461" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B461" t="s">
+        <v>935</v>
+      </c>
+      <c r="C461" s="1">
+        <v>143</v>
+      </c>
+      <c r="D461" s="1">
+        <v>243</v>
+      </c>
+      <c r="E461" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F461" s="1">
+        <v>11</v>
+      </c>
+      <c r="G461" s="1"/>
+      <c r="H461" t="s">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="462" spans="1:8">
+      <c r="A462" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B462" t="s">
+        <v>937</v>
+      </c>
+      <c r="C462" s="1">
+        <v>143</v>
+      </c>
+      <c r="D462" s="1">
+        <v>243</v>
+      </c>
+      <c r="E462" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F462" s="1">
+        <v>12</v>
+      </c>
+      <c r="G462" s="1"/>
+      <c r="H462" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="463" spans="1:8">
+      <c r="A463" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B463" t="s">
+        <v>939</v>
+      </c>
+      <c r="C463" s="1">
+        <v>143</v>
+      </c>
+      <c r="D463" s="1">
+        <v>243</v>
+      </c>
+      <c r="E463" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F463" s="1">
+        <v>13</v>
+      </c>
+      <c r="G463" s="1"/>
+      <c r="H463" t="s">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="464" spans="1:8">
+      <c r="A464" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B464" t="s">
+        <v>941</v>
+      </c>
+      <c r="C464" s="1">
+        <v>143</v>
+      </c>
+      <c r="D464" s="1">
+        <v>243</v>
+      </c>
+      <c r="E464" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F464" s="1">
+        <v>14</v>
+      </c>
+      <c r="G464" s="1"/>
+      <c r="H464" t="s">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="465" spans="1:8">
+      <c r="A465" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B465" t="s">
+        <v>943</v>
+      </c>
+      <c r="C465" s="1">
+        <v>143</v>
+      </c>
+      <c r="D465" s="1">
+        <v>243</v>
+      </c>
+      <c r="E465" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F465" s="1">
+        <v>16</v>
+      </c>
+      <c r="G465" s="1"/>
+      <c r="H465" t="s">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="466" spans="1:8">
+      <c r="A466" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B466" t="s">
+        <v>945</v>
+      </c>
+      <c r="C466" s="1">
+        <v>143</v>
+      </c>
+      <c r="D466" s="1">
+        <v>243</v>
+      </c>
+      <c r="E466" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F466" s="1">
+        <v>17</v>
+      </c>
+      <c r="G466" s="1"/>
+      <c r="H466" t="s">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="467" spans="1:8">
+      <c r="A467" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B467" t="s">
+        <v>947</v>
+      </c>
+      <c r="C467" s="1">
+        <v>143</v>
+      </c>
+      <c r="D467" s="1">
+        <v>243</v>
+      </c>
+      <c r="E467" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F467" s="1">
+        <v>18</v>
+      </c>
+      <c r="G467" s="1"/>
+      <c r="H467" t="s">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="468" spans="1:8">
+      <c r="A468" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B468" t="s">
+        <v>949</v>
+      </c>
+      <c r="C468" s="1">
+        <v>143</v>
+      </c>
+      <c r="D468" s="1">
+        <v>243</v>
+      </c>
+      <c r="E468" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F468" s="1">
+        <v>20</v>
+      </c>
+      <c r="G468" s="1"/>
+      <c r="H468" t="s">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="469" spans="1:8">
+      <c r="A469" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B469" t="s">
+        <v>951</v>
+      </c>
+      <c r="C469" s="1">
+        <v>143</v>
+      </c>
+      <c r="D469" s="1">
+        <v>243</v>
+      </c>
+      <c r="E469" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F469" s="1">
+        <v>22</v>
+      </c>
+      <c r="G469" s="1"/>
+      <c r="H469" t="s">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="470" spans="1:8">
+      <c r="A470" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B470" t="s">
+        <v>953</v>
+      </c>
+      <c r="C470" s="1">
+        <v>143</v>
+      </c>
+      <c r="D470" s="1">
+        <v>243</v>
+      </c>
+      <c r="E470" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F470" s="1">
+        <v>23</v>
+      </c>
+      <c r="G470" s="1"/>
+      <c r="H470" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="471" spans="1:8">
+      <c r="A471" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B471" t="s">
+        <v>955</v>
+      </c>
+      <c r="C471" s="1">
+        <v>143</v>
+      </c>
+      <c r="D471" s="1">
+        <v>243</v>
+      </c>
+      <c r="E471" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F471" s="1">
+        <v>25</v>
+      </c>
+      <c r="G471" s="1"/>
+      <c r="H471" t="s">
+        <v>956</v>
+      </c>
+    </row>
+    <row r="472" spans="1:8">
+      <c r="A472" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B472" t="s">
+        <v>957</v>
+      </c>
+      <c r="C472" s="1">
+        <v>143</v>
+      </c>
+      <c r="D472" s="1">
+        <v>243</v>
+      </c>
+      <c r="E472" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F472" s="1">
+        <v>30</v>
+      </c>
+      <c r="G472" s="1"/>
+      <c r="H472" t="s">
+        <v>958</v>
+      </c>
+    </row>
+    <row r="473" spans="1:8">
+      <c r="A473" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B473" t="s">
+        <v>959</v>
+      </c>
+      <c r="C473" s="1">
+        <v>143</v>
+      </c>
+      <c r="D473" s="1">
+        <v>243</v>
+      </c>
+      <c r="E473" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F473" s="1">
+        <v>32</v>
+      </c>
+      <c r="G473" s="1"/>
+      <c r="H473" t="s">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="474" spans="1:8">
+      <c r="A474" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B474" t="s">
+        <v>961</v>
+      </c>
+      <c r="C474" s="1">
+        <v>143</v>
+      </c>
+      <c r="D474" s="1">
+        <v>243</v>
+      </c>
+      <c r="E474" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F474" s="1">
+        <v>34</v>
+      </c>
+      <c r="G474" s="1"/>
+      <c r="H474" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="475" spans="1:8">
+      <c r="A475" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B475" t="s">
+        <v>963</v>
+      </c>
+      <c r="C475" s="1">
+        <v>143</v>
+      </c>
+      <c r="D475" s="1">
+        <v>243</v>
+      </c>
+      <c r="E475" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F475" s="1">
+        <v>35</v>
+      </c>
+      <c r="G475" s="1"/>
+      <c r="H475" t="s">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="476" spans="1:8">
+      <c r="A476" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B476" t="s">
+        <v>965</v>
+      </c>
+      <c r="C476" s="1">
+        <v>143</v>
+      </c>
+      <c r="D476" s="1">
+        <v>243</v>
+      </c>
+      <c r="E476" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F476" s="1">
+        <v>36</v>
+      </c>
+      <c r="G476" s="1"/>
+      <c r="H476" t="s">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="477" spans="1:8">
+      <c r="A477" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B477" t="s">
+        <v>967</v>
+      </c>
+      <c r="C477" s="1">
+        <v>143</v>
+      </c>
+      <c r="D477" s="1">
+        <v>243</v>
+      </c>
+      <c r="E477" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F477" s="1">
+        <v>37</v>
+      </c>
+      <c r="G477" s="1"/>
+      <c r="H477" t="s">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="478" spans="1:8">
+      <c r="A478" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B478" t="s">
+        <v>969</v>
+      </c>
+      <c r="C478" s="1">
+        <v>143</v>
+      </c>
+      <c r="D478" s="1">
+        <v>243</v>
+      </c>
+      <c r="E478" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F478" s="1">
+        <v>38</v>
+      </c>
+      <c r="G478" s="1"/>
+      <c r="H478" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="479" spans="1:8">
+      <c r="A479" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B479" t="s">
+        <v>971</v>
+      </c>
+      <c r="C479" s="1">
+        <v>143</v>
+      </c>
+      <c r="D479" s="1">
+        <v>243</v>
+      </c>
+      <c r="E479" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F479" s="1">
+        <v>39</v>
+      </c>
+      <c r="G479" s="1"/>
+      <c r="H479" t="s">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="480" spans="1:8">
+      <c r="A480" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B480" t="s">
+        <v>973</v>
+      </c>
+      <c r="C480" s="1">
+        <v>143</v>
+      </c>
+      <c r="D480" s="1">
+        <v>243</v>
+      </c>
+      <c r="E480" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F480" s="1">
+        <v>40</v>
+      </c>
+      <c r="G480" s="1"/>
+      <c r="H480" t="s">
+        <v>974</v>
+      </c>
+    </row>
+    <row r="481" spans="1:8">
+      <c r="A481" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B481" t="s">
+        <v>975</v>
+      </c>
+      <c r="C481" s="1">
+        <v>143</v>
+      </c>
+      <c r="D481" s="1">
+        <v>243</v>
+      </c>
+      <c r="E481" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F481" s="1">
+        <v>41</v>
+      </c>
+      <c r="G481" s="1"/>
+      <c r="H481" t="s">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="482" spans="1:8">
+      <c r="A482" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B482" t="s">
+        <v>977</v>
+      </c>
+      <c r="C482" s="1">
+        <v>143</v>
+      </c>
+      <c r="D482" s="1">
+        <v>243</v>
+      </c>
+      <c r="E482" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F482" s="1">
+        <v>42</v>
+      </c>
+      <c r="G482" s="1"/>
+      <c r="H482" t="s">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="483" spans="1:8">
+      <c r="A483" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B483" t="s">
+        <v>979</v>
+      </c>
+      <c r="C483" s="1">
+        <v>143</v>
+      </c>
+      <c r="D483" s="1">
+        <v>243</v>
+      </c>
+      <c r="E483" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F483" s="1">
+        <v>43</v>
+      </c>
+      <c r="G483" s="1"/>
+      <c r="H483" t="s">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="484" spans="1:8">
+      <c r="A484" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B484" t="s">
+        <v>981</v>
+      </c>
+      <c r="C484" s="1">
+        <v>143</v>
+      </c>
+      <c r="D484" s="1">
+        <v>243</v>
+      </c>
+      <c r="E484" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F484" s="1">
+        <v>44</v>
+      </c>
+      <c r="G484" s="1"/>
+      <c r="H484" t="s">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="485" spans="1:8">
+      <c r="A485" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B485" t="s">
+        <v>983</v>
+      </c>
+      <c r="C485" s="1">
+        <v>143</v>
+      </c>
+      <c r="D485" s="1">
+        <v>243</v>
+      </c>
+      <c r="E485" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F485" s="1">
+        <v>45</v>
+      </c>
+      <c r="G485" s="1"/>
+      <c r="H485" t="s">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="486" spans="1:8">
+      <c r="A486" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B486" t="s">
+        <v>985</v>
+      </c>
+      <c r="C486" s="1">
+        <v>143</v>
+      </c>
+      <c r="D486" s="1">
+        <v>243</v>
+      </c>
+      <c r="E486" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F486" s="1">
+        <v>46</v>
+      </c>
+      <c r="G486" s="1"/>
+      <c r="H486" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="487" spans="1:8">
+      <c r="A487" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B487" t="s">
+        <v>987</v>
+      </c>
+      <c r="C487" s="1">
+        <v>143</v>
+      </c>
+      <c r="D487" s="1">
+        <v>243</v>
+      </c>
+      <c r="E487" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F487" s="1">
+        <v>47</v>
+      </c>
+      <c r="G487" s="1"/>
+      <c r="H487" t="s">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="488" spans="1:8">
+      <c r="A488" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B488" t="s">
+        <v>989</v>
+      </c>
+      <c r="C488" s="1">
+        <v>143</v>
+      </c>
+      <c r="D488" s="1">
+        <v>243</v>
+      </c>
+      <c r="E488" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F488" s="1">
+        <v>48</v>
+      </c>
+      <c r="G488" s="1"/>
+      <c r="H488" t="s">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="489" spans="1:8">
+      <c r="A489" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B489" t="s">
+        <v>991</v>
+      </c>
+      <c r="C489" s="1">
+        <v>143</v>
+      </c>
+      <c r="D489" s="1">
+        <v>243</v>
+      </c>
+      <c r="E489" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F489" s="1">
+        <v>50</v>
+      </c>
+      <c r="G489" s="1"/>
+      <c r="H489" t="s">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="490" spans="1:8">
+      <c r="A490" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B490" t="s">
+        <v>993</v>
+      </c>
+      <c r="C490" s="1">
+        <v>143</v>
+      </c>
+      <c r="D490" s="1">
+        <v>243</v>
+      </c>
+      <c r="E490" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F490" s="1">
+        <v>52</v>
+      </c>
+      <c r="G490" s="1"/>
+      <c r="H490" t="s">
+        <v>994</v>
+      </c>
+    </row>
+    <row r="491" spans="1:8">
+      <c r="A491" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B491" t="s">
+        <v>995</v>
+      </c>
+      <c r="C491" s="1">
+        <v>143</v>
+      </c>
+      <c r="D491" s="1">
+        <v>243</v>
+      </c>
+      <c r="E491" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F491" s="1">
+        <v>53</v>
+      </c>
+      <c r="G491" s="1"/>
+      <c r="H491" t="s">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="492" spans="1:8">
+      <c r="A492" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B492" t="s">
+        <v>997</v>
+      </c>
+      <c r="C492" s="1">
+        <v>143</v>
+      </c>
+      <c r="D492" s="1">
+        <v>243</v>
+      </c>
+      <c r="E492" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F492" s="1">
+        <v>54</v>
+      </c>
+      <c r="G492" s="1"/>
+      <c r="H492" t="s">
+        <v>998</v>
+      </c>
+    </row>
+    <row r="493" spans="1:8">
+      <c r="A493" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B493" t="s">
+        <v>999</v>
+      </c>
+      <c r="C493" s="1">
+        <v>143</v>
+      </c>
+      <c r="D493" s="1">
+        <v>243</v>
+      </c>
+      <c r="E493" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F493" s="1">
+        <v>56</v>
+      </c>
+      <c r="G493" s="1"/>
+      <c r="H493" t="s">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="494" spans="1:8">
+      <c r="A494" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B494" t="s">
+        <v>1001</v>
+      </c>
+      <c r="C494" s="1">
+        <v>143</v>
+      </c>
+      <c r="D494" s="1">
+        <v>243</v>
+      </c>
+      <c r="E494" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F494" s="1">
+        <v>57</v>
+      </c>
+      <c r="G494" s="1"/>
+      <c r="H494" t="s">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="495" spans="1:8">
+      <c r="A495" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B495" t="s">
+        <v>1003</v>
+      </c>
+      <c r="C495" s="1">
+        <v>143</v>
+      </c>
+      <c r="D495" s="1">
+        <v>243</v>
+      </c>
+      <c r="E495" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F495" s="1">
+        <v>58</v>
+      </c>
+      <c r="G495" s="1"/>
+      <c r="H495" t="s">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="496" spans="1:8">
+      <c r="A496" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B496" t="s">
+        <v>1005</v>
+      </c>
+      <c r="C496" s="1">
+        <v>143</v>
+      </c>
+      <c r="D496" s="1">
+        <v>243</v>
+      </c>
+      <c r="E496" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F496" s="1">
+        <v>59</v>
+      </c>
+      <c r="G496" s="1"/>
+      <c r="H496" t="s">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="497" spans="1:8">
+      <c r="A497" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B497" t="s">
+        <v>1007</v>
+      </c>
+      <c r="C497" s="1">
+        <v>143</v>
+      </c>
+      <c r="D497" s="1">
+        <v>243</v>
+      </c>
+      <c r="E497" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F497" s="1">
+        <v>60</v>
+      </c>
+      <c r="G497" s="1"/>
+      <c r="H497" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="498" spans="1:8">
+      <c r="A498" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B498" t="s">
+        <v>1009</v>
+      </c>
+      <c r="C498" s="1">
+        <v>143</v>
+      </c>
+      <c r="D498" s="1">
+        <v>243</v>
+      </c>
+      <c r="E498" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F498" s="1">
+        <v>61</v>
+      </c>
+      <c r="G498" s="1"/>
+      <c r="H498" t="s">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="499" spans="1:8">
+      <c r="A499" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B499" t="s">
+        <v>1011</v>
+      </c>
+      <c r="C499" s="1">
+        <v>143</v>
+      </c>
+      <c r="D499" s="1">
+        <v>243</v>
+      </c>
+      <c r="E499" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F499" s="1">
+        <v>62</v>
+      </c>
+      <c r="G499" s="1"/>
+      <c r="H499" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="500" spans="1:8">
+      <c r="A500" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B500" t="s">
+        <v>1013</v>
+      </c>
+      <c r="C500" s="1">
+        <v>143</v>
+      </c>
+      <c r="D500" s="1">
+        <v>243</v>
+      </c>
+      <c r="E500" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F500" s="1">
+        <v>63</v>
+      </c>
+      <c r="G500" s="1"/>
+      <c r="H500" t="s">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="501" spans="1:8">
+      <c r="A501" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B501" t="s">
+        <v>1015</v>
+      </c>
+      <c r="C501" s="1">
+        <v>143</v>
+      </c>
+      <c r="D501" s="1">
+        <v>243</v>
+      </c>
+      <c r="E501" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F501" s="1">
+        <v>64</v>
+      </c>
+      <c r="G501" s="1"/>
+      <c r="H501" t="s">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="502" spans="1:8">
+      <c r="A502" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B502" t="s">
+        <v>1017</v>
+      </c>
+      <c r="C502" s="1">
+        <v>143</v>
+      </c>
+      <c r="D502" s="1">
+        <v>243</v>
+      </c>
+      <c r="E502" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F502" s="1">
+        <v>65</v>
+      </c>
+      <c r="G502" s="1"/>
+      <c r="H502" t="s">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="503" spans="1:8">
+      <c r="A503" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B503" t="s">
+        <v>1019</v>
+      </c>
+      <c r="C503" s="1">
+        <v>143</v>
+      </c>
+      <c r="D503" s="1">
+        <v>243</v>
+      </c>
+      <c r="E503" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F503" s="1">
+        <v>67</v>
+      </c>
+      <c r="G503" s="1"/>
+      <c r="H503" t="s">
+        <v>1020</v>
+      </c>
+    </row>
+    <row r="504" spans="1:8">
+      <c r="A504" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B504" t="s">
+        <v>1021</v>
+      </c>
+      <c r="C504" s="1">
+        <v>143</v>
+      </c>
+      <c r="D504" s="1">
+        <v>243</v>
+      </c>
+      <c r="E504" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F504" s="1">
+        <v>68</v>
+      </c>
+      <c r="G504" s="1"/>
+      <c r="H504" t="s">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="505" spans="1:8">
+      <c r="A505" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B505" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C505" s="1">
+        <v>143</v>
+      </c>
+      <c r="D505" s="1">
+        <v>243</v>
+      </c>
+      <c r="E505" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F505" s="1">
+        <v>69</v>
+      </c>
+      <c r="G505" s="1"/>
+      <c r="H505" t="s">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="506" spans="1:8">
+      <c r="A506" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B506" t="s">
+        <v>1025</v>
+      </c>
+      <c r="C506" s="1">
+        <v>143</v>
+      </c>
+      <c r="D506" s="1">
+        <v>243</v>
+      </c>
+      <c r="E506" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F506" s="1">
+        <v>70</v>
+      </c>
+      <c r="G506" s="1"/>
+      <c r="H506" t="s">
+        <v>1026</v>
+      </c>
+    </row>
+    <row r="507" spans="1:8">
+      <c r="A507" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B507" t="s">
+        <v>1027</v>
+      </c>
+      <c r="C507" s="1">
+        <v>143</v>
+      </c>
+      <c r="D507" s="1">
+        <v>243</v>
+      </c>
+      <c r="E507" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F507" s="1">
+        <v>71</v>
+      </c>
+      <c r="G507" s="1"/>
+      <c r="H507" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="508" spans="1:8">
+      <c r="A508" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B508" t="s">
+        <v>1029</v>
+      </c>
+      <c r="C508" s="1">
+        <v>143</v>
+      </c>
+      <c r="D508" s="1">
+        <v>243</v>
+      </c>
+      <c r="E508" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F508" s="1">
+        <v>72</v>
+      </c>
+      <c r="G508" s="1"/>
+      <c r="H508" t="s">
+        <v>1030</v>
+      </c>
+    </row>
+    <row r="509" spans="1:8">
+      <c r="A509" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B509" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C509" s="1">
+        <v>143</v>
+      </c>
+      <c r="D509" s="1">
+        <v>243</v>
+      </c>
+      <c r="E509" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F509" s="1">
+        <v>73</v>
+      </c>
+      <c r="G509" s="1"/>
+      <c r="H509" t="s">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="510" spans="1:8">
+      <c r="A510" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B510" t="s">
+        <v>1033</v>
+      </c>
+      <c r="C510" s="1">
+        <v>143</v>
+      </c>
+      <c r="D510" s="1">
+        <v>243</v>
+      </c>
+      <c r="E510" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F510" s="1">
+        <v>74</v>
+      </c>
+      <c r="G510" s="1"/>
+      <c r="H510" t="s">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="511" spans="1:8">
+      <c r="A511" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B511" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C511" s="1">
+        <v>143</v>
+      </c>
+      <c r="D511" s="1">
+        <v>243</v>
+      </c>
+      <c r="E511" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F511" s="1">
+        <v>75</v>
+      </c>
+      <c r="G511" s="1"/>
+      <c r="H511" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="512" spans="1:8">
+      <c r="A512" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B512" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C512" s="1">
+        <v>143</v>
+      </c>
+      <c r="D512" s="1">
+        <v>243</v>
+      </c>
+      <c r="E512" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F512" s="1">
+        <v>76</v>
+      </c>
+      <c r="G512" s="1"/>
+      <c r="H512" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="513" spans="1:8">
+      <c r="A513" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B513" t="s">
+        <v>1039</v>
+      </c>
+      <c r="C513" s="1">
+        <v>143</v>
+      </c>
+      <c r="D513" s="1">
+        <v>243</v>
+      </c>
+      <c r="E513" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F513" s="1">
+        <v>77</v>
+      </c>
+      <c r="G513" s="1"/>
+      <c r="H513" t="s">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="514" spans="1:8">
+      <c r="A514" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B514" t="s">
+        <v>1041</v>
+      </c>
+      <c r="C514" s="1">
+        <v>143</v>
+      </c>
+      <c r="D514" s="1">
+        <v>243</v>
+      </c>
+      <c r="E514" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F514" s="1">
+        <v>79</v>
+      </c>
+      <c r="G514" s="1"/>
+      <c r="H514" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="515" spans="1:8">
+      <c r="A515" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B515" t="s">
+        <v>1043</v>
+      </c>
+      <c r="C515" s="1">
+        <v>143</v>
+      </c>
+      <c r="D515" s="1">
+        <v>243</v>
+      </c>
+      <c r="E515" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F515" s="1">
+        <v>80</v>
+      </c>
+      <c r="G515" s="1"/>
+      <c r="H515" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="516" spans="1:8">
+      <c r="A516" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B516" t="s">
+        <v>1045</v>
+      </c>
+      <c r="C516" s="1">
+        <v>143</v>
+      </c>
+      <c r="D516" s="1">
+        <v>243</v>
+      </c>
+      <c r="E516" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F516" s="1">
+        <v>81</v>
+      </c>
+      <c r="G516" s="1"/>
+      <c r="H516" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="517" spans="1:8">
+      <c r="A517" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B517" t="s">
+        <v>1047</v>
+      </c>
+      <c r="C517" s="1">
+        <v>143</v>
+      </c>
+      <c r="D517" s="1">
+        <v>243</v>
+      </c>
+      <c r="E517" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F517" s="1">
+        <v>82</v>
+      </c>
+      <c r="G517" s="1"/>
+      <c r="H517" t="s">
+        <v>1048</v>
+      </c>
+    </row>
+    <row r="518" spans="1:8">
+      <c r="A518" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B518" t="s">
+        <v>1049</v>
+      </c>
+      <c r="C518" s="1">
+        <v>143</v>
+      </c>
+      <c r="D518" s="1">
+        <v>243</v>
+      </c>
+      <c r="E518" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F518" s="1">
+        <v>83</v>
+      </c>
+      <c r="G518" s="1"/>
+      <c r="H518" t="s">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="519" spans="1:8">
+      <c r="A519" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B519" t="s">
+        <v>1051</v>
+      </c>
+      <c r="C519" s="1">
+        <v>143</v>
+      </c>
+      <c r="D519" s="1">
+        <v>243</v>
+      </c>
+      <c r="E519" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F519" s="1">
+        <v>84</v>
+      </c>
+      <c r="G519" s="1"/>
+      <c r="H519" t="s">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="520" spans="1:8">
+      <c r="A520" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B520" t="s">
+        <v>1053</v>
+      </c>
+      <c r="C520" s="1">
+        <v>143</v>
+      </c>
+      <c r="D520" s="1">
+        <v>243</v>
+      </c>
+      <c r="E520" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F520" s="1">
+        <v>85</v>
+      </c>
+      <c r="G520" s="1"/>
+      <c r="H520" t="s">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="521" spans="1:8">
+      <c r="A521" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B521" t="s">
+        <v>1055</v>
+      </c>
+      <c r="C521" s="1">
+        <v>143</v>
+      </c>
+      <c r="D521" s="1">
+        <v>243</v>
+      </c>
+      <c r="E521" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F521" s="1">
+        <v>86</v>
+      </c>
+      <c r="G521" s="1"/>
+      <c r="H521" t="s">
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="522" spans="1:8">
+      <c r="A522" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B522" t="s">
+        <v>1057</v>
+      </c>
+      <c r="C522" s="1">
+        <v>143</v>
+      </c>
+      <c r="D522" s="1">
+        <v>243</v>
+      </c>
+      <c r="E522" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F522" s="1">
+        <v>87</v>
+      </c>
+      <c r="G522" s="1"/>
+      <c r="H522" t="s">
+        <v>1058</v>
+      </c>
+    </row>
+    <row r="523" spans="1:8">
+      <c r="A523" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B523" t="s">
+        <v>1059</v>
+      </c>
+      <c r="C523" s="1">
+        <v>143</v>
+      </c>
+      <c r="D523" s="1">
+        <v>243</v>
+      </c>
+      <c r="E523" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F523" s="1">
+        <v>88</v>
+      </c>
+      <c r="G523" s="1"/>
+      <c r="H523" t="s">
+        <v>1060</v>
+      </c>
+    </row>
+    <row r="524" spans="1:8">
+      <c r="A524" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B524" t="s">
+        <v>1061</v>
+      </c>
+      <c r="C524" s="1">
+        <v>143</v>
+      </c>
+      <c r="D524" s="1">
+        <v>243</v>
+      </c>
+      <c r="E524" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F524" s="1">
+        <v>89</v>
+      </c>
+      <c r="G524" s="1"/>
+      <c r="H524" t="s">
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="525" spans="1:8">
+      <c r="A525" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B525" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C525" s="1">
+        <v>143</v>
+      </c>
+      <c r="D525" s="1">
+        <v>243</v>
+      </c>
+      <c r="E525" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F525" s="1">
+        <v>90</v>
+      </c>
+      <c r="G525" s="1"/>
+      <c r="H525" t="s">
+        <v>1064</v>
+      </c>
+    </row>
+    <row r="526" spans="1:8">
+      <c r="A526" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B526" t="s">
+        <v>1065</v>
+      </c>
+      <c r="C526" s="1">
+        <v>143</v>
+      </c>
+      <c r="D526" s="1">
+        <v>243</v>
+      </c>
+      <c r="E526" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F526" s="1">
+        <v>91</v>
+      </c>
+      <c r="G526" s="1"/>
+      <c r="H526" t="s">
+        <v>1066</v>
+      </c>
+    </row>
+    <row r="527" spans="1:8">
+      <c r="A527" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B527" t="s">
+        <v>1067</v>
+      </c>
+      <c r="C527" s="1">
+        <v>143</v>
+      </c>
+      <c r="D527" s="1">
+        <v>243</v>
+      </c>
+      <c r="E527" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F527" s="1">
+        <v>92</v>
+      </c>
+      <c r="G527" s="1"/>
+      <c r="H527" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="528" spans="1:8">
+      <c r="A528" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B528" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C528" s="1">
+        <v>143</v>
+      </c>
+      <c r="D528" s="1">
+        <v>243</v>
+      </c>
+      <c r="E528" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F528" s="1">
+        <v>93</v>
+      </c>
+      <c r="G528" s="1"/>
+      <c r="H528" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="529" spans="1:8">
+      <c r="A529" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B529" t="s">
+        <v>1071</v>
+      </c>
+      <c r="C529" s="1">
+        <v>143</v>
+      </c>
+      <c r="D529" s="1">
+        <v>243</v>
+      </c>
+      <c r="E529" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F529" s="1">
+        <v>94</v>
+      </c>
+      <c r="G529" s="1"/>
+      <c r="H529" t="s">
+        <v>1072</v>
+      </c>
+    </row>
+    <row r="530" spans="1:8">
+      <c r="A530" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B530" t="s">
+        <v>1073</v>
+      </c>
+      <c r="C530" s="1">
+        <v>143</v>
+      </c>
+      <c r="D530" s="1">
+        <v>243</v>
+      </c>
+      <c r="E530" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F530" s="1">
+        <v>96</v>
+      </c>
+      <c r="G530" s="1"/>
+      <c r="H530" t="s">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="531" spans="1:8">
+      <c r="A531" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B531" t="s">
+        <v>1075</v>
+      </c>
+      <c r="C531" s="1">
+        <v>143</v>
+      </c>
+      <c r="D531" s="1">
+        <v>243</v>
+      </c>
+      <c r="E531" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F531" s="1">
+        <v>97</v>
+      </c>
+      <c r="G531" s="1"/>
+      <c r="H531" t="s">
+        <v>1076</v>
+      </c>
+    </row>
+    <row r="532" spans="1:8">
+      <c r="A532" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B532" t="s">
+        <v>1077</v>
+      </c>
+      <c r="C532" s="1">
+        <v>143</v>
+      </c>
+      <c r="D532" s="1">
+        <v>243</v>
+      </c>
+      <c r="E532" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F532" s="1">
+        <v>98</v>
+      </c>
+      <c r="G532" s="1"/>
+      <c r="H532" t="s">
+        <v>1078</v>
+      </c>
+    </row>
+    <row r="533" spans="1:8">
+      <c r="A533" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B533" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C533" s="1">
+        <v>143</v>
+      </c>
+      <c r="D533" s="1">
+        <v>243</v>
+      </c>
+      <c r="E533" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F533" s="1">
+        <v>100</v>
+      </c>
+      <c r="G533" s="1"/>
+      <c r="H533" t="s">
+        <v>1080</v>
+      </c>
+    </row>
+    <row r="534" spans="1:8">
+      <c r="A534" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B534" t="s">
+        <v>1081</v>
+      </c>
+      <c r="C534" s="1">
+        <v>143</v>
+      </c>
+      <c r="D534" s="1">
+        <v>243</v>
+      </c>
+      <c r="E534" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F534" s="1">
+        <v>101</v>
+      </c>
+      <c r="G534" s="1"/>
+      <c r="H534" t="s">
+        <v>1082</v>
+      </c>
+    </row>
+    <row r="535" spans="1:8">
+      <c r="A535" s="2"/>
+      <c r="C535" s="1"/>
+      <c r="D535" s="1"/>
+      <c r="E535" s="1"/>
+      <c r="F535" s="1"/>
+      <c r="G535" s="1"/>
     </row>
   </sheetData>
   <sheetProtection sheet="false" objects="false" scenarios="false" formatCells="false" formatColumns="false" formatRows="false" insertColumns="false" insertRows="false" insertHyperlinks="false" deleteColumns="false" deleteRows="false" selectLockedCells="false" sort="false" autoFilter="false" pivotTables="false" selectUnlockedCells="false"/>

--- a/data/raw/monthly-2026-10.xlsx
+++ b/data/raw/monthly-2026-10.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1083">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1158">
   <si>
     <t>วันที่</t>
   </si>
@@ -3264,6 +3264,231 @@
   </si>
   <si>
     <t>https://ratchakitcha.soc.go.th/documents/132334.pdf</t>
+  </si>
+  <si>
+    <t>07/10/2026</t>
+  </si>
+  <si>
+    <t>ประกาศสำนักนายกรัฐมนตรี เรื่อง แต่งตั้งเอกอัครราชทูตวิสามัญผู้มีอำนาจเต็มประจำสาธารณรัฐกาบูเวร์ดี [นางสาวนิภา  นิรันดร์นุต]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/134305.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศสำนักนายกรัฐมนตรี เรื่อง แต่งตั้งเอกอัครราชทูตวิสามัญผู้มีอำนาจเต็มประจำจอร์เจีย [นายจาตุรนต์  ไชยะคำ]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/134304.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศกระทรวงกลาโหม เรื่อง การรับสมัครทหารกองเกินหรือทหารกองหนุนเข้าทำหน้าที่ทหารกองประจำการเป็นการชั่วคราว (พลทหารอาสา)</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/133575.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศกระทรวงมหาดไทย เรื่อง แก้ไขเพิ่มเติมกฎกระทรวงให้ใช้บังคับผังเมืองรวมจังหวัดเชียงใหม่ พ.ศ. 2555 พ.ศ. 2569</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/134316.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศคณะกรรมการการแข่งขันทางการค้า เรื่อง หลักเกณฑ์การพิจารณาการเข้าซื้อสินทรัพย์หรือหุ้น เพื่อควบคุมนโยบายการบริหารธุรกิจ การอำนวยการ หรือการจัดการที่เป็นการรวมธุรกิจ (ฉบับที่ 2) พ.ศ. 2569</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132354.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศธนาคารแห่งประเทศไทย ที่ 44/2569 เรื่อง การบริหารจัดการความเสี่ยงร้านค้าสำหรับการรับชำระเงินด้วยวิธีการทางอิเล็กทรอนิกส์ (Merchant Fraud Management)</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/133250.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศธนาคารแห่งประเทศไทย ที่ 45/2569 เรื่อง หลักเกณฑ์ วิธีการ และเงื่อนไขการขออนุญาตการประกอบธุรกิจการให้บริการเครื่อง White-label Smart Machine</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/133584.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศธนาคารแห่งประเทศไทย ที่ 46/2569 เรื่อง หลักเกณฑ์ในการกำกับดูแลการประกอบธุรกิจการให้บริการเครื่อง White-label Smart Machine</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/133585.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศธนาคารแห่งประเทศไทย ที่ 47/2569 เรื่อง หลักเกณฑ์การรักษาความมั่นคงปลอดภัยของการให้บริการเครื่อง White-label Smart Machine</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/133586.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศธนาคารแห่งประเทศไทย ที่ 48/2569 เรื่อง การส่งรายงานข้อมูลเกี่ยวกับความเคลื่อนไหวทางการเงินหรือพฤติกรรมการใช้บริการทางการเงินหรือการทำธุรกรรมทางการเงินที่มีลักษณะผิดปกติสำหรับสถาบันการเงินเฉพาะกิจ ต่อธนาคารแห่งประเทศไทย</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/134155.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานควบคุมการแลกเปลี่ยนเงิน เรื่อง การกำหนดหลักเกณฑ์และวิธีปฏิบัติเกี่ยวกับการแลกเปลี่ยนเงิน (ฉบับที่ 38)</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/133572.pdf</t>
+  </si>
+  <si>
+    <t>กระทู้ถามของสมาชิกสภาผู้แทนราษฎร กระทู้ถามที่ 023 ร. เรื่อง การขอแยกพื้นที่บ้านขยับออกจากหมู่บ้านใหม่ ในเขตพื้นที่ตำบลปราสาท อำเภอห้วยทับ จังหวัดศรีสะเกษ [ของ นายอาสพลธ์ สรรณ์ไตรภพ สมาชิกสภาผู้แทนราษฎร พรรคภูมิใจไทย]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131648.pdf</t>
+  </si>
+  <si>
+    <t>กระทู้ถามของสมาชิกสภาผู้แทนราษฎร กระทู้ถามที่ 614 ร. เรื่อง ขอให้รัฐบาลเร่งรัดจัดสรรสวัสดิการและจัดทำประกันภัยกลุ่มเพื่อคุ้มครองความเสี่ยงภัยให้แก่ชุดรักษาความปลอดภัยหมู่บ้าน (ชรบ.) อาสาสมัครป้องกันภัยฝ่ายพลเรือน (อปพร.) และอาสาสมัครกู้ภัย [ของ นางสาวนวินดา สวัสดิ์เดชดี สมาชิกสภาผู้แทนราษฎร พรรคใหม่]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131658.pdf</t>
+  </si>
+  <si>
+    <t>กระทู้ถามของสมาชิกสภาผู้แทนราษฎร กระทู้ถามที่ 615 ร. เรื่อง ขอให้ดำเนินการและชี้แจงผลการสอบเรื่องห้องแชท “ช่วยน้ำเงินด้วย” ระหว่างอธิบดีกรมการปกครอง นายนฤชา โฆษาศิวิไลซ์ และปลัดจังหวัดภูเก็ต นายรุ่งเรือง ธิมาบุตร [ของ นายเฉลิมพงศ์ แสงดี สมาชิกสภาผู้แทนราษฎร พรรคประชาชน]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131659.pdf</t>
+  </si>
+  <si>
+    <t>กระทู้ถามของสมาชิกสภาผู้แทนราษฎร กระทู้ถามที่ 649 ร. เรื่อง การซ่อมบำรุงบ่อบาดาลของภาครัฐให้สามารถใช้งานได้อย่างต่อเนื่อง [ของ นางสาวบุญญาภา นาชัยเวียง ปุณณนิฏฐา สมาชิกสภาผู้แทนราษฎร พรรคภูมิใจไทย]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132199.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำพิพากษาให้จัดการทรัพย์มรดกจำเลย [คดีหมายเลขแดงที่ ล.8249/2569 ให้จัดการทรัพย์กองมรดกของ นายหรือพลฯยงยุทธ แซ่โง้ว โดยนายบดินทร์ บัวหลักเมือง ในฐานะทายาทโดยธรรม ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132500.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง พิทักษ์ทรัพย์เด็ดขาดและจัดการทรัพย์มรดก [คดีหมายเลขแดงที่ ล.8276/2569 ให้พิทักษ์ทรัพย์ของ บริษัทคอนเทนเนอร์ เน็กซัส ซัพพลาย จํากัด หรือบริษัทคอนเทนเนอร์ ซัพพลาย (2000) จํากัด ลูกหนี้ที่ 1 และพิพากษาให้จัดการทรัพย์กองมรดกของ นายบวรชัย วิทยนคร โดยนางณหทัย ครอลอส, นางสาวนันทาศิริ วิทยนคร และนายอภิมุข วิทยนคร ในฐานะทายาทโดยธรรม ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132515.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง พิทักษ์ทรัพย์เด็ดขาดและจัดการทรัพย์มรดก [คดีหมายเลขแดงที่ ล.8342/2569 ให้พิทักษ์ทรัพย์ของ นางสาวจักราพร บินอารี ลูกหนี้ที่ 2 และพิพากษาให้จัดการทรัพย์กองมรดกของ นายยงยุทธ สุขีเกตุ ผโดยนางสาวจักราพร บินอารี ในฐานะทายาทโดยธรรม ลูกหนี้ทีม 1]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132516.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง พิทักษ์ทรัพย์เด็ดขาดและจัดการทรัพย์มรดก [คดีหมายเลขแดงที่ ล.8343/2569  ให้พิทักษ์ทรัพย์ของ นายวรวิช พึ่งร่มฉัตร ลูกหนี้ที่ 1 และพิพากษาให้จัดการทรัพย์กองมรดกของ นายมานพ น้อยชมภู โดยนางสมพร น้อยชมภู ในฐานะทายาทโดยธรรม ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132524.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.E1334/2569 บริษัทเอดี ฮีโร่ ชไนเดอร์ (ประเทศไทย) จำกัด ลูกหนี้ที่ 1, นายกฤษณ์หรือรัชกฤตหรือฐณกฤษ ดิษยวิวัชรวงศ์หรือถาวรธนิตกุลหรือวงศ์ดิษยบุตร ลูกหนี้ที่ 2 และนางเบญญาภา ถาวรธนิตกุล ลูกหนี้ที่ 3]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132509.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.E1422/2569 นางอารีย์ ชูนาค ลูกหนี้ที่ 1 และนายหรือดาบตำรวจสมโชติ รักษ์ทอง ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132465.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.E1458/2569 นายหนุ่มทุ่งโพนทอง ทุ่งโพนทอง ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132534.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.E1465/2569 นายปรีชา พรหมลิ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132471.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.7797/2569 นายธรรมรัตน์ เขียวแก้ว หรือนายธรรมะรัศมิ์ เขียวแก้ว ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132490.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8115/2569 ร้อยตรีหรือนายโชคชัย พวงดอกไม้ ลูกหนี้ที่ 1 และสิบเอกหรือนายชานนท์ จำปารัตน์ ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132467.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8231/2569 บริษัทภวัตโชคชัยการโยธา จำกัด ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132511.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8232/2569 ห้างหุ้นส่วนจำกัด ส. กิจมั่นคงก่อสร้าง ลูกหนี้ที่ 1 และนายมานพ สะหะมาน ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132519.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8233/2569 บริษัทเน็ตเพลย์ จำกัด ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132501.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8242/2569 นางสาวภคภัค หิรัณยรัศมี ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132518.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8243/2569 นางนงเยาว์ ทองคำ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132480.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8244/2569 นายวสันต์ แสงเหลา ลูกหนี้ที่ 1]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132510.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8245/2569 นายธีรศักดิ์ ดีรักษา ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132463.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8246/2569 นางสาวณัฐชานันท์ ศรีจัตุรัสหรืออินคงแสนสุข ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132499.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8247/2569 นางสาวนฤมล คงเพชรศักดิ์ ลูกหนี้ที่ 1 และนางสมยศ คงเพ็ชรศักดิ์ ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132464.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8248/2569 นายศักดิ์ศรี นรสาร ลูกหนี้ที่ 1 และนางสาวรชยาหรือศิวะพร เจริญรัมย์ ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132526.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8252/2569 นายธนา สาธร ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132502.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8253/2569 นายอำนาจ หิรัญงาม ลูกหนี้ที่ 1 และนางสำเนียง หิรัญงาม ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132512.pdf</t>
   </si>
 </sst>
 </file>
@@ -3610,7 +3835,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:H535"/>
+  <dimension ref="A1:H572"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="12.02" customWidth="true" style="0"/>
@@ -16442,12 +16667,900 @@
       </c>
     </row>
     <row r="535" spans="1:8">
-      <c r="A535" s="2"/>
-      <c r="C535" s="1"/>
-      <c r="D535" s="1"/>
-      <c r="E535" s="1"/>
-      <c r="F535" s="1"/>
+      <c r="A535" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B535" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C535" s="1">
+        <v>143</v>
+      </c>
+      <c r="D535" s="1">
+        <v>244</v>
+      </c>
+      <c r="E535" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F535" s="1">
+        <v>1</v>
+      </c>
       <c r="G535" s="1"/>
+      <c r="H535" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="536" spans="1:8">
+      <c r="A536" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B536" t="s">
+        <v>1086</v>
+      </c>
+      <c r="C536" s="1">
+        <v>143</v>
+      </c>
+      <c r="D536" s="1">
+        <v>244</v>
+      </c>
+      <c r="E536" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F536" s="1">
+        <v>2</v>
+      </c>
+      <c r="G536" s="1"/>
+      <c r="H536" t="s">
+        <v>1087</v>
+      </c>
+    </row>
+    <row r="537" spans="1:8">
+      <c r="A537" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B537" t="s">
+        <v>1088</v>
+      </c>
+      <c r="C537" s="1">
+        <v>143</v>
+      </c>
+      <c r="D537" s="1">
+        <v>244</v>
+      </c>
+      <c r="E537" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F537" s="1">
+        <v>3</v>
+      </c>
+      <c r="G537" s="1"/>
+      <c r="H537" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="538" spans="1:8">
+      <c r="A538" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B538" t="s">
+        <v>1090</v>
+      </c>
+      <c r="C538" s="1">
+        <v>143</v>
+      </c>
+      <c r="D538" s="1">
+        <v>244</v>
+      </c>
+      <c r="E538" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F538" s="1">
+        <v>4</v>
+      </c>
+      <c r="G538" s="1"/>
+      <c r="H538" t="s">
+        <v>1091</v>
+      </c>
+    </row>
+    <row r="539" spans="1:8">
+      <c r="A539" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B539" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C539" s="1">
+        <v>143</v>
+      </c>
+      <c r="D539" s="1">
+        <v>244</v>
+      </c>
+      <c r="E539" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F539" s="1">
+        <v>5</v>
+      </c>
+      <c r="G539" s="1"/>
+      <c r="H539" t="s">
+        <v>1093</v>
+      </c>
+    </row>
+    <row r="540" spans="1:8">
+      <c r="A540" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B540" t="s">
+        <v>1094</v>
+      </c>
+      <c r="C540" s="1">
+        <v>143</v>
+      </c>
+      <c r="D540" s="1">
+        <v>244</v>
+      </c>
+      <c r="E540" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F540" s="1">
+        <v>6</v>
+      </c>
+      <c r="G540" s="1"/>
+      <c r="H540" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="541" spans="1:8">
+      <c r="A541" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B541" t="s">
+        <v>1096</v>
+      </c>
+      <c r="C541" s="1">
+        <v>143</v>
+      </c>
+      <c r="D541" s="1">
+        <v>244</v>
+      </c>
+      <c r="E541" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F541" s="1">
+        <v>20</v>
+      </c>
+      <c r="G541" s="1"/>
+      <c r="H541" t="s">
+        <v>1097</v>
+      </c>
+    </row>
+    <row r="542" spans="1:8">
+      <c r="A542" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B542" t="s">
+        <v>1098</v>
+      </c>
+      <c r="C542" s="1">
+        <v>143</v>
+      </c>
+      <c r="D542" s="1">
+        <v>244</v>
+      </c>
+      <c r="E542" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F542" s="1">
+        <v>29</v>
+      </c>
+      <c r="G542" s="1"/>
+      <c r="H542" t="s">
+        <v>1099</v>
+      </c>
+    </row>
+    <row r="543" spans="1:8">
+      <c r="A543" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B543" t="s">
+        <v>1100</v>
+      </c>
+      <c r="C543" s="1">
+        <v>143</v>
+      </c>
+      <c r="D543" s="1">
+        <v>244</v>
+      </c>
+      <c r="E543" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F543" s="1">
+        <v>40</v>
+      </c>
+      <c r="G543" s="1"/>
+      <c r="H543" t="s">
+        <v>1101</v>
+      </c>
+    </row>
+    <row r="544" spans="1:8">
+      <c r="A544" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B544" t="s">
+        <v>1102</v>
+      </c>
+      <c r="C544" s="1">
+        <v>143</v>
+      </c>
+      <c r="D544" s="1">
+        <v>244</v>
+      </c>
+      <c r="E544" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F544" s="1">
+        <v>46</v>
+      </c>
+      <c r="G544" s="1"/>
+      <c r="H544" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="545" spans="1:8">
+      <c r="A545" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B545" t="s">
+        <v>1104</v>
+      </c>
+      <c r="C545" s="1">
+        <v>143</v>
+      </c>
+      <c r="D545" s="1">
+        <v>244</v>
+      </c>
+      <c r="E545" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F545" s="1">
+        <v>49</v>
+      </c>
+      <c r="G545" s="1"/>
+      <c r="H545" t="s">
+        <v>1105</v>
+      </c>
+    </row>
+    <row r="546" spans="1:8">
+      <c r="A546" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B546" t="s">
+        <v>1106</v>
+      </c>
+      <c r="C546" s="1">
+        <v>143</v>
+      </c>
+      <c r="D546" s="1">
+        <v>244</v>
+      </c>
+      <c r="E546" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F546" s="1">
+        <v>55</v>
+      </c>
+      <c r="G546" s="1"/>
+      <c r="H546" t="s">
+        <v>1107</v>
+      </c>
+    </row>
+    <row r="547" spans="1:8">
+      <c r="A547" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B547" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C547" s="1">
+        <v>143</v>
+      </c>
+      <c r="D547" s="1">
+        <v>244</v>
+      </c>
+      <c r="E547" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F547" s="1">
+        <v>60</v>
+      </c>
+      <c r="G547" s="1"/>
+      <c r="H547" t="s">
+        <v>1109</v>
+      </c>
+    </row>
+    <row r="548" spans="1:8">
+      <c r="A548" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B548" t="s">
+        <v>1110</v>
+      </c>
+      <c r="C548" s="1">
+        <v>143</v>
+      </c>
+      <c r="D548" s="1">
+        <v>244</v>
+      </c>
+      <c r="E548" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F548" s="1">
+        <v>70</v>
+      </c>
+      <c r="G548" s="1"/>
+      <c r="H548" t="s">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="549" spans="1:8">
+      <c r="A549" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B549" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C549" s="1">
+        <v>143</v>
+      </c>
+      <c r="D549" s="1">
+        <v>244</v>
+      </c>
+      <c r="E549" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F549" s="1">
+        <v>72</v>
+      </c>
+      <c r="G549" s="1"/>
+      <c r="H549" t="s">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="550" spans="1:8">
+      <c r="A550" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B550" t="s">
+        <v>1114</v>
+      </c>
+      <c r="C550" s="1">
+        <v>143</v>
+      </c>
+      <c r="D550" s="1">
+        <v>244</v>
+      </c>
+      <c r="E550" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F550" s="1">
+        <v>76</v>
+      </c>
+      <c r="G550" s="1"/>
+      <c r="H550" t="s">
+        <v>1115</v>
+      </c>
+    </row>
+    <row r="551" spans="1:8">
+      <c r="A551" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B551" t="s">
+        <v>1116</v>
+      </c>
+      <c r="C551" s="1">
+        <v>143</v>
+      </c>
+      <c r="D551" s="1">
+        <v>244</v>
+      </c>
+      <c r="E551" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F551" s="1">
+        <v>77</v>
+      </c>
+      <c r="G551" s="1"/>
+      <c r="H551" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="552" spans="1:8">
+      <c r="A552" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B552" t="s">
+        <v>1118</v>
+      </c>
+      <c r="C552" s="1">
+        <v>143</v>
+      </c>
+      <c r="D552" s="1">
+        <v>244</v>
+      </c>
+      <c r="E552" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F552" s="1">
+        <v>79</v>
+      </c>
+      <c r="G552" s="1"/>
+      <c r="H552" t="s">
+        <v>1119</v>
+      </c>
+    </row>
+    <row r="553" spans="1:8">
+      <c r="A553" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B553" t="s">
+        <v>1120</v>
+      </c>
+      <c r="C553" s="1">
+        <v>143</v>
+      </c>
+      <c r="D553" s="1">
+        <v>244</v>
+      </c>
+      <c r="E553" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F553" s="1">
+        <v>81</v>
+      </c>
+      <c r="G553" s="1"/>
+      <c r="H553" t="s">
+        <v>1121</v>
+      </c>
+    </row>
+    <row r="554" spans="1:8">
+      <c r="A554" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B554" t="s">
+        <v>1122</v>
+      </c>
+      <c r="C554" s="1">
+        <v>143</v>
+      </c>
+      <c r="D554" s="1">
+        <v>244</v>
+      </c>
+      <c r="E554" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F554" s="1">
+        <v>83</v>
+      </c>
+      <c r="G554" s="1"/>
+      <c r="H554" t="s">
+        <v>1123</v>
+      </c>
+    </row>
+    <row r="555" spans="1:8">
+      <c r="A555" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B555" t="s">
+        <v>1124</v>
+      </c>
+      <c r="C555" s="1">
+        <v>143</v>
+      </c>
+      <c r="D555" s="1">
+        <v>244</v>
+      </c>
+      <c r="E555" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F555" s="1">
+        <v>85</v>
+      </c>
+      <c r="G555" s="1"/>
+      <c r="H555" t="s">
+        <v>1125</v>
+      </c>
+    </row>
+    <row r="556" spans="1:8">
+      <c r="A556" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B556" t="s">
+        <v>1126</v>
+      </c>
+      <c r="C556" s="1">
+        <v>143</v>
+      </c>
+      <c r="D556" s="1">
+        <v>244</v>
+      </c>
+      <c r="E556" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F556" s="1">
+        <v>86</v>
+      </c>
+      <c r="G556" s="1"/>
+      <c r="H556" t="s">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="557" spans="1:8">
+      <c r="A557" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B557" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C557" s="1">
+        <v>143</v>
+      </c>
+      <c r="D557" s="1">
+        <v>244</v>
+      </c>
+      <c r="E557" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F557" s="1">
+        <v>87</v>
+      </c>
+      <c r="G557" s="1"/>
+      <c r="H557" t="s">
+        <v>1129</v>
+      </c>
+    </row>
+    <row r="558" spans="1:8">
+      <c r="A558" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B558" t="s">
+        <v>1130</v>
+      </c>
+      <c r="C558" s="1">
+        <v>143</v>
+      </c>
+      <c r="D558" s="1">
+        <v>244</v>
+      </c>
+      <c r="E558" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F558" s="1">
+        <v>88</v>
+      </c>
+      <c r="G558" s="1"/>
+      <c r="H558" t="s">
+        <v>1131</v>
+      </c>
+    </row>
+    <row r="559" spans="1:8">
+      <c r="A559" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B559" t="s">
+        <v>1132</v>
+      </c>
+      <c r="C559" s="1">
+        <v>143</v>
+      </c>
+      <c r="D559" s="1">
+        <v>244</v>
+      </c>
+      <c r="E559" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F559" s="1">
+        <v>89</v>
+      </c>
+      <c r="G559" s="1"/>
+      <c r="H559" t="s">
+        <v>1133</v>
+      </c>
+    </row>
+    <row r="560" spans="1:8">
+      <c r="A560" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B560" t="s">
+        <v>1134</v>
+      </c>
+      <c r="C560" s="1">
+        <v>143</v>
+      </c>
+      <c r="D560" s="1">
+        <v>244</v>
+      </c>
+      <c r="E560" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F560" s="1">
+        <v>90</v>
+      </c>
+      <c r="G560" s="1"/>
+      <c r="H560" t="s">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="561" spans="1:8">
+      <c r="A561" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B561" t="s">
+        <v>1136</v>
+      </c>
+      <c r="C561" s="1">
+        <v>143</v>
+      </c>
+      <c r="D561" s="1">
+        <v>244</v>
+      </c>
+      <c r="E561" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F561" s="1">
+        <v>91</v>
+      </c>
+      <c r="G561" s="1"/>
+      <c r="H561" t="s">
+        <v>1137</v>
+      </c>
+    </row>
+    <row r="562" spans="1:8">
+      <c r="A562" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B562" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C562" s="1">
+        <v>143</v>
+      </c>
+      <c r="D562" s="1">
+        <v>244</v>
+      </c>
+      <c r="E562" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F562" s="1">
+        <v>92</v>
+      </c>
+      <c r="G562" s="1"/>
+      <c r="H562" t="s">
+        <v>1139</v>
+      </c>
+    </row>
+    <row r="563" spans="1:8">
+      <c r="A563" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B563" t="s">
+        <v>1140</v>
+      </c>
+      <c r="C563" s="1">
+        <v>143</v>
+      </c>
+      <c r="D563" s="1">
+        <v>244</v>
+      </c>
+      <c r="E563" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F563" s="1">
+        <v>93</v>
+      </c>
+      <c r="G563" s="1"/>
+      <c r="H563" t="s">
+        <v>1141</v>
+      </c>
+    </row>
+    <row r="564" spans="1:8">
+      <c r="A564" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B564" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C564" s="1">
+        <v>143</v>
+      </c>
+      <c r="D564" s="1">
+        <v>244</v>
+      </c>
+      <c r="E564" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F564" s="1">
+        <v>94</v>
+      </c>
+      <c r="G564" s="1"/>
+      <c r="H564" t="s">
+        <v>1143</v>
+      </c>
+    </row>
+    <row r="565" spans="1:8">
+      <c r="A565" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B565" t="s">
+        <v>1144</v>
+      </c>
+      <c r="C565" s="1">
+        <v>143</v>
+      </c>
+      <c r="D565" s="1">
+        <v>244</v>
+      </c>
+      <c r="E565" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F565" s="1">
+        <v>95</v>
+      </c>
+      <c r="G565" s="1"/>
+      <c r="H565" t="s">
+        <v>1145</v>
+      </c>
+    </row>
+    <row r="566" spans="1:8">
+      <c r="A566" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B566" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C566" s="1">
+        <v>143</v>
+      </c>
+      <c r="D566" s="1">
+        <v>244</v>
+      </c>
+      <c r="E566" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F566" s="1">
+        <v>96</v>
+      </c>
+      <c r="G566" s="1"/>
+      <c r="H566" t="s">
+        <v>1147</v>
+      </c>
+    </row>
+    <row r="567" spans="1:8">
+      <c r="A567" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B567" t="s">
+        <v>1148</v>
+      </c>
+      <c r="C567" s="1">
+        <v>143</v>
+      </c>
+      <c r="D567" s="1">
+        <v>244</v>
+      </c>
+      <c r="E567" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F567" s="1">
+        <v>97</v>
+      </c>
+      <c r="G567" s="1"/>
+      <c r="H567" t="s">
+        <v>1149</v>
+      </c>
+    </row>
+    <row r="568" spans="1:8">
+      <c r="A568" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B568" t="s">
+        <v>1150</v>
+      </c>
+      <c r="C568" s="1">
+        <v>143</v>
+      </c>
+      <c r="D568" s="1">
+        <v>244</v>
+      </c>
+      <c r="E568" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F568" s="1">
+        <v>98</v>
+      </c>
+      <c r="G568" s="1"/>
+      <c r="H568" t="s">
+        <v>1151</v>
+      </c>
+    </row>
+    <row r="569" spans="1:8">
+      <c r="A569" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B569" t="s">
+        <v>1152</v>
+      </c>
+      <c r="C569" s="1">
+        <v>143</v>
+      </c>
+      <c r="D569" s="1">
+        <v>244</v>
+      </c>
+      <c r="E569" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F569" s="1">
+        <v>99</v>
+      </c>
+      <c r="G569" s="1"/>
+      <c r="H569" t="s">
+        <v>1153</v>
+      </c>
+    </row>
+    <row r="570" spans="1:8">
+      <c r="A570" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B570" t="s">
+        <v>1154</v>
+      </c>
+      <c r="C570" s="1">
+        <v>143</v>
+      </c>
+      <c r="D570" s="1">
+        <v>244</v>
+      </c>
+      <c r="E570" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F570" s="1">
+        <v>100</v>
+      </c>
+      <c r="G570" s="1"/>
+      <c r="H570" t="s">
+        <v>1155</v>
+      </c>
+    </row>
+    <row r="571" spans="1:8">
+      <c r="A571" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B571" t="s">
+        <v>1156</v>
+      </c>
+      <c r="C571" s="1">
+        <v>143</v>
+      </c>
+      <c r="D571" s="1">
+        <v>244</v>
+      </c>
+      <c r="E571" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F571" s="1">
+        <v>101</v>
+      </c>
+      <c r="G571" s="1"/>
+      <c r="H571" t="s">
+        <v>1157</v>
+      </c>
+    </row>
+    <row r="572" spans="1:8">
+      <c r="A572" s="2"/>
+      <c r="C572" s="1"/>
+      <c r="D572" s="1"/>
+      <c r="E572" s="1"/>
+      <c r="F572" s="1"/>
+      <c r="G572" s="1"/>
     </row>
   </sheetData>
   <sheetProtection sheet="false" objects="false" scenarios="false" formatCells="false" formatColumns="false" formatRows="false" insertColumns="false" insertRows="false" insertHyperlinks="false" deleteColumns="false" deleteRows="false" selectLockedCells="false" sort="false" autoFilter="false" pivotTables="false" selectUnlockedCells="false"/>

--- a/data/raw/monthly-2026-10.xlsx
+++ b/data/raw/monthly-2026-10.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1640">
   <si>
     <t>วันที่</t>
   </si>
@@ -3269,6 +3269,1266 @@
     <t>07/10/2026</t>
   </si>
   <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำพิพากษาให้จัดการทรัพย์มรดกของลูกหนี้ที่ ๑ [คดีหมายเลขแดงที่ ล.4716/2561 นายสมมิตร เสาวะระ ลูกหนี้ที่ 1]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131497.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คําพิพากษาให้ลูกหนี้ล้มละลาย [คดีหมายเลขแดงที่ ล.5366/2560 บริษัท แสงสิริ เอ็นเตอร์ไพร้ซ์ จำกัด ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131480.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คําพิพากษาให้ลูกหนี้ล้มละลาย [คดีหมายเลขแดงที่ ล.5301/2563 นายเรวัฒน์ เพชรทอง ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131714.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คําพิพากษาให้ลูกหนี้ล้มละลาย [คดีหมายเลขแดงที่ ล.2556/2564 บริษัท โอเมก้า พีอา โปรเจค จำกัด ลูกหนี้ที่ 1, นายพสคร ปัญญะสังข์ ลูกหนี้ที่ 2, นางสาวนิชาภา ดำรงค์ หรือ นางนิชาภา ปัญญะสังข์ ลูกหนี้ที่ 3]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131478.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คําพิพากษาให้ลูกหนี้ล้มละลาย [คดีหมายเลขแดงที่ ล.5392/2565 นางสุมาลี ทองใหญ่ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131707.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คําพิพากษาให้ลูกหนี้ล้มละลาย [คดีหมายเลขแดงที่ ล.6133/2565 บริษัท ชัญธิชา ทรานสปอร์ต จำกัด ลูกหนี้ที่ 1, นางพนิต พลเยี่ยม ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131583.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คําพิพากษาให้ลูกหนี้ล้มละลาย [คดีหมายเลขแดงที่ ล.6741/2567 บริษัทแอลทียู ออฟชอร์ จำกัด ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131684.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คําพิพากษาให้ลูกหนี้ล้มละลาย [คดีหมายเลขแดงที่ ล.7695/2567 นายภาคภูมิ พงษ์อ้อ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131148.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คําพิพากษาให้ลูกหนี้ล้มละลาย [คดีหมายเลขแดงที่ ล.8549/2567 ห้างหุ้นส่วนจำกัด กายธรรม ยูนิฟอร์ม ดีไซน์ โดยนายจิรภัทร หรือธนโชค หรือ อชิรณัญช์ ล้อมธนากวิน หรือไผ่ล้อมวงศ์ ผู้ชำระบัญชี ลูกหนี้ที่ 1 นายจิรภัทร หรือธนโชค หรือ อชิรณัญช์ ล้อมธนากวิน หรือไผ่ล้อมวงศ์ ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131697.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คําพิพากษาให้ลูกหนี้ล้มละลาย [คดีหมายเลขแดงที่ ล.9583/2567 บริษัทไมร่า เทคโนโลยี จำกัด ลูกหนี้ที่ 1, นายชัยเมศร์ สิริจริยาพรรณ หรือนายสุเมธ ชัยกิจพัฒนา ลูกหนี้ที่ 2 และบริษัทพี.ซี.เบสท์บาย จำกัด ลูกหนี้ที่ 3]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131448.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คําพิพากษาให้ลูกหนี้ล้มละลาย [คดีหมายเลขแดงที่ ล.9757/2567 บริษัทเบญทอยส์ กรุ๊ป จำกัด ลูกหนี้ที่ 1, นายสมหวัง หรือพีระวิทย์ มีสมบูรณ์ ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131373.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คําพิพากษาให้ลูกหนี้ล้มละลาย [คดีหมายเลขแดงที่ ล.132/2568 นางสาวชนากานต์ หรือปภาดา ทับทิม ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131545.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คําพิพากษาให้ลูกหนี้ล้มละลาย [คดีหมายเลขแดงที่ ล.427/2568 นางสาวพีรญา หรือผกาแก้ว จิตรักษ์โข หรือจิตรักษ์ ลูกหนี้ที่ 1, นายเชาวน์วริศร์ หรือสุรศักดิ์ จิตรักษ์โข หรือจิตรักษ์ ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131457.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คําพิพากษาให้ลูกหนี้ล้มละลาย [คดีหมายเลขแดงที่ ล.1246/2568 นางสาวภาวิณี สรสิทธิ์ ลูกหนี้ที่ 1]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131455.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คําพิพากษาให้ลูกหนี้ล้มละลาย [คดีหมายเลขแดงที่ ล.1810/2568 นายสิรภัทร รุ่งเรือง ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131712.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คําพิพากษาให้ลูกหนี้ล้มละลาย [คดีหมายเลขแดงที่ ล.2028/2568 นายมรกต ธูสรานนท์ ลูกหนี้ที่ 1, นายนักรบเทียนเกษม หรือชินบัญชร สรโยธิน ลูกหนี้ที่ 2, นายอนุวัติ สามเสน ลูกหนี้ที่ 3, นายทนุธรรม รุ่งรัศมี ลูกหนี้ที่ 4, นายพงศ์พันธุ์ แผ่กระโทก ลูกหนี้ที่ 5 และนางสาวสุพรรณี นาคสุทธิ์ ลูกหนี้ที่ 6]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131333.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คําพิพากษาให้ลูกหนี้ล้มละลาย [คดีหมายเลขแดงที่ ล.2229/2568 นายอภิรักษ์ หรือธราพิชญ์ แก้วระยับ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131682.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คําพิพากษาให้ลูกหนี้ล้มละลาย [คดีหมายเลขแดงที่ ล.3731/2568 นางสาวฐนิตนันท์ เสรี ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131554.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คําพิพากษาให้ลูกหนี้ล้มละลาย [คดีหมายเลขแดงที่ ล.3781/2568 นางสายฝน เพ็ชรขำ ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131347.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คําพิพากษาให้ลูกหนี้ล้มละลาย [คดีหมายเลขแดงที่ ล.4591/2568 นายน้อย ทองคลอด ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131692.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คําพิพากษาให้ลูกหนี้ล้มละลาย [คดีหมายเลขแดงที่ ล.4673/2568 นายอิทธิกร หรืออํานาจ เบิกบาล ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131549.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คําพิพากษาให้ลูกหนี้ล้มละลาย [คดีหมายเลขแดงที่ ล.6009/2568 บริษัทวิน วิน เวิร์คส ซัพพลายเออร์ จำกัด โดยนางสาวสุภัทรา ธรรมเจริญ นางสมศรี ก้อนทอง และนางสาววรรณสร ธรรมเจริญ ในฐานะผู้ชำระบัญชี ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/130619.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คําพิพากษาให้ลูกหนี้ล้มละลาย [คดีหมายเลขแดงที่ ล.6443/2568 นางสาวสมัชญาหรือวันนา คำจันทะราช ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/130612.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คําพิพากษาให้ลูกหนี้ล้มละลาย [คดีหมายเลขแดงที่ ล.6559/2568 นายสายยนต์ ชาบุญมา ลูกหนี้ที่ 1]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131482.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คําพิพากษาให้ลูกหนี้ล้มละลาย [คดีหมายเลขแดงที่ ล.6559/2568 นางเดือนเพ็ญ ชาบุญมา ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132033.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คําพิพากษาให้ลูกหนี้ล้มละลาย [คดีหมายเลขแดงที่ ล.6593/2568 บริษัท ซี พี เค เฮ้าส์ซิ่ง โปรดัคท์ จำกัด ลูกหนี้ที่ 1]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131504.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คําพิพากษาให้ลูกหนี้ล้มละลาย [คดีหมายเลขแดงที่ ล.6598/2568 นางสาวอรทัย จันทร์อินทร์ หรืออุปัชฌาย์ ลูกหนี้ที่ 1]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131483.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คําพิพากษาให้ลูกหนี้ล้มละลาย [คดีหมายเลขแดงที่ ล.6881/2568 นางสาวจิดาภา ฐานธัญญา ลูกหนี้ที่ 1 และนายสกล จันทะศรี ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131445.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คําพิพากษาให้ลูกหนี้ล้มละลาย [คดีหมายเลขแดงที่ ล.7118/2568 นางสาวทองกวาว เจ๊กมา ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131568.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คําพิพากษาให้ลูกหนี้ล้มละลาย [คดีหมายเลขแดงที่ ล.8067/2568 นางยุพิน ธิตินันทน์ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131556.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คําพิพากษาให้ลูกหนี้ล้มละลาย [คดีหมายเลขแดงที่ ล.8338/2568 นายกฤษธาดา หรืออสมา ทองลือ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131468.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คําพิพากษาให้ลูกหนี้ล้มละลาย [คดีหมายเลขแดงที่ ล.8550/2568 นางสาวกิ่งดาว ละหานนอก ลูกหนี้ที่ 1, นายศรายุทธ ละหานนอก ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131715.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คําพิพากษาให้ลูกหนี้ล้มละลาย [คดีหมายเลขแดงที่ ล.8576/2568 นายอนุวัฒน์ สมตน ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131369.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คําพิพากษาให้ลูกหนี้ล้มละลาย [คดีหมายเลขแดงที่ ล.8674/2568 นางสาวนิลวรรณ แซ่เติ๋น ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131370.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คําพิพากษาให้ลูกหนี้ล้มละลาย [คดีหมายเลขแดงที่ ล.8694/2568 บริษัท เอทีดี2003 จำกัด ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131688.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คําพิพากษาให้ลูกหนี้ล้มละลาย [คดีหมายเลขแดงที่ ล.8697/2568 นายไพโรจน์ หรือไพโรจย์ หรือฐากูร สุวรรณเลิศ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131133.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คําพิพากษาให้ลูกหนี้ล้มละลาย [คดีหมายเลขแดงที่ ล.8791/2568 นายรณกฤต ฐิติสาธวี ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131376.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คําพิพากษาให้ลูกหนี้ล้มละลาย [คดีหมายเลขแดงที่ ล.8907/2568 นายศิรินท์ เต็งเดชกุลธร ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131372.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คําพิพากษาให้ลูกหนี้ล้มละลาย [คดีหมายเลขแดงที่ ล.8925/2568 บริษัทแอลฟ่า สปินนิ่ง จำกัด ลูกหนี้ที่ 1 และบริษัทแอลฟ่าเท็กซ์อินดัสตรีส จำกัด ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131374.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คําพิพากษาให้ลูกหนี้ล้มละลาย [คดีหมายเลขแดงที่ ล.9117/2568 ห้างหุ้นส่วนจำกัด ท่าเยี่ยมการโยธา ลูกหนี้ที่ 1 นายสมบูรณ์ บองกระโทก ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131683.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คําพิพากษาให้ลูกหนี้ล้มละลาย [คดีหมายเลขแดงที่ ล.9130/2568 นายนิรุท ทองขาว ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131443.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คําพิพากษาให้ลูกหนี้ล้มละลาย [คดีหมายเลขแดงที่ ล.9167/2568 นางสาวรพีพัตร พรมสุริน ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131530.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คําพิพากษาให้ลูกหนี้ล้มละลาย [คดีหมายเลขแดงที่ ล.9181/2568 นางสาวอารียา หม้อน้ำร้อน ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131630.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คําพิพากษาให้ลูกหนี้ล้มละลาย [คดีหมายเลขแดงที่ ล.9241/2568 นายพงศธร ครุธคำรพ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131562.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คําพิพากษาให้ลูกหนี้ล้มละลาย [คดีหมายเลขแดงที่ ล.9358/2568 นางสาวชุลี ฉิมโพธิ์กลาง ลูกหนี้ที่ 1, นางสาวสุพัตรา อุไรวรรณ ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131566.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คําพิพากษาให้ลูกหนี้ล้มละลาย [คดีหมายเลขแดงที่ ล.9440/2568 นางสาวปาลิดา พัทธ์นิธิศ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131528.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คําพิพากษาให้ลูกหนี้ล้มละลาย [คดีหมายเลขแดงที่ ล.9444/2568 นางสาวจารุณี จัตุรงค์ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131539.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คําพิพากษาให้ลูกหนี้ล้มละลาย [คดีหมายเลขแดงที่ ล.9564/2568 นางสุคนธา วิเศษรัตน์ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131350.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คําพิพากษาให้ลูกหนี้ล้มละลาย [คดีหมายเลขแดงที่ ล.9575/2568 นายวร์ศักดิ์ หรือวรศักดิ์ ขันทอง ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131525.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คําพิพากษาให้ลูกหนี้ล้มละลาย [คดีหมายเลขแดงที่ ล.9652/2568 นางอรทัย หรือศรัญรักษ์ ชื่นชม ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131674.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คําพิพากษาให้ลูกหนี้ล้มละลาย [คดีหมายเลขแดงที่ ล.9667/2568 นายแอ็นธนา สมจิต ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131527.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คําพิพากษาให้ลูกหนี้ล้มละลาย [คดีหมายเลขแดงที่ ล.9784/2568 นายจตุพร ศรันย์พานิช ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131699.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คําพิพากษาให้ลูกหนี้ล้มละลาย [คดีหมายเลขแดงที่ ล.9793/2568 นางสาวพรปวีณ์ จำปา ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131371.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คําพิพากษาให้ลูกหนี้ล้มละลาย [คดีหมายเลขแดงที่ ล.9837/2568 นายภูเอกนันท์ หรือภัทราวุช รักราม ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131536.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คําพิพากษาให้ลูกหนี้ล้มละลาย [คดีหมายเลขแดงที่ ล.9976/2568 นางสาวมีนา หรือขติญา พวงผกา หรือชีพสมใจ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131375.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คําพิพากษาให้ลูกหนี้ล้มละลาย [คดีหมายเลขแดงที่ ล.9984/2568 บริษัทอินดิเพนเด้นท์ นิวส์ เซ็นเตอร์ จำกัด ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131669.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คําพิพากษาให้ลูกหนี้ล้มละลาย [คดีหมายเลขแดงที่ ล.10038/2568 นายชัยวุธ สุขขี ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131716.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คําพิพากษาให้ลูกหนี้ล้มละลาย [คดีหมายเลขแดงที่ ล.10290/2568 นางสาวสุวิมล หล้าปวงคำ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131479.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คําพิพากษาให้ลูกหนี้ล้มละลาย [คดีหมายเลขแดงที่ ล.10337/2568 นางปิมประภา พลซา ลูกหนี้ที่ 1, นายสุวรรณ พลซา ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131702.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คําพิพากษาให้ลูกหนี้ล้มละลาย [คดีหมายเลขแดงที่ ล.10410/2568 นางสาวปนัดดา ชุ่มจิตร ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131352.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คําพิพากษาให้ลูกหนี้ล้มละลาย [คดีหมายเลขแดงที่ ล.10583/2568 นางนุชนาทหรือกมนมาศ ชูสงฆ์ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131555.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คําพิพากษาให้ลูกหนี้ล้มละลาย [คดีหมายเลขแดงที่ ล.10600/2568 สิบตํารวจโท หรือนายสมชาย เพชรัตน์ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131550.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คําพิพากษาให้ลูกหนี้ล้มละลาย [คดีหมายเลขแดงที่ ล.10635/2568 นางสาวกัณต์ชญา หมุดบิลและ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131348.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คําพิพากษาให้ลูกหนี้ล้มละลาย [คดีหมายเลขแดงที่ ล.10843/2568 นายปริญญา อร่ามแก้ว ลูกหนี้ที่ 1, นางสาวธันยชนก อร่ามแก้ว ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131559.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่องคําพิพากษาให้ลูกหนี้ล้มละลาย [คดีหมายเลขแดงที่ ล.11033/2568 นายเชิดวงศ์ บุญกมลสวัสดิ์ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131681.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คําพิพากษาให้ลูกหนี้ล้มละลาย [คดีหมายเลขแดงที่ ล.11101/2568 นายขวัญชัย ทารัตน์ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131459.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คําพิพากษาให้ลูกหนี้ล้มละลาย [คดีหมายเลขแดงที่ ล.11122/2568 นางสาว หรือนางรัฐชภร หรือนัชกัณณ์ธัญพร เชียงทอง หรือเครือวิเศษ ลูกหนี้ที่ 1, นายวิสุทธิ์ เครือวิเศษ ลูกหนี้ที่ 2, นางสาววีรยา เครือวิเศษ ลูกหนี้ที่ 3]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131467.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คําพิพากษาให้ลูกหนี้ล้มละลาย [คดีหมายเลขแดงที่ ล.11152/2568 นายดม หรืออุดม จันทร์แช่ม ลูกหนี้ที่ 1, นาง หรือนางสาวพัดชรี หรือพัชรี จันทร์แช่ม หรือเปรมจิต ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131472.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คําพิพากษาให้ลูกหนี้ล้มละลาย [คดีหมายเลขแดงที่ ล.11219/2568 นางธัญญารัตน์ นิชิบุญเจริญศิริ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131505.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คําพิพากษาให้ลูกหนี้ล้มละลาย [คดีหมายเลขแดงที่ ล.11279/2568 นายคมกฤช พรหมเรืองเดช ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131560.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คําพิพากษาให้ลูกหนี้ล้มละลาย [คดีหมายเลขแดงที่ ล.11283/2568 นางสมพร เหลาทอง ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131492.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คําพิพากษาให้ลูกหนี้ล้มละลาย [คดีหมายเลขแดงที่ ล.11469/2568 นายสรสิช ศุภกิจโยธิน ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131498.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คําพิพากษาให้ลูกหนี้ล้มละลาย [คดีหมายเลขแดงที่ ล.11473/2568 นายธนากร พรณรงค์ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131557.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คําพิพากษาให้ลูกหนี้ล้มละลาย [คดีหมายเลขแดงที่ ล.11522/2568 นางจันทร์เพ็ญ ศรีเหลาหรือทองสุข ลูกหนี้ที่ 1, นางสาวนิศารัตน์ พลับใหญ่ ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131451.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คําพิพากษาให้ลูกหนี้ล้มละลาย [คดีหมายเลขแดงที่ ล.11562/2568 นางสาวจารุกาญ ปานเพชร ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131461.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คําพิพากษาให้ลูกหนี้ล้มละลาย [คดีหมายเลขแดงที่ ล.E564/2568 พระ หรือนายเลิศฤทธิ์ เนียมลอย ลูกหนี้ที่ 1]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131900.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คําพิพากษาให้ลูกหนี้ล้มละลาย [คดีหมายเลขแดงที่ ล.E564/2568 นายธนกฤษ พนาวรรณ ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131346.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คําพิพากษาให้ลูกหนี้ล้มละลาย [คดีหมายเลขแดงที่ ล.E929/2568 นายคุณากร ซอนดอก ลูกหนี้ที่ 1, นายสมภาร ซอนดอก ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131147.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คําพิพากษาให้ลูกหนี้ล้มละลาย [คดีหมายเลขแดงที่ ล.E1537/2568 นางนุชกัญญาหรือนุชรา ลิ้มสุวัฒนาหรือทาคํานาง ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131353.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คําพิพากษาให้ลูกหนี้ล้มละลาย [คดีหมายเลขแดงที่ ล.E1605/2568 นางสาวธารินี ฤาชา ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131355.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คําพิพากษาให้ลูกหนี้ล้มละลาย [คดีหมายเลขแดงที่ ล.E1701/2568 นายสมคิด โชคสิริทรัพย์ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131354.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คําพิพากษาให้ลูกหนี้ล้มละลาย [คดีหมายเลขแดงที่ ล.61/2569 นายชาญยุทธิ์ ไหวพริบ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131701.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คําพิพากษาให้ลูกหนี้ล้มละลาย [คดีหมายเลขแดงที่ ล.100/2569 นายอธิภัทร กระชงโชติ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131444.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คําพิพากษาให้ลูกหนี้ล้มละลาย [คดีหมายเลขแดงที่ ล.172/2569 นายคมสันต์ สุธรรมบวรชัย ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131452.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คําพิพากษาให้ลูกหนี้ล้มละลาย [คดีหมายเลขแดงที่ ล.223/2569 นายสถาพร มีเนียม ลูกหนี้ที่ 1, นางสาวกนกพร นิลเหลือง ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131474.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คําพิพากษาให้ลูกหนี้ล้มละลาย [คดีหมายเลขแดงที่ ล.263/2569 นางสาวนุชจรีย์ โพธิ์ชัย ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131458.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คําพิพากษาให้ลูกหนี้ล้มละลาย [คดีหมายเลขแดงที่ ล.306/2569 นางสาวสุภาพร มาลี หรือบุญเพ็ง ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131680.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คําพิพากษาให้ลูกหนี้ล้มละลาย [คดีหมายเลขแดงที่ ล.406/2569 นางสาวอภิญญา ข้อจักร ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131696.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คําพิพากษาให้ลูกหนี้ล้มละลาย [คดีหมายเลขแดงที่ ล.438/2569 นายสุทิน สิงห์ธร ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131511.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คําพิพากษาให้ลูกหนี้ล้มละลาย [คดีหมายเลขแดงที่ ล.470/2569 นางสาวน้ำผึ้ง กิลาโภช ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131689.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำพิพากษาให้ลูกหนี้ล้มละลาย [คดีหมายเลขแดงที่ ล.492/2569 นายเสกสรร ศรีด้วง ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131332.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คําพิพากษาให้ลูกหนี้ล้มละลาย [คดีหมายเลขแดงที่ ล.569/2569 นายวัฒนา สวนศรี ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131694.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คําพิพากษาให้ลูกหนี้ล้มละลาย [คดีหมายเลขแดงที่ ล.612/2569 นางสาวภัทรนันท์ ดีขุนทด ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131717.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คําพิพากษาให้ลูกหนี้ล้มละลาย [คดีหมายเลขแดงที่ ล.648/2569 นางสาวอัมภาพร วงพิลา ลูกหนี้ที่ 1, นายยุรนันท์ มาลัย ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131540.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คําพิพากษาให้ลูกหนี้ล้มละลาย [คดีหมายเลขแดงที่ ล.734/2569 นางสาววราภรณ์ ไทรเล็กทิม ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131685.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คําพิพากษาให้ลูกหนี้ล้มละลาย [คดีหมายเลขแดงที่ ล.847/2569 นางสาวทิพย์ภาวรรณ์ จารเมือง ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131499.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คําพิพากษาให้ลูกหนี้ล้มละลาย [คดีหมายเลขแดงที่ ล.856/2569 นายคมสันต์ ลือพา ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131703.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คําพิพากษาให้ลูกหนี้ล้มละลาย [คดีหมายเลขแดงที่ ล.860/2569 นางสาวมณีรัตน์ แก้วปีลา ลูกหนี้ที่ 1, นายสรรเสริญ เทศเซ็น ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131471.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คําพิพากษาให้ลูกหนี้ล้มละลาย [คดีหมายเลขแดงที่ ล.903/2569 นางสาวปิยพร คุณสุข ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131349.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คําพิพากษาให้ลูกหนี้ล้มละลาย [คดีหมายเลขแดงที่ ล.1038/2569 นายธนวัฒน สุทธคุณ ลูกหนี้ที่ 1, นางชุติกาญจน์ สุทธคุณ ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131551.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คําพิพากษาให้ลูกหนี้ล้มละลาย [คดีหมายเลขแดงที่ ล.1860/2569 นายนัฐพงษ์ เปียกชัยภูมิ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131718.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คําพิพากษาให้ลูกหนี้ล้มละลาย [คดีหมายเลขแดงที่ ล.E38/2569 นางสาวบุญนาค สิมสีดา ลูกหนี้ที่ 1, นางวิลัย เหง้าศรี ลูกหนี้ที่ 2, นางศศิธร ฟักขาว ลูกหนี้ที่ 3]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131487.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คําพิพากษาให้ลูกหนี้ล้มละลาย [คดีหมายเลขแดงที่ ล.E62/2569 นางสาว หรือนางเดือนเพ็ญ ทาฟู หรือสันติวงค์ ลูกหนี้ที่ 1, นายวิโรจน์ สันติวงค์ ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131454.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คําพิพากษาให้ลูกหนี้ทั้งสองล้มละลาย [คดีหมายเลขแดงที่ ล.9594/2568 นางสาวเนตรดาว ศิลป์ชัย ลูกหนี้ที่ 1 นายพัทยา เหมเมือง ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131538.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง ปลดล้มลูกหนี้จากล้มละลาย [คดีหมายเลขแดงที่ ล.3720/2557 นายกฤตภาส ดิลกพัทธ์โชติ หรือจูละพันธ์ ลูกหนี้ที่ 1 นางสุนันทา แซ่เจียม หรือแซ่เจียม ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131470.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง ปลดลูกหนี้จากล้มละลาย [คดีหมายเลขแดงที่ ล.3376/2559  นายยุทธนา เชื้อวงศ์พรหม ลูกหนี้ที่ 1นางสาวนุช  หอมระรื่น ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131534.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง ปลดลูกหนี้จากล้มละลาย [คดีหมายเลขแดงที่ ล.271/2560 นางดาวรุ้ง แก้วเมือง ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131537.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง ปลดลูกหนี้จากล้มละลาย [คดีหมายเลขแดงที่ ล.526/2560 นางสิริสุดา ปานสุรา หรือช้างอาดร์ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131708.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง ปลดลูกหนี้จากล้มละลาย [คดีหมายเลขแดงที่ ล.1040/2560 นายสงกรานต์ โตวงษ์ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131522.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง ปลดลูกหนี้จากล้มละลาย [คดีหมายเลขแดงที่ ล.1432/2560 นายธนัชหรือณพลหรือสมาน เลิศสัตยานุศักดิ์ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131506.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง ปลดลูกหนี้จากล้มละลาย [คดีหมายเลขแดงที่ ล.1736/2560 นางสาวประพาส วิเวกวิน ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131485.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง ปลดลูกหนี้จากล้มละลาย [ดีหมายเลขแดงที่ ล.1801/2560 นายทัตเทพ หรือสุชาติ หอมจันทร์ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/130880.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง ปลดลูกหนี้จากล้มละลาย [คดีหมายเลขแดงที่ ล.2636/2560 นายจำรัส ชนิลกุล ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131486.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง ปลดลูกหนี้จากล้มละลาย [คดีหมายเลขแดงที่ ล.2769/2560 นายทรงศิลป์ ประดับศรี ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131547.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง ปลดลูกหนี้จากล้มละลาย [คดีหมายเลขแดงที่ ล.3557/2560 นายวิชาญ ขนอม ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131489.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง ปลดลูกหนี้จากล้มละลาย [คดีหมายเลขแดงที่ ล.4451/2560 นายวัชโรทัย แก้วสุขใส ลูกหนี้ที่ 1]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131514.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง ปลดลูกหนี้จากล้มละลาย [คดีหมายเลขแดงที่ ล.4534/2560 นางสาวมณีวรรณ หรือ วสุธิดา ประทีป ณ ถลาง ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131507.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง ปลดลูกหนี้จากล้มละลาย [คดีหมายเลขแดงที่ ล.4687/2560 ดาบตำรวจหรือจ่าสิบตำรวจประดิษฐ์ ดาทุมมา ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131491.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง ปลดลูกหนี้จากล้มละลาย [คดีหมายเลขแดงที่ ล.5457/2560 นายสิทธิชัย หรือรัชพงศ์ หรือนายพีระวิทย์ เปาชัย ลูกหนี้ที่ 1]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131517.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง ปลดลูกหนี้จากล้มละลาย [คดีหมายเลขแดงที่ ล.99/2561 นายอรรณพ โพธิ์สิน ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131544.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง ปลดลูกหนี้จากล้มละลาย [คดีหมายเลขแดงที่ ล.146/2561 นายธวัชชัย เสนสุข ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131496.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง ปลดลูกหนี้จากล้มละลาย [คดีหมายเลขแดงที่ ล.906/2561 นางสาว หรือนางสุชาดา บริบูรณ์สมบัติ หรือนางเบญญาดา ฟักเล็ก ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131476.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง ปลดลูกหนี้จากล้มละลาย [คดีหมายเลขแดงที่ ล.968/2561 นายจักรธร ชัยยะคำ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131523.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง ปลดลูกหนี้จากล้มละลาย [คดีหมายเลขแดงที่ ล.1177/2561 นายวีระยุทธ์ มณีวรรณ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131488.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง ปลดลูกหนี้จากล้มละลาย [คดีหมายเลขแดงที่ ล.1287/2561 นายเสน่ห์ รอดดำ ลูกหนี้ที่ 1 นางสาวอังคณา ปทุมรุ่ง ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131644.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง ปลดลูกหนี้จากล้มละลาย [คดีหมายเลขแดงที่ ล.1447/2561 นางวีระวัลย์หรือเรวดี พีเตอร์เซ่น ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131365.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง ปลดลูกหนี้จากล้มละลาย [คดีหมายเลขแดงที่ ล.1647/2561 นายดุสิต กตัญญู ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131642.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง ปลดลูกหนี้จากล้มละลาย [คดีหมายเลขแดงที่ ล.1663/2561 นายอัครวินฒ์ ประทุมศิลป์ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131677.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง ปลดลูกหนี้จากล้มละลาย [คดีหมายเลขแดงที่ ล.1809/2561 นายเดชา อนันต์ธนาพงษ์ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131543.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง ปลดลูกหนี้จากล้มละลาย [คดีหมายเลขแดงที่ ล.2119/2561 นายเทียนชัย ชัชวาลย์ ลูกหนี้ที่ 1 นายศุภวิทย์ ชุมพล ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131635.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง ปลดลูกหนี้จากล้มละลาย [คดีหมายเลขแดงที่ ล.2207/2561 นางสาวดอกอ้อ หมอนทอง ในฐานะหุ้นส่วนผู้จัดการของห้างหุ้นส่วนจำกัด สกรีน แอร์ แอนด์ ซัพพลาย ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131516.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง ปลดลูกหนี้จากล้มละลาย [คดีหมายเลขแดงที่ ล.2750/2561 นางสาวศิริรัตน์ ดุมไม้ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131139.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง ปลดลูกหนี้จากล้มละลาย [คดีหมายเลขแดงที่ ล.3026/2561 นายวรัญญู เนียมดี ลูกหนี้ที่ 1 นางอาธิติญา เนียมดี ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131503.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง ปลดลูกหนี้จากล้มละลาย [คดีหมายเลขแดงที่ ล.3842/2561 นายพงษ์พันธ์ ตรีกุล ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131529.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง ปลดลูกหนี้จากล้มละลาย [คดีหมายเลขแดงที่ ล.4930/2561 นายอำนาจ จันทารักษ์ หรือจันทรารักษ์ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131490.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง ปลดลูกหนี้จากล้มละลาย [คดีหมายเลขแดงที่ ล.627/2562 นายสมชาย วงเวียน ลูกหนี้ที่ 1, นางสาวแพรวพลอย มาฤทธิ์ ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131535.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง ปลดลูกหนี้จากล้มละลาย [คดีหมายเลขแดงที่ ล.2022/2562 นายบรรจง อาจหาญ หรือนายโกวิทยศกร อาจหาญ ลูกหนี้ที่ 3]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131132.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง ปลดลูกหนี้จากล้มละลาย [คดีหมายเลขแดงที่ ล.5114/2562 นายอนุรักษ์ บุญเชิด ในฐานะหุ้นส่วนผู้จัดการห้างหุ้นส่วนจํากัด เอ.ที.เค อินดัสเทรียล มอเตอร์เวอร์ค ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131558.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง ปลดลูกหนี้จากล้มละลาย [คดีหมายเลขแดงที่ ล.1128/2563 นางสาวศศิธร บุญญา ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/130913.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง ปลดลูกหนี้จากล้มละลาย [คดีหมายเลขแดงที่ ล.2119/2563 นางวนิดา สุระวนิชกุล ลูกหนี้ที่ 1 นายศักดา สุระวนิชกุล ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/130063.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง ปลดลูกหนี้จากล้มละลาย [คดีหมายเลขแดงที่ ล.3650/2563 นายนัฐพัฒน์ หรือณัฐวุฒิ อัมพรพิสิฏฐ์ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131464.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง ปลดลูกหนี้จากล้มละลาย [คดีหมายเลขแดงที่ ล.3972/2563 นางสาวน้ำทิพย์ นาคประคอง ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131134.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง ปลดลูกหนี้จากล้มละลาย [คดีหมายเลขแดงที่ ล.4296/2563 นางสาววรัชชญาหรือพาณีหรือพาณี กสิณฤกษ์ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131137.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง ปลดลูกหนี้จากล้มละลาย [คดีหมายเลขแดงที่ ล.5502/2563 นางสมปอง แพงแก้ว หรือ นางเสาวลักษณ์ ปัถวัลย์ ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131337.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง ปลดลูกหนี้จากล้มละลาย [คดีหมายเลขแดงที่ ล.6142/2563 พันจ่าเอกหรือนายเสถียร กางโสภา ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131135.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง ปลดลูกหนี้จากล้มละลาย [คดีหมายเลขแดงที่ ล.906/2564 นางสาวสุรัชรา ทองสวนแก้ว ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131344.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง ปลดลูกหนี้จากล้มละลาย [คดีหมายเลขแดงที่ ล.914/2564 นางสาวณัฏฐ์กานต์ รักนาค ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131509.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง ปลดลูกหนี้จากล้มละลาย [คดีหมายเลขแดงที่ ล.2228/2564 นายธนทรัพย์หรือยงยุทธ บุญหนัก ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131343.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง ปลดลูกหนี้จากล้มละลาย [คดีหมายเลขแดงที่ ล.2837/2564 นางสาวปรีดา รักษาศิริ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131513.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง ปลดลูกหนี้จากล้มละลาย [คดีหมายเลขแดงที่ ล.3563/2564 นางอัมรา บุญเนาว์ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/130961.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง ปลดลูกหนี้จากล้มละลาย [คดีหมายเลขแดงที่ ล.3801/2564 พันจ่าอากาศเอก หรือนายมานะ สัมมาสาร ลูกหนี้ที่ 4]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131502.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง ปลดลูกหนี้จากล้มละลาย [คดีหมายเลขแดงที่ ล.4094/2564 นายณัฐตพล หรือนิลันต์ สิงห์แม ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131584.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง ปลดลูกหนี้จากล้มละลาย [คดีหมายเลขแดงที่ ล.4746/2564 นางสาวกัญญารัชต์ ธิติวัฒน์ชญานิน ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131138.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง ปลดลูกหนี้จากล้มละลาย [คดีหมายเลขแดงที่ ล.5278/2564 นางสาวกนกอร พรหมขวัญ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131342.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง ปลดลูกหนี้จากล้มละลาย [คดีหมายเลขแดงที่ ล.E9/2564 นางฐิติกาญจญ์ สงวนรัตน์ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131518.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง ปลดลูกหนี้จากล้มละลาย [คดีหมายเลขแดงที่ ล.290/2565 นางสาวศิรดา จันทร์บัว ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131673.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง ปลดลูกหนี้จากล้มละลาย [คดีหมายเลขแดงที่ ล.427/2565 นายกิตติศักดิ์ พิศภา ลูกหนี้ที่ 1, นายสมชาย ประวังตภู ลูกหนี้ที่ 2 และนายณัฐกิตติ์ อนุตรพงศ์ ลูกหนี้ที่ 3]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131121.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง ปลดลูกหนี้จากล้มละลาย [คดีหมายเลขแดงที่ ล.789/2565 นายเกรียงไกร แก้ววันทา ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131686.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง ปลดลูกหนี้จากล้มละลาย [คดีหมายเลขแดงที่ ล.1270/2565 นางสาวธนภรณ์ นันทะคำนิตย์ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131366.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง ปลดลูกหนี้จากล้มละลาย [คดีหมายเลขแดงที่ ล.1677/2565 นางหรือนางสาวกฤติกาหรือธัณย์จิรา ทองเสมียนหรือเมธินทร์ศิรธัช ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131654.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง ปลดลูกหนี้จากล้มละลาย [คดีหมายเลขแดงที่ ล.1919/2565 นางสาวทิพนภา เผ่าพงษ์ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131469.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง ปลดลูกหนี้จากล้มละลาย [คดีหมายเลขแดงที่ ล.2788/2565 นางสาวรุ่งตะวัน โพธิสุวรรณ์ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131361.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง ปลดลูกหนี้จากล้มละลาย [คดีหมายเลขแดงที่ ล.2974/2565 นายอริยพงษ์ เตชะโรจน์กุล ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131651.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง ปลดลูกหนี้จากล้มละลาย [คดีหมายเลขแดงที่ ล.3232/2565 นางผกามาศ กล่ำเดช ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131351.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง ปลดลูกหนี้จากล้มละลาย [คดีหมายเลขแดงที่ ล.4511/2565 นายเสน่ห์ สงบแท้ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131118.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง ปลดลูกหนี้จากล้มละลาย [คดีหมายเลขแดงที่ ล.4798/2565 นางสาวขวัญจิรา ไวยวัฒถา ลูกหนี้</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131341.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง ปลดลูกหนี้จากล้มละลาย [คดีหมายเลขแดงที่ ล.4873/2565 นายปรีชา แสงอรุณ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131678.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง ปลดลูกหนี้จากล้มละลาย [คดีหมายเลขแดงที่ ล.4889/2565 นางสาวหนูนิตย์ พลเสน ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131526.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง ปลดลูกหนี้จากล้มละลาย [คดีหมายเลขแดงที่ ล.5030/2565 นางสาวอารีญา มงคลเรืองฤทธิ์ หรือนางสาวจิณณ์วรา มงคลเรืองฤทธิ์ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131494.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง ปลดลูกหนี้จากล้มละลาย [คดีหมายเลขแดงที่ ล.5038/2565 นายสุราษฎร์ ฉิมบุตร ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131664.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง ปลดลูกหนี้จากล้มละลาย [คดีหมายเลขแดงที่ ล.5151/2565 นายฉัตรชัย เริ่มแรก ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131633.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง ปลดลูกหนี้จากล้มละลาย [คดีหมายเลขแดงที่ ล.5286/2565 นางสมพร ขุมสุขหรือประเสริฐทองกร ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131136.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง ปลดลูกหนี้จากล้มละลาย [คดีหมายเลขแดงที่ ล.5456/2565 นายศรีประเสริฐ เครือยศ ลูกหนี้ที่ 1 และนางสาววิรมนภัสหรือนางพิไลพร ช่วยชนะหรือเครือยศ ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131463.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง ปลดลูกหนี้จากล้มละลาย [คดีหมายเลขแดงที่ ล.5566/2565 นายสุริยา จิตรนาวี ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131520.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง ปลดลูกหนี้จากล้มละลาย [คดีหมายเลขแดงที่ ล.5911/2565 นางกานต์ฉัตร ทองกลัด ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131362.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง ปลดลูกหนี้จากล้มละลาย [คดีหมายเลขแดงที่ ล.5995/2565 นายสนธยา นุชเรืองศรี ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131141.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง ปลดจำเลยจากล้มละลาย [คดีหมายเลขแดงที่ ล.6065/2565 นายเฉลิมชัย ตุ้นสกุล ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131120.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง ปลดลูกหนี้จากล้มละลาย [คดีหมายเลขแดงที่ ล.6382/2565 นายยุทธ ชนะศึก ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131465.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง ปลดลูกหนี้จากล้มละลาย [คดีหมายเลขแดงที่ ล.6390/2565 นายคำนวล ตุ้มทอง ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131142.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง ปลดลูกหนี้จากล้มละลาย [คดีหมายเลขแดงที่ ล.6414/2565 นางสาวหรือนางกัญจน์รัตน์หรือจันทร์ธิภา พันธนสารถิรกุลหรือเรียงใหม่หรืออินทมาต ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131473.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง ปลดลูกหนี้จากล้มละลาย [คดีหมายเลขแดงที่ ล.6437/2565 นายนรงชัย รุ่งเรืองวิจิตร ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131140.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง ปลดลูกหนี้จากล้มละลาย [คดีหมายเลขแดงที่ ล.6498/2565 นายไชยยศ กุญชร ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131691.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง ปลดลูกหนี้จากล้มละลาย [คดีหมายเลขแดงที่ ล.6661/2565 นางสาวนิตยา ประสมศรี ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131360.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง ปลดลูกหนี้จากล้มละลาย [คดีหมายเลขแดงที่ ล.7038/2565 นางจินดา ตั้งไพบูลย์ หรือนางจินดา กุญชโร ลูกหนี้ที่ 1]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131345.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง ปลดลูกหนี้จากล้มละลาย [คดีหมายเลขแดงที่ ล.404/2566 นางกานต์พิชชา หรือกาญจนา วงษ์ขวัญเมือง ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131462.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง ปลดลูกหนี้จากล้มละลาย [คดีหมายเลขแดงที่ ล.532/2566 นายสุวัฒน์ชัย โลหคุณาพันธ์ หรือนายสุวัฒชัย ศักดิ์พัฒนโชค ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131119.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง ปลดลูกหนี้จากล้มละลาย [คดีหมายเลขแดงที่ ล.590/2566 นางสาวปุณณิภัทร์ หรือลักขณา ท้าวทัญ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131358.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง ปลดลูกหนี้จากล้มละลาย [คดีหมายเลขแดงที่ ล.610/2566 นางอาพัตรา พูลทรัพย์ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131149.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง ปลดลูกหนี้จากล้มละลาย [คดีหมายเลขแดงที่ ล.773/2566 นายไชยา โสดาตา ลูกหนี้ที่ 1, นางจิระพรรณ โสดาตา ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131553.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง ปลดลูกหนี้จากล้มละลาย [คดีหมายเลขแดงที่ ล.803/2566 นายสุชาติ ศรีมาตย์ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131449.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง ปลดลูกหนี้จากล้มละลาย [คดีหมายเลขแดงที่ ล.897/2566 นายสวัสดิ์ จำปาศรี หรือ พันตํารวจเอกสวัสดิ์ จําปาศรี ลูกหนี้ที่ 1]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131704.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง ปลดลูกหนี้จากล้มละลาย [คดีหมายเลขแดงที่ ล.933/2566 นายพงษ์สิทธิ์ เจริญสุข ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131359.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง ปลดลูกหนี้จากล้มละลาย [คดีหมายเลขแดงที่ ล.960/2566 นางสาวภารตี เดโชกำธร ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131650.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง ปลดลูกหนี้จากล้มละลาย [คดีหมายเลขแดงที่ ล.969/2566 นางสาวสุกัญญา รอดเพ็ชร ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131515.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง ปลดลูกหนี้จากล้มละลาย [คดีหมายเลขแดงที่ ล.1091/2566 พันจ่าโท หรือ นายพิเชษฐ์ มูลศรีแก้ว ลูกหนี้ที่ 1, พันจ่าเอก หรือ นายอนุกูล การดี ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131690.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง ปลดลูกหนี้จากล้มละลาย [คดีหมายเลขแดงที่ ล.1134/2566 นางสุจิตรา ลีสวัสดิ์ตระกูล ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131706.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง ปลดลูกหนี้จากล้มละลาย [คดีหมายเลขแดงที่ ล.1163/2566 พันจ่าเอก หรือนายสุรชัย อนุวงศ์วรเวทย์ ลูกหนี้ที่ 1 นาวาตรี หรือนายมนัส ศรีเพ็ชร ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131564.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง ปลดลูกหนี้จากล้มละลาย [คดีหมายเลขแดงที่ ล.1179/2566 นางสาวพัทธ์ธีรา โชติเลอศักดิ์ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131653.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง ปลดลูกหนี้จากล้มละลาย [คดีหมายเลขแดงที่ ล.1204/2566 นายหรือจ่าสิบตํารวจอนุชา คนชาญ ลูกหนี้ที่ 1]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131565.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง ปลดลูกหนี้จากล้มละลาย [คดีหมายเลขแดงที่ ล.1206/2566 นายเฉลิมพงษ์ ผลทวี ลูกหนี้ที่ 3 นางสาวพรวิภา คุ้มไทย ลูกหนี้ที่ 4]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131705.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง ปลดลูกหนี้จากล้มละลาย [คดีหมายเลขแดงที่ ล.1311/2566 นางอัญชิษฐา หรือนางสาวอมลิณรัศมิ์ ภักเกลี้ยง หรือ ปันทะวัน ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131687.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง ปลดลูกหนี้ทั้งสองจากล้มละลาย [คดีหมายเลขแดงที่ ล.3526/2561 นายหงษ์หยก สุวรรณประทีป ลูกหนี้ที่ 1, นางสาวสายบัว แก้วเขียว ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131493.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง ปลดลูกหนี้ที่ ๑ จากล้มละลาย [คดีหมายเลขแดงที่ ล.1346/2561 นายบุญเลิศ แตงอ่อน ลูกหนี้ที่ 1]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131466.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง ยกเลิกการล้มละลาย [คดีหมายเลขแดงที่ ล.8673/2568 นายวิชัย ประทับใจ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131450.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง ยกเลิกการล้มละลายของลูกหนี้ทั้งสอง [คดีหมายเลขแดงที่ ล.10857/2568 นายธนากูลหรือเฉลิมพล บุปผะโพธิ์ ลูกหนี้ที่ 1 นางเมทิกา บุปผะโพธิ์ ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131542.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง ยกเลิกการล้มละลายของลูกหนี้ที่ ๒ [คดีหมายเลขแดงที่ ล.5726/2568 นายชัยเดช พิฆาตไพรี ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131440.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง แก้ไขเพิ่มเติมคำสั่งศาลให้พิจารณาคดีใหม่ [คดีหมายเลขแดงที่ ล.4290/2568 นายแมททิว เอฟเวิร์น เจียมจิตร ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/130064.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง แก้ไขคำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ 11157/2550  นายพรชัย ฉัตรนรัตนกุล โดย นางสาวสิริประภา ฉัตรนรัตนกุล ในฐานะทายาทโดยธรรมของลูกหนี้ ที่ 4]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131173.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง แก้ไขประกาศคำพิพากษาล้มละลาย [คดีหมายเลขแดงที่ ล.3263/2561 นายเจริญสิน หรือคุณาพุฒิ ซาฮู หรือ พระเจริญสิน ซาฮู ในฐานะหุ้นส่วนผู้จัดการของ ห้างหุ้นส่วนจำกัด ซาฮู ครีเอชั่น ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131495.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง แก้ไขชื่อลูกหนี้ที่ ๑ ในประกาศคำพิพากษาให้ลูกหนี้ทั้งสามล้มละลาย [คดีหมายเลขแดงที่ ล.3494/2563 ห้างหุ้นส่วนจำกัด โชคชัย ๒๐๐๗ การเกษตร ลูกหนี้ที่ 1]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131524.pdf</t>
+  </si>
+  <si>
     <t>ประกาศสำนักนายกรัฐมนตรี เรื่อง แต่งตั้งเอกอัครราชทูตวิสามัญผู้มีอำนาจเต็มประจำสาธารณรัฐกาบูเวร์ดี [นางสาวนิภา  นิรันดร์นุต]</t>
   </si>
   <si>
@@ -3489,6 +4749,192 @@
   </si>
   <si>
     <t>https://ratchakitcha.soc.go.th/documents/132512.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8254/2569 นายประเวศ ชมหอม ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132533.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8255/2569 นางสาวกรกมล พันเปี่ยม ลูกหนี้ที่ 1 และนายสาธิต วังคำ ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132489.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8256/2569 นางสาวกิตติ์ลภัส ศิริปรีชาเจริญกุล ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132506.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8257/2569 นายธนกฤต หรือสุรชัย ส่งพิพัฒน์หรือสัญนุจิตต์ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132474.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8260/2569 นางสมหมาย ล่ำสัน ลูกหนี้ที่ 1 และนายสำอางค์ ล่ำสัน ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132523.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8261/2569 นางสาวรุ่งทิพย์ โฉมเกรย ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132505.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8262/2569 นางสาวปัถยาหรือภัทรปภา บุญประเสริฐ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132487.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8263/2569 สิบเอกสุทัศน์ ดัชถุยาวัตร ลูกหนี้ที่ 1 และนางสาววริยา สิยาชีพ ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132472.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8264/2569 นายพรพรหมหรือทัพพ์ปภพ อินทรเชษฐหรืออัศวโรจนมงคล ลูกหนี้ที่ 1 และนางเกวลินหรือวรัญช์ธิตา วงษ์พัฒนเศรษฐหรืออัศวโรจนมงคล ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132531.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8265/2569 นายชาญชัย บุกบุญ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132484.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8267/2569 นายสมศักดิ์ ผอมฉิม ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132527.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8268/2569 นายปริญญา ประชานอก ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132481.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8269/2569 บริษัทซีทีเอช ธนบุรี จำกัด โดยนายอำนาจ บูจีระ ผู้ชำระบัญชี ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132470.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8271/2569 นายณัฐดนัย ชูชีพ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132529.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8273/2569 นางหฤทัย พรหมสิทธิ์ ลูกหนี้ที่ 1 และว่าที่ร้อยตรีสุระพันธ์ พรหมสิทธิ์ ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132513.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8274/2569 นางสาวพัชรินทร์ แสงสุวรรณ ลูกหนี้ที่ 1 และนางสาวฐปนภัสร์ มุกดาประกร ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132483.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8277/2569 บริษัทแม็กซ์กร รวมสโตร์ จำกัด ลูกหนี้ที่ 1, นายปกรณ์ ศรีขาว ลูกหนี้ที่ 2 และนางหรือนางสาวรื่นนิรา ศรีริเลี้ยงหรือศรีขาว ลูกหนี้ที่ 3]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132532.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8279/2569 นายสุวัฒน์หรือยุทธกร จันทสิงห์หรือพลศรศาสตร์ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132503.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8280/2569 นายภัทร์กรหรือกฤตภาส เกตุพุดหรือเกตุสกุลไชย ลูกหนี้ที่ 1 และนางสาวรัตติกาลหรือปทิตตา ไชยช่อฟ้าหรือเกตุสกุลไชย ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132485.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8281/2569 บริษัทคอมพลีทอินทีเรียคอร์ปอเรชั่น จำกัด ลูกหนี้ที่ 1 และนายชลิต อมตเวทย์ ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132514.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8282/2569 นางสาวพีระพรรณ เศษโชติ ลูกหนี้ที่ 1 และนายศิริวัฒน์ ช้างเกตุ ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132521.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8283/2569 นายสุทธิพจน์ หรือฐากฤต หรือรุ่งฤทธิ์ เตชะวงศ์สกุล ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132530.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8285/2569 นางสาวสรณา เนียมมาลา ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132522.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8286/2569 นายวิเชียร ผิวเหลือง ลูกหนี้ที่ 1 และนางสาวณัฏฐิกาหรือนุจรีย์ เคหารมย์ ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132504.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8340/2569 นายพีรพนธ์ เกตุประเสริฐ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132528.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8341/2569 นางจันทร์จุรี เอื้อนทอง ลูกหนี้ที่ 1 และนายสาโรจน์ เอื้อนทอง ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132520.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8357/2569 นางสาวมนต์ณภัค กู้เจริญศิริสุข ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132507.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8358/2569 นางสาวสุกัญญา แดงพูลผล ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132525.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8359/2569 นางสาวพิธาวรรณหรืออภิชญา วรวงศ์ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132517.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8360/2569 นายชัยวัฒน์ ปัสสะ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132508.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8361/2569 บริษัทโซ ไฟน์ จีเวลส์ จำกัด ลูกหนี้ที่ 1 และนายอาชีช วสันลาล ซาวานี ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132476.pdf</t>
   </si>
 </sst>
 </file>
@@ -3835,7 +5281,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:H572"/>
+  <dimension ref="A1:H813"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="12.02" customWidth="true" style="0"/>
@@ -16677,10 +18123,10 @@
         <v>143</v>
       </c>
       <c r="D535" s="1">
-        <v>244</v>
+        <v>149</v>
       </c>
       <c r="E535" s="1" t="s">
-        <v>100</v>
+        <v>19</v>
       </c>
       <c r="F535" s="1">
         <v>1</v>
@@ -16701,10 +18147,10 @@
         <v>143</v>
       </c>
       <c r="D536" s="1">
-        <v>244</v>
+        <v>149</v>
       </c>
       <c r="E536" s="1" t="s">
-        <v>100</v>
+        <v>19</v>
       </c>
       <c r="F536" s="1">
         <v>2</v>
@@ -16725,10 +18171,10 @@
         <v>143</v>
       </c>
       <c r="D537" s="1">
-        <v>244</v>
+        <v>149</v>
       </c>
       <c r="E537" s="1" t="s">
-        <v>100</v>
+        <v>19</v>
       </c>
       <c r="F537" s="1">
         <v>3</v>
@@ -16749,10 +18195,10 @@
         <v>143</v>
       </c>
       <c r="D538" s="1">
-        <v>244</v>
+        <v>149</v>
       </c>
       <c r="E538" s="1" t="s">
-        <v>100</v>
+        <v>19</v>
       </c>
       <c r="F538" s="1">
         <v>4</v>
@@ -16773,10 +18219,10 @@
         <v>143</v>
       </c>
       <c r="D539" s="1">
-        <v>244</v>
+        <v>149</v>
       </c>
       <c r="E539" s="1" t="s">
-        <v>100</v>
+        <v>19</v>
       </c>
       <c r="F539" s="1">
         <v>5</v>
@@ -16797,10 +18243,10 @@
         <v>143</v>
       </c>
       <c r="D540" s="1">
-        <v>244</v>
+        <v>149</v>
       </c>
       <c r="E540" s="1" t="s">
-        <v>100</v>
+        <v>19</v>
       </c>
       <c r="F540" s="1">
         <v>6</v>
@@ -16821,13 +18267,13 @@
         <v>143</v>
       </c>
       <c r="D541" s="1">
-        <v>244</v>
+        <v>149</v>
       </c>
       <c r="E541" s="1" t="s">
-        <v>100</v>
+        <v>19</v>
       </c>
       <c r="F541" s="1">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="G541" s="1"/>
       <c r="H541" t="s">
@@ -16845,13 +18291,13 @@
         <v>143</v>
       </c>
       <c r="D542" s="1">
-        <v>244</v>
+        <v>149</v>
       </c>
       <c r="E542" s="1" t="s">
-        <v>100</v>
+        <v>19</v>
       </c>
       <c r="F542" s="1">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="G542" s="1"/>
       <c r="H542" t="s">
@@ -16869,13 +18315,13 @@
         <v>143</v>
       </c>
       <c r="D543" s="1">
-        <v>244</v>
+        <v>149</v>
       </c>
       <c r="E543" s="1" t="s">
-        <v>100</v>
+        <v>19</v>
       </c>
       <c r="F543" s="1">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="G543" s="1"/>
       <c r="H543" t="s">
@@ -16893,13 +18339,13 @@
         <v>143</v>
       </c>
       <c r="D544" s="1">
-        <v>244</v>
+        <v>149</v>
       </c>
       <c r="E544" s="1" t="s">
-        <v>100</v>
+        <v>19</v>
       </c>
       <c r="F544" s="1">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="G544" s="1"/>
       <c r="H544" t="s">
@@ -16917,13 +18363,13 @@
         <v>143</v>
       </c>
       <c r="D545" s="1">
-        <v>244</v>
+        <v>149</v>
       </c>
       <c r="E545" s="1" t="s">
-        <v>100</v>
+        <v>19</v>
       </c>
       <c r="F545" s="1">
-        <v>49</v>
+        <v>11</v>
       </c>
       <c r="G545" s="1"/>
       <c r="H545" t="s">
@@ -16941,13 +18387,13 @@
         <v>143</v>
       </c>
       <c r="D546" s="1">
-        <v>244</v>
+        <v>149</v>
       </c>
       <c r="E546" s="1" t="s">
-        <v>100</v>
+        <v>19</v>
       </c>
       <c r="F546" s="1">
-        <v>55</v>
+        <v>12</v>
       </c>
       <c r="G546" s="1"/>
       <c r="H546" t="s">
@@ -16965,13 +18411,13 @@
         <v>143</v>
       </c>
       <c r="D547" s="1">
-        <v>244</v>
+        <v>149</v>
       </c>
       <c r="E547" s="1" t="s">
-        <v>100</v>
+        <v>19</v>
       </c>
       <c r="F547" s="1">
-        <v>60</v>
+        <v>13</v>
       </c>
       <c r="G547" s="1"/>
       <c r="H547" t="s">
@@ -16989,13 +18435,13 @@
         <v>143</v>
       </c>
       <c r="D548" s="1">
-        <v>244</v>
+        <v>149</v>
       </c>
       <c r="E548" s="1" t="s">
-        <v>100</v>
+        <v>19</v>
       </c>
       <c r="F548" s="1">
-        <v>70</v>
+        <v>14</v>
       </c>
       <c r="G548" s="1"/>
       <c r="H548" t="s">
@@ -17013,13 +18459,13 @@
         <v>143</v>
       </c>
       <c r="D549" s="1">
-        <v>244</v>
+        <v>149</v>
       </c>
       <c r="E549" s="1" t="s">
-        <v>100</v>
+        <v>19</v>
       </c>
       <c r="F549" s="1">
-        <v>72</v>
+        <v>15</v>
       </c>
       <c r="G549" s="1"/>
       <c r="H549" t="s">
@@ -17037,13 +18483,13 @@
         <v>143</v>
       </c>
       <c r="D550" s="1">
-        <v>244</v>
+        <v>149</v>
       </c>
       <c r="E550" s="1" t="s">
-        <v>100</v>
+        <v>19</v>
       </c>
       <c r="F550" s="1">
-        <v>76</v>
+        <v>16</v>
       </c>
       <c r="G550" s="1"/>
       <c r="H550" t="s">
@@ -17061,13 +18507,13 @@
         <v>143</v>
       </c>
       <c r="D551" s="1">
-        <v>244</v>
+        <v>149</v>
       </c>
       <c r="E551" s="1" t="s">
-        <v>100</v>
+        <v>19</v>
       </c>
       <c r="F551" s="1">
-        <v>77</v>
+        <v>17</v>
       </c>
       <c r="G551" s="1"/>
       <c r="H551" t="s">
@@ -17085,13 +18531,13 @@
         <v>143</v>
       </c>
       <c r="D552" s="1">
-        <v>244</v>
+        <v>149</v>
       </c>
       <c r="E552" s="1" t="s">
-        <v>100</v>
+        <v>19</v>
       </c>
       <c r="F552" s="1">
-        <v>79</v>
+        <v>18</v>
       </c>
       <c r="G552" s="1"/>
       <c r="H552" t="s">
@@ -17109,13 +18555,13 @@
         <v>143</v>
       </c>
       <c r="D553" s="1">
-        <v>244</v>
+        <v>149</v>
       </c>
       <c r="E553" s="1" t="s">
-        <v>100</v>
+        <v>19</v>
       </c>
       <c r="F553" s="1">
-        <v>81</v>
+        <v>19</v>
       </c>
       <c r="G553" s="1"/>
       <c r="H553" t="s">
@@ -17133,13 +18579,13 @@
         <v>143</v>
       </c>
       <c r="D554" s="1">
-        <v>244</v>
+        <v>149</v>
       </c>
       <c r="E554" s="1" t="s">
-        <v>100</v>
+        <v>19</v>
       </c>
       <c r="F554" s="1">
-        <v>83</v>
+        <v>20</v>
       </c>
       <c r="G554" s="1"/>
       <c r="H554" t="s">
@@ -17157,13 +18603,13 @@
         <v>143</v>
       </c>
       <c r="D555" s="1">
-        <v>244</v>
+        <v>149</v>
       </c>
       <c r="E555" s="1" t="s">
-        <v>100</v>
+        <v>19</v>
       </c>
       <c r="F555" s="1">
-        <v>85</v>
+        <v>21</v>
       </c>
       <c r="G555" s="1"/>
       <c r="H555" t="s">
@@ -17181,13 +18627,13 @@
         <v>143</v>
       </c>
       <c r="D556" s="1">
-        <v>244</v>
+        <v>149</v>
       </c>
       <c r="E556" s="1" t="s">
-        <v>100</v>
+        <v>19</v>
       </c>
       <c r="F556" s="1">
-        <v>86</v>
+        <v>22</v>
       </c>
       <c r="G556" s="1"/>
       <c r="H556" t="s">
@@ -17205,13 +18651,13 @@
         <v>143</v>
       </c>
       <c r="D557" s="1">
-        <v>244</v>
+        <v>149</v>
       </c>
       <c r="E557" s="1" t="s">
-        <v>100</v>
+        <v>19</v>
       </c>
       <c r="F557" s="1">
-        <v>87</v>
+        <v>23</v>
       </c>
       <c r="G557" s="1"/>
       <c r="H557" t="s">
@@ -17229,13 +18675,13 @@
         <v>143</v>
       </c>
       <c r="D558" s="1">
-        <v>244</v>
+        <v>149</v>
       </c>
       <c r="E558" s="1" t="s">
-        <v>100</v>
+        <v>19</v>
       </c>
       <c r="F558" s="1">
-        <v>88</v>
+        <v>24</v>
       </c>
       <c r="G558" s="1"/>
       <c r="H558" t="s">
@@ -17253,13 +18699,13 @@
         <v>143</v>
       </c>
       <c r="D559" s="1">
-        <v>244</v>
+        <v>149</v>
       </c>
       <c r="E559" s="1" t="s">
-        <v>100</v>
+        <v>19</v>
       </c>
       <c r="F559" s="1">
-        <v>89</v>
+        <v>25</v>
       </c>
       <c r="G559" s="1"/>
       <c r="H559" t="s">
@@ -17277,13 +18723,13 @@
         <v>143</v>
       </c>
       <c r="D560" s="1">
-        <v>244</v>
+        <v>149</v>
       </c>
       <c r="E560" s="1" t="s">
-        <v>100</v>
+        <v>19</v>
       </c>
       <c r="F560" s="1">
-        <v>90</v>
+        <v>26</v>
       </c>
       <c r="G560" s="1"/>
       <c r="H560" t="s">
@@ -17301,13 +18747,13 @@
         <v>143</v>
       </c>
       <c r="D561" s="1">
-        <v>244</v>
+        <v>149</v>
       </c>
       <c r="E561" s="1" t="s">
-        <v>100</v>
+        <v>19</v>
       </c>
       <c r="F561" s="1">
-        <v>91</v>
+        <v>27</v>
       </c>
       <c r="G561" s="1"/>
       <c r="H561" t="s">
@@ -17325,13 +18771,13 @@
         <v>143</v>
       </c>
       <c r="D562" s="1">
-        <v>244</v>
+        <v>149</v>
       </c>
       <c r="E562" s="1" t="s">
-        <v>100</v>
+        <v>19</v>
       </c>
       <c r="F562" s="1">
-        <v>92</v>
+        <v>28</v>
       </c>
       <c r="G562" s="1"/>
       <c r="H562" t="s">
@@ -17349,13 +18795,13 @@
         <v>143</v>
       </c>
       <c r="D563" s="1">
-        <v>244</v>
+        <v>149</v>
       </c>
       <c r="E563" s="1" t="s">
-        <v>100</v>
+        <v>19</v>
       </c>
       <c r="F563" s="1">
-        <v>93</v>
+        <v>29</v>
       </c>
       <c r="G563" s="1"/>
       <c r="H563" t="s">
@@ -17373,13 +18819,13 @@
         <v>143</v>
       </c>
       <c r="D564" s="1">
-        <v>244</v>
+        <v>149</v>
       </c>
       <c r="E564" s="1" t="s">
-        <v>100</v>
+        <v>19</v>
       </c>
       <c r="F564" s="1">
-        <v>94</v>
+        <v>30</v>
       </c>
       <c r="G564" s="1"/>
       <c r="H564" t="s">
@@ -17397,13 +18843,13 @@
         <v>143</v>
       </c>
       <c r="D565" s="1">
-        <v>244</v>
+        <v>149</v>
       </c>
       <c r="E565" s="1" t="s">
-        <v>100</v>
+        <v>19</v>
       </c>
       <c r="F565" s="1">
-        <v>95</v>
+        <v>31</v>
       </c>
       <c r="G565" s="1"/>
       <c r="H565" t="s">
@@ -17421,13 +18867,13 @@
         <v>143</v>
       </c>
       <c r="D566" s="1">
-        <v>244</v>
+        <v>149</v>
       </c>
       <c r="E566" s="1" t="s">
-        <v>100</v>
+        <v>19</v>
       </c>
       <c r="F566" s="1">
-        <v>96</v>
+        <v>32</v>
       </c>
       <c r="G566" s="1"/>
       <c r="H566" t="s">
@@ -17445,13 +18891,13 @@
         <v>143</v>
       </c>
       <c r="D567" s="1">
-        <v>244</v>
+        <v>149</v>
       </c>
       <c r="E567" s="1" t="s">
-        <v>100</v>
+        <v>19</v>
       </c>
       <c r="F567" s="1">
-        <v>97</v>
+        <v>33</v>
       </c>
       <c r="G567" s="1"/>
       <c r="H567" t="s">
@@ -17469,13 +18915,13 @@
         <v>143</v>
       </c>
       <c r="D568" s="1">
-        <v>244</v>
+        <v>149</v>
       </c>
       <c r="E568" s="1" t="s">
-        <v>100</v>
+        <v>19</v>
       </c>
       <c r="F568" s="1">
-        <v>98</v>
+        <v>34</v>
       </c>
       <c r="G568" s="1"/>
       <c r="H568" t="s">
@@ -17493,13 +18939,13 @@
         <v>143</v>
       </c>
       <c r="D569" s="1">
-        <v>244</v>
+        <v>149</v>
       </c>
       <c r="E569" s="1" t="s">
-        <v>100</v>
+        <v>19</v>
       </c>
       <c r="F569" s="1">
-        <v>99</v>
+        <v>35</v>
       </c>
       <c r="G569" s="1"/>
       <c r="H569" t="s">
@@ -17517,13 +18963,13 @@
         <v>143</v>
       </c>
       <c r="D570" s="1">
-        <v>244</v>
+        <v>149</v>
       </c>
       <c r="E570" s="1" t="s">
-        <v>100</v>
+        <v>19</v>
       </c>
       <c r="F570" s="1">
-        <v>100</v>
+        <v>36</v>
       </c>
       <c r="G570" s="1"/>
       <c r="H570" t="s">
@@ -17541,13 +18987,13 @@
         <v>143</v>
       </c>
       <c r="D571" s="1">
-        <v>244</v>
+        <v>149</v>
       </c>
       <c r="E571" s="1" t="s">
-        <v>100</v>
+        <v>19</v>
       </c>
       <c r="F571" s="1">
-        <v>101</v>
+        <v>37</v>
       </c>
       <c r="G571" s="1"/>
       <c r="H571" t="s">
@@ -17555,12 +19001,5796 @@
       </c>
     </row>
     <row r="572" spans="1:8">
-      <c r="A572" s="2"/>
-      <c r="C572" s="1"/>
-      <c r="D572" s="1"/>
-      <c r="E572" s="1"/>
-      <c r="F572" s="1"/>
+      <c r="A572" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B572" t="s">
+        <v>1158</v>
+      </c>
+      <c r="C572" s="1">
+        <v>143</v>
+      </c>
+      <c r="D572" s="1">
+        <v>149</v>
+      </c>
+      <c r="E572" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F572" s="1">
+        <v>38</v>
+      </c>
       <c r="G572" s="1"/>
+      <c r="H572" t="s">
+        <v>1159</v>
+      </c>
+    </row>
+    <row r="573" spans="1:8">
+      <c r="A573" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B573" t="s">
+        <v>1160</v>
+      </c>
+      <c r="C573" s="1">
+        <v>143</v>
+      </c>
+      <c r="D573" s="1">
+        <v>149</v>
+      </c>
+      <c r="E573" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F573" s="1">
+        <v>39</v>
+      </c>
+      <c r="G573" s="1"/>
+      <c r="H573" t="s">
+        <v>1161</v>
+      </c>
+    </row>
+    <row r="574" spans="1:8">
+      <c r="A574" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B574" t="s">
+        <v>1162</v>
+      </c>
+      <c r="C574" s="1">
+        <v>143</v>
+      </c>
+      <c r="D574" s="1">
+        <v>149</v>
+      </c>
+      <c r="E574" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F574" s="1">
+        <v>40</v>
+      </c>
+      <c r="G574" s="1"/>
+      <c r="H574" t="s">
+        <v>1163</v>
+      </c>
+    </row>
+    <row r="575" spans="1:8">
+      <c r="A575" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B575" t="s">
+        <v>1164</v>
+      </c>
+      <c r="C575" s="1">
+        <v>143</v>
+      </c>
+      <c r="D575" s="1">
+        <v>149</v>
+      </c>
+      <c r="E575" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F575" s="1">
+        <v>41</v>
+      </c>
+      <c r="G575" s="1"/>
+      <c r="H575" t="s">
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="576" spans="1:8">
+      <c r="A576" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B576" t="s">
+        <v>1166</v>
+      </c>
+      <c r="C576" s="1">
+        <v>143</v>
+      </c>
+      <c r="D576" s="1">
+        <v>149</v>
+      </c>
+      <c r="E576" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F576" s="1">
+        <v>42</v>
+      </c>
+      <c r="G576" s="1"/>
+      <c r="H576" t="s">
+        <v>1167</v>
+      </c>
+    </row>
+    <row r="577" spans="1:8">
+      <c r="A577" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B577" t="s">
+        <v>1168</v>
+      </c>
+      <c r="C577" s="1">
+        <v>143</v>
+      </c>
+      <c r="D577" s="1">
+        <v>149</v>
+      </c>
+      <c r="E577" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F577" s="1">
+        <v>43</v>
+      </c>
+      <c r="G577" s="1"/>
+      <c r="H577" t="s">
+        <v>1169</v>
+      </c>
+    </row>
+    <row r="578" spans="1:8">
+      <c r="A578" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B578" t="s">
+        <v>1170</v>
+      </c>
+      <c r="C578" s="1">
+        <v>143</v>
+      </c>
+      <c r="D578" s="1">
+        <v>149</v>
+      </c>
+      <c r="E578" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F578" s="1">
+        <v>44</v>
+      </c>
+      <c r="G578" s="1"/>
+      <c r="H578" t="s">
+        <v>1171</v>
+      </c>
+    </row>
+    <row r="579" spans="1:8">
+      <c r="A579" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B579" t="s">
+        <v>1172</v>
+      </c>
+      <c r="C579" s="1">
+        <v>143</v>
+      </c>
+      <c r="D579" s="1">
+        <v>149</v>
+      </c>
+      <c r="E579" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F579" s="1">
+        <v>45</v>
+      </c>
+      <c r="G579" s="1"/>
+      <c r="H579" t="s">
+        <v>1173</v>
+      </c>
+    </row>
+    <row r="580" spans="1:8">
+      <c r="A580" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B580" t="s">
+        <v>1174</v>
+      </c>
+      <c r="C580" s="1">
+        <v>143</v>
+      </c>
+      <c r="D580" s="1">
+        <v>149</v>
+      </c>
+      <c r="E580" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F580" s="1">
+        <v>46</v>
+      </c>
+      <c r="G580" s="1"/>
+      <c r="H580" t="s">
+        <v>1175</v>
+      </c>
+    </row>
+    <row r="581" spans="1:8">
+      <c r="A581" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B581" t="s">
+        <v>1176</v>
+      </c>
+      <c r="C581" s="1">
+        <v>143</v>
+      </c>
+      <c r="D581" s="1">
+        <v>149</v>
+      </c>
+      <c r="E581" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F581" s="1">
+        <v>47</v>
+      </c>
+      <c r="G581" s="1"/>
+      <c r="H581" t="s">
+        <v>1177</v>
+      </c>
+    </row>
+    <row r="582" spans="1:8">
+      <c r="A582" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B582" t="s">
+        <v>1178</v>
+      </c>
+      <c r="C582" s="1">
+        <v>143</v>
+      </c>
+      <c r="D582" s="1">
+        <v>149</v>
+      </c>
+      <c r="E582" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F582" s="1">
+        <v>48</v>
+      </c>
+      <c r="G582" s="1"/>
+      <c r="H582" t="s">
+        <v>1179</v>
+      </c>
+    </row>
+    <row r="583" spans="1:8">
+      <c r="A583" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B583" t="s">
+        <v>1180</v>
+      </c>
+      <c r="C583" s="1">
+        <v>143</v>
+      </c>
+      <c r="D583" s="1">
+        <v>149</v>
+      </c>
+      <c r="E583" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F583" s="1">
+        <v>49</v>
+      </c>
+      <c r="G583" s="1"/>
+      <c r="H583" t="s">
+        <v>1181</v>
+      </c>
+    </row>
+    <row r="584" spans="1:8">
+      <c r="A584" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B584" t="s">
+        <v>1182</v>
+      </c>
+      <c r="C584" s="1">
+        <v>143</v>
+      </c>
+      <c r="D584" s="1">
+        <v>149</v>
+      </c>
+      <c r="E584" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F584" s="1">
+        <v>50</v>
+      </c>
+      <c r="G584" s="1"/>
+      <c r="H584" t="s">
+        <v>1183</v>
+      </c>
+    </row>
+    <row r="585" spans="1:8">
+      <c r="A585" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B585" t="s">
+        <v>1184</v>
+      </c>
+      <c r="C585" s="1">
+        <v>143</v>
+      </c>
+      <c r="D585" s="1">
+        <v>149</v>
+      </c>
+      <c r="E585" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F585" s="1">
+        <v>51</v>
+      </c>
+      <c r="G585" s="1"/>
+      <c r="H585" t="s">
+        <v>1185</v>
+      </c>
+    </row>
+    <row r="586" spans="1:8">
+      <c r="A586" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B586" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C586" s="1">
+        <v>143</v>
+      </c>
+      <c r="D586" s="1">
+        <v>149</v>
+      </c>
+      <c r="E586" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F586" s="1">
+        <v>52</v>
+      </c>
+      <c r="G586" s="1"/>
+      <c r="H586" t="s">
+        <v>1187</v>
+      </c>
+    </row>
+    <row r="587" spans="1:8">
+      <c r="A587" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B587" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C587" s="1">
+        <v>143</v>
+      </c>
+      <c r="D587" s="1">
+        <v>149</v>
+      </c>
+      <c r="E587" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F587" s="1">
+        <v>53</v>
+      </c>
+      <c r="G587" s="1"/>
+      <c r="H587" t="s">
+        <v>1189</v>
+      </c>
+    </row>
+    <row r="588" spans="1:8">
+      <c r="A588" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B588" t="s">
+        <v>1190</v>
+      </c>
+      <c r="C588" s="1">
+        <v>143</v>
+      </c>
+      <c r="D588" s="1">
+        <v>149</v>
+      </c>
+      <c r="E588" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F588" s="1">
+        <v>54</v>
+      </c>
+      <c r="G588" s="1"/>
+      <c r="H588" t="s">
+        <v>1191</v>
+      </c>
+    </row>
+    <row r="589" spans="1:8">
+      <c r="A589" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B589" t="s">
+        <v>1192</v>
+      </c>
+      <c r="C589" s="1">
+        <v>143</v>
+      </c>
+      <c r="D589" s="1">
+        <v>149</v>
+      </c>
+      <c r="E589" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F589" s="1">
+        <v>55</v>
+      </c>
+      <c r="G589" s="1"/>
+      <c r="H589" t="s">
+        <v>1193</v>
+      </c>
+    </row>
+    <row r="590" spans="1:8">
+      <c r="A590" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B590" t="s">
+        <v>1194</v>
+      </c>
+      <c r="C590" s="1">
+        <v>143</v>
+      </c>
+      <c r="D590" s="1">
+        <v>149</v>
+      </c>
+      <c r="E590" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F590" s="1">
+        <v>56</v>
+      </c>
+      <c r="G590" s="1"/>
+      <c r="H590" t="s">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="591" spans="1:8">
+      <c r="A591" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B591" t="s">
+        <v>1196</v>
+      </c>
+      <c r="C591" s="1">
+        <v>143</v>
+      </c>
+      <c r="D591" s="1">
+        <v>149</v>
+      </c>
+      <c r="E591" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F591" s="1">
+        <v>57</v>
+      </c>
+      <c r="G591" s="1"/>
+      <c r="H591" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="592" spans="1:8">
+      <c r="A592" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B592" t="s">
+        <v>1198</v>
+      </c>
+      <c r="C592" s="1">
+        <v>143</v>
+      </c>
+      <c r="D592" s="1">
+        <v>149</v>
+      </c>
+      <c r="E592" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F592" s="1">
+        <v>58</v>
+      </c>
+      <c r="G592" s="1"/>
+      <c r="H592" t="s">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="593" spans="1:8">
+      <c r="A593" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B593" t="s">
+        <v>1200</v>
+      </c>
+      <c r="C593" s="1">
+        <v>143</v>
+      </c>
+      <c r="D593" s="1">
+        <v>149</v>
+      </c>
+      <c r="E593" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F593" s="1">
+        <v>59</v>
+      </c>
+      <c r="G593" s="1"/>
+      <c r="H593" t="s">
+        <v>1201</v>
+      </c>
+    </row>
+    <row r="594" spans="1:8">
+      <c r="A594" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B594" t="s">
+        <v>1202</v>
+      </c>
+      <c r="C594" s="1">
+        <v>143</v>
+      </c>
+      <c r="D594" s="1">
+        <v>149</v>
+      </c>
+      <c r="E594" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F594" s="1">
+        <v>60</v>
+      </c>
+      <c r="G594" s="1"/>
+      <c r="H594" t="s">
+        <v>1203</v>
+      </c>
+    </row>
+    <row r="595" spans="1:8">
+      <c r="A595" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B595" t="s">
+        <v>1204</v>
+      </c>
+      <c r="C595" s="1">
+        <v>143</v>
+      </c>
+      <c r="D595" s="1">
+        <v>149</v>
+      </c>
+      <c r="E595" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F595" s="1">
+        <v>61</v>
+      </c>
+      <c r="G595" s="1"/>
+      <c r="H595" t="s">
+        <v>1205</v>
+      </c>
+    </row>
+    <row r="596" spans="1:8">
+      <c r="A596" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B596" t="s">
+        <v>1206</v>
+      </c>
+      <c r="C596" s="1">
+        <v>143</v>
+      </c>
+      <c r="D596" s="1">
+        <v>149</v>
+      </c>
+      <c r="E596" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F596" s="1">
+        <v>62</v>
+      </c>
+      <c r="G596" s="1"/>
+      <c r="H596" t="s">
+        <v>1207</v>
+      </c>
+    </row>
+    <row r="597" spans="1:8">
+      <c r="A597" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B597" t="s">
+        <v>1208</v>
+      </c>
+      <c r="C597" s="1">
+        <v>143</v>
+      </c>
+      <c r="D597" s="1">
+        <v>149</v>
+      </c>
+      <c r="E597" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F597" s="1">
+        <v>63</v>
+      </c>
+      <c r="G597" s="1"/>
+      <c r="H597" t="s">
+        <v>1209</v>
+      </c>
+    </row>
+    <row r="598" spans="1:8">
+      <c r="A598" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B598" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C598" s="1">
+        <v>143</v>
+      </c>
+      <c r="D598" s="1">
+        <v>149</v>
+      </c>
+      <c r="E598" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F598" s="1">
+        <v>64</v>
+      </c>
+      <c r="G598" s="1"/>
+      <c r="H598" t="s">
+        <v>1211</v>
+      </c>
+    </row>
+    <row r="599" spans="1:8">
+      <c r="A599" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B599" t="s">
+        <v>1212</v>
+      </c>
+      <c r="C599" s="1">
+        <v>143</v>
+      </c>
+      <c r="D599" s="1">
+        <v>149</v>
+      </c>
+      <c r="E599" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F599" s="1">
+        <v>65</v>
+      </c>
+      <c r="G599" s="1"/>
+      <c r="H599" t="s">
+        <v>1213</v>
+      </c>
+    </row>
+    <row r="600" spans="1:8">
+      <c r="A600" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B600" t="s">
+        <v>1214</v>
+      </c>
+      <c r="C600" s="1">
+        <v>143</v>
+      </c>
+      <c r="D600" s="1">
+        <v>149</v>
+      </c>
+      <c r="E600" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F600" s="1">
+        <v>66</v>
+      </c>
+      <c r="G600" s="1"/>
+      <c r="H600" t="s">
+        <v>1215</v>
+      </c>
+    </row>
+    <row r="601" spans="1:8">
+      <c r="A601" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B601" t="s">
+        <v>1216</v>
+      </c>
+      <c r="C601" s="1">
+        <v>143</v>
+      </c>
+      <c r="D601" s="1">
+        <v>149</v>
+      </c>
+      <c r="E601" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F601" s="1">
+        <v>67</v>
+      </c>
+      <c r="G601" s="1"/>
+      <c r="H601" t="s">
+        <v>1217</v>
+      </c>
+    </row>
+    <row r="602" spans="1:8">
+      <c r="A602" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B602" t="s">
+        <v>1218</v>
+      </c>
+      <c r="C602" s="1">
+        <v>143</v>
+      </c>
+      <c r="D602" s="1">
+        <v>149</v>
+      </c>
+      <c r="E602" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F602" s="1">
+        <v>68</v>
+      </c>
+      <c r="G602" s="1"/>
+      <c r="H602" t="s">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="603" spans="1:8">
+      <c r="A603" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B603" t="s">
+        <v>1220</v>
+      </c>
+      <c r="C603" s="1">
+        <v>143</v>
+      </c>
+      <c r="D603" s="1">
+        <v>149</v>
+      </c>
+      <c r="E603" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F603" s="1">
+        <v>69</v>
+      </c>
+      <c r="G603" s="1"/>
+      <c r="H603" t="s">
+        <v>1221</v>
+      </c>
+    </row>
+    <row r="604" spans="1:8">
+      <c r="A604" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B604" t="s">
+        <v>1222</v>
+      </c>
+      <c r="C604" s="1">
+        <v>143</v>
+      </c>
+      <c r="D604" s="1">
+        <v>149</v>
+      </c>
+      <c r="E604" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F604" s="1">
+        <v>70</v>
+      </c>
+      <c r="G604" s="1"/>
+      <c r="H604" t="s">
+        <v>1223</v>
+      </c>
+    </row>
+    <row r="605" spans="1:8">
+      <c r="A605" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B605" t="s">
+        <v>1224</v>
+      </c>
+      <c r="C605" s="1">
+        <v>143</v>
+      </c>
+      <c r="D605" s="1">
+        <v>149</v>
+      </c>
+      <c r="E605" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F605" s="1">
+        <v>71</v>
+      </c>
+      <c r="G605" s="1"/>
+      <c r="H605" t="s">
+        <v>1225</v>
+      </c>
+    </row>
+    <row r="606" spans="1:8">
+      <c r="A606" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B606" t="s">
+        <v>1226</v>
+      </c>
+      <c r="C606" s="1">
+        <v>143</v>
+      </c>
+      <c r="D606" s="1">
+        <v>149</v>
+      </c>
+      <c r="E606" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F606" s="1">
+        <v>72</v>
+      </c>
+      <c r="G606" s="1"/>
+      <c r="H606" t="s">
+        <v>1227</v>
+      </c>
+    </row>
+    <row r="607" spans="1:8">
+      <c r="A607" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B607" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C607" s="1">
+        <v>143</v>
+      </c>
+      <c r="D607" s="1">
+        <v>149</v>
+      </c>
+      <c r="E607" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F607" s="1">
+        <v>73</v>
+      </c>
+      <c r="G607" s="1"/>
+      <c r="H607" t="s">
+        <v>1229</v>
+      </c>
+    </row>
+    <row r="608" spans="1:8">
+      <c r="A608" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B608" t="s">
+        <v>1230</v>
+      </c>
+      <c r="C608" s="1">
+        <v>143</v>
+      </c>
+      <c r="D608" s="1">
+        <v>149</v>
+      </c>
+      <c r="E608" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F608" s="1">
+        <v>74</v>
+      </c>
+      <c r="G608" s="1"/>
+      <c r="H608" t="s">
+        <v>1231</v>
+      </c>
+    </row>
+    <row r="609" spans="1:8">
+      <c r="A609" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B609" t="s">
+        <v>1232</v>
+      </c>
+      <c r="C609" s="1">
+        <v>143</v>
+      </c>
+      <c r="D609" s="1">
+        <v>149</v>
+      </c>
+      <c r="E609" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F609" s="1">
+        <v>75</v>
+      </c>
+      <c r="G609" s="1"/>
+      <c r="H609" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="610" spans="1:8">
+      <c r="A610" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B610" t="s">
+        <v>1234</v>
+      </c>
+      <c r="C610" s="1">
+        <v>143</v>
+      </c>
+      <c r="D610" s="1">
+        <v>149</v>
+      </c>
+      <c r="E610" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F610" s="1">
+        <v>76</v>
+      </c>
+      <c r="G610" s="1"/>
+      <c r="H610" t="s">
+        <v>1235</v>
+      </c>
+    </row>
+    <row r="611" spans="1:8">
+      <c r="A611" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B611" t="s">
+        <v>1236</v>
+      </c>
+      <c r="C611" s="1">
+        <v>143</v>
+      </c>
+      <c r="D611" s="1">
+        <v>149</v>
+      </c>
+      <c r="E611" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F611" s="1">
+        <v>77</v>
+      </c>
+      <c r="G611" s="1"/>
+      <c r="H611" t="s">
+        <v>1237</v>
+      </c>
+    </row>
+    <row r="612" spans="1:8">
+      <c r="A612" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B612" t="s">
+        <v>1238</v>
+      </c>
+      <c r="C612" s="1">
+        <v>143</v>
+      </c>
+      <c r="D612" s="1">
+        <v>149</v>
+      </c>
+      <c r="E612" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F612" s="1">
+        <v>78</v>
+      </c>
+      <c r="G612" s="1"/>
+      <c r="H612" t="s">
+        <v>1239</v>
+      </c>
+    </row>
+    <row r="613" spans="1:8">
+      <c r="A613" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B613" t="s">
+        <v>1240</v>
+      </c>
+      <c r="C613" s="1">
+        <v>143</v>
+      </c>
+      <c r="D613" s="1">
+        <v>149</v>
+      </c>
+      <c r="E613" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F613" s="1">
+        <v>79</v>
+      </c>
+      <c r="G613" s="1"/>
+      <c r="H613" t="s">
+        <v>1241</v>
+      </c>
+    </row>
+    <row r="614" spans="1:8">
+      <c r="A614" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B614" t="s">
+        <v>1242</v>
+      </c>
+      <c r="C614" s="1">
+        <v>143</v>
+      </c>
+      <c r="D614" s="1">
+        <v>149</v>
+      </c>
+      <c r="E614" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F614" s="1">
+        <v>80</v>
+      </c>
+      <c r="G614" s="1"/>
+      <c r="H614" t="s">
+        <v>1243</v>
+      </c>
+    </row>
+    <row r="615" spans="1:8">
+      <c r="A615" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B615" t="s">
+        <v>1244</v>
+      </c>
+      <c r="C615" s="1">
+        <v>143</v>
+      </c>
+      <c r="D615" s="1">
+        <v>149</v>
+      </c>
+      <c r="E615" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F615" s="1">
+        <v>81</v>
+      </c>
+      <c r="G615" s="1"/>
+      <c r="H615" t="s">
+        <v>1245</v>
+      </c>
+    </row>
+    <row r="616" spans="1:8">
+      <c r="A616" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B616" t="s">
+        <v>1246</v>
+      </c>
+      <c r="C616" s="1">
+        <v>143</v>
+      </c>
+      <c r="D616" s="1">
+        <v>149</v>
+      </c>
+      <c r="E616" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F616" s="1">
+        <v>82</v>
+      </c>
+      <c r="G616" s="1"/>
+      <c r="H616" t="s">
+        <v>1247</v>
+      </c>
+    </row>
+    <row r="617" spans="1:8">
+      <c r="A617" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B617" t="s">
+        <v>1248</v>
+      </c>
+      <c r="C617" s="1">
+        <v>143</v>
+      </c>
+      <c r="D617" s="1">
+        <v>149</v>
+      </c>
+      <c r="E617" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F617" s="1">
+        <v>83</v>
+      </c>
+      <c r="G617" s="1"/>
+      <c r="H617" t="s">
+        <v>1249</v>
+      </c>
+    </row>
+    <row r="618" spans="1:8">
+      <c r="A618" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B618" t="s">
+        <v>1250</v>
+      </c>
+      <c r="C618" s="1">
+        <v>143</v>
+      </c>
+      <c r="D618" s="1">
+        <v>149</v>
+      </c>
+      <c r="E618" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F618" s="1">
+        <v>84</v>
+      </c>
+      <c r="G618" s="1"/>
+      <c r="H618" t="s">
+        <v>1251</v>
+      </c>
+    </row>
+    <row r="619" spans="1:8">
+      <c r="A619" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B619" t="s">
+        <v>1252</v>
+      </c>
+      <c r="C619" s="1">
+        <v>143</v>
+      </c>
+      <c r="D619" s="1">
+        <v>149</v>
+      </c>
+      <c r="E619" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F619" s="1">
+        <v>85</v>
+      </c>
+      <c r="G619" s="1"/>
+      <c r="H619" t="s">
+        <v>1253</v>
+      </c>
+    </row>
+    <row r="620" spans="1:8">
+      <c r="A620" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B620" t="s">
+        <v>1254</v>
+      </c>
+      <c r="C620" s="1">
+        <v>143</v>
+      </c>
+      <c r="D620" s="1">
+        <v>149</v>
+      </c>
+      <c r="E620" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F620" s="1">
+        <v>86</v>
+      </c>
+      <c r="G620" s="1"/>
+      <c r="H620" t="s">
+        <v>1255</v>
+      </c>
+    </row>
+    <row r="621" spans="1:8">
+      <c r="A621" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B621" t="s">
+        <v>1256</v>
+      </c>
+      <c r="C621" s="1">
+        <v>143</v>
+      </c>
+      <c r="D621" s="1">
+        <v>149</v>
+      </c>
+      <c r="E621" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F621" s="1">
+        <v>87</v>
+      </c>
+      <c r="G621" s="1"/>
+      <c r="H621" t="s">
+        <v>1257</v>
+      </c>
+    </row>
+    <row r="622" spans="1:8">
+      <c r="A622" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B622" t="s">
+        <v>1258</v>
+      </c>
+      <c r="C622" s="1">
+        <v>143</v>
+      </c>
+      <c r="D622" s="1">
+        <v>149</v>
+      </c>
+      <c r="E622" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F622" s="1">
+        <v>88</v>
+      </c>
+      <c r="G622" s="1"/>
+      <c r="H622" t="s">
+        <v>1259</v>
+      </c>
+    </row>
+    <row r="623" spans="1:8">
+      <c r="A623" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B623" t="s">
+        <v>1260</v>
+      </c>
+      <c r="C623" s="1">
+        <v>143</v>
+      </c>
+      <c r="D623" s="1">
+        <v>149</v>
+      </c>
+      <c r="E623" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F623" s="1">
+        <v>89</v>
+      </c>
+      <c r="G623" s="1"/>
+      <c r="H623" t="s">
+        <v>1261</v>
+      </c>
+    </row>
+    <row r="624" spans="1:8">
+      <c r="A624" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B624" t="s">
+        <v>1262</v>
+      </c>
+      <c r="C624" s="1">
+        <v>143</v>
+      </c>
+      <c r="D624" s="1">
+        <v>149</v>
+      </c>
+      <c r="E624" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F624" s="1">
+        <v>90</v>
+      </c>
+      <c r="G624" s="1"/>
+      <c r="H624" t="s">
+        <v>1263</v>
+      </c>
+    </row>
+    <row r="625" spans="1:8">
+      <c r="A625" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B625" t="s">
+        <v>1264</v>
+      </c>
+      <c r="C625" s="1">
+        <v>143</v>
+      </c>
+      <c r="D625" s="1">
+        <v>149</v>
+      </c>
+      <c r="E625" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F625" s="1">
+        <v>91</v>
+      </c>
+      <c r="G625" s="1"/>
+      <c r="H625" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="626" spans="1:8">
+      <c r="A626" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B626" t="s">
+        <v>1266</v>
+      </c>
+      <c r="C626" s="1">
+        <v>143</v>
+      </c>
+      <c r="D626" s="1">
+        <v>149</v>
+      </c>
+      <c r="E626" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F626" s="1">
+        <v>92</v>
+      </c>
+      <c r="G626" s="1"/>
+      <c r="H626" t="s">
+        <v>1267</v>
+      </c>
+    </row>
+    <row r="627" spans="1:8">
+      <c r="A627" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B627" t="s">
+        <v>1268</v>
+      </c>
+      <c r="C627" s="1">
+        <v>143</v>
+      </c>
+      <c r="D627" s="1">
+        <v>149</v>
+      </c>
+      <c r="E627" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F627" s="1">
+        <v>93</v>
+      </c>
+      <c r="G627" s="1"/>
+      <c r="H627" t="s">
+        <v>1269</v>
+      </c>
+    </row>
+    <row r="628" spans="1:8">
+      <c r="A628" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B628" t="s">
+        <v>1270</v>
+      </c>
+      <c r="C628" s="1">
+        <v>143</v>
+      </c>
+      <c r="D628" s="1">
+        <v>149</v>
+      </c>
+      <c r="E628" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F628" s="1">
+        <v>94</v>
+      </c>
+      <c r="G628" s="1"/>
+      <c r="H628" t="s">
+        <v>1271</v>
+      </c>
+    </row>
+    <row r="629" spans="1:8">
+      <c r="A629" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B629" t="s">
+        <v>1272</v>
+      </c>
+      <c r="C629" s="1">
+        <v>143</v>
+      </c>
+      <c r="D629" s="1">
+        <v>149</v>
+      </c>
+      <c r="E629" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F629" s="1">
+        <v>95</v>
+      </c>
+      <c r="G629" s="1"/>
+      <c r="H629" t="s">
+        <v>1273</v>
+      </c>
+    </row>
+    <row r="630" spans="1:8">
+      <c r="A630" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B630" t="s">
+        <v>1274</v>
+      </c>
+      <c r="C630" s="1">
+        <v>143</v>
+      </c>
+      <c r="D630" s="1">
+        <v>149</v>
+      </c>
+      <c r="E630" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F630" s="1">
+        <v>96</v>
+      </c>
+      <c r="G630" s="1"/>
+      <c r="H630" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="631" spans="1:8">
+      <c r="A631" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B631" t="s">
+        <v>1276</v>
+      </c>
+      <c r="C631" s="1">
+        <v>143</v>
+      </c>
+      <c r="D631" s="1">
+        <v>149</v>
+      </c>
+      <c r="E631" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F631" s="1">
+        <v>97</v>
+      </c>
+      <c r="G631" s="1"/>
+      <c r="H631" t="s">
+        <v>1277</v>
+      </c>
+    </row>
+    <row r="632" spans="1:8">
+      <c r="A632" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B632" t="s">
+        <v>1278</v>
+      </c>
+      <c r="C632" s="1">
+        <v>143</v>
+      </c>
+      <c r="D632" s="1">
+        <v>149</v>
+      </c>
+      <c r="E632" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F632" s="1">
+        <v>98</v>
+      </c>
+      <c r="G632" s="1"/>
+      <c r="H632" t="s">
+        <v>1279</v>
+      </c>
+    </row>
+    <row r="633" spans="1:8">
+      <c r="A633" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B633" t="s">
+        <v>1280</v>
+      </c>
+      <c r="C633" s="1">
+        <v>143</v>
+      </c>
+      <c r="D633" s="1">
+        <v>149</v>
+      </c>
+      <c r="E633" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F633" s="1">
+        <v>99</v>
+      </c>
+      <c r="G633" s="1"/>
+      <c r="H633" t="s">
+        <v>1281</v>
+      </c>
+    </row>
+    <row r="634" spans="1:8">
+      <c r="A634" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B634" t="s">
+        <v>1282</v>
+      </c>
+      <c r="C634" s="1">
+        <v>143</v>
+      </c>
+      <c r="D634" s="1">
+        <v>149</v>
+      </c>
+      <c r="E634" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F634" s="1">
+        <v>100</v>
+      </c>
+      <c r="G634" s="1"/>
+      <c r="H634" t="s">
+        <v>1283</v>
+      </c>
+    </row>
+    <row r="635" spans="1:8">
+      <c r="A635" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B635" t="s">
+        <v>1284</v>
+      </c>
+      <c r="C635" s="1">
+        <v>143</v>
+      </c>
+      <c r="D635" s="1">
+        <v>149</v>
+      </c>
+      <c r="E635" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F635" s="1">
+        <v>101</v>
+      </c>
+      <c r="G635" s="1"/>
+      <c r="H635" t="s">
+        <v>1285</v>
+      </c>
+    </row>
+    <row r="636" spans="1:8">
+      <c r="A636" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B636" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C636" s="1">
+        <v>143</v>
+      </c>
+      <c r="D636" s="1">
+        <v>149</v>
+      </c>
+      <c r="E636" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F636" s="1">
+        <v>102</v>
+      </c>
+      <c r="G636" s="1"/>
+      <c r="H636" t="s">
+        <v>1287</v>
+      </c>
+    </row>
+    <row r="637" spans="1:8">
+      <c r="A637" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B637" t="s">
+        <v>1288</v>
+      </c>
+      <c r="C637" s="1">
+        <v>143</v>
+      </c>
+      <c r="D637" s="1">
+        <v>149</v>
+      </c>
+      <c r="E637" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F637" s="1">
+        <v>103</v>
+      </c>
+      <c r="G637" s="1"/>
+      <c r="H637" t="s">
+        <v>1289</v>
+      </c>
+    </row>
+    <row r="638" spans="1:8">
+      <c r="A638" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B638" t="s">
+        <v>1290</v>
+      </c>
+      <c r="C638" s="1">
+        <v>143</v>
+      </c>
+      <c r="D638" s="1">
+        <v>149</v>
+      </c>
+      <c r="E638" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F638" s="1">
+        <v>104</v>
+      </c>
+      <c r="G638" s="1"/>
+      <c r="H638" t="s">
+        <v>1291</v>
+      </c>
+    </row>
+    <row r="639" spans="1:8">
+      <c r="A639" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B639" t="s">
+        <v>1292</v>
+      </c>
+      <c r="C639" s="1">
+        <v>143</v>
+      </c>
+      <c r="D639" s="1">
+        <v>149</v>
+      </c>
+      <c r="E639" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F639" s="1">
+        <v>105</v>
+      </c>
+      <c r="G639" s="1"/>
+      <c r="H639" t="s">
+        <v>1293</v>
+      </c>
+    </row>
+    <row r="640" spans="1:8">
+      <c r="A640" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B640" t="s">
+        <v>1294</v>
+      </c>
+      <c r="C640" s="1">
+        <v>143</v>
+      </c>
+      <c r="D640" s="1">
+        <v>149</v>
+      </c>
+      <c r="E640" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F640" s="1">
+        <v>106</v>
+      </c>
+      <c r="G640" s="1"/>
+      <c r="H640" t="s">
+        <v>1295</v>
+      </c>
+    </row>
+    <row r="641" spans="1:8">
+      <c r="A641" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B641" t="s">
+        <v>1296</v>
+      </c>
+      <c r="C641" s="1">
+        <v>143</v>
+      </c>
+      <c r="D641" s="1">
+        <v>149</v>
+      </c>
+      <c r="E641" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F641" s="1">
+        <v>107</v>
+      </c>
+      <c r="G641" s="1"/>
+      <c r="H641" t="s">
+        <v>1297</v>
+      </c>
+    </row>
+    <row r="642" spans="1:8">
+      <c r="A642" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B642" t="s">
+        <v>1298</v>
+      </c>
+      <c r="C642" s="1">
+        <v>143</v>
+      </c>
+      <c r="D642" s="1">
+        <v>149</v>
+      </c>
+      <c r="E642" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F642" s="1">
+        <v>108</v>
+      </c>
+      <c r="G642" s="1"/>
+      <c r="H642" t="s">
+        <v>1299</v>
+      </c>
+    </row>
+    <row r="643" spans="1:8">
+      <c r="A643" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B643" t="s">
+        <v>1300</v>
+      </c>
+      <c r="C643" s="1">
+        <v>143</v>
+      </c>
+      <c r="D643" s="1">
+        <v>149</v>
+      </c>
+      <c r="E643" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F643" s="1">
+        <v>109</v>
+      </c>
+      <c r="G643" s="1"/>
+      <c r="H643" t="s">
+        <v>1301</v>
+      </c>
+    </row>
+    <row r="644" spans="1:8">
+      <c r="A644" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B644" t="s">
+        <v>1302</v>
+      </c>
+      <c r="C644" s="1">
+        <v>143</v>
+      </c>
+      <c r="D644" s="1">
+        <v>149</v>
+      </c>
+      <c r="E644" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F644" s="1">
+        <v>110</v>
+      </c>
+      <c r="G644" s="1"/>
+      <c r="H644" t="s">
+        <v>1303</v>
+      </c>
+    </row>
+    <row r="645" spans="1:8">
+      <c r="A645" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B645" t="s">
+        <v>1304</v>
+      </c>
+      <c r="C645" s="1">
+        <v>143</v>
+      </c>
+      <c r="D645" s="1">
+        <v>149</v>
+      </c>
+      <c r="E645" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F645" s="1">
+        <v>111</v>
+      </c>
+      <c r="G645" s="1"/>
+      <c r="H645" t="s">
+        <v>1305</v>
+      </c>
+    </row>
+    <row r="646" spans="1:8">
+      <c r="A646" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B646" t="s">
+        <v>1306</v>
+      </c>
+      <c r="C646" s="1">
+        <v>143</v>
+      </c>
+      <c r="D646" s="1">
+        <v>149</v>
+      </c>
+      <c r="E646" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F646" s="1">
+        <v>112</v>
+      </c>
+      <c r="G646" s="1"/>
+      <c r="H646" t="s">
+        <v>1307</v>
+      </c>
+    </row>
+    <row r="647" spans="1:8">
+      <c r="A647" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B647" t="s">
+        <v>1308</v>
+      </c>
+      <c r="C647" s="1">
+        <v>143</v>
+      </c>
+      <c r="D647" s="1">
+        <v>149</v>
+      </c>
+      <c r="E647" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F647" s="1">
+        <v>113</v>
+      </c>
+      <c r="G647" s="1"/>
+      <c r="H647" t="s">
+        <v>1309</v>
+      </c>
+    </row>
+    <row r="648" spans="1:8">
+      <c r="A648" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B648" t="s">
+        <v>1310</v>
+      </c>
+      <c r="C648" s="1">
+        <v>143</v>
+      </c>
+      <c r="D648" s="1">
+        <v>149</v>
+      </c>
+      <c r="E648" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F648" s="1">
+        <v>114</v>
+      </c>
+      <c r="G648" s="1"/>
+      <c r="H648" t="s">
+        <v>1311</v>
+      </c>
+    </row>
+    <row r="649" spans="1:8">
+      <c r="A649" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B649" t="s">
+        <v>1312</v>
+      </c>
+      <c r="C649" s="1">
+        <v>143</v>
+      </c>
+      <c r="D649" s="1">
+        <v>149</v>
+      </c>
+      <c r="E649" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F649" s="1">
+        <v>115</v>
+      </c>
+      <c r="G649" s="1"/>
+      <c r="H649" t="s">
+        <v>1313</v>
+      </c>
+    </row>
+    <row r="650" spans="1:8">
+      <c r="A650" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B650" t="s">
+        <v>1314</v>
+      </c>
+      <c r="C650" s="1">
+        <v>143</v>
+      </c>
+      <c r="D650" s="1">
+        <v>149</v>
+      </c>
+      <c r="E650" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F650" s="1">
+        <v>116</v>
+      </c>
+      <c r="G650" s="1"/>
+      <c r="H650" t="s">
+        <v>1315</v>
+      </c>
+    </row>
+    <row r="651" spans="1:8">
+      <c r="A651" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B651" t="s">
+        <v>1316</v>
+      </c>
+      <c r="C651" s="1">
+        <v>143</v>
+      </c>
+      <c r="D651" s="1">
+        <v>149</v>
+      </c>
+      <c r="E651" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F651" s="1">
+        <v>117</v>
+      </c>
+      <c r="G651" s="1"/>
+      <c r="H651" t="s">
+        <v>1317</v>
+      </c>
+    </row>
+    <row r="652" spans="1:8">
+      <c r="A652" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B652" t="s">
+        <v>1318</v>
+      </c>
+      <c r="C652" s="1">
+        <v>143</v>
+      </c>
+      <c r="D652" s="1">
+        <v>149</v>
+      </c>
+      <c r="E652" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F652" s="1">
+        <v>118</v>
+      </c>
+      <c r="G652" s="1"/>
+      <c r="H652" t="s">
+        <v>1319</v>
+      </c>
+    </row>
+    <row r="653" spans="1:8">
+      <c r="A653" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B653" t="s">
+        <v>1320</v>
+      </c>
+      <c r="C653" s="1">
+        <v>143</v>
+      </c>
+      <c r="D653" s="1">
+        <v>149</v>
+      </c>
+      <c r="E653" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F653" s="1">
+        <v>119</v>
+      </c>
+      <c r="G653" s="1"/>
+      <c r="H653" t="s">
+        <v>1321</v>
+      </c>
+    </row>
+    <row r="654" spans="1:8">
+      <c r="A654" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B654" t="s">
+        <v>1322</v>
+      </c>
+      <c r="C654" s="1">
+        <v>143</v>
+      </c>
+      <c r="D654" s="1">
+        <v>149</v>
+      </c>
+      <c r="E654" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F654" s="1">
+        <v>120</v>
+      </c>
+      <c r="G654" s="1"/>
+      <c r="H654" t="s">
+        <v>1323</v>
+      </c>
+    </row>
+    <row r="655" spans="1:8">
+      <c r="A655" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B655" t="s">
+        <v>1324</v>
+      </c>
+      <c r="C655" s="1">
+        <v>143</v>
+      </c>
+      <c r="D655" s="1">
+        <v>149</v>
+      </c>
+      <c r="E655" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F655" s="1">
+        <v>121</v>
+      </c>
+      <c r="G655" s="1"/>
+      <c r="H655" t="s">
+        <v>1325</v>
+      </c>
+    </row>
+    <row r="656" spans="1:8">
+      <c r="A656" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B656" t="s">
+        <v>1326</v>
+      </c>
+      <c r="C656" s="1">
+        <v>143</v>
+      </c>
+      <c r="D656" s="1">
+        <v>149</v>
+      </c>
+      <c r="E656" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F656" s="1">
+        <v>122</v>
+      </c>
+      <c r="G656" s="1"/>
+      <c r="H656" t="s">
+        <v>1327</v>
+      </c>
+    </row>
+    <row r="657" spans="1:8">
+      <c r="A657" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B657" t="s">
+        <v>1328</v>
+      </c>
+      <c r="C657" s="1">
+        <v>143</v>
+      </c>
+      <c r="D657" s="1">
+        <v>149</v>
+      </c>
+      <c r="E657" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F657" s="1">
+        <v>123</v>
+      </c>
+      <c r="G657" s="1"/>
+      <c r="H657" t="s">
+        <v>1329</v>
+      </c>
+    </row>
+    <row r="658" spans="1:8">
+      <c r="A658" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B658" t="s">
+        <v>1330</v>
+      </c>
+      <c r="C658" s="1">
+        <v>143</v>
+      </c>
+      <c r="D658" s="1">
+        <v>149</v>
+      </c>
+      <c r="E658" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F658" s="1">
+        <v>124</v>
+      </c>
+      <c r="G658" s="1"/>
+      <c r="H658" t="s">
+        <v>1331</v>
+      </c>
+    </row>
+    <row r="659" spans="1:8">
+      <c r="A659" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B659" t="s">
+        <v>1332</v>
+      </c>
+      <c r="C659" s="1">
+        <v>143</v>
+      </c>
+      <c r="D659" s="1">
+        <v>149</v>
+      </c>
+      <c r="E659" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F659" s="1">
+        <v>125</v>
+      </c>
+      <c r="G659" s="1"/>
+      <c r="H659" t="s">
+        <v>1333</v>
+      </c>
+    </row>
+    <row r="660" spans="1:8">
+      <c r="A660" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B660" t="s">
+        <v>1334</v>
+      </c>
+      <c r="C660" s="1">
+        <v>143</v>
+      </c>
+      <c r="D660" s="1">
+        <v>149</v>
+      </c>
+      <c r="E660" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F660" s="1">
+        <v>126</v>
+      </c>
+      <c r="G660" s="1"/>
+      <c r="H660" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="661" spans="1:8">
+      <c r="A661" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B661" t="s">
+        <v>1336</v>
+      </c>
+      <c r="C661" s="1">
+        <v>143</v>
+      </c>
+      <c r="D661" s="1">
+        <v>149</v>
+      </c>
+      <c r="E661" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F661" s="1">
+        <v>127</v>
+      </c>
+      <c r="G661" s="1"/>
+      <c r="H661" t="s">
+        <v>1337</v>
+      </c>
+    </row>
+    <row r="662" spans="1:8">
+      <c r="A662" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B662" t="s">
+        <v>1338</v>
+      </c>
+      <c r="C662" s="1">
+        <v>143</v>
+      </c>
+      <c r="D662" s="1">
+        <v>149</v>
+      </c>
+      <c r="E662" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F662" s="1">
+        <v>128</v>
+      </c>
+      <c r="G662" s="1"/>
+      <c r="H662" t="s">
+        <v>1339</v>
+      </c>
+    </row>
+    <row r="663" spans="1:8">
+      <c r="A663" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B663" t="s">
+        <v>1340</v>
+      </c>
+      <c r="C663" s="1">
+        <v>143</v>
+      </c>
+      <c r="D663" s="1">
+        <v>149</v>
+      </c>
+      <c r="E663" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F663" s="1">
+        <v>129</v>
+      </c>
+      <c r="G663" s="1"/>
+      <c r="H663" t="s">
+        <v>1341</v>
+      </c>
+    </row>
+    <row r="664" spans="1:8">
+      <c r="A664" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B664" t="s">
+        <v>1342</v>
+      </c>
+      <c r="C664" s="1">
+        <v>143</v>
+      </c>
+      <c r="D664" s="1">
+        <v>149</v>
+      </c>
+      <c r="E664" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F664" s="1">
+        <v>130</v>
+      </c>
+      <c r="G664" s="1"/>
+      <c r="H664" t="s">
+        <v>1343</v>
+      </c>
+    </row>
+    <row r="665" spans="1:8">
+      <c r="A665" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B665" t="s">
+        <v>1344</v>
+      </c>
+      <c r="C665" s="1">
+        <v>143</v>
+      </c>
+      <c r="D665" s="1">
+        <v>149</v>
+      </c>
+      <c r="E665" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F665" s="1">
+        <v>131</v>
+      </c>
+      <c r="G665" s="1"/>
+      <c r="H665" t="s">
+        <v>1345</v>
+      </c>
+    </row>
+    <row r="666" spans="1:8">
+      <c r="A666" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B666" t="s">
+        <v>1346</v>
+      </c>
+      <c r="C666" s="1">
+        <v>143</v>
+      </c>
+      <c r="D666" s="1">
+        <v>149</v>
+      </c>
+      <c r="E666" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F666" s="1">
+        <v>132</v>
+      </c>
+      <c r="G666" s="1"/>
+      <c r="H666" t="s">
+        <v>1347</v>
+      </c>
+    </row>
+    <row r="667" spans="1:8">
+      <c r="A667" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B667" t="s">
+        <v>1348</v>
+      </c>
+      <c r="C667" s="1">
+        <v>143</v>
+      </c>
+      <c r="D667" s="1">
+        <v>149</v>
+      </c>
+      <c r="E667" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F667" s="1">
+        <v>133</v>
+      </c>
+      <c r="G667" s="1"/>
+      <c r="H667" t="s">
+        <v>1349</v>
+      </c>
+    </row>
+    <row r="668" spans="1:8">
+      <c r="A668" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B668" t="s">
+        <v>1350</v>
+      </c>
+      <c r="C668" s="1">
+        <v>143</v>
+      </c>
+      <c r="D668" s="1">
+        <v>149</v>
+      </c>
+      <c r="E668" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F668" s="1">
+        <v>134</v>
+      </c>
+      <c r="G668" s="1"/>
+      <c r="H668" t="s">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="669" spans="1:8">
+      <c r="A669" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B669" t="s">
+        <v>1352</v>
+      </c>
+      <c r="C669" s="1">
+        <v>143</v>
+      </c>
+      <c r="D669" s="1">
+        <v>149</v>
+      </c>
+      <c r="E669" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F669" s="1">
+        <v>135</v>
+      </c>
+      <c r="G669" s="1"/>
+      <c r="H669" t="s">
+        <v>1353</v>
+      </c>
+    </row>
+    <row r="670" spans="1:8">
+      <c r="A670" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B670" t="s">
+        <v>1354</v>
+      </c>
+      <c r="C670" s="1">
+        <v>143</v>
+      </c>
+      <c r="D670" s="1">
+        <v>149</v>
+      </c>
+      <c r="E670" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F670" s="1">
+        <v>136</v>
+      </c>
+      <c r="G670" s="1"/>
+      <c r="H670" t="s">
+        <v>1355</v>
+      </c>
+    </row>
+    <row r="671" spans="1:8">
+      <c r="A671" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B671" t="s">
+        <v>1356</v>
+      </c>
+      <c r="C671" s="1">
+        <v>143</v>
+      </c>
+      <c r="D671" s="1">
+        <v>149</v>
+      </c>
+      <c r="E671" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F671" s="1">
+        <v>137</v>
+      </c>
+      <c r="G671" s="1"/>
+      <c r="H671" t="s">
+        <v>1357</v>
+      </c>
+    </row>
+    <row r="672" spans="1:8">
+      <c r="A672" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B672" t="s">
+        <v>1358</v>
+      </c>
+      <c r="C672" s="1">
+        <v>143</v>
+      </c>
+      <c r="D672" s="1">
+        <v>149</v>
+      </c>
+      <c r="E672" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F672" s="1">
+        <v>138</v>
+      </c>
+      <c r="G672" s="1"/>
+      <c r="H672" t="s">
+        <v>1359</v>
+      </c>
+    </row>
+    <row r="673" spans="1:8">
+      <c r="A673" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B673" t="s">
+        <v>1360</v>
+      </c>
+      <c r="C673" s="1">
+        <v>143</v>
+      </c>
+      <c r="D673" s="1">
+        <v>149</v>
+      </c>
+      <c r="E673" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F673" s="1">
+        <v>139</v>
+      </c>
+      <c r="G673" s="1"/>
+      <c r="H673" t="s">
+        <v>1361</v>
+      </c>
+    </row>
+    <row r="674" spans="1:8">
+      <c r="A674" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B674" t="s">
+        <v>1362</v>
+      </c>
+      <c r="C674" s="1">
+        <v>143</v>
+      </c>
+      <c r="D674" s="1">
+        <v>149</v>
+      </c>
+      <c r="E674" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F674" s="1">
+        <v>140</v>
+      </c>
+      <c r="G674" s="1"/>
+      <c r="H674" t="s">
+        <v>1363</v>
+      </c>
+    </row>
+    <row r="675" spans="1:8">
+      <c r="A675" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B675" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C675" s="1">
+        <v>143</v>
+      </c>
+      <c r="D675" s="1">
+        <v>149</v>
+      </c>
+      <c r="E675" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F675" s="1">
+        <v>141</v>
+      </c>
+      <c r="G675" s="1"/>
+      <c r="H675" t="s">
+        <v>1365</v>
+      </c>
+    </row>
+    <row r="676" spans="1:8">
+      <c r="A676" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B676" t="s">
+        <v>1366</v>
+      </c>
+      <c r="C676" s="1">
+        <v>143</v>
+      </c>
+      <c r="D676" s="1">
+        <v>149</v>
+      </c>
+      <c r="E676" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F676" s="1">
+        <v>142</v>
+      </c>
+      <c r="G676" s="1"/>
+      <c r="H676" t="s">
+        <v>1367</v>
+      </c>
+    </row>
+    <row r="677" spans="1:8">
+      <c r="A677" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B677" t="s">
+        <v>1368</v>
+      </c>
+      <c r="C677" s="1">
+        <v>143</v>
+      </c>
+      <c r="D677" s="1">
+        <v>149</v>
+      </c>
+      <c r="E677" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F677" s="1">
+        <v>143</v>
+      </c>
+      <c r="G677" s="1"/>
+      <c r="H677" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="678" spans="1:8">
+      <c r="A678" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B678" t="s">
+        <v>1370</v>
+      </c>
+      <c r="C678" s="1">
+        <v>143</v>
+      </c>
+      <c r="D678" s="1">
+        <v>149</v>
+      </c>
+      <c r="E678" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F678" s="1">
+        <v>144</v>
+      </c>
+      <c r="G678" s="1"/>
+      <c r="H678" t="s">
+        <v>1371</v>
+      </c>
+    </row>
+    <row r="679" spans="1:8">
+      <c r="A679" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B679" t="s">
+        <v>1372</v>
+      </c>
+      <c r="C679" s="1">
+        <v>143</v>
+      </c>
+      <c r="D679" s="1">
+        <v>149</v>
+      </c>
+      <c r="E679" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F679" s="1">
+        <v>145</v>
+      </c>
+      <c r="G679" s="1"/>
+      <c r="H679" t="s">
+        <v>1373</v>
+      </c>
+    </row>
+    <row r="680" spans="1:8">
+      <c r="A680" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B680" t="s">
+        <v>1374</v>
+      </c>
+      <c r="C680" s="1">
+        <v>143</v>
+      </c>
+      <c r="D680" s="1">
+        <v>149</v>
+      </c>
+      <c r="E680" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F680" s="1">
+        <v>146</v>
+      </c>
+      <c r="G680" s="1"/>
+      <c r="H680" t="s">
+        <v>1375</v>
+      </c>
+    </row>
+    <row r="681" spans="1:8">
+      <c r="A681" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B681" t="s">
+        <v>1376</v>
+      </c>
+      <c r="C681" s="1">
+        <v>143</v>
+      </c>
+      <c r="D681" s="1">
+        <v>149</v>
+      </c>
+      <c r="E681" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F681" s="1">
+        <v>147</v>
+      </c>
+      <c r="G681" s="1"/>
+      <c r="H681" t="s">
+        <v>1377</v>
+      </c>
+    </row>
+    <row r="682" spans="1:8">
+      <c r="A682" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B682" t="s">
+        <v>1378</v>
+      </c>
+      <c r="C682" s="1">
+        <v>143</v>
+      </c>
+      <c r="D682" s="1">
+        <v>149</v>
+      </c>
+      <c r="E682" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F682" s="1">
+        <v>148</v>
+      </c>
+      <c r="G682" s="1"/>
+      <c r="H682" t="s">
+        <v>1379</v>
+      </c>
+    </row>
+    <row r="683" spans="1:8">
+      <c r="A683" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B683" t="s">
+        <v>1380</v>
+      </c>
+      <c r="C683" s="1">
+        <v>143</v>
+      </c>
+      <c r="D683" s="1">
+        <v>149</v>
+      </c>
+      <c r="E683" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F683" s="1">
+        <v>149</v>
+      </c>
+      <c r="G683" s="1"/>
+      <c r="H683" t="s">
+        <v>1381</v>
+      </c>
+    </row>
+    <row r="684" spans="1:8">
+      <c r="A684" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B684" t="s">
+        <v>1382</v>
+      </c>
+      <c r="C684" s="1">
+        <v>143</v>
+      </c>
+      <c r="D684" s="1">
+        <v>149</v>
+      </c>
+      <c r="E684" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F684" s="1">
+        <v>150</v>
+      </c>
+      <c r="G684" s="1"/>
+      <c r="H684" t="s">
+        <v>1383</v>
+      </c>
+    </row>
+    <row r="685" spans="1:8">
+      <c r="A685" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B685" t="s">
+        <v>1384</v>
+      </c>
+      <c r="C685" s="1">
+        <v>143</v>
+      </c>
+      <c r="D685" s="1">
+        <v>149</v>
+      </c>
+      <c r="E685" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F685" s="1">
+        <v>151</v>
+      </c>
+      <c r="G685" s="1"/>
+      <c r="H685" t="s">
+        <v>1385</v>
+      </c>
+    </row>
+    <row r="686" spans="1:8">
+      <c r="A686" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B686" t="s">
+        <v>1386</v>
+      </c>
+      <c r="C686" s="1">
+        <v>143</v>
+      </c>
+      <c r="D686" s="1">
+        <v>149</v>
+      </c>
+      <c r="E686" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F686" s="1">
+        <v>152</v>
+      </c>
+      <c r="G686" s="1"/>
+      <c r="H686" t="s">
+        <v>1387</v>
+      </c>
+    </row>
+    <row r="687" spans="1:8">
+      <c r="A687" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B687" t="s">
+        <v>1388</v>
+      </c>
+      <c r="C687" s="1">
+        <v>143</v>
+      </c>
+      <c r="D687" s="1">
+        <v>149</v>
+      </c>
+      <c r="E687" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F687" s="1">
+        <v>153</v>
+      </c>
+      <c r="G687" s="1"/>
+      <c r="H687" t="s">
+        <v>1389</v>
+      </c>
+    </row>
+    <row r="688" spans="1:8">
+      <c r="A688" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B688" t="s">
+        <v>1390</v>
+      </c>
+      <c r="C688" s="1">
+        <v>143</v>
+      </c>
+      <c r="D688" s="1">
+        <v>149</v>
+      </c>
+      <c r="E688" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F688" s="1">
+        <v>154</v>
+      </c>
+      <c r="G688" s="1"/>
+      <c r="H688" t="s">
+        <v>1391</v>
+      </c>
+    </row>
+    <row r="689" spans="1:8">
+      <c r="A689" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B689" t="s">
+        <v>1392</v>
+      </c>
+      <c r="C689" s="1">
+        <v>143</v>
+      </c>
+      <c r="D689" s="1">
+        <v>149</v>
+      </c>
+      <c r="E689" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F689" s="1">
+        <v>155</v>
+      </c>
+      <c r="G689" s="1"/>
+      <c r="H689" t="s">
+        <v>1393</v>
+      </c>
+    </row>
+    <row r="690" spans="1:8">
+      <c r="A690" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B690" t="s">
+        <v>1394</v>
+      </c>
+      <c r="C690" s="1">
+        <v>143</v>
+      </c>
+      <c r="D690" s="1">
+        <v>149</v>
+      </c>
+      <c r="E690" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F690" s="1">
+        <v>156</v>
+      </c>
+      <c r="G690" s="1"/>
+      <c r="H690" t="s">
+        <v>1395</v>
+      </c>
+    </row>
+    <row r="691" spans="1:8">
+      <c r="A691" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B691" t="s">
+        <v>1396</v>
+      </c>
+      <c r="C691" s="1">
+        <v>143</v>
+      </c>
+      <c r="D691" s="1">
+        <v>149</v>
+      </c>
+      <c r="E691" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F691" s="1">
+        <v>157</v>
+      </c>
+      <c r="G691" s="1"/>
+      <c r="H691" t="s">
+        <v>1397</v>
+      </c>
+    </row>
+    <row r="692" spans="1:8">
+      <c r="A692" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B692" t="s">
+        <v>1398</v>
+      </c>
+      <c r="C692" s="1">
+        <v>143</v>
+      </c>
+      <c r="D692" s="1">
+        <v>149</v>
+      </c>
+      <c r="E692" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F692" s="1">
+        <v>158</v>
+      </c>
+      <c r="G692" s="1"/>
+      <c r="H692" t="s">
+        <v>1399</v>
+      </c>
+    </row>
+    <row r="693" spans="1:8">
+      <c r="A693" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B693" t="s">
+        <v>1400</v>
+      </c>
+      <c r="C693" s="1">
+        <v>143</v>
+      </c>
+      <c r="D693" s="1">
+        <v>149</v>
+      </c>
+      <c r="E693" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F693" s="1">
+        <v>159</v>
+      </c>
+      <c r="G693" s="1"/>
+      <c r="H693" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="694" spans="1:8">
+      <c r="A694" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B694" t="s">
+        <v>1402</v>
+      </c>
+      <c r="C694" s="1">
+        <v>143</v>
+      </c>
+      <c r="D694" s="1">
+        <v>149</v>
+      </c>
+      <c r="E694" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F694" s="1">
+        <v>160</v>
+      </c>
+      <c r="G694" s="1"/>
+      <c r="H694" t="s">
+        <v>1403</v>
+      </c>
+    </row>
+    <row r="695" spans="1:8">
+      <c r="A695" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B695" t="s">
+        <v>1404</v>
+      </c>
+      <c r="C695" s="1">
+        <v>143</v>
+      </c>
+      <c r="D695" s="1">
+        <v>149</v>
+      </c>
+      <c r="E695" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F695" s="1">
+        <v>161</v>
+      </c>
+      <c r="G695" s="1"/>
+      <c r="H695" t="s">
+        <v>1405</v>
+      </c>
+    </row>
+    <row r="696" spans="1:8">
+      <c r="A696" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B696" t="s">
+        <v>1406</v>
+      </c>
+      <c r="C696" s="1">
+        <v>143</v>
+      </c>
+      <c r="D696" s="1">
+        <v>149</v>
+      </c>
+      <c r="E696" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F696" s="1">
+        <v>162</v>
+      </c>
+      <c r="G696" s="1"/>
+      <c r="H696" t="s">
+        <v>1407</v>
+      </c>
+    </row>
+    <row r="697" spans="1:8">
+      <c r="A697" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B697" t="s">
+        <v>1408</v>
+      </c>
+      <c r="C697" s="1">
+        <v>143</v>
+      </c>
+      <c r="D697" s="1">
+        <v>149</v>
+      </c>
+      <c r="E697" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F697" s="1">
+        <v>163</v>
+      </c>
+      <c r="G697" s="1"/>
+      <c r="H697" t="s">
+        <v>1409</v>
+      </c>
+    </row>
+    <row r="698" spans="1:8">
+      <c r="A698" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B698" t="s">
+        <v>1410</v>
+      </c>
+      <c r="C698" s="1">
+        <v>143</v>
+      </c>
+      <c r="D698" s="1">
+        <v>149</v>
+      </c>
+      <c r="E698" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F698" s="1">
+        <v>164</v>
+      </c>
+      <c r="G698" s="1"/>
+      <c r="H698" t="s">
+        <v>1411</v>
+      </c>
+    </row>
+    <row r="699" spans="1:8">
+      <c r="A699" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B699" t="s">
+        <v>1412</v>
+      </c>
+      <c r="C699" s="1">
+        <v>143</v>
+      </c>
+      <c r="D699" s="1">
+        <v>149</v>
+      </c>
+      <c r="E699" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F699" s="1">
+        <v>165</v>
+      </c>
+      <c r="G699" s="1"/>
+      <c r="H699" t="s">
+        <v>1413</v>
+      </c>
+    </row>
+    <row r="700" spans="1:8">
+      <c r="A700" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B700" t="s">
+        <v>1414</v>
+      </c>
+      <c r="C700" s="1">
+        <v>143</v>
+      </c>
+      <c r="D700" s="1">
+        <v>149</v>
+      </c>
+      <c r="E700" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F700" s="1">
+        <v>166</v>
+      </c>
+      <c r="G700" s="1"/>
+      <c r="H700" t="s">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="701" spans="1:8">
+      <c r="A701" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B701" t="s">
+        <v>1416</v>
+      </c>
+      <c r="C701" s="1">
+        <v>143</v>
+      </c>
+      <c r="D701" s="1">
+        <v>149</v>
+      </c>
+      <c r="E701" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F701" s="1">
+        <v>167</v>
+      </c>
+      <c r="G701" s="1"/>
+      <c r="H701" t="s">
+        <v>1417</v>
+      </c>
+    </row>
+    <row r="702" spans="1:8">
+      <c r="A702" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B702" t="s">
+        <v>1418</v>
+      </c>
+      <c r="C702" s="1">
+        <v>143</v>
+      </c>
+      <c r="D702" s="1">
+        <v>149</v>
+      </c>
+      <c r="E702" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F702" s="1">
+        <v>168</v>
+      </c>
+      <c r="G702" s="1"/>
+      <c r="H702" t="s">
+        <v>1419</v>
+      </c>
+    </row>
+    <row r="703" spans="1:8">
+      <c r="A703" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B703" t="s">
+        <v>1420</v>
+      </c>
+      <c r="C703" s="1">
+        <v>143</v>
+      </c>
+      <c r="D703" s="1">
+        <v>149</v>
+      </c>
+      <c r="E703" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F703" s="1">
+        <v>169</v>
+      </c>
+      <c r="G703" s="1"/>
+      <c r="H703" t="s">
+        <v>1421</v>
+      </c>
+    </row>
+    <row r="704" spans="1:8">
+      <c r="A704" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B704" t="s">
+        <v>1422</v>
+      </c>
+      <c r="C704" s="1">
+        <v>143</v>
+      </c>
+      <c r="D704" s="1">
+        <v>149</v>
+      </c>
+      <c r="E704" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F704" s="1">
+        <v>170</v>
+      </c>
+      <c r="G704" s="1"/>
+      <c r="H704" t="s">
+        <v>1423</v>
+      </c>
+    </row>
+    <row r="705" spans="1:8">
+      <c r="A705" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B705" t="s">
+        <v>1424</v>
+      </c>
+      <c r="C705" s="1">
+        <v>143</v>
+      </c>
+      <c r="D705" s="1">
+        <v>149</v>
+      </c>
+      <c r="E705" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F705" s="1">
+        <v>171</v>
+      </c>
+      <c r="G705" s="1"/>
+      <c r="H705" t="s">
+        <v>1425</v>
+      </c>
+    </row>
+    <row r="706" spans="1:8">
+      <c r="A706" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B706" t="s">
+        <v>1426</v>
+      </c>
+      <c r="C706" s="1">
+        <v>143</v>
+      </c>
+      <c r="D706" s="1">
+        <v>149</v>
+      </c>
+      <c r="E706" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F706" s="1">
+        <v>172</v>
+      </c>
+      <c r="G706" s="1"/>
+      <c r="H706" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="707" spans="1:8">
+      <c r="A707" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B707" t="s">
+        <v>1428</v>
+      </c>
+      <c r="C707" s="1">
+        <v>143</v>
+      </c>
+      <c r="D707" s="1">
+        <v>149</v>
+      </c>
+      <c r="E707" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F707" s="1">
+        <v>173</v>
+      </c>
+      <c r="G707" s="1"/>
+      <c r="H707" t="s">
+        <v>1429</v>
+      </c>
+    </row>
+    <row r="708" spans="1:8">
+      <c r="A708" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B708" t="s">
+        <v>1430</v>
+      </c>
+      <c r="C708" s="1">
+        <v>143</v>
+      </c>
+      <c r="D708" s="1">
+        <v>149</v>
+      </c>
+      <c r="E708" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F708" s="1">
+        <v>174</v>
+      </c>
+      <c r="G708" s="1"/>
+      <c r="H708" t="s">
+        <v>1431</v>
+      </c>
+    </row>
+    <row r="709" spans="1:8">
+      <c r="A709" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B709" t="s">
+        <v>1432</v>
+      </c>
+      <c r="C709" s="1">
+        <v>143</v>
+      </c>
+      <c r="D709" s="1">
+        <v>149</v>
+      </c>
+      <c r="E709" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F709" s="1">
+        <v>175</v>
+      </c>
+      <c r="G709" s="1"/>
+      <c r="H709" t="s">
+        <v>1433</v>
+      </c>
+    </row>
+    <row r="710" spans="1:8">
+      <c r="A710" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B710" t="s">
+        <v>1434</v>
+      </c>
+      <c r="C710" s="1">
+        <v>143</v>
+      </c>
+      <c r="D710" s="1">
+        <v>149</v>
+      </c>
+      <c r="E710" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F710" s="1">
+        <v>176</v>
+      </c>
+      <c r="G710" s="1"/>
+      <c r="H710" t="s">
+        <v>1435</v>
+      </c>
+    </row>
+    <row r="711" spans="1:8">
+      <c r="A711" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B711" t="s">
+        <v>1436</v>
+      </c>
+      <c r="C711" s="1">
+        <v>143</v>
+      </c>
+      <c r="D711" s="1">
+        <v>149</v>
+      </c>
+      <c r="E711" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F711" s="1">
+        <v>177</v>
+      </c>
+      <c r="G711" s="1"/>
+      <c r="H711" t="s">
+        <v>1437</v>
+      </c>
+    </row>
+    <row r="712" spans="1:8">
+      <c r="A712" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B712" t="s">
+        <v>1438</v>
+      </c>
+      <c r="C712" s="1">
+        <v>143</v>
+      </c>
+      <c r="D712" s="1">
+        <v>149</v>
+      </c>
+      <c r="E712" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F712" s="1">
+        <v>178</v>
+      </c>
+      <c r="G712" s="1"/>
+      <c r="H712" t="s">
+        <v>1439</v>
+      </c>
+    </row>
+    <row r="713" spans="1:8">
+      <c r="A713" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B713" t="s">
+        <v>1440</v>
+      </c>
+      <c r="C713" s="1">
+        <v>143</v>
+      </c>
+      <c r="D713" s="1">
+        <v>149</v>
+      </c>
+      <c r="E713" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F713" s="1">
+        <v>179</v>
+      </c>
+      <c r="G713" s="1"/>
+      <c r="H713" t="s">
+        <v>1441</v>
+      </c>
+    </row>
+    <row r="714" spans="1:8">
+      <c r="A714" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B714" t="s">
+        <v>1442</v>
+      </c>
+      <c r="C714" s="1">
+        <v>143</v>
+      </c>
+      <c r="D714" s="1">
+        <v>149</v>
+      </c>
+      <c r="E714" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F714" s="1">
+        <v>180</v>
+      </c>
+      <c r="G714" s="1"/>
+      <c r="H714" t="s">
+        <v>1443</v>
+      </c>
+    </row>
+    <row r="715" spans="1:8">
+      <c r="A715" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B715" t="s">
+        <v>1444</v>
+      </c>
+      <c r="C715" s="1">
+        <v>143</v>
+      </c>
+      <c r="D715" s="1">
+        <v>149</v>
+      </c>
+      <c r="E715" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F715" s="1">
+        <v>181</v>
+      </c>
+      <c r="G715" s="1"/>
+      <c r="H715" t="s">
+        <v>1445</v>
+      </c>
+    </row>
+    <row r="716" spans="1:8">
+      <c r="A716" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B716" t="s">
+        <v>1446</v>
+      </c>
+      <c r="C716" s="1">
+        <v>143</v>
+      </c>
+      <c r="D716" s="1">
+        <v>149</v>
+      </c>
+      <c r="E716" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F716" s="1">
+        <v>182</v>
+      </c>
+      <c r="G716" s="1"/>
+      <c r="H716" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="717" spans="1:8">
+      <c r="A717" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B717" t="s">
+        <v>1448</v>
+      </c>
+      <c r="C717" s="1">
+        <v>143</v>
+      </c>
+      <c r="D717" s="1">
+        <v>149</v>
+      </c>
+      <c r="E717" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F717" s="1">
+        <v>183</v>
+      </c>
+      <c r="G717" s="1"/>
+      <c r="H717" t="s">
+        <v>1449</v>
+      </c>
+    </row>
+    <row r="718" spans="1:8">
+      <c r="A718" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B718" t="s">
+        <v>1450</v>
+      </c>
+      <c r="C718" s="1">
+        <v>143</v>
+      </c>
+      <c r="D718" s="1">
+        <v>149</v>
+      </c>
+      <c r="E718" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F718" s="1">
+        <v>184</v>
+      </c>
+      <c r="G718" s="1"/>
+      <c r="H718" t="s">
+        <v>1451</v>
+      </c>
+    </row>
+    <row r="719" spans="1:8">
+      <c r="A719" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B719" t="s">
+        <v>1452</v>
+      </c>
+      <c r="C719" s="1">
+        <v>143</v>
+      </c>
+      <c r="D719" s="1">
+        <v>149</v>
+      </c>
+      <c r="E719" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F719" s="1">
+        <v>185</v>
+      </c>
+      <c r="G719" s="1"/>
+      <c r="H719" t="s">
+        <v>1453</v>
+      </c>
+    </row>
+    <row r="720" spans="1:8">
+      <c r="A720" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B720" t="s">
+        <v>1454</v>
+      </c>
+      <c r="C720" s="1">
+        <v>143</v>
+      </c>
+      <c r="D720" s="1">
+        <v>149</v>
+      </c>
+      <c r="E720" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F720" s="1">
+        <v>186</v>
+      </c>
+      <c r="G720" s="1"/>
+      <c r="H720" t="s">
+        <v>1455</v>
+      </c>
+    </row>
+    <row r="721" spans="1:8">
+      <c r="A721" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B721" t="s">
+        <v>1456</v>
+      </c>
+      <c r="C721" s="1">
+        <v>143</v>
+      </c>
+      <c r="D721" s="1">
+        <v>149</v>
+      </c>
+      <c r="E721" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F721" s="1">
+        <v>187</v>
+      </c>
+      <c r="G721" s="1"/>
+      <c r="H721" t="s">
+        <v>1457</v>
+      </c>
+    </row>
+    <row r="722" spans="1:8">
+      <c r="A722" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B722" t="s">
+        <v>1458</v>
+      </c>
+      <c r="C722" s="1">
+        <v>143</v>
+      </c>
+      <c r="D722" s="1">
+        <v>149</v>
+      </c>
+      <c r="E722" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F722" s="1">
+        <v>188</v>
+      </c>
+      <c r="G722" s="1"/>
+      <c r="H722" t="s">
+        <v>1459</v>
+      </c>
+    </row>
+    <row r="723" spans="1:8">
+      <c r="A723" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B723" t="s">
+        <v>1460</v>
+      </c>
+      <c r="C723" s="1">
+        <v>143</v>
+      </c>
+      <c r="D723" s="1">
+        <v>149</v>
+      </c>
+      <c r="E723" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F723" s="1">
+        <v>189</v>
+      </c>
+      <c r="G723" s="1"/>
+      <c r="H723" t="s">
+        <v>1461</v>
+      </c>
+    </row>
+    <row r="724" spans="1:8">
+      <c r="A724" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B724" t="s">
+        <v>1462</v>
+      </c>
+      <c r="C724" s="1">
+        <v>143</v>
+      </c>
+      <c r="D724" s="1">
+        <v>149</v>
+      </c>
+      <c r="E724" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F724" s="1">
+        <v>190</v>
+      </c>
+      <c r="G724" s="1"/>
+      <c r="H724" t="s">
+        <v>1463</v>
+      </c>
+    </row>
+    <row r="725" spans="1:8">
+      <c r="A725" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B725" t="s">
+        <v>1464</v>
+      </c>
+      <c r="C725" s="1">
+        <v>143</v>
+      </c>
+      <c r="D725" s="1">
+        <v>149</v>
+      </c>
+      <c r="E725" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F725" s="1">
+        <v>191</v>
+      </c>
+      <c r="G725" s="1"/>
+      <c r="H725" t="s">
+        <v>1465</v>
+      </c>
+    </row>
+    <row r="726" spans="1:8">
+      <c r="A726" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B726" t="s">
+        <v>1466</v>
+      </c>
+      <c r="C726" s="1">
+        <v>143</v>
+      </c>
+      <c r="D726" s="1">
+        <v>149</v>
+      </c>
+      <c r="E726" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F726" s="1">
+        <v>192</v>
+      </c>
+      <c r="G726" s="1"/>
+      <c r="H726" t="s">
+        <v>1467</v>
+      </c>
+    </row>
+    <row r="727" spans="1:8">
+      <c r="A727" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B727" t="s">
+        <v>1468</v>
+      </c>
+      <c r="C727" s="1">
+        <v>143</v>
+      </c>
+      <c r="D727" s="1">
+        <v>149</v>
+      </c>
+      <c r="E727" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F727" s="1">
+        <v>193</v>
+      </c>
+      <c r="G727" s="1"/>
+      <c r="H727" t="s">
+        <v>1469</v>
+      </c>
+    </row>
+    <row r="728" spans="1:8">
+      <c r="A728" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B728" t="s">
+        <v>1470</v>
+      </c>
+      <c r="C728" s="1">
+        <v>143</v>
+      </c>
+      <c r="D728" s="1">
+        <v>149</v>
+      </c>
+      <c r="E728" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F728" s="1">
+        <v>194</v>
+      </c>
+      <c r="G728" s="1"/>
+      <c r="H728" t="s">
+        <v>1471</v>
+      </c>
+    </row>
+    <row r="729" spans="1:8">
+      <c r="A729" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B729" t="s">
+        <v>1472</v>
+      </c>
+      <c r="C729" s="1">
+        <v>143</v>
+      </c>
+      <c r="D729" s="1">
+        <v>149</v>
+      </c>
+      <c r="E729" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F729" s="1">
+        <v>195</v>
+      </c>
+      <c r="G729" s="1"/>
+      <c r="H729" t="s">
+        <v>1473</v>
+      </c>
+    </row>
+    <row r="730" spans="1:8">
+      <c r="A730" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B730" t="s">
+        <v>1474</v>
+      </c>
+      <c r="C730" s="1">
+        <v>143</v>
+      </c>
+      <c r="D730" s="1">
+        <v>149</v>
+      </c>
+      <c r="E730" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F730" s="1">
+        <v>196</v>
+      </c>
+      <c r="G730" s="1"/>
+      <c r="H730" t="s">
+        <v>1475</v>
+      </c>
+    </row>
+    <row r="731" spans="1:8">
+      <c r="A731" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B731" t="s">
+        <v>1476</v>
+      </c>
+      <c r="C731" s="1">
+        <v>143</v>
+      </c>
+      <c r="D731" s="1">
+        <v>149</v>
+      </c>
+      <c r="E731" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F731" s="1">
+        <v>197</v>
+      </c>
+      <c r="G731" s="1"/>
+      <c r="H731" t="s">
+        <v>1477</v>
+      </c>
+    </row>
+    <row r="732" spans="1:8">
+      <c r="A732" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B732" t="s">
+        <v>1478</v>
+      </c>
+      <c r="C732" s="1">
+        <v>143</v>
+      </c>
+      <c r="D732" s="1">
+        <v>149</v>
+      </c>
+      <c r="E732" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F732" s="1">
+        <v>198</v>
+      </c>
+      <c r="G732" s="1"/>
+      <c r="H732" t="s">
+        <v>1479</v>
+      </c>
+    </row>
+    <row r="733" spans="1:8">
+      <c r="A733" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B733" t="s">
+        <v>1480</v>
+      </c>
+      <c r="C733" s="1">
+        <v>143</v>
+      </c>
+      <c r="D733" s="1">
+        <v>149</v>
+      </c>
+      <c r="E733" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F733" s="1">
+        <v>199</v>
+      </c>
+      <c r="G733" s="1"/>
+      <c r="H733" t="s">
+        <v>1481</v>
+      </c>
+    </row>
+    <row r="734" spans="1:8">
+      <c r="A734" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B734" t="s">
+        <v>1482</v>
+      </c>
+      <c r="C734" s="1">
+        <v>143</v>
+      </c>
+      <c r="D734" s="1">
+        <v>149</v>
+      </c>
+      <c r="E734" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F734" s="1">
+        <v>200</v>
+      </c>
+      <c r="G734" s="1"/>
+      <c r="H734" t="s">
+        <v>1483</v>
+      </c>
+    </row>
+    <row r="735" spans="1:8">
+      <c r="A735" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B735" t="s">
+        <v>1484</v>
+      </c>
+      <c r="C735" s="1">
+        <v>143</v>
+      </c>
+      <c r="D735" s="1">
+        <v>149</v>
+      </c>
+      <c r="E735" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F735" s="1">
+        <v>201</v>
+      </c>
+      <c r="G735" s="1"/>
+      <c r="H735" t="s">
+        <v>1485</v>
+      </c>
+    </row>
+    <row r="736" spans="1:8">
+      <c r="A736" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B736" t="s">
+        <v>1486</v>
+      </c>
+      <c r="C736" s="1">
+        <v>143</v>
+      </c>
+      <c r="D736" s="1">
+        <v>149</v>
+      </c>
+      <c r="E736" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F736" s="1">
+        <v>202</v>
+      </c>
+      <c r="G736" s="1"/>
+      <c r="H736" t="s">
+        <v>1487</v>
+      </c>
+    </row>
+    <row r="737" spans="1:8">
+      <c r="A737" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B737" t="s">
+        <v>1488</v>
+      </c>
+      <c r="C737" s="1">
+        <v>143</v>
+      </c>
+      <c r="D737" s="1">
+        <v>149</v>
+      </c>
+      <c r="E737" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F737" s="1">
+        <v>203</v>
+      </c>
+      <c r="G737" s="1"/>
+      <c r="H737" t="s">
+        <v>1489</v>
+      </c>
+    </row>
+    <row r="738" spans="1:8">
+      <c r="A738" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B738" t="s">
+        <v>1490</v>
+      </c>
+      <c r="C738" s="1">
+        <v>143</v>
+      </c>
+      <c r="D738" s="1">
+        <v>149</v>
+      </c>
+      <c r="E738" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F738" s="1">
+        <v>204</v>
+      </c>
+      <c r="G738" s="1"/>
+      <c r="H738" t="s">
+        <v>1491</v>
+      </c>
+    </row>
+    <row r="739" spans="1:8">
+      <c r="A739" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B739" t="s">
+        <v>1492</v>
+      </c>
+      <c r="C739" s="1">
+        <v>143</v>
+      </c>
+      <c r="D739" s="1">
+        <v>149</v>
+      </c>
+      <c r="E739" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F739" s="1">
+        <v>205</v>
+      </c>
+      <c r="G739" s="1"/>
+      <c r="H739" t="s">
+        <v>1493</v>
+      </c>
+    </row>
+    <row r="740" spans="1:8">
+      <c r="A740" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B740" t="s">
+        <v>1494</v>
+      </c>
+      <c r="C740" s="1">
+        <v>143</v>
+      </c>
+      <c r="D740" s="1">
+        <v>149</v>
+      </c>
+      <c r="E740" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F740" s="1">
+        <v>206</v>
+      </c>
+      <c r="G740" s="1"/>
+      <c r="H740" t="s">
+        <v>1495</v>
+      </c>
+    </row>
+    <row r="741" spans="1:8">
+      <c r="A741" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B741" t="s">
+        <v>1496</v>
+      </c>
+      <c r="C741" s="1">
+        <v>143</v>
+      </c>
+      <c r="D741" s="1">
+        <v>149</v>
+      </c>
+      <c r="E741" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F741" s="1">
+        <v>207</v>
+      </c>
+      <c r="G741" s="1"/>
+      <c r="H741" t="s">
+        <v>1497</v>
+      </c>
+    </row>
+    <row r="742" spans="1:8">
+      <c r="A742" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B742" t="s">
+        <v>1498</v>
+      </c>
+      <c r="C742" s="1">
+        <v>143</v>
+      </c>
+      <c r="D742" s="1">
+        <v>149</v>
+      </c>
+      <c r="E742" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F742" s="1">
+        <v>208</v>
+      </c>
+      <c r="G742" s="1"/>
+      <c r="H742" t="s">
+        <v>1499</v>
+      </c>
+    </row>
+    <row r="743" spans="1:8">
+      <c r="A743" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B743" t="s">
+        <v>1500</v>
+      </c>
+      <c r="C743" s="1">
+        <v>143</v>
+      </c>
+      <c r="D743" s="1">
+        <v>149</v>
+      </c>
+      <c r="E743" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F743" s="1">
+        <v>209</v>
+      </c>
+      <c r="G743" s="1"/>
+      <c r="H743" t="s">
+        <v>1501</v>
+      </c>
+    </row>
+    <row r="744" spans="1:8">
+      <c r="A744" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B744" t="s">
+        <v>1502</v>
+      </c>
+      <c r="C744" s="1">
+        <v>143</v>
+      </c>
+      <c r="D744" s="1">
+        <v>149</v>
+      </c>
+      <c r="E744" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F744" s="1">
+        <v>210</v>
+      </c>
+      <c r="G744" s="1"/>
+      <c r="H744" t="s">
+        <v>1503</v>
+      </c>
+    </row>
+    <row r="745" spans="1:8">
+      <c r="A745" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B745" t="s">
+        <v>1504</v>
+      </c>
+      <c r="C745" s="1">
+        <v>143</v>
+      </c>
+      <c r="D745" s="1">
+        <v>244</v>
+      </c>
+      <c r="E745" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F745" s="1">
+        <v>1</v>
+      </c>
+      <c r="G745" s="1"/>
+      <c r="H745" t="s">
+        <v>1505</v>
+      </c>
+    </row>
+    <row r="746" spans="1:8">
+      <c r="A746" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B746" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C746" s="1">
+        <v>143</v>
+      </c>
+      <c r="D746" s="1">
+        <v>244</v>
+      </c>
+      <c r="E746" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F746" s="1">
+        <v>2</v>
+      </c>
+      <c r="G746" s="1"/>
+      <c r="H746" t="s">
+        <v>1507</v>
+      </c>
+    </row>
+    <row r="747" spans="1:8">
+      <c r="A747" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B747" t="s">
+        <v>1508</v>
+      </c>
+      <c r="C747" s="1">
+        <v>143</v>
+      </c>
+      <c r="D747" s="1">
+        <v>244</v>
+      </c>
+      <c r="E747" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F747" s="1">
+        <v>3</v>
+      </c>
+      <c r="G747" s="1"/>
+      <c r="H747" t="s">
+        <v>1509</v>
+      </c>
+    </row>
+    <row r="748" spans="1:8">
+      <c r="A748" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B748" t="s">
+        <v>1510</v>
+      </c>
+      <c r="C748" s="1">
+        <v>143</v>
+      </c>
+      <c r="D748" s="1">
+        <v>244</v>
+      </c>
+      <c r="E748" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F748" s="1">
+        <v>4</v>
+      </c>
+      <c r="G748" s="1"/>
+      <c r="H748" t="s">
+        <v>1511</v>
+      </c>
+    </row>
+    <row r="749" spans="1:8">
+      <c r="A749" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B749" t="s">
+        <v>1512</v>
+      </c>
+      <c r="C749" s="1">
+        <v>143</v>
+      </c>
+      <c r="D749" s="1">
+        <v>244</v>
+      </c>
+      <c r="E749" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F749" s="1">
+        <v>5</v>
+      </c>
+      <c r="G749" s="1"/>
+      <c r="H749" t="s">
+        <v>1513</v>
+      </c>
+    </row>
+    <row r="750" spans="1:8">
+      <c r="A750" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B750" t="s">
+        <v>1514</v>
+      </c>
+      <c r="C750" s="1">
+        <v>143</v>
+      </c>
+      <c r="D750" s="1">
+        <v>244</v>
+      </c>
+      <c r="E750" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F750" s="1">
+        <v>6</v>
+      </c>
+      <c r="G750" s="1"/>
+      <c r="H750" t="s">
+        <v>1515</v>
+      </c>
+    </row>
+    <row r="751" spans="1:8">
+      <c r="A751" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B751" t="s">
+        <v>1516</v>
+      </c>
+      <c r="C751" s="1">
+        <v>143</v>
+      </c>
+      <c r="D751" s="1">
+        <v>244</v>
+      </c>
+      <c r="E751" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F751" s="1">
+        <v>20</v>
+      </c>
+      <c r="G751" s="1"/>
+      <c r="H751" t="s">
+        <v>1517</v>
+      </c>
+    </row>
+    <row r="752" spans="1:8">
+      <c r="A752" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B752" t="s">
+        <v>1518</v>
+      </c>
+      <c r="C752" s="1">
+        <v>143</v>
+      </c>
+      <c r="D752" s="1">
+        <v>244</v>
+      </c>
+      <c r="E752" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F752" s="1">
+        <v>29</v>
+      </c>
+      <c r="G752" s="1"/>
+      <c r="H752" t="s">
+        <v>1519</v>
+      </c>
+    </row>
+    <row r="753" spans="1:8">
+      <c r="A753" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B753" t="s">
+        <v>1520</v>
+      </c>
+      <c r="C753" s="1">
+        <v>143</v>
+      </c>
+      <c r="D753" s="1">
+        <v>244</v>
+      </c>
+      <c r="E753" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F753" s="1">
+        <v>40</v>
+      </c>
+      <c r="G753" s="1"/>
+      <c r="H753" t="s">
+        <v>1521</v>
+      </c>
+    </row>
+    <row r="754" spans="1:8">
+      <c r="A754" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B754" t="s">
+        <v>1522</v>
+      </c>
+      <c r="C754" s="1">
+        <v>143</v>
+      </c>
+      <c r="D754" s="1">
+        <v>244</v>
+      </c>
+      <c r="E754" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F754" s="1">
+        <v>46</v>
+      </c>
+      <c r="G754" s="1"/>
+      <c r="H754" t="s">
+        <v>1523</v>
+      </c>
+    </row>
+    <row r="755" spans="1:8">
+      <c r="A755" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B755" t="s">
+        <v>1524</v>
+      </c>
+      <c r="C755" s="1">
+        <v>143</v>
+      </c>
+      <c r="D755" s="1">
+        <v>244</v>
+      </c>
+      <c r="E755" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F755" s="1">
+        <v>49</v>
+      </c>
+      <c r="G755" s="1"/>
+      <c r="H755" t="s">
+        <v>1525</v>
+      </c>
+    </row>
+    <row r="756" spans="1:8">
+      <c r="A756" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B756" t="s">
+        <v>1526</v>
+      </c>
+      <c r="C756" s="1">
+        <v>143</v>
+      </c>
+      <c r="D756" s="1">
+        <v>244</v>
+      </c>
+      <c r="E756" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F756" s="1">
+        <v>55</v>
+      </c>
+      <c r="G756" s="1"/>
+      <c r="H756" t="s">
+        <v>1527</v>
+      </c>
+    </row>
+    <row r="757" spans="1:8">
+      <c r="A757" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B757" t="s">
+        <v>1528</v>
+      </c>
+      <c r="C757" s="1">
+        <v>143</v>
+      </c>
+      <c r="D757" s="1">
+        <v>244</v>
+      </c>
+      <c r="E757" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F757" s="1">
+        <v>60</v>
+      </c>
+      <c r="G757" s="1"/>
+      <c r="H757" t="s">
+        <v>1529</v>
+      </c>
+    </row>
+    <row r="758" spans="1:8">
+      <c r="A758" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B758" t="s">
+        <v>1530</v>
+      </c>
+      <c r="C758" s="1">
+        <v>143</v>
+      </c>
+      <c r="D758" s="1">
+        <v>244</v>
+      </c>
+      <c r="E758" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F758" s="1">
+        <v>70</v>
+      </c>
+      <c r="G758" s="1"/>
+      <c r="H758" t="s">
+        <v>1531</v>
+      </c>
+    </row>
+    <row r="759" spans="1:8">
+      <c r="A759" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B759" t="s">
+        <v>1532</v>
+      </c>
+      <c r="C759" s="1">
+        <v>143</v>
+      </c>
+      <c r="D759" s="1">
+        <v>244</v>
+      </c>
+      <c r="E759" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F759" s="1">
+        <v>72</v>
+      </c>
+      <c r="G759" s="1"/>
+      <c r="H759" t="s">
+        <v>1533</v>
+      </c>
+    </row>
+    <row r="760" spans="1:8">
+      <c r="A760" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B760" t="s">
+        <v>1534</v>
+      </c>
+      <c r="C760" s="1">
+        <v>143</v>
+      </c>
+      <c r="D760" s="1">
+        <v>244</v>
+      </c>
+      <c r="E760" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F760" s="1">
+        <v>76</v>
+      </c>
+      <c r="G760" s="1"/>
+      <c r="H760" t="s">
+        <v>1535</v>
+      </c>
+    </row>
+    <row r="761" spans="1:8">
+      <c r="A761" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B761" t="s">
+        <v>1536</v>
+      </c>
+      <c r="C761" s="1">
+        <v>143</v>
+      </c>
+      <c r="D761" s="1">
+        <v>244</v>
+      </c>
+      <c r="E761" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F761" s="1">
+        <v>77</v>
+      </c>
+      <c r="G761" s="1"/>
+      <c r="H761" t="s">
+        <v>1537</v>
+      </c>
+    </row>
+    <row r="762" spans="1:8">
+      <c r="A762" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B762" t="s">
+        <v>1538</v>
+      </c>
+      <c r="C762" s="1">
+        <v>143</v>
+      </c>
+      <c r="D762" s="1">
+        <v>244</v>
+      </c>
+      <c r="E762" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F762" s="1">
+        <v>79</v>
+      </c>
+      <c r="G762" s="1"/>
+      <c r="H762" t="s">
+        <v>1539</v>
+      </c>
+    </row>
+    <row r="763" spans="1:8">
+      <c r="A763" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B763" t="s">
+        <v>1540</v>
+      </c>
+      <c r="C763" s="1">
+        <v>143</v>
+      </c>
+      <c r="D763" s="1">
+        <v>244</v>
+      </c>
+      <c r="E763" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F763" s="1">
+        <v>81</v>
+      </c>
+      <c r="G763" s="1"/>
+      <c r="H763" t="s">
+        <v>1541</v>
+      </c>
+    </row>
+    <row r="764" spans="1:8">
+      <c r="A764" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B764" t="s">
+        <v>1542</v>
+      </c>
+      <c r="C764" s="1">
+        <v>143</v>
+      </c>
+      <c r="D764" s="1">
+        <v>244</v>
+      </c>
+      <c r="E764" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F764" s="1">
+        <v>83</v>
+      </c>
+      <c r="G764" s="1"/>
+      <c r="H764" t="s">
+        <v>1543</v>
+      </c>
+    </row>
+    <row r="765" spans="1:8">
+      <c r="A765" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B765" t="s">
+        <v>1544</v>
+      </c>
+      <c r="C765" s="1">
+        <v>143</v>
+      </c>
+      <c r="D765" s="1">
+        <v>244</v>
+      </c>
+      <c r="E765" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F765" s="1">
+        <v>85</v>
+      </c>
+      <c r="G765" s="1"/>
+      <c r="H765" t="s">
+        <v>1545</v>
+      </c>
+    </row>
+    <row r="766" spans="1:8">
+      <c r="A766" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B766" t="s">
+        <v>1546</v>
+      </c>
+      <c r="C766" s="1">
+        <v>143</v>
+      </c>
+      <c r="D766" s="1">
+        <v>244</v>
+      </c>
+      <c r="E766" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F766" s="1">
+        <v>86</v>
+      </c>
+      <c r="G766" s="1"/>
+      <c r="H766" t="s">
+        <v>1547</v>
+      </c>
+    </row>
+    <row r="767" spans="1:8">
+      <c r="A767" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B767" t="s">
+        <v>1548</v>
+      </c>
+      <c r="C767" s="1">
+        <v>143</v>
+      </c>
+      <c r="D767" s="1">
+        <v>244</v>
+      </c>
+      <c r="E767" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F767" s="1">
+        <v>87</v>
+      </c>
+      <c r="G767" s="1"/>
+      <c r="H767" t="s">
+        <v>1549</v>
+      </c>
+    </row>
+    <row r="768" spans="1:8">
+      <c r="A768" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B768" t="s">
+        <v>1550</v>
+      </c>
+      <c r="C768" s="1">
+        <v>143</v>
+      </c>
+      <c r="D768" s="1">
+        <v>244</v>
+      </c>
+      <c r="E768" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F768" s="1">
+        <v>88</v>
+      </c>
+      <c r="G768" s="1"/>
+      <c r="H768" t="s">
+        <v>1551</v>
+      </c>
+    </row>
+    <row r="769" spans="1:8">
+      <c r="A769" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B769" t="s">
+        <v>1552</v>
+      </c>
+      <c r="C769" s="1">
+        <v>143</v>
+      </c>
+      <c r="D769" s="1">
+        <v>244</v>
+      </c>
+      <c r="E769" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F769" s="1">
+        <v>89</v>
+      </c>
+      <c r="G769" s="1"/>
+      <c r="H769" t="s">
+        <v>1553</v>
+      </c>
+    </row>
+    <row r="770" spans="1:8">
+      <c r="A770" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B770" t="s">
+        <v>1554</v>
+      </c>
+      <c r="C770" s="1">
+        <v>143</v>
+      </c>
+      <c r="D770" s="1">
+        <v>244</v>
+      </c>
+      <c r="E770" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F770" s="1">
+        <v>90</v>
+      </c>
+      <c r="G770" s="1"/>
+      <c r="H770" t="s">
+        <v>1555</v>
+      </c>
+    </row>
+    <row r="771" spans="1:8">
+      <c r="A771" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B771" t="s">
+        <v>1556</v>
+      </c>
+      <c r="C771" s="1">
+        <v>143</v>
+      </c>
+      <c r="D771" s="1">
+        <v>244</v>
+      </c>
+      <c r="E771" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F771" s="1">
+        <v>91</v>
+      </c>
+      <c r="G771" s="1"/>
+      <c r="H771" t="s">
+        <v>1557</v>
+      </c>
+    </row>
+    <row r="772" spans="1:8">
+      <c r="A772" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B772" t="s">
+        <v>1558</v>
+      </c>
+      <c r="C772" s="1">
+        <v>143</v>
+      </c>
+      <c r="D772" s="1">
+        <v>244</v>
+      </c>
+      <c r="E772" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F772" s="1">
+        <v>92</v>
+      </c>
+      <c r="G772" s="1"/>
+      <c r="H772" t="s">
+        <v>1559</v>
+      </c>
+    </row>
+    <row r="773" spans="1:8">
+      <c r="A773" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B773" t="s">
+        <v>1560</v>
+      </c>
+      <c r="C773" s="1">
+        <v>143</v>
+      </c>
+      <c r="D773" s="1">
+        <v>244</v>
+      </c>
+      <c r="E773" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F773" s="1">
+        <v>93</v>
+      </c>
+      <c r="G773" s="1"/>
+      <c r="H773" t="s">
+        <v>1561</v>
+      </c>
+    </row>
+    <row r="774" spans="1:8">
+      <c r="A774" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B774" t="s">
+        <v>1562</v>
+      </c>
+      <c r="C774" s="1">
+        <v>143</v>
+      </c>
+      <c r="D774" s="1">
+        <v>244</v>
+      </c>
+      <c r="E774" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F774" s="1">
+        <v>94</v>
+      </c>
+      <c r="G774" s="1"/>
+      <c r="H774" t="s">
+        <v>1563</v>
+      </c>
+    </row>
+    <row r="775" spans="1:8">
+      <c r="A775" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B775" t="s">
+        <v>1564</v>
+      </c>
+      <c r="C775" s="1">
+        <v>143</v>
+      </c>
+      <c r="D775" s="1">
+        <v>244</v>
+      </c>
+      <c r="E775" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F775" s="1">
+        <v>95</v>
+      </c>
+      <c r="G775" s="1"/>
+      <c r="H775" t="s">
+        <v>1565</v>
+      </c>
+    </row>
+    <row r="776" spans="1:8">
+      <c r="A776" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B776" t="s">
+        <v>1566</v>
+      </c>
+      <c r="C776" s="1">
+        <v>143</v>
+      </c>
+      <c r="D776" s="1">
+        <v>244</v>
+      </c>
+      <c r="E776" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F776" s="1">
+        <v>96</v>
+      </c>
+      <c r="G776" s="1"/>
+      <c r="H776" t="s">
+        <v>1567</v>
+      </c>
+    </row>
+    <row r="777" spans="1:8">
+      <c r="A777" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B777" t="s">
+        <v>1568</v>
+      </c>
+      <c r="C777" s="1">
+        <v>143</v>
+      </c>
+      <c r="D777" s="1">
+        <v>244</v>
+      </c>
+      <c r="E777" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F777" s="1">
+        <v>97</v>
+      </c>
+      <c r="G777" s="1"/>
+      <c r="H777" t="s">
+        <v>1569</v>
+      </c>
+    </row>
+    <row r="778" spans="1:8">
+      <c r="A778" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B778" t="s">
+        <v>1570</v>
+      </c>
+      <c r="C778" s="1">
+        <v>143</v>
+      </c>
+      <c r="D778" s="1">
+        <v>244</v>
+      </c>
+      <c r="E778" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F778" s="1">
+        <v>98</v>
+      </c>
+      <c r="G778" s="1"/>
+      <c r="H778" t="s">
+        <v>1571</v>
+      </c>
+    </row>
+    <row r="779" spans="1:8">
+      <c r="A779" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B779" t="s">
+        <v>1572</v>
+      </c>
+      <c r="C779" s="1">
+        <v>143</v>
+      </c>
+      <c r="D779" s="1">
+        <v>244</v>
+      </c>
+      <c r="E779" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F779" s="1">
+        <v>99</v>
+      </c>
+      <c r="G779" s="1"/>
+      <c r="H779" t="s">
+        <v>1573</v>
+      </c>
+    </row>
+    <row r="780" spans="1:8">
+      <c r="A780" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B780" t="s">
+        <v>1574</v>
+      </c>
+      <c r="C780" s="1">
+        <v>143</v>
+      </c>
+      <c r="D780" s="1">
+        <v>244</v>
+      </c>
+      <c r="E780" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F780" s="1">
+        <v>100</v>
+      </c>
+      <c r="G780" s="1"/>
+      <c r="H780" t="s">
+        <v>1575</v>
+      </c>
+    </row>
+    <row r="781" spans="1:8">
+      <c r="A781" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B781" t="s">
+        <v>1576</v>
+      </c>
+      <c r="C781" s="1">
+        <v>143</v>
+      </c>
+      <c r="D781" s="1">
+        <v>244</v>
+      </c>
+      <c r="E781" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F781" s="1">
+        <v>101</v>
+      </c>
+      <c r="G781" s="1"/>
+      <c r="H781" t="s">
+        <v>1577</v>
+      </c>
+    </row>
+    <row r="782" spans="1:8">
+      <c r="A782" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B782" t="s">
+        <v>1578</v>
+      </c>
+      <c r="C782" s="1">
+        <v>143</v>
+      </c>
+      <c r="D782" s="1">
+        <v>244</v>
+      </c>
+      <c r="E782" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F782" s="1">
+        <v>102</v>
+      </c>
+      <c r="G782" s="1"/>
+      <c r="H782" t="s">
+        <v>1579</v>
+      </c>
+    </row>
+    <row r="783" spans="1:8">
+      <c r="A783" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B783" t="s">
+        <v>1580</v>
+      </c>
+      <c r="C783" s="1">
+        <v>143</v>
+      </c>
+      <c r="D783" s="1">
+        <v>244</v>
+      </c>
+      <c r="E783" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F783" s="1">
+        <v>103</v>
+      </c>
+      <c r="G783" s="1"/>
+      <c r="H783" t="s">
+        <v>1581</v>
+      </c>
+    </row>
+    <row r="784" spans="1:8">
+      <c r="A784" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B784" t="s">
+        <v>1582</v>
+      </c>
+      <c r="C784" s="1">
+        <v>143</v>
+      </c>
+      <c r="D784" s="1">
+        <v>244</v>
+      </c>
+      <c r="E784" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F784" s="1">
+        <v>104</v>
+      </c>
+      <c r="G784" s="1"/>
+      <c r="H784" t="s">
+        <v>1583</v>
+      </c>
+    </row>
+    <row r="785" spans="1:8">
+      <c r="A785" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B785" t="s">
+        <v>1584</v>
+      </c>
+      <c r="C785" s="1">
+        <v>143</v>
+      </c>
+      <c r="D785" s="1">
+        <v>244</v>
+      </c>
+      <c r="E785" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F785" s="1">
+        <v>105</v>
+      </c>
+      <c r="G785" s="1"/>
+      <c r="H785" t="s">
+        <v>1585</v>
+      </c>
+    </row>
+    <row r="786" spans="1:8">
+      <c r="A786" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B786" t="s">
+        <v>1586</v>
+      </c>
+      <c r="C786" s="1">
+        <v>143</v>
+      </c>
+      <c r="D786" s="1">
+        <v>244</v>
+      </c>
+      <c r="E786" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F786" s="1">
+        <v>106</v>
+      </c>
+      <c r="G786" s="1"/>
+      <c r="H786" t="s">
+        <v>1587</v>
+      </c>
+    </row>
+    <row r="787" spans="1:8">
+      <c r="A787" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B787" t="s">
+        <v>1588</v>
+      </c>
+      <c r="C787" s="1">
+        <v>143</v>
+      </c>
+      <c r="D787" s="1">
+        <v>244</v>
+      </c>
+      <c r="E787" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F787" s="1">
+        <v>107</v>
+      </c>
+      <c r="G787" s="1"/>
+      <c r="H787" t="s">
+        <v>1589</v>
+      </c>
+    </row>
+    <row r="788" spans="1:8">
+      <c r="A788" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B788" t="s">
+        <v>1590</v>
+      </c>
+      <c r="C788" s="1">
+        <v>143</v>
+      </c>
+      <c r="D788" s="1">
+        <v>244</v>
+      </c>
+      <c r="E788" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F788" s="1">
+        <v>108</v>
+      </c>
+      <c r="G788" s="1"/>
+      <c r="H788" t="s">
+        <v>1591</v>
+      </c>
+    </row>
+    <row r="789" spans="1:8">
+      <c r="A789" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B789" t="s">
+        <v>1592</v>
+      </c>
+      <c r="C789" s="1">
+        <v>143</v>
+      </c>
+      <c r="D789" s="1">
+        <v>244</v>
+      </c>
+      <c r="E789" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F789" s="1">
+        <v>109</v>
+      </c>
+      <c r="G789" s="1"/>
+      <c r="H789" t="s">
+        <v>1593</v>
+      </c>
+    </row>
+    <row r="790" spans="1:8">
+      <c r="A790" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B790" t="s">
+        <v>1594</v>
+      </c>
+      <c r="C790" s="1">
+        <v>143</v>
+      </c>
+      <c r="D790" s="1">
+        <v>244</v>
+      </c>
+      <c r="E790" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F790" s="1">
+        <v>110</v>
+      </c>
+      <c r="G790" s="1"/>
+      <c r="H790" t="s">
+        <v>1595</v>
+      </c>
+    </row>
+    <row r="791" spans="1:8">
+      <c r="A791" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B791" t="s">
+        <v>1596</v>
+      </c>
+      <c r="C791" s="1">
+        <v>143</v>
+      </c>
+      <c r="D791" s="1">
+        <v>244</v>
+      </c>
+      <c r="E791" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F791" s="1">
+        <v>111</v>
+      </c>
+      <c r="G791" s="1"/>
+      <c r="H791" t="s">
+        <v>1597</v>
+      </c>
+    </row>
+    <row r="792" spans="1:8">
+      <c r="A792" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B792" t="s">
+        <v>1598</v>
+      </c>
+      <c r="C792" s="1">
+        <v>143</v>
+      </c>
+      <c r="D792" s="1">
+        <v>244</v>
+      </c>
+      <c r="E792" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F792" s="1">
+        <v>112</v>
+      </c>
+      <c r="G792" s="1"/>
+      <c r="H792" t="s">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="793" spans="1:8">
+      <c r="A793" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B793" t="s">
+        <v>1600</v>
+      </c>
+      <c r="C793" s="1">
+        <v>143</v>
+      </c>
+      <c r="D793" s="1">
+        <v>244</v>
+      </c>
+      <c r="E793" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F793" s="1">
+        <v>113</v>
+      </c>
+      <c r="G793" s="1"/>
+      <c r="H793" t="s">
+        <v>1601</v>
+      </c>
+    </row>
+    <row r="794" spans="1:8">
+      <c r="A794" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B794" t="s">
+        <v>1602</v>
+      </c>
+      <c r="C794" s="1">
+        <v>143</v>
+      </c>
+      <c r="D794" s="1">
+        <v>244</v>
+      </c>
+      <c r="E794" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F794" s="1">
+        <v>114</v>
+      </c>
+      <c r="G794" s="1"/>
+      <c r="H794" t="s">
+        <v>1603</v>
+      </c>
+    </row>
+    <row r="795" spans="1:8">
+      <c r="A795" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B795" t="s">
+        <v>1604</v>
+      </c>
+      <c r="C795" s="1">
+        <v>143</v>
+      </c>
+      <c r="D795" s="1">
+        <v>244</v>
+      </c>
+      <c r="E795" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F795" s="1">
+        <v>115</v>
+      </c>
+      <c r="G795" s="1"/>
+      <c r="H795" t="s">
+        <v>1605</v>
+      </c>
+    </row>
+    <row r="796" spans="1:8">
+      <c r="A796" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B796" t="s">
+        <v>1606</v>
+      </c>
+      <c r="C796" s="1">
+        <v>143</v>
+      </c>
+      <c r="D796" s="1">
+        <v>244</v>
+      </c>
+      <c r="E796" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F796" s="1">
+        <v>116</v>
+      </c>
+      <c r="G796" s="1"/>
+      <c r="H796" t="s">
+        <v>1607</v>
+      </c>
+    </row>
+    <row r="797" spans="1:8">
+      <c r="A797" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B797" t="s">
+        <v>1608</v>
+      </c>
+      <c r="C797" s="1">
+        <v>143</v>
+      </c>
+      <c r="D797" s="1">
+        <v>244</v>
+      </c>
+      <c r="E797" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F797" s="1">
+        <v>117</v>
+      </c>
+      <c r="G797" s="1"/>
+      <c r="H797" t="s">
+        <v>1609</v>
+      </c>
+    </row>
+    <row r="798" spans="1:8">
+      <c r="A798" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B798" t="s">
+        <v>1610</v>
+      </c>
+      <c r="C798" s="1">
+        <v>143</v>
+      </c>
+      <c r="D798" s="1">
+        <v>244</v>
+      </c>
+      <c r="E798" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F798" s="1">
+        <v>118</v>
+      </c>
+      <c r="G798" s="1"/>
+      <c r="H798" t="s">
+        <v>1611</v>
+      </c>
+    </row>
+    <row r="799" spans="1:8">
+      <c r="A799" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B799" t="s">
+        <v>1612</v>
+      </c>
+      <c r="C799" s="1">
+        <v>143</v>
+      </c>
+      <c r="D799" s="1">
+        <v>244</v>
+      </c>
+      <c r="E799" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F799" s="1">
+        <v>120</v>
+      </c>
+      <c r="G799" s="1"/>
+      <c r="H799" t="s">
+        <v>1613</v>
+      </c>
+    </row>
+    <row r="800" spans="1:8">
+      <c r="A800" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B800" t="s">
+        <v>1614</v>
+      </c>
+      <c r="C800" s="1">
+        <v>143</v>
+      </c>
+      <c r="D800" s="1">
+        <v>244</v>
+      </c>
+      <c r="E800" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F800" s="1">
+        <v>121</v>
+      </c>
+      <c r="G800" s="1"/>
+      <c r="H800" t="s">
+        <v>1615</v>
+      </c>
+    </row>
+    <row r="801" spans="1:8">
+      <c r="A801" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B801" t="s">
+        <v>1616</v>
+      </c>
+      <c r="C801" s="1">
+        <v>143</v>
+      </c>
+      <c r="D801" s="1">
+        <v>244</v>
+      </c>
+      <c r="E801" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F801" s="1">
+        <v>122</v>
+      </c>
+      <c r="G801" s="1"/>
+      <c r="H801" t="s">
+        <v>1617</v>
+      </c>
+    </row>
+    <row r="802" spans="1:8">
+      <c r="A802" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B802" t="s">
+        <v>1618</v>
+      </c>
+      <c r="C802" s="1">
+        <v>143</v>
+      </c>
+      <c r="D802" s="1">
+        <v>244</v>
+      </c>
+      <c r="E802" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F802" s="1">
+        <v>123</v>
+      </c>
+      <c r="G802" s="1"/>
+      <c r="H802" t="s">
+        <v>1619</v>
+      </c>
+    </row>
+    <row r="803" spans="1:8">
+      <c r="A803" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B803" t="s">
+        <v>1620</v>
+      </c>
+      <c r="C803" s="1">
+        <v>143</v>
+      </c>
+      <c r="D803" s="1">
+        <v>244</v>
+      </c>
+      <c r="E803" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F803" s="1">
+        <v>124</v>
+      </c>
+      <c r="G803" s="1"/>
+      <c r="H803" t="s">
+        <v>1621</v>
+      </c>
+    </row>
+    <row r="804" spans="1:8">
+      <c r="A804" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B804" t="s">
+        <v>1622</v>
+      </c>
+      <c r="C804" s="1">
+        <v>143</v>
+      </c>
+      <c r="D804" s="1">
+        <v>244</v>
+      </c>
+      <c r="E804" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F804" s="1">
+        <v>125</v>
+      </c>
+      <c r="G804" s="1"/>
+      <c r="H804" t="s">
+        <v>1623</v>
+      </c>
+    </row>
+    <row r="805" spans="1:8">
+      <c r="A805" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B805" t="s">
+        <v>1624</v>
+      </c>
+      <c r="C805" s="1">
+        <v>143</v>
+      </c>
+      <c r="D805" s="1">
+        <v>244</v>
+      </c>
+      <c r="E805" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F805" s="1">
+        <v>126</v>
+      </c>
+      <c r="G805" s="1"/>
+      <c r="H805" t="s">
+        <v>1625</v>
+      </c>
+    </row>
+    <row r="806" spans="1:8">
+      <c r="A806" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B806" t="s">
+        <v>1626</v>
+      </c>
+      <c r="C806" s="1">
+        <v>143</v>
+      </c>
+      <c r="D806" s="1">
+        <v>244</v>
+      </c>
+      <c r="E806" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F806" s="1">
+        <v>127</v>
+      </c>
+      <c r="G806" s="1"/>
+      <c r="H806" t="s">
+        <v>1627</v>
+      </c>
+    </row>
+    <row r="807" spans="1:8">
+      <c r="A807" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B807" t="s">
+        <v>1628</v>
+      </c>
+      <c r="C807" s="1">
+        <v>143</v>
+      </c>
+      <c r="D807" s="1">
+        <v>244</v>
+      </c>
+      <c r="E807" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F807" s="1">
+        <v>128</v>
+      </c>
+      <c r="G807" s="1"/>
+      <c r="H807" t="s">
+        <v>1629</v>
+      </c>
+    </row>
+    <row r="808" spans="1:8">
+      <c r="A808" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B808" t="s">
+        <v>1630</v>
+      </c>
+      <c r="C808" s="1">
+        <v>143</v>
+      </c>
+      <c r="D808" s="1">
+        <v>244</v>
+      </c>
+      <c r="E808" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F808" s="1">
+        <v>129</v>
+      </c>
+      <c r="G808" s="1"/>
+      <c r="H808" t="s">
+        <v>1631</v>
+      </c>
+    </row>
+    <row r="809" spans="1:8">
+      <c r="A809" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B809" t="s">
+        <v>1632</v>
+      </c>
+      <c r="C809" s="1">
+        <v>143</v>
+      </c>
+      <c r="D809" s="1">
+        <v>244</v>
+      </c>
+      <c r="E809" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F809" s="1">
+        <v>130</v>
+      </c>
+      <c r="G809" s="1"/>
+      <c r="H809" t="s">
+        <v>1633</v>
+      </c>
+    </row>
+    <row r="810" spans="1:8">
+      <c r="A810" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B810" t="s">
+        <v>1634</v>
+      </c>
+      <c r="C810" s="1">
+        <v>143</v>
+      </c>
+      <c r="D810" s="1">
+        <v>244</v>
+      </c>
+      <c r="E810" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F810" s="1">
+        <v>131</v>
+      </c>
+      <c r="G810" s="1"/>
+      <c r="H810" t="s">
+        <v>1635</v>
+      </c>
+    </row>
+    <row r="811" spans="1:8">
+      <c r="A811" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B811" t="s">
+        <v>1636</v>
+      </c>
+      <c r="C811" s="1">
+        <v>143</v>
+      </c>
+      <c r="D811" s="1">
+        <v>244</v>
+      </c>
+      <c r="E811" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F811" s="1">
+        <v>132</v>
+      </c>
+      <c r="G811" s="1"/>
+      <c r="H811" t="s">
+        <v>1637</v>
+      </c>
+    </row>
+    <row r="812" spans="1:8">
+      <c r="A812" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B812" t="s">
+        <v>1638</v>
+      </c>
+      <c r="C812" s="1">
+        <v>143</v>
+      </c>
+      <c r="D812" s="1">
+        <v>244</v>
+      </c>
+      <c r="E812" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F812" s="1">
+        <v>133</v>
+      </c>
+      <c r="G812" s="1"/>
+      <c r="H812" t="s">
+        <v>1639</v>
+      </c>
+    </row>
+    <row r="813" spans="1:8">
+      <c r="A813" s="2"/>
+      <c r="C813" s="1"/>
+      <c r="D813" s="1"/>
+      <c r="E813" s="1"/>
+      <c r="F813" s="1"/>
+      <c r="G813" s="1"/>
     </row>
   </sheetData>
   <sheetProtection sheet="false" objects="false" scenarios="false" formatCells="false" formatColumns="false" formatRows="false" insertColumns="false" insertRows="false" insertHyperlinks="false" deleteColumns="false" deleteRows="false" selectLockedCells="false" sort="false" autoFilter="false" pivotTables="false" selectUnlockedCells="false"/>

--- a/data/raw/monthly-2026-10.xlsx
+++ b/data/raw/monthly-2026-10.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1640">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1797">
   <si>
     <t>วันที่</t>
   </si>
@@ -4935,6 +4935,477 @@
   </si>
   <si>
     <t>https://ratchakitcha.soc.go.th/documents/132476.pdf</t>
+  </si>
+  <si>
+    <t>08/10/2026</t>
+  </si>
+  <si>
+    <t>ประกาศสำนักนายกรัฐมนตรี เรื่อง พระราชทานพระบรมราชานุญาตให้เรียกคืนเครื่องราชอิสริยาภรณ์ [นายสมเชาว์  สิทธิเชนทร์]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/134122.pdf</t>
+  </si>
+  <si>
+    <t>หมายกำหนดการ ที่ ๒๔/๒๕๖๙ หมายกำหนดการพระราชพิธีทรงบำเพ็ญพระราชกุศลวันนวมินทรมหาราช  พุทธศักราช  ๒๕๖๙</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/134243.pdf</t>
+  </si>
+  <si>
+    <t>แก้คำผิด ประกาศสำนักนายกรัฐมนตรี เรื่อง พระราชทานเครื่องราชอิสริยาภรณ์อันเป็นที่เชิดชูยิ่งช้างเผือกและเครื่องราชอิสริยาภรณ์อันมีเกียรติยศยิ่งมงกุฎไทย ชั้นต่ำกว่าสายสะพาย [ซึ่งประกาศในราชกิจจานุเบกษา เล่ม ๑๓๒ ตอนที่ ๑๗ ข วันที่ ๒ มิถุนายน ๒๕๕๘ (เล่มที่ ๑๔/๖) หน้า ๙๒] เรื่อง พระราชทานเครื่องราชอิสริยาภรณ์อันเป็นที่เชิดชูยิ่งช้างเผือกและเครื่องราชอิสริยาภรณ์อันมีเกียรติยศยิ่งมงกุฎไทย ชั้นสายสะพาย [ซึ่งประกาศในราชกิจจานุเบกษา เล่ม ๑๓๙ ตอนพิเศษ ๑ ข วันที่ ๑๔ กุมภาพันธ์ ๒๕๖๕ หน้า ๖๐] เรื่อง พระราชทานเครื่องราชอิสริยาภรณ์อันเป็นที่เชิดชูยิ่งช้างเผือกและเครื่องราชอิสริยาภรณ์อันมีเกียรติยศยิ่งมงกุฎไทย ชั้นต่ำกว่าสายสะพาย [ซึ่งประกาศในราชกิจจานุเบกษา เล่ม 139 ตอนพิเศษ ๓ ข วันที่ ๓๑ มีนาคม ๒๕๖๕ (เล่มที่ ๑๔/๘) หน้า ๑๗๒] พระบรมราชโองการ ประกาศ เรื่อง พระราชทานเครื่องราชอิสริยาภรณ์อันเป็นที่เชิดชูยิ่งช้างเผือกและเครื่องราชอิสริยาภรณ์อันมีเกียรติยศยิ่งมงกุฎไทย ชั้นต่ำกว่าสายสะพาย [ซึ่งประกาศในราชกิจจานุเบกษา เล่ม ๑๔๐ ตอนพิเศษ ๓ ข วันที่ ๒๑ พฤศจิกายน ๒๕๖๖ (เล่มที่ ๑๔/๕) หน้า ๑๘๐ หน้า ๑๘๒ หน้า ๒๐๖] เรื่อง พระราชทานเครื่องราชอิสริยาภรณ์อันเป็นที่เชิดชูยิ่งช้างเผือกและเครื่องราชอิสริยาภรณ์อันมีเกียรติยศยิ่งมงกุฎไทย ชั้นสายสะพาย [ซึ่งประกาศในราชกิจจานุเบกษา เล่ม ๑๔๑ ตอนพิเศษ ๑ ข วันที่ ๑๓ สิงหาคม ๒๕๖๗ หน้า ๗๖] เรื่อง พระราชทานเครื่องราชอิสริยาภรณ์อันเป็นที่เชิดชูยิ่งช้างเผือกและเครื่องราชอิสริยาภรณ์อันมีเกียรติยศยิ่งมงกุฎไทย ชั้นต่ำกว่าสายสะพาย เล่ม ๑๔๓ ตอนพิเศษ ๓ ข วันที่ ๒๗ เมษายน ๒๕๖๙ หน้า ๖๔๓๗ หน้า ๖๔๓๘]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/127811.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศกรมสรรพสามิต เรื่อง ลักษณะเครื่องหมายแสดงการเสียภาษีจดทะเบียน (ฉบับที่ 11/2569)</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/129326.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศวุฒิสภา เรื่อง  ตั้งคณะกรรมาธิการสามัญเพื่อทำหน้าที่ตรวจสอบประวัติ ความประพฤติ และพฤติกรรมทางจริยธรรมของบุคคลผู้ได้รับการเสนอชื่อให้ดำรงตำแหน่งกรรมการตรวจเงินแผ่น [จำนวน 15 ราย 1 นายกัมพล สุภาแพ่ง ฯลฯ]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/129281.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศวุฒิสภา เรื่อง  ตั้งกรรมาธิการในคณะกรรมาธิการสามัญประจำวุฒิสภา แทนตำแหน่งที่ว่าง [จำนวน 3 ราย 1 พลตำรวจตรี สุนทร ขวัญเพ็ชร ฯลฯ]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/129230.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศวุฒิสภา เรื่อง ตั้งกรรมาธิการในคณะกรรมาธิการวิสามัญการพิทักษ์และเทิดทูนสถาบันพระมหากษัตริย์ แทนตำแหน่งที่ว่าง [นายศุภชัย สมเจริญ]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/129229.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศสภาผู้แทนราษฎร เรื่อง ข้าราชการรัฐสภาฝ่ายการเมืองขอลาออกจากตำแหน่ง [นายเดชรัต สุขกำเนิด]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/129218.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศสภาผู้แทนราษฎร เรื่อง แต่งตั้งข้าราชการรัฐสภาฝ่ายการเมือง [นายนรากร นาเมืองรักษ์]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/129220.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศสภาผู้แทนราษฎร เรื่อง แต่งตั้งข้าราชการรัฐสภาฝ่ายการเมือง [นายกิตติ สมทรัพย์]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/129219.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศศาลจังหวัดนครศรีธรรมราช เรื่อง ศาลมีคำสั่งให้ นายสุรชัย ด่านวัฒนานุสรณ์ เป็นคนสาบสูญ</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/21493.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศศาลจังหวัดพัทยา เรื่อง มีคำสั่งให้ นางสาวจีรวรรณ นางาม หรือปฐวีนันท์ เป็นคนสาบสูญ</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/122921.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศศาลจังหวัดมหาสารคาม เรื่อง ขอให้เป็นคนสาบสูญ [นายวิรัน ราชนา]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/125821.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศศาลจังหวัดมหาสารคาม เรื่อง เพิกถอนคำสั่งให้เป็นคนสาบสูญ [นายที จะริยามา]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/125822.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศศาลจังหวัดลำปาง เรื่อง ศาลมีคำสั่งว่า นางณัฐชล ใจอ้าย หรือนางสาวณัฐยา วงศ์มา เป็นคนสาบสูญ</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/124356.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศศาลจังหวัดลำปาง เรื่อง ศาลมีคำสั่งว่า นายชูชาติ มนอา เป็นคนสาบสูญ</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/125817.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศศาลจังหวัดสุรินทร์ เรื่อง ศาลมีคำสั่งให้ นางสาวผัด อุดมดัน เป็นคนสาบสูญ</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/52827.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศศาลจังหวัดสุรินทร์ เรื่อง ศาลมีคำสั่งให้ นายไพรลินข์ ศรีดาจันทร์ เป็นคนสาบสูญ</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/53680.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศศาลจังหวัดอุบลราชธานี เรื่อง  ให้ นายวินเซนต์ เดวิด แอนดรูว์ส เป็นคนสาบสูญ</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/126305.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศอธิบดีกรมสรรพากร  เรื่อง รายชื่อผู้รับทำการวิจัยและพัฒนาเทคโนโลยีและนวัตกรรม (ฉบับที่ 314)</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/128338.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศนายทะเบียนพรรคการเมือง เรื่อง การเปลี่ยนแปลงข้อบังคับพรรคและคณะกรรมการบริหารพรรคผู้นำ (เดิมชื่อพรรคตะวันใหม่)</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/129340.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศนายทะเบียนพรรคการเมือง เรื่อง การเปลี่ยนแปลงข้อบังคับพรรค และคณะกรรมการบริหารพรรคไทยอนุรักษ์ (เดิมชื่อพรรควิชั่นใหม่)</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132645.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศนายทะเบียนมูลนิธิจังหวัดกาญจนบุรี เรื่อง จดทะเบียนจัดตั้ง "มูลนิธิรัตนกิจ"</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/37325.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศนายทะเบียนมูลนิธิจังหวัดขอนแก่น เรื่อง จดทะเบียนจัดตั้ง "มูลนิธิหลวงปู่น้อย ญาณวโร"</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/52549.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศนายทะเบียนมูลนิธิจังหวัดประจวบคีรีขันธ์ เรื่อง จดทะเบียนจัดตั้ง "มูลนิธิประจวบต้องไปต่อ"</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/129049.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศนายทะเบียนมูลนิธิจังหวัดนครปฐม เรื่อง จดทะเบียนแก้ไขเพิ่มเติมข้อบังคับของมูลนิธิ [มูลนิธิผัสสะบริสุทธิ์]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/128779.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศนายทะเบียนมูลนิธิจังหวัดราชบุรี เรื่อง จดทะเบียนแก้ไขเพิ่มเติมข้อบังคับมูลนิธิ [มูลนิธิทุนการศึกษากองพลพัฒนาที่ 1]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/37324.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศนายทะเบียนมูลนิธิจังหวัดศรีสะเกษ เรื่อง จดทะเบียนแก้ไขเพิ่มเติมข้อบังคับมูลนิธิ [มูลนิธิหลวงปู่สรวง]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/37362.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศนายทะเบียนมูลนิธิจังหวัดหนองคาย เรื่อง จดทะเบียนการแก้ไขเพิ่มเติมข้อบังคับของมูลนิธิ [มูลนิธิโรงเรียนปทุมเทพวิทยาคาร]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/129047.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศนายทะเบียนมูลนิธิจังหวัดศรีสะเกษ เรื่อง จดทะเบียนการแต่งตั้งคณะกรรมการมูลนิธิขึ้นใหม่ทั้งชุดของ "มูลนิธิเด็กขาดแคลนอำเภอภูสิงห์"</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/128780.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศนายทะเบียนสมาคมประจำจังหวัดขอนแแก่น เรื่อง จดทะเบียนจัดตั้งสมาคมศิษย์เก่าวิทยาลัยการปกครองท้องถิ่น มหาวิทยาลัยขอนแก่น</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/52550.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศนายทะเบียนสมาคมประจำจังหวัดประจวบคีรีขันธ์ เรื่อง จัดตั้งสมาคมยุทธศิลป์มวยไทย</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/129050.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศนายทะเบียนสมาคมประจำจังหวัดพิจิตร เรื่อง จดทะเบียนจัดตั้งสหพันธ์สมาคมผู้ประกอบการไทยจังหวัดพิจิตร</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/52715.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศนายทะเบียนสมาคมประจำจังหวัดสงขลา เรื่อง จดทะเบียนจัดตั้งสมาคม โนรา 168</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/37550.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศนายทะเบียนสมาคมประจำจังหวัดชลบุรี เรื่อง จดทะเบียนแก้ไขเพิ่มเติมข้อบังคับของสมาคม [สมาคมฮกเขะโคะ นิชิเร็น โชชู ในประเทศไทย]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/37424.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศนายทะเบียนสมาคมประจำจังหวัดบุรีรัมย์ เรื่อง จดทะเบียนแก้ไขเพิ่มเติมข้อบังคับของสมาคม [สมาคมศิษย์เก่าโรงเรียนบุรีรัมย์พิทยาคม]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/129001.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศนายทะเบียนสมาคมประจำจังหวัดประจวบคีรีขันธ์ เรื่อง จดทะเบียนแก้ไขเพิ่มเติมข้อบังคับของสมาคม [สมาคมธุรกิจการท่องเที่ยวจังหวัดประจวบคีรีขันธ์]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/129063.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศนายทะเบียนสมาคมประจำจังหวัดศรีสะเกษ เรื่อง จดทะเบียนการแก้ไขเพิ่มเติมข้อบังคับสมาคมคนตาบอดจังหวัดศรีสะเกษ</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/128781.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศนายทะเบียนสมาคมประจำจังหวัดอำนาจเจริญ เรื่อง จดทะเบียนการเปลี่ยนแปลงกรรมการสมาคมของสมาคมครูและบุคลากรทางการศึกษาอำเภอพนา</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/128998.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศนายทะเบียนสมาคมประจำจังหวัดบุรีรัมย์ เรื่อง จดทะเบียนการแต่งตั้งกรรมการของสมาคมขี้นใหม่ทั้งชุด  [สมาคมศิษย์เก่าโรงเรียนบุรีรัมย์พิทยาคม]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/129031.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศนายทะเบียนสมาคมประจำจังหวัดสมุทรสาคร เรื่อง จดทะเบียนการแต่งตั้งกรรมการของสมาคมขึ้นใหม่ทั้งชุด [สมาคมการบินบลูเบิร์ด]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/52520.pdf</t>
+  </si>
+  <si>
+    <t>ระเบียบคณะกรรมการจัดสรรที่ดินกลาง ว่าด้วยการกำหนดค่าใช้จ่าย หลักเกณฑ์และวิธีการจัดเก็บค่าใช้จ่ายในการบำรุงรักษาและการจัดการสาธารณูปโภค และการจัดทำบัญชี (ฉบับที่ 2) พ.ศ. 2569</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/133794.pdf</t>
+  </si>
+  <si>
+    <t>ระเบียบคณะกรรมการจัดสรรที่ดินกลาง ว่าด้วยการนำหลักประกันอย่างอื่นมาค้ำประกันแทนสัญญาค้ำประกันการบำรุงรักษาสาธารณูปโภค พ.ศ. 2569</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/133795.pdf</t>
+  </si>
+  <si>
+    <t>ระเบียบคณะกรรมการจัดสรรที่ดินกลาง ว่าด้วยการพ้นจากหน้าที่บำรุงรักษาสาธารณูปโภคของผู้จัดสรรที่ดิน  พ.ศ. 2569</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/133796.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศกระทรวงการคลัง เรื่อง กำหนดองค์การสาธารณกุศล ตามมาตรา 107 (1) (2) และมาตรา 108 (1) (2) แห่งพระราชบัญญัติภาษีสรรพสามิต พ.ศ. 2560 (ฉบับที่ 7)</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/130195.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศกระทรวงการคลัง ว่าด้วยภาษีเงินได้และภาษีมูลค่าเพิ่ม (ฉบับที่ 880) เรื่อง กำหนดองค์การ สถานสาธารณกุศล สถานพยาบาล และสถานศึกษา ตามมาตรา 47 (7) (ข) แห่งประมวลรัษฎากร และมาตรา 3 (4) (ข) แห่งพระราชกฤษฎีกาออกตามความในประมวลรัษฎากร ว่าด้วยการยกเว้นภาษีมูลค่าเพิ่ม (ฉบับที่ 239) พ.ศ. 2534 ซึ่งแก้ไขเพิ่มเติมโดยพระราชกฤษฎีกาออกตามความในประมวลรัษฎากร ว่าด้วยการยกเว้นภาษีมูลค่าเพิ่ม (ฉบับที่ 254) พ.ศ. 2535</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/130404.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศกระทรวงเกษตรและสหกรณ์ เรื่อง กำหนดด่านตรวจพืช (ฉบับที่ 4) พ.ศ. 2569</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/130717.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศกระทรวงเกษตรและสหกรณ์ เรื่อง ยกเลิกและกำหนดมาตรฐานสินค้าเกษตร : การปฏิบัติที่ดีสำหรับการผลิตทุเรียนแช่เยือกแข็ง ตามพระราชบัญญัติมาตรฐานสินค้าเกษตร พ.ศ. 2551</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/130090.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศกระทรวงสาธารณสุข เรื่อง กำหนดเจ้าหน้าที่ของรัฐผู้มีอำนาจปรับเป็นพินัยตามกฎหมาย ว่าด้วยเครื่องมือแพทย์และกฎหมายว่าด้วยเครื่องสำอาง (ฉบับที่ 2) พ.ศ. 2569</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132193.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศกรมป่าไม้ เรื่อง กำหนดให้บริเวณพื้นที่ป่าสงวนแห่งชาติ ป่าแม่ตาล และป่าแม่ยุย ในท้องที่ตำบลบ้านตาล อำเภอฮอด จังหวัดเชียงใหม่ เป็นป่านันทนาการ</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131546.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศกรมป่าไม้ เรื่อง จัดตั้งป่าชุมชนบ้านพุบ่อง ท้องที่ตำบลห้วยขมิ้น อำเภอด่านช้าง จังหวัดสุพรรณบุรี</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131203.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศกรมป่าไม้ เรื่อง เพิกถอนป่าชุมชนบ้านสระแก้ว บางส่วน ท้องที่ตำบลไทรทอง อำเภอชัยบุรี จังหวัดสุราษฎร์ธานี</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131204.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศกรมการศาสนา เรื่อง การจัดระบบข้อมูลข้อมูลข่าวสารส่วนบุคคล ตามพระราชบัญญัติข้อมูลข่าวสารของราชการ พ.ศ. 2540 ของกรมการศาสนา</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/130541.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศกรมอนามัย เรื่อง กำหนดรายชื่อหน่วยบริการสาธารณสุขที่สามารถรับบริจาคอาหารสำหรับทารกหรืออาหารสำหรับเด็กเล็กในกรณีจำเป็น พ.ศ. 2569</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131198.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศสำนักงานมาตรฐานผลิตภัณฑ์อุตสาหกรรม เรื่อง แต่งตั้งผู้ตรวจสอบการทำผลิตภัณฑ์อุตสาหกรรม (ฉบับที่ 74) พ.ศ. 2569</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/131269.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำพิพากษาให้จัดการทรัพย์มรดกจำเลย [คดีหมายเลขแดงที่ ล.8266/2569 ใให้จัดการทรัพย์กองมรดกของ นายสุรพงษ์ จงวิวัฒน์จิตต์  โดยนายธาริชหรือวรุตม์ ธาดารัชตะพรหรือจงวิวัฒน์จิตต์ นายโชคกนกนันท์หรือณัทณพงศ์หรือกฤษฏิ์ ณทัตศุภดาหรือจงวิวัฒน์จิตต์ และนายรณหาญหรือปิยวัฒน์ จงวิวัฒน์จิตต์ ในฐานะทายาทโดยธรรมทั้งสาม ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132685.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.E1470/2569 นายพราน พลาสูรย์ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132715.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.E1471/2569 นายณภัทรสัณห์ หรืออิทธิพงศ์ มายรรยงค์ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132629.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.E1472/2569 บริษัทสุขรมย์ อินเตอร์เทค จำกัด ลูกหนี้ที่ 1 และนายไชยรัตน์ สุขรมย์ ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132712.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.E1473/2569 นางสาวเรืองศรี วิชัยดิษฐ ลูกหนี้ที่ 1 และนายอิทธิกร ชูขำ ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132651.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.E1474/2569 นางสาวอิงอร แซ่พ่าง ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132619.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.E1478/2569 นางสาวฐิตามินทร์ ธีรัตน์กุลจิรา ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132621.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.E1480/2569 บริษัท เฉิน ซิง จำกัด ลูกหนี้ที่ 1 และนายวิชัย เหลียวชนะ ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132611.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.E1484/2569 นายสรวิชญ์ บุญทศ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132626.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8234/2569 นางสาวกนกทิพย์หรือณัฏฐพัชร วงศ์วิเชียร ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132670.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8235/2569 นางสาวสุธาวรรณ โห้สุวรรณ ลูกหนี้ที่ 1 และนายโกวิทย์ เวียงนนท์ ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132625.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8236/2569 พันตำรวจโทหญิงหรือนางสาวปารีรัตน์ วงศ์กาไสย ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132636.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8237/2569 นางวราภรณ์ วินิจสร ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132665.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8238/2569 นางสาวปาหนัน รุ่งสันเทียะ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132618.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8239/2569 บริษัทเดโชเบ จำกัด ลูกหนี้ที่ 1 และบริษัทไทโย จำกัด ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132616.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8240/2569 นางสาวณัฏฐนิช จึงพัฒนา ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132539.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8241/2569 นางสาวอรอุมา ศรีธรรมโฆษ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132699.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8250/2569 นายชุมพล สองทอง ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132630.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8251/2569 นายภรต วราภิญโญ ลูกหนี้ที่ 1 และนางสาวกานดาภร กิตติศัพท์ ลูกหนี้ที่ 2]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132680.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8270/2569 นางสาวรัตดา สีเตาปูน ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132681.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8272/2569 นายเดชา ม่วงงาม ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132660.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8300/2569 นางสาวนงค์พะงา พฤฒิกุลประดับ ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132689.pdf</t>
+  </si>
+  <si>
+    <t>ประกาศเจ้าพนักงานพิทักษ์ทรัพย์ เรื่อง คำสั่งพิทักษ์ทรัพย์เด็ดขาด [คดีหมายเลขแดงที่ ล.8301/2569 นางสาวญาปกาหรือเปมิกาหรือชุดาภัค เอียดมะโน ลูกหนี้]</t>
+  </si>
+  <si>
+    <t>https://ratchakitcha.soc.go.th/documents/132662.pdf</t>
   </si>
 </sst>
 </file>
@@ -5281,7 +5752,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:H813"/>
+  <dimension ref="A1:H891"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="12.02" customWidth="true" style="0"/>
@@ -24785,12 +25256,1884 @@
       </c>
     </row>
     <row r="813" spans="1:8">
-      <c r="A813" s="2"/>
-      <c r="C813" s="1"/>
-      <c r="D813" s="1"/>
-      <c r="E813" s="1"/>
-      <c r="F813" s="1"/>
+      <c r="A813" s="2" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B813" t="s">
+        <v>1641</v>
+      </c>
+      <c r="C813" s="1">
+        <v>143</v>
+      </c>
+      <c r="D813" s="1">
+        <v>66</v>
+      </c>
+      <c r="E813" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="F813" s="1">
+        <v>1</v>
+      </c>
       <c r="G813" s="1"/>
+      <c r="H813" t="s">
+        <v>1642</v>
+      </c>
+    </row>
+    <row r="814" spans="1:8">
+      <c r="A814" s="2" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B814" t="s">
+        <v>1643</v>
+      </c>
+      <c r="C814" s="1">
+        <v>143</v>
+      </c>
+      <c r="D814" s="1">
+        <v>66</v>
+      </c>
+      <c r="E814" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="F814" s="1">
+        <v>2</v>
+      </c>
+      <c r="G814" s="1"/>
+      <c r="H814" t="s">
+        <v>1644</v>
+      </c>
+    </row>
+    <row r="815" spans="1:8">
+      <c r="A815" s="2" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B815" t="s">
+        <v>1645</v>
+      </c>
+      <c r="C815" s="1">
+        <v>143</v>
+      </c>
+      <c r="D815" s="1">
+        <v>66</v>
+      </c>
+      <c r="E815" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="F815" s="1">
+        <v>3</v>
+      </c>
+      <c r="G815" s="1"/>
+      <c r="H815" t="s">
+        <v>1646</v>
+      </c>
+    </row>
+    <row r="816" spans="1:8">
+      <c r="A816" s="2" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B816" t="s">
+        <v>1647</v>
+      </c>
+      <c r="C816" s="1">
+        <v>143</v>
+      </c>
+      <c r="D816" s="1">
+        <v>150</v>
+      </c>
+      <c r="E816" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F816" s="1">
+        <v>1</v>
+      </c>
+      <c r="G816" s="1"/>
+      <c r="H816" t="s">
+        <v>1648</v>
+      </c>
+    </row>
+    <row r="817" spans="1:8">
+      <c r="A817" s="2" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B817" t="s">
+        <v>1649</v>
+      </c>
+      <c r="C817" s="1">
+        <v>143</v>
+      </c>
+      <c r="D817" s="1">
+        <v>150</v>
+      </c>
+      <c r="E817" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F817" s="1">
+        <v>2</v>
+      </c>
+      <c r="G817" s="1"/>
+      <c r="H817" t="s">
+        <v>1650</v>
+      </c>
+    </row>
+    <row r="818" spans="1:8">
+      <c r="A818" s="2" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B818" t="s">
+        <v>1651</v>
+      </c>
+      <c r="C818" s="1">
+        <v>143</v>
+      </c>
+      <c r="D818" s="1">
+        <v>150</v>
+      </c>
+      <c r="E818" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F818" s="1">
+        <v>3</v>
+      </c>
+      <c r="G818" s="1"/>
+      <c r="H818" t="s">
+        <v>1652</v>
+      </c>
+    </row>
+    <row r="819" spans="1:8">
+      <c r="A819" s="2" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B819" t="s">
+        <v>1653</v>
+      </c>
+      <c r="C819" s="1">
+        <v>143</v>
+      </c>
+      <c r="D819" s="1">
+        <v>150</v>
+      </c>
+      <c r="E819" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F819" s="1">
+        <v>4</v>
+      </c>
+      <c r="G819" s="1"/>
+      <c r="H819" t="s">
+        <v>1654</v>
+      </c>
+    </row>
+    <row r="820" spans="1:8">
+      <c r="A820" s="2" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B820" t="s">
+        <v>1655</v>
+      </c>
+      <c r="C820" s="1">
+        <v>143</v>
+      </c>
+      <c r="D820" s="1">
+        <v>150</v>
+      </c>
+      <c r="E820" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F820" s="1">
+        <v>5</v>
+      </c>
+      <c r="G820" s="1"/>
+      <c r="H820" t="s">
+        <v>1656</v>
+      </c>
+    </row>
+    <row r="821" spans="1:8">
+      <c r="A821" s="2" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B821" t="s">
+        <v>1657</v>
+      </c>
+      <c r="C821" s="1">
+        <v>143</v>
+      </c>
+      <c r="D821" s="1">
+        <v>150</v>
+      </c>
+      <c r="E821" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F821" s="1">
+        <v>6</v>
+      </c>
+      <c r="G821" s="1"/>
+      <c r="H821" t="s">
+        <v>1658</v>
+      </c>
+    </row>
+    <row r="822" spans="1:8">
+      <c r="A822" s="2" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B822" t="s">
+        <v>1659</v>
+      </c>
+      <c r="C822" s="1">
+        <v>143</v>
+      </c>
+      <c r="D822" s="1">
+        <v>150</v>
+      </c>
+      <c r="E822" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F822" s="1">
+        <v>7</v>
+      </c>
+      <c r="G822" s="1"/>
+      <c r="H822" t="s">
+        <v>1660</v>
+      </c>
+    </row>
+    <row r="823" spans="1:8">
+      <c r="A823" s="2" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B823" t="s">
+        <v>1661</v>
+      </c>
+      <c r="C823" s="1">
+        <v>143</v>
+      </c>
+      <c r="D823" s="1">
+        <v>150</v>
+      </c>
+      <c r="E823" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F823" s="1">
+        <v>8</v>
+      </c>
+      <c r="G823" s="1"/>
+      <c r="H823" t="s">
+        <v>1662</v>
+      </c>
+    </row>
+    <row r="824" spans="1:8">
+      <c r="A824" s="2" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B824" t="s">
+        <v>1663</v>
+      </c>
+      <c r="C824" s="1">
+        <v>143</v>
+      </c>
+      <c r="D824" s="1">
+        <v>150</v>
+      </c>
+      <c r="E824" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F824" s="1">
+        <v>10</v>
+      </c>
+      <c r="G824" s="1"/>
+      <c r="H824" t="s">
+        <v>1664</v>
+      </c>
+    </row>
+    <row r="825" spans="1:8">
+      <c r="A825" s="2" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B825" t="s">
+        <v>1665</v>
+      </c>
+      <c r="C825" s="1">
+        <v>143</v>
+      </c>
+      <c r="D825" s="1">
+        <v>150</v>
+      </c>
+      <c r="E825" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F825" s="1">
+        <v>11</v>
+      </c>
+      <c r="G825" s="1"/>
+      <c r="H825" t="s">
+        <v>1666</v>
+      </c>
+    </row>
+    <row r="826" spans="1:8">
+      <c r="A826" s="2" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B826" t="s">
+        <v>1667</v>
+      </c>
+      <c r="C826" s="1">
+        <v>143</v>
+      </c>
+      <c r="D826" s="1">
+        <v>150</v>
+      </c>
+      <c r="E826" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F826" s="1">
+        <v>12</v>
+      </c>
+      <c r="G826" s="1"/>
+      <c r="H826" t="s">
+        <v>1668</v>
+      </c>
+    </row>
+    <row r="827" spans="1:8">
+      <c r="A827" s="2" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B827" t="s">
+        <v>1669</v>
+      </c>
+      <c r="C827" s="1">
+        <v>143</v>
+      </c>
+      <c r="D827" s="1">
+        <v>150</v>
+      </c>
+      <c r="E827" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F827" s="1">
+        <v>13</v>
+      </c>
+      <c r="G827" s="1"/>
+      <c r="H827" t="s">
+        <v>1670</v>
+      </c>
+    </row>
+    <row r="828" spans="1:8">
+      <c r="A828" s="2" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B828" t="s">
+        <v>1671</v>
+      </c>
+      <c r="C828" s="1">
+        <v>143</v>
+      </c>
+      <c r="D828" s="1">
+        <v>150</v>
+      </c>
+      <c r="E828" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F828" s="1">
+        <v>15</v>
+      </c>
+      <c r="G828" s="1"/>
+      <c r="H828" t="s">
+        <v>1672</v>
+      </c>
+    </row>
+    <row r="829" spans="1:8">
+      <c r="A829" s="2" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B829" t="s">
+        <v>1673</v>
+      </c>
+      <c r="C829" s="1">
+        <v>143</v>
+      </c>
+      <c r="D829" s="1">
+        <v>150</v>
+      </c>
+      <c r="E829" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F829" s="1">
+        <v>16</v>
+      </c>
+      <c r="G829" s="1"/>
+      <c r="H829" t="s">
+        <v>1674</v>
+      </c>
+    </row>
+    <row r="830" spans="1:8">
+      <c r="A830" s="2" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B830" t="s">
+        <v>1675</v>
+      </c>
+      <c r="C830" s="1">
+        <v>143</v>
+      </c>
+      <c r="D830" s="1">
+        <v>150</v>
+      </c>
+      <c r="E830" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F830" s="1">
+        <v>17</v>
+      </c>
+      <c r="G830" s="1"/>
+      <c r="H830" t="s">
+        <v>1676</v>
+      </c>
+    </row>
+    <row r="831" spans="1:8">
+      <c r="A831" s="2" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B831" t="s">
+        <v>1677</v>
+      </c>
+      <c r="C831" s="1">
+        <v>143</v>
+      </c>
+      <c r="D831" s="1">
+        <v>150</v>
+      </c>
+      <c r="E831" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F831" s="1">
+        <v>18</v>
+      </c>
+      <c r="G831" s="1"/>
+      <c r="H831" t="s">
+        <v>1678</v>
+      </c>
+    </row>
+    <row r="832" spans="1:8">
+      <c r="A832" s="2" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B832" t="s">
+        <v>1679</v>
+      </c>
+      <c r="C832" s="1">
+        <v>143</v>
+      </c>
+      <c r="D832" s="1">
+        <v>150</v>
+      </c>
+      <c r="E832" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F832" s="1">
+        <v>19</v>
+      </c>
+      <c r="G832" s="1"/>
+      <c r="H832" t="s">
+        <v>1680</v>
+      </c>
+    </row>
+    <row r="833" spans="1:8">
+      <c r="A833" s="2" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B833" t="s">
+        <v>1681</v>
+      </c>
+      <c r="C833" s="1">
+        <v>143</v>
+      </c>
+      <c r="D833" s="1">
+        <v>150</v>
+      </c>
+      <c r="E833" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F833" s="1">
+        <v>20</v>
+      </c>
+      <c r="G833" s="1"/>
+      <c r="H833" t="s">
+        <v>1682</v>
+      </c>
+    </row>
+    <row r="834" spans="1:8">
+      <c r="A834" s="2" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B834" t="s">
+        <v>1683</v>
+      </c>
+      <c r="C834" s="1">
+        <v>143</v>
+      </c>
+      <c r="D834" s="1">
+        <v>150</v>
+      </c>
+      <c r="E834" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F834" s="1">
+        <v>57</v>
+      </c>
+      <c r="G834" s="1"/>
+      <c r="H834" t="s">
+        <v>1684</v>
+      </c>
+    </row>
+    <row r="835" spans="1:8">
+      <c r="A835" s="2" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B835" t="s">
+        <v>1685</v>
+      </c>
+      <c r="C835" s="1">
+        <v>143</v>
+      </c>
+      <c r="D835" s="1">
+        <v>150</v>
+      </c>
+      <c r="E835" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F835" s="1">
+        <v>61</v>
+      </c>
+      <c r="G835" s="1"/>
+      <c r="H835" t="s">
+        <v>1686</v>
+      </c>
+    </row>
+    <row r="836" spans="1:8">
+      <c r="A836" s="2" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B836" t="s">
+        <v>1687</v>
+      </c>
+      <c r="C836" s="1">
+        <v>143</v>
+      </c>
+      <c r="D836" s="1">
+        <v>150</v>
+      </c>
+      <c r="E836" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F836" s="1">
+        <v>63</v>
+      </c>
+      <c r="G836" s="1"/>
+      <c r="H836" t="s">
+        <v>1688</v>
+      </c>
+    </row>
+    <row r="837" spans="1:8">
+      <c r="A837" s="2" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B837" t="s">
+        <v>1689</v>
+      </c>
+      <c r="C837" s="1">
+        <v>143</v>
+      </c>
+      <c r="D837" s="1">
+        <v>150</v>
+      </c>
+      <c r="E837" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F837" s="1">
+        <v>65</v>
+      </c>
+      <c r="G837" s="1"/>
+      <c r="H837" t="s">
+        <v>1690</v>
+      </c>
+    </row>
+    <row r="838" spans="1:8">
+      <c r="A838" s="2" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B838" t="s">
+        <v>1691</v>
+      </c>
+      <c r="C838" s="1">
+        <v>143</v>
+      </c>
+      <c r="D838" s="1">
+        <v>150</v>
+      </c>
+      <c r="E838" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F838" s="1">
+        <v>67</v>
+      </c>
+      <c r="G838" s="1"/>
+      <c r="H838" t="s">
+        <v>1692</v>
+      </c>
+    </row>
+    <row r="839" spans="1:8">
+      <c r="A839" s="2" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B839" t="s">
+        <v>1693</v>
+      </c>
+      <c r="C839" s="1">
+        <v>143</v>
+      </c>
+      <c r="D839" s="1">
+        <v>150</v>
+      </c>
+      <c r="E839" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F839" s="1">
+        <v>69</v>
+      </c>
+      <c r="G839" s="1"/>
+      <c r="H839" t="s">
+        <v>1694</v>
+      </c>
+    </row>
+    <row r="840" spans="1:8">
+      <c r="A840" s="2" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B840" t="s">
+        <v>1695</v>
+      </c>
+      <c r="C840" s="1">
+        <v>143</v>
+      </c>
+      <c r="D840" s="1">
+        <v>150</v>
+      </c>
+      <c r="E840" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F840" s="1">
+        <v>70</v>
+      </c>
+      <c r="G840" s="1"/>
+      <c r="H840" t="s">
+        <v>1696</v>
+      </c>
+    </row>
+    <row r="841" spans="1:8">
+      <c r="A841" s="2" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B841" t="s">
+        <v>1697</v>
+      </c>
+      <c r="C841" s="1">
+        <v>143</v>
+      </c>
+      <c r="D841" s="1">
+        <v>150</v>
+      </c>
+      <c r="E841" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F841" s="1">
+        <v>73</v>
+      </c>
+      <c r="G841" s="1"/>
+      <c r="H841" t="s">
+        <v>1698</v>
+      </c>
+    </row>
+    <row r="842" spans="1:8">
+      <c r="A842" s="2" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B842" t="s">
+        <v>1699</v>
+      </c>
+      <c r="C842" s="1">
+        <v>143</v>
+      </c>
+      <c r="D842" s="1">
+        <v>150</v>
+      </c>
+      <c r="E842" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F842" s="1">
+        <v>78</v>
+      </c>
+      <c r="G842" s="1"/>
+      <c r="H842" t="s">
+        <v>1700</v>
+      </c>
+    </row>
+    <row r="843" spans="1:8">
+      <c r="A843" s="2" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B843" t="s">
+        <v>1701</v>
+      </c>
+      <c r="C843" s="1">
+        <v>143</v>
+      </c>
+      <c r="D843" s="1">
+        <v>150</v>
+      </c>
+      <c r="E843" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F843" s="1">
+        <v>80</v>
+      </c>
+      <c r="G843" s="1"/>
+      <c r="H843" t="s">
+        <v>1702</v>
+      </c>
+    </row>
+    <row r="844" spans="1:8">
+      <c r="A844" s="2" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B844" t="s">
+        <v>1703</v>
+      </c>
+      <c r="C844" s="1">
+        <v>143</v>
+      </c>
+      <c r="D844" s="1">
+        <v>150</v>
+      </c>
+      <c r="E844" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F844" s="1">
+        <v>82</v>
+      </c>
+      <c r="G844" s="1"/>
+      <c r="H844" t="s">
+        <v>1704</v>
+      </c>
+    </row>
+    <row r="845" spans="1:8">
+      <c r="A845" s="2" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B845" t="s">
+        <v>1705</v>
+      </c>
+      <c r="C845" s="1">
+        <v>143</v>
+      </c>
+      <c r="D845" s="1">
+        <v>150</v>
+      </c>
+      <c r="E845" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F845" s="1">
+        <v>84</v>
+      </c>
+      <c r="G845" s="1"/>
+      <c r="H845" t="s">
+        <v>1706</v>
+      </c>
+    </row>
+    <row r="846" spans="1:8">
+      <c r="A846" s="2" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B846" t="s">
+        <v>1707</v>
+      </c>
+      <c r="C846" s="1">
+        <v>143</v>
+      </c>
+      <c r="D846" s="1">
+        <v>150</v>
+      </c>
+      <c r="E846" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F846" s="1">
+        <v>86</v>
+      </c>
+      <c r="G846" s="1"/>
+      <c r="H846" t="s">
+        <v>1708</v>
+      </c>
+    </row>
+    <row r="847" spans="1:8">
+      <c r="A847" s="2" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B847" t="s">
+        <v>1709</v>
+      </c>
+      <c r="C847" s="1">
+        <v>143</v>
+      </c>
+      <c r="D847" s="1">
+        <v>150</v>
+      </c>
+      <c r="E847" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F847" s="1">
+        <v>88</v>
+      </c>
+      <c r="G847" s="1"/>
+      <c r="H847" t="s">
+        <v>1710</v>
+      </c>
+    </row>
+    <row r="848" spans="1:8">
+      <c r="A848" s="2" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B848" t="s">
+        <v>1711</v>
+      </c>
+      <c r="C848" s="1">
+        <v>143</v>
+      </c>
+      <c r="D848" s="1">
+        <v>150</v>
+      </c>
+      <c r="E848" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F848" s="1">
+        <v>89</v>
+      </c>
+      <c r="G848" s="1"/>
+      <c r="H848" t="s">
+        <v>1712</v>
+      </c>
+    </row>
+    <row r="849" spans="1:8">
+      <c r="A849" s="2" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B849" t="s">
+        <v>1713</v>
+      </c>
+      <c r="C849" s="1">
+        <v>143</v>
+      </c>
+      <c r="D849" s="1">
+        <v>150</v>
+      </c>
+      <c r="E849" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F849" s="1">
+        <v>91</v>
+      </c>
+      <c r="G849" s="1"/>
+      <c r="H849" t="s">
+        <v>1714</v>
+      </c>
+    </row>
+    <row r="850" spans="1:8">
+      <c r="A850" s="2" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B850" t="s">
+        <v>1715</v>
+      </c>
+      <c r="C850" s="1">
+        <v>143</v>
+      </c>
+      <c r="D850" s="1">
+        <v>150</v>
+      </c>
+      <c r="E850" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F850" s="1">
+        <v>94</v>
+      </c>
+      <c r="G850" s="1"/>
+      <c r="H850" t="s">
+        <v>1716</v>
+      </c>
+    </row>
+    <row r="851" spans="1:8">
+      <c r="A851" s="2" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B851" t="s">
+        <v>1717</v>
+      </c>
+      <c r="C851" s="1">
+        <v>143</v>
+      </c>
+      <c r="D851" s="1">
+        <v>150</v>
+      </c>
+      <c r="E851" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F851" s="1">
+        <v>95</v>
+      </c>
+      <c r="G851" s="1"/>
+      <c r="H851" t="s">
+        <v>1718</v>
+      </c>
+    </row>
+    <row r="852" spans="1:8">
+      <c r="A852" s="2" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B852" t="s">
+        <v>1719</v>
+      </c>
+      <c r="C852" s="1">
+        <v>143</v>
+      </c>
+      <c r="D852" s="1">
+        <v>150</v>
+      </c>
+      <c r="E852" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F852" s="1">
+        <v>97</v>
+      </c>
+      <c r="G852" s="1"/>
+      <c r="H852" t="s">
+        <v>1720</v>
+      </c>
+    </row>
+    <row r="853" spans="1:8">
+      <c r="A853" s="2" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B853" t="s">
+        <v>1721</v>
+      </c>
+      <c r="C853" s="1">
+        <v>143</v>
+      </c>
+      <c r="D853" s="1">
+        <v>150</v>
+      </c>
+      <c r="E853" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F853" s="1">
+        <v>99</v>
+      </c>
+      <c r="G853" s="1"/>
+      <c r="H853" t="s">
+        <v>1722</v>
+      </c>
+    </row>
+    <row r="854" spans="1:8">
+      <c r="A854" s="2" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B854" t="s">
+        <v>1723</v>
+      </c>
+      <c r="C854" s="1">
+        <v>143</v>
+      </c>
+      <c r="D854" s="1">
+        <v>245</v>
+      </c>
+      <c r="E854" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F854" s="1">
+        <v>1</v>
+      </c>
+      <c r="G854" s="1"/>
+      <c r="H854" t="s">
+        <v>1724</v>
+      </c>
+    </row>
+    <row r="855" spans="1:8">
+      <c r="A855" s="2" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B855" t="s">
+        <v>1725</v>
+      </c>
+      <c r="C855" s="1">
+        <v>143</v>
+      </c>
+      <c r="D855" s="1">
+        <v>245</v>
+      </c>
+      <c r="E855" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F855" s="1">
+        <v>2</v>
+      </c>
+      <c r="G855" s="1"/>
+      <c r="H855" t="s">
+        <v>1726</v>
+      </c>
+    </row>
+    <row r="856" spans="1:8">
+      <c r="A856" s="2" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B856" t="s">
+        <v>1727</v>
+      </c>
+      <c r="C856" s="1">
+        <v>143</v>
+      </c>
+      <c r="D856" s="1">
+        <v>245</v>
+      </c>
+      <c r="E856" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F856" s="1">
+        <v>6</v>
+      </c>
+      <c r="G856" s="1"/>
+      <c r="H856" t="s">
+        <v>1728</v>
+      </c>
+    </row>
+    <row r="857" spans="1:8">
+      <c r="A857" s="2" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B857" t="s">
+        <v>1729</v>
+      </c>
+      <c r="C857" s="1">
+        <v>143</v>
+      </c>
+      <c r="D857" s="1">
+        <v>245</v>
+      </c>
+      <c r="E857" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F857" s="1">
+        <v>14</v>
+      </c>
+      <c r="G857" s="1"/>
+      <c r="H857" t="s">
+        <v>1730</v>
+      </c>
+    </row>
+    <row r="858" spans="1:8">
+      <c r="A858" s="2" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B858" t="s">
+        <v>1731</v>
+      </c>
+      <c r="C858" s="1">
+        <v>143</v>
+      </c>
+      <c r="D858" s="1">
+        <v>245</v>
+      </c>
+      <c r="E858" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F858" s="1">
+        <v>15</v>
+      </c>
+      <c r="G858" s="1"/>
+      <c r="H858" t="s">
+        <v>1732</v>
+      </c>
+    </row>
+    <row r="859" spans="1:8">
+      <c r="A859" s="2" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B859" t="s">
+        <v>1733</v>
+      </c>
+      <c r="C859" s="1">
+        <v>143</v>
+      </c>
+      <c r="D859" s="1">
+        <v>245</v>
+      </c>
+      <c r="E859" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F859" s="1">
+        <v>16</v>
+      </c>
+      <c r="G859" s="1"/>
+      <c r="H859" t="s">
+        <v>1734</v>
+      </c>
+    </row>
+    <row r="860" spans="1:8">
+      <c r="A860" s="2" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B860" t="s">
+        <v>1735</v>
+      </c>
+      <c r="C860" s="1">
+        <v>143</v>
+      </c>
+      <c r="D860" s="1">
+        <v>245</v>
+      </c>
+      <c r="E860" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F860" s="1">
+        <v>17</v>
+      </c>
+      <c r="G860" s="1"/>
+      <c r="H860" t="s">
+        <v>1736</v>
+      </c>
+    </row>
+    <row r="861" spans="1:8">
+      <c r="A861" s="2" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B861" t="s">
+        <v>1737</v>
+      </c>
+      <c r="C861" s="1">
+        <v>143</v>
+      </c>
+      <c r="D861" s="1">
+        <v>245</v>
+      </c>
+      <c r="E861" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F861" s="1">
+        <v>18</v>
+      </c>
+      <c r="G861" s="1"/>
+      <c r="H861" t="s">
+        <v>1738</v>
+      </c>
+    </row>
+    <row r="862" spans="1:8">
+      <c r="A862" s="2" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B862" t="s">
+        <v>1739</v>
+      </c>
+      <c r="C862" s="1">
+        <v>143</v>
+      </c>
+      <c r="D862" s="1">
+        <v>245</v>
+      </c>
+      <c r="E862" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F862" s="1">
+        <v>19</v>
+      </c>
+      <c r="G862" s="1"/>
+      <c r="H862" t="s">
+        <v>1740</v>
+      </c>
+    </row>
+    <row r="863" spans="1:8">
+      <c r="A863" s="2" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B863" t="s">
+        <v>1741</v>
+      </c>
+      <c r="C863" s="1">
+        <v>143</v>
+      </c>
+      <c r="D863" s="1">
+        <v>245</v>
+      </c>
+      <c r="E863" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F863" s="1">
+        <v>20</v>
+      </c>
+      <c r="G863" s="1"/>
+      <c r="H863" t="s">
+        <v>1742</v>
+      </c>
+    </row>
+    <row r="864" spans="1:8">
+      <c r="A864" s="2" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B864" t="s">
+        <v>1743</v>
+      </c>
+      <c r="C864" s="1">
+        <v>143</v>
+      </c>
+      <c r="D864" s="1">
+        <v>245</v>
+      </c>
+      <c r="E864" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F864" s="1">
+        <v>21</v>
+      </c>
+      <c r="G864" s="1"/>
+      <c r="H864" t="s">
+        <v>1744</v>
+      </c>
+    </row>
+    <row r="865" spans="1:8">
+      <c r="A865" s="2" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B865" t="s">
+        <v>1745</v>
+      </c>
+      <c r="C865" s="1">
+        <v>143</v>
+      </c>
+      <c r="D865" s="1">
+        <v>245</v>
+      </c>
+      <c r="E865" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F865" s="1">
+        <v>22</v>
+      </c>
+      <c r="G865" s="1"/>
+      <c r="H865" t="s">
+        <v>1746</v>
+      </c>
+    </row>
+    <row r="866" spans="1:8">
+      <c r="A866" s="2" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B866" t="s">
+        <v>1747</v>
+      </c>
+      <c r="C866" s="1">
+        <v>143</v>
+      </c>
+      <c r="D866" s="1">
+        <v>245</v>
+      </c>
+      <c r="E866" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F866" s="1">
+        <v>24</v>
+      </c>
+      <c r="G866" s="1"/>
+      <c r="H866" t="s">
+        <v>1748</v>
+      </c>
+    </row>
+    <row r="867" spans="1:8">
+      <c r="A867" s="2" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B867" t="s">
+        <v>1749</v>
+      </c>
+      <c r="C867" s="1">
+        <v>143</v>
+      </c>
+      <c r="D867" s="1">
+        <v>245</v>
+      </c>
+      <c r="E867" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F867" s="1">
+        <v>25</v>
+      </c>
+      <c r="G867" s="1"/>
+      <c r="H867" t="s">
+        <v>1750</v>
+      </c>
+    </row>
+    <row r="868" spans="1:8">
+      <c r="A868" s="2" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B868" t="s">
+        <v>1751</v>
+      </c>
+      <c r="C868" s="1">
+        <v>143</v>
+      </c>
+      <c r="D868" s="1">
+        <v>245</v>
+      </c>
+      <c r="E868" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F868" s="1">
+        <v>26</v>
+      </c>
+      <c r="G868" s="1"/>
+      <c r="H868" t="s">
+        <v>1752</v>
+      </c>
+    </row>
+    <row r="869" spans="1:8">
+      <c r="A869" s="2" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B869" t="s">
+        <v>1753</v>
+      </c>
+      <c r="C869" s="1">
+        <v>143</v>
+      </c>
+      <c r="D869" s="1">
+        <v>245</v>
+      </c>
+      <c r="E869" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F869" s="1">
+        <v>27</v>
+      </c>
+      <c r="G869" s="1"/>
+      <c r="H869" t="s">
+        <v>1754</v>
+      </c>
+    </row>
+    <row r="870" spans="1:8">
+      <c r="A870" s="2" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B870" t="s">
+        <v>1755</v>
+      </c>
+      <c r="C870" s="1">
+        <v>143</v>
+      </c>
+      <c r="D870" s="1">
+        <v>245</v>
+      </c>
+      <c r="E870" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F870" s="1">
+        <v>28</v>
+      </c>
+      <c r="G870" s="1"/>
+      <c r="H870" t="s">
+        <v>1756</v>
+      </c>
+    </row>
+    <row r="871" spans="1:8">
+      <c r="A871" s="2" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B871" t="s">
+        <v>1757</v>
+      </c>
+      <c r="C871" s="1">
+        <v>143</v>
+      </c>
+      <c r="D871" s="1">
+        <v>245</v>
+      </c>
+      <c r="E871" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F871" s="1">
+        <v>29</v>
+      </c>
+      <c r="G871" s="1"/>
+      <c r="H871" t="s">
+        <v>1758</v>
+      </c>
+    </row>
+    <row r="872" spans="1:8">
+      <c r="A872" s="2" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B872" t="s">
+        <v>1759</v>
+      </c>
+      <c r="C872" s="1">
+        <v>143</v>
+      </c>
+      <c r="D872" s="1">
+        <v>245</v>
+      </c>
+      <c r="E872" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F872" s="1">
+        <v>30</v>
+      </c>
+      <c r="G872" s="1"/>
+      <c r="H872" t="s">
+        <v>1760</v>
+      </c>
+    </row>
+    <row r="873" spans="1:8">
+      <c r="A873" s="2" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B873" t="s">
+        <v>1761</v>
+      </c>
+      <c r="C873" s="1">
+        <v>143</v>
+      </c>
+      <c r="D873" s="1">
+        <v>245</v>
+      </c>
+      <c r="E873" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F873" s="1">
+        <v>31</v>
+      </c>
+      <c r="G873" s="1"/>
+      <c r="H873" t="s">
+        <v>1762</v>
+      </c>
+    </row>
+    <row r="874" spans="1:8">
+      <c r="A874" s="2" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B874" t="s">
+        <v>1763</v>
+      </c>
+      <c r="C874" s="1">
+        <v>143</v>
+      </c>
+      <c r="D874" s="1">
+        <v>245</v>
+      </c>
+      <c r="E874" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F874" s="1">
+        <v>32</v>
+      </c>
+      <c r="G874" s="1"/>
+      <c r="H874" t="s">
+        <v>1764</v>
+      </c>
+    </row>
+    <row r="875" spans="1:8">
+      <c r="A875" s="2" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B875" t="s">
+        <v>1765</v>
+      </c>
+      <c r="C875" s="1">
+        <v>143</v>
+      </c>
+      <c r="D875" s="1">
+        <v>245</v>
+      </c>
+      <c r="E875" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F875" s="1">
+        <v>33</v>
+      </c>
+      <c r="G875" s="1"/>
+      <c r="H875" t="s">
+        <v>1766</v>
+      </c>
+    </row>
+    <row r="876" spans="1:8">
+      <c r="A876" s="2" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B876" t="s">
+        <v>1767</v>
+      </c>
+      <c r="C876" s="1">
+        <v>143</v>
+      </c>
+      <c r="D876" s="1">
+        <v>245</v>
+      </c>
+      <c r="E876" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F876" s="1">
+        <v>34</v>
+      </c>
+      <c r="G876" s="1"/>
+      <c r="H876" t="s">
+        <v>1768</v>
+      </c>
+    </row>
+    <row r="877" spans="1:8">
+      <c r="A877" s="2" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B877" t="s">
+        <v>1769</v>
+      </c>
+      <c r="C877" s="1">
+        <v>143</v>
+      </c>
+      <c r="D877" s="1">
+        <v>245</v>
+      </c>
+      <c r="E877" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F877" s="1">
+        <v>35</v>
+      </c>
+      <c r="G877" s="1"/>
+      <c r="H877" t="s">
+        <v>1770</v>
+      </c>
+    </row>
+    <row r="878" spans="1:8">
+      <c r="A878" s="2" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B878" t="s">
+        <v>1771</v>
+      </c>
+      <c r="C878" s="1">
+        <v>143</v>
+      </c>
+      <c r="D878" s="1">
+        <v>245</v>
+      </c>
+      <c r="E878" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F878" s="1">
+        <v>36</v>
+      </c>
+      <c r="G878" s="1"/>
+      <c r="H878" t="s">
+        <v>1772</v>
+      </c>
+    </row>
+    <row r="879" spans="1:8">
+      <c r="A879" s="2" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B879" t="s">
+        <v>1773</v>
+      </c>
+      <c r="C879" s="1">
+        <v>143</v>
+      </c>
+      <c r="D879" s="1">
+        <v>245</v>
+      </c>
+      <c r="E879" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F879" s="1">
+        <v>37</v>
+      </c>
+      <c r="G879" s="1"/>
+      <c r="H879" t="s">
+        <v>1774</v>
+      </c>
+    </row>
+    <row r="880" spans="1:8">
+      <c r="A880" s="2" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B880" t="s">
+        <v>1775</v>
+      </c>
+      <c r="C880" s="1">
+        <v>143</v>
+      </c>
+      <c r="D880" s="1">
+        <v>245</v>
+      </c>
+      <c r="E880" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F880" s="1">
+        <v>38</v>
+      </c>
+      <c r="G880" s="1"/>
+      <c r="H880" t="s">
+        <v>1776</v>
+      </c>
+    </row>
+    <row r="881" spans="1:8">
+      <c r="A881" s="2" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B881" t="s">
+        <v>1777</v>
+      </c>
+      <c r="C881" s="1">
+        <v>143</v>
+      </c>
+      <c r="D881" s="1">
+        <v>245</v>
+      </c>
+      <c r="E881" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F881" s="1">
+        <v>39</v>
+      </c>
+      <c r="G881" s="1"/>
+      <c r="H881" t="s">
+        <v>1778</v>
+      </c>
+    </row>
+    <row r="882" spans="1:8">
+      <c r="A882" s="2" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B882" t="s">
+        <v>1779</v>
+      </c>
+      <c r="C882" s="1">
+        <v>143</v>
+      </c>
+      <c r="D882" s="1">
+        <v>245</v>
+      </c>
+      <c r="E882" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F882" s="1">
+        <v>40</v>
+      </c>
+      <c r="G882" s="1"/>
+      <c r="H882" t="s">
+        <v>1780</v>
+      </c>
+    </row>
+    <row r="883" spans="1:8">
+      <c r="A883" s="2" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B883" t="s">
+        <v>1781</v>
+      </c>
+      <c r="C883" s="1">
+        <v>143</v>
+      </c>
+      <c r="D883" s="1">
+        <v>245</v>
+      </c>
+      <c r="E883" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F883" s="1">
+        <v>41</v>
+      </c>
+      <c r="G883" s="1"/>
+      <c r="H883" t="s">
+        <v>1782</v>
+      </c>
+    </row>
+    <row r="884" spans="1:8">
+      <c r="A884" s="2" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B884" t="s">
+        <v>1783</v>
+      </c>
+      <c r="C884" s="1">
+        <v>143</v>
+      </c>
+      <c r="D884" s="1">
+        <v>245</v>
+      </c>
+      <c r="E884" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F884" s="1">
+        <v>42</v>
+      </c>
+      <c r="G884" s="1"/>
+      <c r="H884" t="s">
+        <v>1784</v>
+      </c>
+    </row>
+    <row r="885" spans="1:8">
+      <c r="A885" s="2" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B885" t="s">
+        <v>1785</v>
+      </c>
+      <c r="C885" s="1">
+        <v>143</v>
+      </c>
+      <c r="D885" s="1">
+        <v>245</v>
+      </c>
+      <c r="E885" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F885" s="1">
+        <v>43</v>
+      </c>
+      <c r="G885" s="1"/>
+      <c r="H885" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="886" spans="1:8">
+      <c r="A886" s="2" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B886" t="s">
+        <v>1787</v>
+      </c>
+      <c r="C886" s="1">
+        <v>143</v>
+      </c>
+      <c r="D886" s="1">
+        <v>245</v>
+      </c>
+      <c r="E886" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F886" s="1">
+        <v>44</v>
+      </c>
+      <c r="G886" s="1"/>
+      <c r="H886" t="s">
+        <v>1788</v>
+      </c>
+    </row>
+    <row r="887" spans="1:8">
+      <c r="A887" s="2" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B887" t="s">
+        <v>1789</v>
+      </c>
+      <c r="C887" s="1">
+        <v>143</v>
+      </c>
+      <c r="D887" s="1">
+        <v>245</v>
+      </c>
+      <c r="E887" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F887" s="1">
+        <v>45</v>
+      </c>
+      <c r="G887" s="1"/>
+      <c r="H887" t="s">
+        <v>1790</v>
+      </c>
+    </row>
+    <row r="888" spans="1:8">
+      <c r="A888" s="2" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B888" t="s">
+        <v>1791</v>
+      </c>
+      <c r="C888" s="1">
+        <v>143</v>
+      </c>
+      <c r="D888" s="1">
+        <v>245</v>
+      </c>
+      <c r="E888" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F888" s="1">
+        <v>46</v>
+      </c>
+      <c r="G888" s="1"/>
+      <c r="H888" t="s">
+        <v>1792</v>
+      </c>
+    </row>
+    <row r="889" spans="1:8">
+      <c r="A889" s="2" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B889" t="s">
+        <v>1793</v>
+      </c>
+      <c r="C889" s="1">
+        <v>143</v>
+      </c>
+      <c r="D889" s="1">
+        <v>245</v>
+      </c>
+      <c r="E889" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F889" s="1">
+        <v>47</v>
+      </c>
+      <c r="G889" s="1"/>
+      <c r="H889" t="s">
+        <v>1794</v>
+      </c>
+    </row>
+    <row r="890" spans="1:8">
+      <c r="A890" s="2" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B890" t="s">
+        <v>1795</v>
+      </c>
+      <c r="C890" s="1">
+        <v>143</v>
+      </c>
+      <c r="D890" s="1">
+        <v>245</v>
+      </c>
+      <c r="E890" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F890" s="1">
+        <v>48</v>
+      </c>
+      <c r="G890" s="1"/>
+      <c r="H890" t="s">
+        <v>1796</v>
+      </c>
+    </row>
+    <row r="891" spans="1:8">
+      <c r="A891" s="2"/>
+      <c r="C891" s="1"/>
+      <c r="D891" s="1"/>
+      <c r="E891" s="1"/>
+      <c r="F891" s="1"/>
+      <c r="G891" s="1"/>
     </row>
   </sheetData>
   <sheetProtection sheet="false" objects="false" scenarios="false" formatCells="false" formatColumns="false" formatRows="false" insertColumns="false" insertRows="false" insertHyperlinks="false" deleteColumns="false" deleteRows="false" selectLockedCells="false" sort="false" autoFilter="false" pivotTables="false" selectUnlockedCells="false"/>
